--- a/erlb.xlsx
+++ b/erlb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Haw\logs\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C879EF13-09F2-449C-A028-35367975FC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522B470B-F4AB-4779-B7E4-95D991A123EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{54DBC823-74FD-41B1-B15F-EAE87DE01D59}"/>
   </bookViews>
@@ -34,20 +34,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="713">
   <si>
     <t>Revolution</t>
   </si>
@@ -2807,6 +2799,12 @@
   </si>
   <si>
     <t>Motor Amps</t>
+  </si>
+  <si>
+    <t>Unit Outlet</t>
+  </si>
+  <si>
+    <t>Inlet</t>
   </si>
 </sst>
 </file>
@@ -4789,17 +4787,413 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="79" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="77" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4807,21 +5201,18 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4831,27 +5222,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4872,381 +5245,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="79" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="77" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -18906,25 +18904,25 @@
   <sheetData>
     <row r="1" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="271" t="s">
+      <c r="A2" s="293" t="s">
         <v>540</v>
       </c>
-      <c r="B2" s="271"/>
-      <c r="C2" s="273" t="s">
+      <c r="B2" s="293"/>
+      <c r="C2" s="295" t="s">
         <v>250</v>
       </c>
-      <c r="D2" s="273"/>
-      <c r="E2" s="273"/>
-      <c r="F2" s="273"/>
-      <c r="G2" s="273"/>
-      <c r="H2" s="273"/>
-      <c r="I2" s="270" t="s">
+      <c r="D2" s="295"/>
+      <c r="E2" s="295"/>
+      <c r="F2" s="295"/>
+      <c r="G2" s="295"/>
+      <c r="H2" s="295"/>
+      <c r="I2" s="292" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="271"/>
-      <c r="B3" s="271"/>
+      <c r="A3" s="293"/>
+      <c r="B3" s="293"/>
       <c r="C3" s="138" t="s">
         <v>527</v>
       </c>
@@ -18943,13 +18941,13 @@
       <c r="H3" s="138" t="s">
         <v>248</v>
       </c>
-      <c r="I3" s="270"/>
+      <c r="I3" s="292"/>
     </row>
     <row r="4" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="269" t="s">
+      <c r="A4" s="291" t="s">
         <v>541</v>
       </c>
-      <c r="B4" s="269"/>
+      <c r="B4" s="291"/>
       <c r="C4" s="62" t="s">
         <v>247</v>
       </c>
@@ -18973,10 +18971,10 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="272" t="s">
+      <c r="A5" s="294" t="s">
         <v>543</v>
       </c>
-      <c r="B5" s="272"/>
+      <c r="B5" s="294"/>
       <c r="C5" s="62" t="s">
         <v>247</v>
       </c>
@@ -19000,10 +18998,10 @@
       </c>
     </row>
     <row r="6" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="269" t="s">
+      <c r="A6" s="291" t="s">
         <v>542</v>
       </c>
-      <c r="B6" s="269"/>
+      <c r="B6" s="291"/>
       <c r="C6" s="62" t="s">
         <v>247</v>
       </c>
@@ -19027,10 +19025,10 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="269" t="s">
+      <c r="A7" s="291" t="s">
         <v>533</v>
       </c>
-      <c r="B7" s="269"/>
+      <c r="B7" s="291"/>
       <c r="C7" s="62" t="s">
         <v>246</v>
       </c>
@@ -19607,48 +19605,48 @@
   <sheetData>
     <row r="1" spans="2:27" ht="11.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="342" t="s">
+      <c r="B2" s="252" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="343"/>
-      <c r="D2" s="342" t="s">
+      <c r="C2" s="254"/>
+      <c r="D2" s="252" t="s">
         <v>235</v>
       </c>
-      <c r="E2" s="344"/>
-      <c r="F2" s="344"/>
-      <c r="G2" s="344"/>
-      <c r="H2" s="344"/>
-      <c r="I2" s="343"/>
-      <c r="J2" s="342" t="s">
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="253"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="252" t="s">
         <v>236</v>
       </c>
-      <c r="K2" s="344"/>
-      <c r="L2" s="344"/>
-      <c r="M2" s="344"/>
-      <c r="N2" s="344"/>
-      <c r="O2" s="343"/>
-      <c r="P2" s="342" t="s">
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="M2" s="253"/>
+      <c r="N2" s="253"/>
+      <c r="O2" s="254"/>
+      <c r="P2" s="252" t="s">
         <v>235</v>
       </c>
-      <c r="Q2" s="344"/>
-      <c r="R2" s="344"/>
-      <c r="S2" s="344"/>
-      <c r="T2" s="344"/>
-      <c r="U2" s="343"/>
-      <c r="V2" s="342" t="s">
+      <c r="Q2" s="253"/>
+      <c r="R2" s="253"/>
+      <c r="S2" s="253"/>
+      <c r="T2" s="253"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="252" t="s">
         <v>236</v>
       </c>
-      <c r="W2" s="344"/>
-      <c r="X2" s="344"/>
-      <c r="Y2" s="344"/>
-      <c r="Z2" s="344"/>
-      <c r="AA2" s="343"/>
+      <c r="W2" s="253"/>
+      <c r="X2" s="253"/>
+      <c r="Y2" s="253"/>
+      <c r="Z2" s="253"/>
+      <c r="AA2" s="254"/>
     </row>
     <row r="3" spans="2:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="381" t="s">
+      <c r="B3" s="362" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="382"/>
+      <c r="C3" s="363"/>
       <c r="D3" s="184" t="s">
         <v>117</v>
       </c>
@@ -19723,10 +19721,10 @@
       </c>
     </row>
     <row r="4" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="347" t="s">
+      <c r="B4" s="264" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="348"/>
+      <c r="C4" s="265"/>
       <c r="D4" s="141" t="s">
         <v>234</v>
       </c>
@@ -19755,43 +19753,43 @@
       <c r="AA4" s="158"/>
     </row>
     <row r="5" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="349"/>
-      <c r="C5" s="376"/>
-      <c r="D5" s="351" t="s">
+      <c r="B5" s="266"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="352"/>
-      <c r="J5" s="351" t="s">
+      <c r="E5" s="256"/>
+      <c r="F5" s="256"/>
+      <c r="G5" s="256"/>
+      <c r="H5" s="256"/>
+      <c r="I5" s="269"/>
+      <c r="J5" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="337"/>
-      <c r="L5" s="337"/>
-      <c r="M5" s="337"/>
-      <c r="N5" s="337"/>
-      <c r="O5" s="352"/>
-      <c r="P5" s="351" t="s">
+      <c r="K5" s="256"/>
+      <c r="L5" s="256"/>
+      <c r="M5" s="256"/>
+      <c r="N5" s="256"/>
+      <c r="O5" s="269"/>
+      <c r="P5" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="337"/>
-      <c r="R5" s="337"/>
-      <c r="S5" s="337"/>
-      <c r="T5" s="337"/>
-      <c r="U5" s="352"/>
-      <c r="V5" s="351" t="s">
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="269"/>
+      <c r="V5" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="W5" s="337"/>
-      <c r="X5" s="337"/>
-      <c r="Y5" s="337"/>
-      <c r="Z5" s="337"/>
-      <c r="AA5" s="352"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
+      <c r="AA5" s="269"/>
     </row>
     <row r="6" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="383" t="s">
+      <c r="B6" s="364" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="72" t="s">
@@ -19825,7 +19823,7 @@
       <c r="AA6" s="161"/>
     </row>
     <row r="7" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="383"/>
+      <c r="B7" s="364"/>
       <c r="C7" s="72" t="s">
         <v>61</v>
       </c>
@@ -19857,7 +19855,7 @@
       <c r="AA7" s="161"/>
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="377" t="s">
+      <c r="B8" s="358" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="72" t="s">
@@ -19891,7 +19889,7 @@
       <c r="AA8" s="161"/>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="378"/>
+      <c r="B9" s="359"/>
       <c r="C9" s="72" t="s">
         <v>12</v>
       </c>
@@ -19923,7 +19921,7 @@
       <c r="AA9" s="161"/>
     </row>
     <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="377" t="s">
+      <c r="B10" s="358" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="72" t="s">
@@ -19957,7 +19955,7 @@
       <c r="AA10" s="161"/>
     </row>
     <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="378"/>
+      <c r="B11" s="359"/>
       <c r="C11" s="76" t="s">
         <v>12</v>
       </c>
@@ -19989,10 +19987,10 @@
       <c r="AA11" s="161"/>
     </row>
     <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="356" t="s">
+      <c r="B12" s="276" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="357"/>
+      <c r="C12" s="277"/>
       <c r="D12" s="142" t="s">
         <v>122</v>
       </c>
@@ -20021,10 +20019,10 @@
       <c r="AA12" s="161"/>
     </row>
     <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="379" t="s">
+      <c r="B13" s="360" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="380"/>
+      <c r="C13" s="361"/>
       <c r="D13" s="144" t="s">
         <v>122</v>
       </c>
@@ -20053,46 +20051,46 @@
       <c r="AA13" s="165"/>
     </row>
     <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="359"/>
-      <c r="C14" s="360"/>
-      <c r="D14" s="358" t="s">
+      <c r="B14" s="279"/>
+      <c r="C14" s="280"/>
+      <c r="D14" s="278" t="s">
         <v>105</v>
       </c>
-      <c r="E14" s="256"/>
-      <c r="F14" s="256"/>
-      <c r="G14" s="256"/>
-      <c r="H14" s="256"/>
-      <c r="I14" s="350"/>
-      <c r="J14" s="358" t="s">
+      <c r="E14" s="250"/>
+      <c r="F14" s="250"/>
+      <c r="G14" s="250"/>
+      <c r="H14" s="250"/>
+      <c r="I14" s="267"/>
+      <c r="J14" s="278" t="s">
         <v>232</v>
       </c>
-      <c r="K14" s="256"/>
-      <c r="L14" s="256"/>
-      <c r="M14" s="256"/>
-      <c r="N14" s="256"/>
-      <c r="O14" s="350"/>
-      <c r="P14" s="358" t="s">
+      <c r="K14" s="250"/>
+      <c r="L14" s="250"/>
+      <c r="M14" s="250"/>
+      <c r="N14" s="250"/>
+      <c r="O14" s="267"/>
+      <c r="P14" s="278" t="s">
         <v>232</v>
       </c>
-      <c r="Q14" s="256"/>
-      <c r="R14" s="256"/>
-      <c r="S14" s="256"/>
-      <c r="T14" s="256"/>
-      <c r="U14" s="350"/>
-      <c r="V14" s="358" t="s">
+      <c r="Q14" s="250"/>
+      <c r="R14" s="250"/>
+      <c r="S14" s="250"/>
+      <c r="T14" s="250"/>
+      <c r="U14" s="267"/>
+      <c r="V14" s="278" t="s">
         <v>232</v>
       </c>
-      <c r="W14" s="256"/>
-      <c r="X14" s="256"/>
-      <c r="Y14" s="256"/>
-      <c r="Z14" s="256"/>
-      <c r="AA14" s="350"/>
+      <c r="W14" s="250"/>
+      <c r="X14" s="250"/>
+      <c r="Y14" s="250"/>
+      <c r="Z14" s="250"/>
+      <c r="AA14" s="267"/>
     </row>
     <row r="15" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="359" t="s">
+      <c r="B15" s="279" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="360"/>
+      <c r="C15" s="280"/>
       <c r="D15" s="143" t="s">
         <v>135</v>
       </c>
@@ -20121,10 +20119,10 @@
       <c r="AA15" s="161"/>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="359" t="s">
+      <c r="B16" s="279" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="360"/>
+      <c r="C16" s="280"/>
       <c r="D16" s="142" t="s">
         <v>135</v>
       </c>
@@ -20153,10 +20151,10 @@
       <c r="AA16" s="161"/>
     </row>
     <row r="17" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="359" t="s">
+      <c r="B17" s="279" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="360"/>
+      <c r="C17" s="280"/>
       <c r="D17" s="142" t="s">
         <v>135</v>
       </c>
@@ -20185,10 +20183,10 @@
       <c r="AA17" s="161"/>
     </row>
     <row r="18" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="359" t="s">
+      <c r="B18" s="279" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="360"/>
+      <c r="C18" s="280"/>
       <c r="D18" s="142" t="s">
         <v>135</v>
       </c>
@@ -20217,46 +20215,46 @@
       <c r="AA18" s="161"/>
     </row>
     <row r="19" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="359"/>
-      <c r="C19" s="360"/>
-      <c r="D19" s="384" t="s">
+      <c r="B19" s="279"/>
+      <c r="C19" s="280"/>
+      <c r="D19" s="366" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="385"/>
-      <c r="F19" s="385"/>
-      <c r="G19" s="385"/>
-      <c r="H19" s="385"/>
-      <c r="I19" s="386"/>
-      <c r="J19" s="351" t="s">
+      <c r="E19" s="367"/>
+      <c r="F19" s="367"/>
+      <c r="G19" s="367"/>
+      <c r="H19" s="367"/>
+      <c r="I19" s="368"/>
+      <c r="J19" s="268" t="s">
         <v>65</v>
       </c>
-      <c r="K19" s="337"/>
-      <c r="L19" s="337"/>
-      <c r="M19" s="337"/>
-      <c r="N19" s="337"/>
-      <c r="O19" s="352"/>
-      <c r="P19" s="351" t="s">
+      <c r="K19" s="256"/>
+      <c r="L19" s="256"/>
+      <c r="M19" s="256"/>
+      <c r="N19" s="256"/>
+      <c r="O19" s="269"/>
+      <c r="P19" s="268" t="s">
         <v>65</v>
       </c>
-      <c r="Q19" s="337"/>
-      <c r="R19" s="337"/>
-      <c r="S19" s="337"/>
-      <c r="T19" s="337"/>
-      <c r="U19" s="352"/>
-      <c r="V19" s="351" t="s">
+      <c r="Q19" s="256"/>
+      <c r="R19" s="256"/>
+      <c r="S19" s="256"/>
+      <c r="T19" s="256"/>
+      <c r="U19" s="269"/>
+      <c r="V19" s="268" t="s">
         <v>65</v>
       </c>
-      <c r="W19" s="337"/>
-      <c r="X19" s="337"/>
-      <c r="Y19" s="337"/>
-      <c r="Z19" s="337"/>
-      <c r="AA19" s="352"/>
+      <c r="W19" s="256"/>
+      <c r="X19" s="256"/>
+      <c r="Y19" s="256"/>
+      <c r="Z19" s="256"/>
+      <c r="AA19" s="269"/>
     </row>
     <row r="20" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="353" t="s">
+      <c r="B20" s="272" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="361"/>
+      <c r="C20" s="288"/>
       <c r="D20" s="142" t="s">
         <v>233</v>
       </c>
@@ -20285,10 +20283,10 @@
       <c r="AA20" s="161"/>
     </row>
     <row r="21" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="353" t="s">
+      <c r="B21" s="272" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="361"/>
+      <c r="C21" s="288"/>
       <c r="D21" s="142" t="s">
         <v>233</v>
       </c>
@@ -20317,10 +20315,10 @@
       <c r="AA21" s="161"/>
     </row>
     <row r="22" spans="2:37" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="362" t="s">
+      <c r="B22" s="289" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="363"/>
+      <c r="C22" s="290"/>
       <c r="D22" s="145" t="s">
         <v>121</v>
       </c>
@@ -20383,52 +20381,52 @@
       <c r="AA29"/>
     </row>
     <row r="30" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="375" t="s">
+      <c r="B30" s="356" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="375"/>
-      <c r="D30" s="372" t="s">
+      <c r="C30" s="356"/>
+      <c r="D30" s="353" t="s">
         <v>644</v>
       </c>
-      <c r="E30" s="372"/>
-      <c r="F30" s="372"/>
-      <c r="G30" s="372"/>
-      <c r="H30" s="372" t="s">
+      <c r="E30" s="353"/>
+      <c r="F30" s="353"/>
+      <c r="G30" s="353"/>
+      <c r="H30" s="353" t="s">
         <v>17</v>
       </c>
-      <c r="I30" s="372"/>
-      <c r="J30" s="372"/>
-      <c r="K30" s="372"/>
-      <c r="L30" s="372" t="s">
+      <c r="I30" s="353"/>
+      <c r="J30" s="353"/>
+      <c r="K30" s="353"/>
+      <c r="L30" s="353" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="372"/>
-      <c r="N30" s="372"/>
-      <c r="O30" s="372"/>
-      <c r="P30" s="372" t="s">
+      <c r="M30" s="353"/>
+      <c r="N30" s="353"/>
+      <c r="O30" s="353"/>
+      <c r="P30" s="353" t="s">
         <v>13</v>
       </c>
-      <c r="Q30" s="372"/>
-      <c r="R30" s="372"/>
-      <c r="S30" s="372"/>
-      <c r="T30" s="372" t="s">
+      <c r="Q30" s="353"/>
+      <c r="R30" s="353"/>
+      <c r="S30" s="353"/>
+      <c r="T30" s="353" t="s">
         <v>20</v>
       </c>
-      <c r="U30" s="372"/>
-      <c r="V30" s="372"/>
-      <c r="W30" s="372"/>
-      <c r="X30" s="372" t="s">
+      <c r="U30" s="353"/>
+      <c r="V30" s="353"/>
+      <c r="W30" s="353"/>
+      <c r="X30" s="353" t="s">
         <v>553</v>
       </c>
-      <c r="Y30" s="372"/>
-      <c r="Z30" s="372"/>
-      <c r="AA30" s="372"/>
+      <c r="Y30" s="353"/>
+      <c r="Z30" s="353"/>
+      <c r="AA30" s="353"/>
     </row>
     <row r="31" spans="2:37" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="373" t="s">
+      <c r="B31" s="354" t="s">
         <v>632</v>
       </c>
-      <c r="C31" s="374"/>
+      <c r="C31" s="355"/>
       <c r="D31" s="232" t="s">
         <v>641</v>
       </c>
@@ -20503,10 +20501,10 @@
       </c>
     </row>
     <row r="32" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="290" t="s">
+      <c r="B32" s="314" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="290"/>
+      <c r="C32" s="314"/>
       <c r="D32" s="231" t="s">
         <v>234</v>
       </c>
@@ -20545,34 +20543,34 @@
       <c r="AK32" s="190"/>
     </row>
     <row r="33" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="284" t="s">
+      <c r="B33" s="306" t="s">
         <v>646</v>
       </c>
-      <c r="C33" s="285"/>
-      <c r="D33" s="285"/>
-      <c r="E33" s="285"/>
-      <c r="F33" s="285"/>
-      <c r="G33" s="285"/>
-      <c r="H33" s="285"/>
-      <c r="I33" s="285"/>
-      <c r="J33" s="285"/>
-      <c r="K33" s="285"/>
-      <c r="L33" s="285"/>
-      <c r="M33" s="285"/>
-      <c r="N33" s="285"/>
-      <c r="O33" s="285"/>
-      <c r="P33" s="285"/>
-      <c r="Q33" s="285"/>
-      <c r="R33" s="285"/>
-      <c r="S33" s="285"/>
-      <c r="T33" s="285"/>
-      <c r="U33" s="285"/>
-      <c r="V33" s="285"/>
-      <c r="W33" s="285"/>
-      <c r="X33" s="285"/>
-      <c r="Y33" s="285"/>
-      <c r="Z33" s="285"/>
-      <c r="AA33" s="286"/>
+      <c r="C33" s="307"/>
+      <c r="D33" s="307"/>
+      <c r="E33" s="307"/>
+      <c r="F33" s="307"/>
+      <c r="G33" s="307"/>
+      <c r="H33" s="307"/>
+      <c r="I33" s="307"/>
+      <c r="J33" s="307"/>
+      <c r="K33" s="307"/>
+      <c r="L33" s="307"/>
+      <c r="M33" s="307"/>
+      <c r="N33" s="307"/>
+      <c r="O33" s="307"/>
+      <c r="P33" s="307"/>
+      <c r="Q33" s="307"/>
+      <c r="R33" s="307"/>
+      <c r="S33" s="307"/>
+      <c r="T33" s="307"/>
+      <c r="U33" s="307"/>
+      <c r="V33" s="307"/>
+      <c r="W33" s="307"/>
+      <c r="X33" s="307"/>
+      <c r="Y33" s="307"/>
+      <c r="Z33" s="307"/>
+      <c r="AA33" s="308"/>
       <c r="AD33" s="194"/>
       <c r="AE33" s="216" t="s">
         <v>585</v>
@@ -20585,7 +20583,7 @@
       <c r="AK33" s="208"/>
     </row>
     <row r="34" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="292" t="s">
+      <c r="B34" s="316" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="111" t="s">
@@ -20618,10 +20616,10 @@
       <c r="Z34" s="62"/>
       <c r="AA34" s="148"/>
       <c r="AD34" s="194"/>
-      <c r="AE34" s="370" t="s">
+      <c r="AE34" s="270" t="s">
         <v>632</v>
       </c>
-      <c r="AF34" s="371"/>
+      <c r="AF34" s="271"/>
       <c r="AG34" s="151" t="s">
         <v>223</v>
       </c>
@@ -20637,7 +20635,7 @@
       <c r="AK34" s="193"/>
     </row>
     <row r="35" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="292"/>
+      <c r="B35" s="316"/>
       <c r="C35" s="111" t="s">
         <v>61</v>
       </c>
@@ -20668,10 +20666,10 @@
       <c r="Z35" s="62"/>
       <c r="AA35" s="148"/>
       <c r="AD35" s="194"/>
-      <c r="AE35" s="370" t="s">
+      <c r="AE35" s="270" t="s">
         <v>31</v>
       </c>
-      <c r="AF35" s="371"/>
+      <c r="AF35" s="271"/>
       <c r="AG35" s="31"/>
       <c r="AH35" s="89"/>
       <c r="AI35" s="89"/>
@@ -20679,7 +20677,7 @@
       <c r="AK35" s="193"/>
     </row>
     <row r="36" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="292" t="s">
+      <c r="B36" s="316" t="s">
         <v>33</v>
       </c>
       <c r="C36" s="111" t="s">
@@ -20712,18 +20710,18 @@
       <c r="Z36" s="62"/>
       <c r="AA36" s="148"/>
       <c r="AD36" s="194"/>
-      <c r="AE36" s="243" t="s">
+      <c r="AE36" s="247" t="s">
         <v>30</v>
       </c>
-      <c r="AF36" s="243"/>
-      <c r="AG36" s="243"/>
-      <c r="AH36" s="243"/>
-      <c r="AI36" s="243"/>
-      <c r="AJ36" s="243"/>
+      <c r="AF36" s="247"/>
+      <c r="AG36" s="247"/>
+      <c r="AH36" s="247"/>
+      <c r="AI36" s="247"/>
+      <c r="AJ36" s="247"/>
       <c r="AK36" s="193"/>
     </row>
     <row r="37" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="292"/>
+      <c r="B37" s="316"/>
       <c r="C37" s="111" t="s">
         <v>12</v>
       </c>
@@ -20754,7 +20752,7 @@
       <c r="Z37" s="62"/>
       <c r="AA37" s="148"/>
       <c r="AD37" s="194"/>
-      <c r="AE37" s="369" t="s">
+      <c r="AE37" s="273" t="s">
         <v>1</v>
       </c>
       <c r="AF37" s="151" t="s">
@@ -20767,7 +20765,7 @@
       <c r="AK37" s="193"/>
     </row>
     <row r="38" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="292" t="s">
+      <c r="B38" s="316" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="111" t="s">
@@ -20800,7 +20798,7 @@
       <c r="Z38" s="62"/>
       <c r="AA38" s="148"/>
       <c r="AD38" s="194"/>
-      <c r="AE38" s="369"/>
+      <c r="AE38" s="273"/>
       <c r="AF38" s="151" t="s">
         <v>61</v>
       </c>
@@ -20811,7 +20809,7 @@
       <c r="AK38" s="193"/>
     </row>
     <row r="39" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="292"/>
+      <c r="B39" s="316"/>
       <c r="C39" s="111" t="s">
         <v>12</v>
       </c>
@@ -20842,7 +20840,7 @@
       <c r="Z39" s="62"/>
       <c r="AA39" s="148"/>
       <c r="AD39" s="194"/>
-      <c r="AE39" s="369" t="s">
+      <c r="AE39" s="273" t="s">
         <v>624</v>
       </c>
       <c r="AF39" s="151" t="s">
@@ -20855,10 +20853,10 @@
       <c r="AK39" s="193"/>
     </row>
     <row r="40" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="292" t="s">
+      <c r="B40" s="316" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="292"/>
+      <c r="C40" s="316"/>
       <c r="D40" s="2" t="s">
         <v>122</v>
       </c>
@@ -20886,7 +20884,7 @@
       <c r="Z40" s="62"/>
       <c r="AA40" s="148"/>
       <c r="AD40" s="194"/>
-      <c r="AE40" s="369"/>
+      <c r="AE40" s="273"/>
       <c r="AF40" s="151" t="s">
         <v>12</v>
       </c>
@@ -20897,10 +20895,10 @@
       <c r="AK40" s="193"/>
     </row>
     <row r="41" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="292" t="s">
+      <c r="B41" s="316" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="292"/>
+      <c r="C41" s="316"/>
       <c r="D41" s="2" t="s">
         <v>122</v>
       </c>
@@ -20928,7 +20926,7 @@
       <c r="Z41" s="62"/>
       <c r="AA41" s="148"/>
       <c r="AD41" s="194"/>
-      <c r="AE41" s="369" t="s">
+      <c r="AE41" s="273" t="s">
         <v>634</v>
       </c>
       <c r="AF41" s="151" t="s">
@@ -20941,36 +20939,36 @@
       <c r="AK41" s="193"/>
     </row>
     <row r="42" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="284" t="s">
+      <c r="B42" s="306" t="s">
         <v>647</v>
       </c>
-      <c r="C42" s="285"/>
-      <c r="D42" s="285"/>
-      <c r="E42" s="285"/>
-      <c r="F42" s="285"/>
-      <c r="G42" s="285"/>
-      <c r="H42" s="285"/>
-      <c r="I42" s="285"/>
-      <c r="J42" s="285"/>
-      <c r="K42" s="285"/>
-      <c r="L42" s="285"/>
-      <c r="M42" s="285"/>
-      <c r="N42" s="285"/>
-      <c r="O42" s="285"/>
-      <c r="P42" s="285"/>
-      <c r="Q42" s="285"/>
-      <c r="R42" s="285"/>
-      <c r="S42" s="285"/>
-      <c r="T42" s="285"/>
-      <c r="U42" s="285"/>
-      <c r="V42" s="285"/>
-      <c r="W42" s="285"/>
-      <c r="X42" s="285"/>
-      <c r="Y42" s="285"/>
-      <c r="Z42" s="285"/>
-      <c r="AA42" s="286"/>
+      <c r="C42" s="307"/>
+      <c r="D42" s="307"/>
+      <c r="E42" s="307"/>
+      <c r="F42" s="307"/>
+      <c r="G42" s="307"/>
+      <c r="H42" s="307"/>
+      <c r="I42" s="307"/>
+      <c r="J42" s="307"/>
+      <c r="K42" s="307"/>
+      <c r="L42" s="307"/>
+      <c r="M42" s="307"/>
+      <c r="N42" s="307"/>
+      <c r="O42" s="307"/>
+      <c r="P42" s="307"/>
+      <c r="Q42" s="307"/>
+      <c r="R42" s="307"/>
+      <c r="S42" s="307"/>
+      <c r="T42" s="307"/>
+      <c r="U42" s="307"/>
+      <c r="V42" s="307"/>
+      <c r="W42" s="307"/>
+      <c r="X42" s="307"/>
+      <c r="Y42" s="307"/>
+      <c r="Z42" s="307"/>
+      <c r="AA42" s="308"/>
       <c r="AD42" s="194"/>
-      <c r="AE42" s="369"/>
+      <c r="AE42" s="273"/>
       <c r="AF42" s="151" t="s">
         <v>12</v>
       </c>
@@ -20981,10 +20979,10 @@
       <c r="AK42" s="193"/>
     </row>
     <row r="43" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="258" t="s">
+      <c r="B43" s="357" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="258"/>
+      <c r="C43" s="357"/>
       <c r="D43" s="2" t="s">
         <v>135</v>
       </c>
@@ -21012,10 +21010,10 @@
       <c r="Z43" s="62"/>
       <c r="AA43" s="148"/>
       <c r="AD43" s="194"/>
-      <c r="AE43" s="367" t="s">
+      <c r="AE43" s="281" t="s">
         <v>635</v>
       </c>
-      <c r="AF43" s="367"/>
+      <c r="AF43" s="281"/>
       <c r="AG43" s="218"/>
       <c r="AH43" s="218"/>
       <c r="AI43" s="218"/>
@@ -21023,10 +21021,10 @@
       <c r="AK43" s="210"/>
     </row>
     <row r="44" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="258" t="s">
+      <c r="B44" s="357" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="258"/>
+      <c r="C44" s="357"/>
       <c r="D44" s="2" t="s">
         <v>135</v>
       </c>
@@ -21054,10 +21052,10 @@
       <c r="Z44" s="62"/>
       <c r="AA44" s="148"/>
       <c r="AD44" s="194"/>
-      <c r="AE44" s="367" t="s">
+      <c r="AE44" s="281" t="s">
         <v>636</v>
       </c>
-      <c r="AF44" s="367"/>
+      <c r="AF44" s="281"/>
       <c r="AG44" s="218"/>
       <c r="AH44" s="218"/>
       <c r="AI44" s="218"/>
@@ -21065,10 +21063,10 @@
       <c r="AK44" s="210"/>
     </row>
     <row r="45" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="258" t="s">
+      <c r="B45" s="357" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="258"/>
+      <c r="C45" s="357"/>
       <c r="D45" s="2" t="s">
         <v>135</v>
       </c>
@@ -21096,21 +21094,21 @@
       <c r="Z45" s="62"/>
       <c r="AA45" s="148"/>
       <c r="AD45" s="194"/>
-      <c r="AE45" s="241" t="s">
+      <c r="AE45" s="285" t="s">
         <v>107</v>
       </c>
-      <c r="AF45" s="368"/>
-      <c r="AG45" s="368"/>
-      <c r="AH45" s="368"/>
-      <c r="AI45" s="368"/>
-      <c r="AJ45" s="242"/>
+      <c r="AF45" s="286"/>
+      <c r="AG45" s="286"/>
+      <c r="AH45" s="286"/>
+      <c r="AI45" s="286"/>
+      <c r="AJ45" s="287"/>
       <c r="AK45" s="210"/>
     </row>
     <row r="46" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="258" t="s">
+      <c r="B46" s="357" t="s">
         <v>64</v>
       </c>
-      <c r="C46" s="258"/>
+      <c r="C46" s="357"/>
       <c r="D46" s="2" t="s">
         <v>135</v>
       </c>
@@ -21138,10 +21136,10 @@
       <c r="Z46" s="62"/>
       <c r="AA46" s="148"/>
       <c r="AD46" s="194"/>
-      <c r="AE46" s="241" t="s">
+      <c r="AE46" s="285" t="s">
         <v>634</v>
       </c>
-      <c r="AF46" s="242"/>
+      <c r="AF46" s="287"/>
       <c r="AG46" s="218"/>
       <c r="AH46" s="218"/>
       <c r="AI46" s="218"/>
@@ -21149,39 +21147,39 @@
       <c r="AK46" s="210"/>
     </row>
     <row r="47" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="284" t="s">
+      <c r="B47" s="306" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="285"/>
-      <c r="D47" s="285"/>
-      <c r="E47" s="285"/>
-      <c r="F47" s="285"/>
-      <c r="G47" s="285"/>
-      <c r="H47" s="285"/>
-      <c r="I47" s="285"/>
-      <c r="J47" s="285"/>
-      <c r="K47" s="285"/>
-      <c r="L47" s="285"/>
-      <c r="M47" s="285"/>
-      <c r="N47" s="285"/>
-      <c r="O47" s="285"/>
-      <c r="P47" s="285"/>
-      <c r="Q47" s="285"/>
-      <c r="R47" s="285"/>
-      <c r="S47" s="285"/>
-      <c r="T47" s="285"/>
-      <c r="U47" s="285"/>
-      <c r="V47" s="285"/>
-      <c r="W47" s="285"/>
-      <c r="X47" s="285"/>
-      <c r="Y47" s="285"/>
-      <c r="Z47" s="285"/>
-      <c r="AA47" s="286"/>
+      <c r="C47" s="307"/>
+      <c r="D47" s="307"/>
+      <c r="E47" s="307"/>
+      <c r="F47" s="307"/>
+      <c r="G47" s="307"/>
+      <c r="H47" s="307"/>
+      <c r="I47" s="307"/>
+      <c r="J47" s="307"/>
+      <c r="K47" s="307"/>
+      <c r="L47" s="307"/>
+      <c r="M47" s="307"/>
+      <c r="N47" s="307"/>
+      <c r="O47" s="307"/>
+      <c r="P47" s="307"/>
+      <c r="Q47" s="307"/>
+      <c r="R47" s="307"/>
+      <c r="S47" s="307"/>
+      <c r="T47" s="307"/>
+      <c r="U47" s="307"/>
+      <c r="V47" s="307"/>
+      <c r="W47" s="307"/>
+      <c r="X47" s="307"/>
+      <c r="Y47" s="307"/>
+      <c r="Z47" s="307"/>
+      <c r="AA47" s="308"/>
       <c r="AD47" s="194"/>
-      <c r="AE47" s="241" t="s">
+      <c r="AE47" s="285" t="s">
         <v>624</v>
       </c>
-      <c r="AF47" s="242"/>
+      <c r="AF47" s="287"/>
       <c r="AG47" s="218"/>
       <c r="AH47" s="218"/>
       <c r="AI47" s="218"/>
@@ -21189,10 +21187,10 @@
       <c r="AK47" s="193"/>
     </row>
     <row r="48" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="258" t="s">
+      <c r="B48" s="357" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="258"/>
+      <c r="C48" s="357"/>
       <c r="D48" s="2" t="s">
         <v>233</v>
       </c>
@@ -21220,10 +21218,10 @@
       <c r="Z48" s="62"/>
       <c r="AA48" s="148"/>
       <c r="AD48" s="194"/>
-      <c r="AE48" s="241" t="s">
+      <c r="AE48" s="285" t="s">
         <v>635</v>
       </c>
-      <c r="AF48" s="242"/>
+      <c r="AF48" s="287"/>
       <c r="AG48" s="218"/>
       <c r="AH48" s="218"/>
       <c r="AI48" s="218"/>
@@ -21231,10 +21229,10 @@
       <c r="AK48" s="193"/>
     </row>
     <row r="49" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="258" t="s">
+      <c r="B49" s="357" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="258"/>
+      <c r="C49" s="357"/>
       <c r="D49" s="2" t="s">
         <v>233</v>
       </c>
@@ -21262,10 +21260,10 @@
       <c r="Z49" s="62"/>
       <c r="AA49" s="148"/>
       <c r="AD49" s="194"/>
-      <c r="AE49" s="241" t="s">
+      <c r="AE49" s="285" t="s">
         <v>637</v>
       </c>
-      <c r="AF49" s="242"/>
+      <c r="AF49" s="287"/>
       <c r="AG49" s="218"/>
       <c r="AH49" s="218"/>
       <c r="AI49" s="218"/>
@@ -21273,10 +21271,10 @@
       <c r="AK49" s="193"/>
     </row>
     <row r="50" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="258" t="s">
+      <c r="B50" s="357" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="258"/>
+      <c r="C50" s="357"/>
       <c r="D50" s="2" t="s">
         <v>121</v>
       </c>
@@ -21304,22 +21302,22 @@
       <c r="Z50" s="62"/>
       <c r="AA50" s="148"/>
       <c r="AD50" s="194"/>
-      <c r="AE50" s="241" t="s">
+      <c r="AE50" s="285" t="s">
         <v>65</v>
       </c>
-      <c r="AF50" s="368"/>
-      <c r="AG50" s="368"/>
-      <c r="AH50" s="368"/>
-      <c r="AI50" s="368"/>
-      <c r="AJ50" s="242"/>
+      <c r="AF50" s="286"/>
+      <c r="AG50" s="286"/>
+      <c r="AH50" s="286"/>
+      <c r="AI50" s="286"/>
+      <c r="AJ50" s="287"/>
       <c r="AK50" s="193"/>
     </row>
     <row r="51" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AD51" s="194"/>
-      <c r="AE51" s="241" t="s">
+      <c r="AE51" s="285" t="s">
         <v>639</v>
       </c>
-      <c r="AF51" s="242"/>
+      <c r="AF51" s="287"/>
       <c r="AG51" s="218"/>
       <c r="AH51" s="218"/>
       <c r="AI51" s="218"/>
@@ -21328,10 +21326,10 @@
     </row>
     <row r="52" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AD52" s="194"/>
-      <c r="AE52" s="241" t="s">
+      <c r="AE52" s="285" t="s">
         <v>638</v>
       </c>
-      <c r="AF52" s="242"/>
+      <c r="AF52" s="287"/>
       <c r="AG52" s="218"/>
       <c r="AH52" s="218"/>
       <c r="AI52" s="218"/>
@@ -21340,10 +21338,10 @@
     </row>
     <row r="53" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AD53" s="194"/>
-      <c r="AE53" s="241" t="s">
+      <c r="AE53" s="285" t="s">
         <v>640</v>
       </c>
-      <c r="AF53" s="242"/>
+      <c r="AF53" s="287"/>
       <c r="AG53" s="218"/>
       <c r="AH53" s="218"/>
       <c r="AI53" s="218"/>
@@ -21377,6 +21375,16 @@
     <mergeCell ref="D19:I19"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="J19:O19"/>
+    <mergeCell ref="J14:O14"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="B15:C15"/>
@@ -21388,16 +21396,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="J19:O19"/>
-    <mergeCell ref="J14:O14"/>
-    <mergeCell ref="B18:C18"/>
     <mergeCell ref="V2:AA2"/>
     <mergeCell ref="V5:AA5"/>
     <mergeCell ref="V14:AA14"/>
@@ -21478,15 +21476,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="391" t="s">
+      <c r="B2" s="374" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="391"/>
-      <c r="D2" s="391"/>
-      <c r="E2" s="391"/>
-      <c r="F2" s="391"/>
-      <c r="G2" s="391"/>
-      <c r="H2" s="391"/>
+      <c r="C2" s="374"/>
+      <c r="D2" s="374"/>
+      <c r="E2" s="374"/>
+      <c r="F2" s="374"/>
+      <c r="G2" s="374"/>
+      <c r="H2" s="374"/>
     </row>
     <row r="3" spans="2:28" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -21512,15 +21510,15 @@
       </c>
     </row>
     <row r="4" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="255" t="s">
+      <c r="B4" s="249" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="256"/>
-      <c r="D4" s="256"/>
-      <c r="E4" s="256"/>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="257"/>
+      <c r="C4" s="250"/>
+      <c r="D4" s="250"/>
+      <c r="E4" s="250"/>
+      <c r="F4" s="250"/>
+      <c r="G4" s="250"/>
+      <c r="H4" s="251"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
@@ -21572,10 +21570,10 @@
       <c r="L6"/>
       <c r="M6"/>
       <c r="Y6" s="194"/>
-      <c r="Z6" s="241" t="s">
+      <c r="Z6" s="285" t="s">
         <v>663</v>
       </c>
-      <c r="AA6" s="242"/>
+      <c r="AA6" s="287"/>
       <c r="AB6" s="193"/>
     </row>
     <row r="7" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -21671,15 +21669,15 @@
       <c r="AB10" s="193"/>
     </row>
     <row r="11" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="255" t="s">
+      <c r="B11" s="249" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="261"/>
-      <c r="D11" s="261"/>
-      <c r="E11" s="261"/>
-      <c r="F11" s="261"/>
-      <c r="G11" s="261"/>
-      <c r="H11" s="309"/>
+      <c r="C11" s="373"/>
+      <c r="D11" s="373"/>
+      <c r="E11" s="373"/>
+      <c r="F11" s="373"/>
+      <c r="G11" s="373"/>
+      <c r="H11" s="333"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11"/>
@@ -21731,22 +21729,22 @@
       <c r="L13"/>
       <c r="M13"/>
       <c r="Y13" s="194"/>
-      <c r="Z13" s="241" t="s">
+      <c r="Z13" s="285" t="s">
         <v>107</v>
       </c>
-      <c r="AA13" s="242"/>
+      <c r="AA13" s="287"/>
       <c r="AB13" s="193"/>
     </row>
     <row r="14" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="255" t="s">
+      <c r="B14" s="249" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="261"/>
-      <c r="D14" s="261"/>
-      <c r="E14" s="261"/>
-      <c r="F14" s="261"/>
-      <c r="G14" s="261"/>
-      <c r="H14" s="309"/>
+      <c r="C14" s="373"/>
+      <c r="D14" s="373"/>
+      <c r="E14" s="373"/>
+      <c r="F14" s="373"/>
+      <c r="G14" s="373"/>
+      <c r="H14" s="333"/>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14"/>
@@ -21805,15 +21803,15 @@
       <c r="AB16" s="210"/>
     </row>
     <row r="17" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="255" t="s">
+      <c r="B17" s="249" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="261"/>
-      <c r="D17" s="261"/>
-      <c r="E17" s="261"/>
-      <c r="F17" s="261"/>
-      <c r="G17" s="261"/>
-      <c r="H17" s="309"/>
+      <c r="C17" s="373"/>
+      <c r="D17" s="373"/>
+      <c r="E17" s="373"/>
+      <c r="F17" s="373"/>
+      <c r="G17" s="373"/>
+      <c r="H17" s="333"/>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17"/>
@@ -21865,10 +21863,10 @@
       <c r="L19"/>
       <c r="M19"/>
       <c r="Y19" s="194"/>
-      <c r="Z19" s="241" t="s">
+      <c r="Z19" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="AA19" s="242"/>
+      <c r="AA19" s="287"/>
       <c r="AB19" s="193"/>
     </row>
     <row r="20" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -21960,16 +21958,16 @@
       <c r="AB24" s="193"/>
     </row>
     <row r="25" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J25" s="391" t="s">
+      <c r="J25" s="374" t="s">
         <v>90</v>
       </c>
-      <c r="K25" s="391"/>
-      <c r="L25" s="391"/>
-      <c r="M25" s="391"/>
-      <c r="N25" s="391"/>
-      <c r="O25" s="391"/>
-      <c r="P25" s="391"/>
-      <c r="Q25" s="391"/>
+      <c r="K25" s="374"/>
+      <c r="L25" s="374"/>
+      <c r="M25" s="374"/>
+      <c r="N25" s="374"/>
+      <c r="O25" s="374"/>
+      <c r="P25" s="374"/>
+      <c r="Q25" s="374"/>
       <c r="Y25" s="194"/>
       <c r="Z25" s="230" t="s">
         <v>662</v>
@@ -21978,10 +21976,10 @@
       <c r="AB25" s="193"/>
     </row>
     <row r="26" spans="2:28" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J26" s="245" t="s">
+      <c r="J26" s="377" t="s">
         <v>40</v>
       </c>
-      <c r="K26" s="246"/>
+      <c r="K26" s="378"/>
       <c r="L26" s="184" t="s">
         <v>117</v>
       </c>
@@ -22006,26 +22004,26 @@
       <c r="AB26" s="193"/>
     </row>
     <row r="27" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J27" s="255" t="s">
+      <c r="J27" s="249" t="s">
         <v>30</v>
       </c>
-      <c r="K27" s="256"/>
-      <c r="L27" s="256"/>
-      <c r="M27" s="256"/>
-      <c r="N27" s="256"/>
-      <c r="O27" s="256"/>
-      <c r="P27" s="256"/>
-      <c r="Q27" s="257"/>
+      <c r="K27" s="250"/>
+      <c r="L27" s="250"/>
+      <c r="M27" s="250"/>
+      <c r="N27" s="250"/>
+      <c r="O27" s="250"/>
+      <c r="P27" s="250"/>
+      <c r="Q27" s="251"/>
       <c r="Y27" s="196"/>
       <c r="Z27" s="197"/>
       <c r="AA27" s="223"/>
       <c r="AB27" s="198"/>
     </row>
     <row r="28" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J28" s="249" t="s">
+      <c r="J28" s="379" t="s">
         <v>91</v>
       </c>
-      <c r="K28" s="250"/>
+      <c r="K28" s="380"/>
       <c r="L28" s="36"/>
       <c r="M28" s="36"/>
       <c r="N28" s="36"/>
@@ -22034,7 +22032,7 @@
       <c r="Q28" s="37"/>
     </row>
     <row r="29" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J29" s="389" t="s">
+      <c r="J29" s="371" t="s">
         <v>92</v>
       </c>
       <c r="K29" s="34" t="s">
@@ -22048,7 +22046,7 @@
       <c r="Q29" s="45"/>
     </row>
     <row r="30" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J30" s="393"/>
+      <c r="J30" s="376"/>
       <c r="K30" s="34" t="s">
         <v>94</v>
       </c>
@@ -22067,7 +22065,7 @@
       <c r="W30" s="190"/>
     </row>
     <row r="31" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J31" s="390"/>
+      <c r="J31" s="372"/>
       <c r="K31" s="34" t="s">
         <v>95</v>
       </c>
@@ -22086,7 +22084,7 @@
       <c r="W31" s="208"/>
     </row>
     <row r="32" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J32" s="389" t="s">
+      <c r="J32" s="371" t="s">
         <v>100</v>
       </c>
       <c r="K32" s="34" t="s">
@@ -22099,15 +22097,15 @@
       <c r="P32" s="40"/>
       <c r="Q32" s="45"/>
       <c r="S32" s="194"/>
-      <c r="T32" s="243" t="s">
+      <c r="T32" s="247" t="s">
         <v>663</v>
       </c>
-      <c r="U32" s="243"/>
-      <c r="V32" s="243"/>
+      <c r="U32" s="247"/>
+      <c r="V32" s="247"/>
       <c r="W32" s="193"/>
     </row>
     <row r="33" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J33" s="393"/>
+      <c r="J33" s="376"/>
       <c r="K33" s="34" t="s">
         <v>93</v>
       </c>
@@ -22126,7 +22124,7 @@
       <c r="W33" s="193"/>
     </row>
     <row r="34" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J34" s="393"/>
+      <c r="J34" s="376"/>
       <c r="K34" s="34" t="s">
         <v>97</v>
       </c>
@@ -22149,7 +22147,7 @@
       <c r="W34" s="193"/>
     </row>
     <row r="35" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J35" s="390"/>
+      <c r="J35" s="372"/>
       <c r="K35" s="34" t="s">
         <v>98</v>
       </c>
@@ -22168,7 +22166,7 @@
       <c r="W35" s="193"/>
     </row>
     <row r="36" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J36" s="389" t="s">
+      <c r="J36" s="371" t="s">
         <v>319</v>
       </c>
       <c r="K36" s="34" t="s">
@@ -22189,7 +22187,7 @@
       <c r="W36" s="193"/>
     </row>
     <row r="37" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J37" s="393"/>
+      <c r="J37" s="376"/>
       <c r="K37" s="34" t="s">
         <v>93</v>
       </c>
@@ -22208,7 +22206,7 @@
       <c r="W37" s="193"/>
     </row>
     <row r="38" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J38" s="393"/>
+      <c r="J38" s="376"/>
       <c r="K38" s="34" t="s">
         <v>94</v>
       </c>
@@ -22227,7 +22225,7 @@
       <c r="W38" s="193"/>
     </row>
     <row r="39" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J39" s="390"/>
+      <c r="J39" s="372"/>
       <c r="K39" s="34" t="s">
         <v>95</v>
       </c>
@@ -22246,7 +22244,7 @@
       <c r="W39" s="193"/>
     </row>
     <row r="40" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J40" s="389" t="s">
+      <c r="J40" s="371" t="s">
         <v>99</v>
       </c>
       <c r="K40" s="34" t="s">
@@ -22269,7 +22267,7 @@
       <c r="X40"/>
     </row>
     <row r="41" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J41" s="393"/>
+      <c r="J41" s="376"/>
       <c r="K41" s="34" t="s">
         <v>93</v>
       </c>
@@ -22290,7 +22288,7 @@
       <c r="X41"/>
     </row>
     <row r="42" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J42" s="393"/>
+      <c r="J42" s="376"/>
       <c r="K42" s="34" t="s">
         <v>97</v>
       </c>
@@ -22311,7 +22309,7 @@
       <c r="X42"/>
     </row>
     <row r="43" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J43" s="393"/>
+      <c r="J43" s="376"/>
       <c r="K43" s="102" t="s">
         <v>98</v>
       </c>
@@ -22323,25 +22321,25 @@
       <c r="Q43" s="37"/>
       <c r="R43"/>
       <c r="S43" s="194"/>
-      <c r="T43" s="243" t="s">
+      <c r="T43" s="247" t="s">
         <v>107</v>
       </c>
-      <c r="U43" s="243"/>
+      <c r="U43" s="247"/>
       <c r="V43" s="235"/>
       <c r="W43" s="193"/>
       <c r="X43"/>
     </row>
     <row r="44" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J44" s="392" t="s">
+      <c r="J44" s="375" t="s">
         <v>107</v>
       </c>
-      <c r="K44" s="392"/>
-      <c r="L44" s="392"/>
-      <c r="M44" s="392"/>
-      <c r="N44" s="392"/>
-      <c r="O44" s="392"/>
-      <c r="P44" s="392"/>
-      <c r="Q44" s="392"/>
+      <c r="K44" s="375"/>
+      <c r="L44" s="375"/>
+      <c r="M44" s="375"/>
+      <c r="N44" s="375"/>
+      <c r="O44" s="375"/>
+      <c r="P44" s="375"/>
+      <c r="Q44" s="375"/>
       <c r="S44" s="194"/>
       <c r="T44" s="227" t="s">
         <v>649</v>
@@ -22351,10 +22349,10 @@
       <c r="W44" s="193"/>
     </row>
     <row r="45" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J45" s="292" t="s">
+      <c r="J45" s="316" t="s">
         <v>42</v>
       </c>
-      <c r="K45" s="292"/>
+      <c r="K45" s="316"/>
       <c r="L45" s="62"/>
       <c r="M45" s="62"/>
       <c r="N45" s="62"/>
@@ -22370,10 +22368,10 @@
       <c r="W45" s="193"/>
     </row>
     <row r="46" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J46" s="387" t="s">
+      <c r="J46" s="369" t="s">
         <v>314</v>
       </c>
-      <c r="K46" s="388"/>
+      <c r="K46" s="370"/>
       <c r="L46" s="62"/>
       <c r="M46" s="62"/>
       <c r="N46" s="62"/>
@@ -22389,10 +22387,10 @@
       <c r="W46" s="193"/>
     </row>
     <row r="47" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J47" s="387" t="s">
+      <c r="J47" s="369" t="s">
         <v>322</v>
       </c>
-      <c r="K47" s="388"/>
+      <c r="K47" s="370"/>
       <c r="L47" s="62"/>
       <c r="M47" s="62"/>
       <c r="N47" s="62"/>
@@ -22408,10 +22406,10 @@
       <c r="W47" s="193"/>
     </row>
     <row r="48" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J48" s="387" t="s">
+      <c r="J48" s="369" t="s">
         <v>321</v>
       </c>
-      <c r="K48" s="388"/>
+      <c r="K48" s="370"/>
       <c r="L48" s="62"/>
       <c r="M48" s="62"/>
       <c r="N48" s="62"/>
@@ -22427,10 +22425,10 @@
       <c r="W48" s="193"/>
     </row>
     <row r="49" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J49" s="387" t="s">
+      <c r="J49" s="369" t="s">
         <v>320</v>
       </c>
-      <c r="K49" s="388"/>
+      <c r="K49" s="370"/>
       <c r="L49" s="62"/>
       <c r="M49" s="62"/>
       <c r="N49" s="62"/>
@@ -22446,7 +22444,7 @@
       <c r="W49" s="193"/>
     </row>
     <row r="50" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J50" s="389" t="s">
+      <c r="J50" s="371" t="s">
         <v>37</v>
       </c>
       <c r="K50" s="111" t="s">
@@ -22467,7 +22465,7 @@
       <c r="W50" s="193"/>
     </row>
     <row r="51" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J51" s="390"/>
+      <c r="J51" s="372"/>
       <c r="K51" s="111" t="s">
         <v>318</v>
       </c>
@@ -22486,10 +22484,10 @@
       <c r="W51" s="193"/>
     </row>
     <row r="52" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J52" s="387" t="s">
+      <c r="J52" s="369" t="s">
         <v>64</v>
       </c>
-      <c r="K52" s="388"/>
+      <c r="K52" s="370"/>
       <c r="L52" s="62"/>
       <c r="M52" s="62"/>
       <c r="N52" s="62"/>
@@ -22505,10 +22503,10 @@
       <c r="W52" s="193"/>
     </row>
     <row r="53" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J53" s="387" t="s">
+      <c r="J53" s="369" t="s">
         <v>10</v>
       </c>
-      <c r="K53" s="388"/>
+      <c r="K53" s="370"/>
       <c r="L53" s="62"/>
       <c r="M53" s="62"/>
       <c r="N53" s="62"/>
@@ -22524,10 +22522,10 @@
       <c r="W53" s="193"/>
     </row>
     <row r="54" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J54" s="387" t="s">
+      <c r="J54" s="369" t="s">
         <v>315</v>
       </c>
-      <c r="K54" s="388"/>
+      <c r="K54" s="370"/>
       <c r="L54" s="62"/>
       <c r="M54" s="62"/>
       <c r="N54" s="62"/>
@@ -22543,10 +22541,10 @@
       <c r="W54" s="193"/>
     </row>
     <row r="55" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J55" s="387" t="s">
+      <c r="J55" s="369" t="s">
         <v>316</v>
       </c>
-      <c r="K55" s="388"/>
+      <c r="K55" s="370"/>
       <c r="L55" s="62"/>
       <c r="M55" s="62"/>
       <c r="N55" s="62"/>
@@ -22629,22 +22627,22 @@
   <sheetData>
     <row r="1" spans="2:20" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="244" t="s">
+      <c r="B2" s="258" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="244"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="244"/>
-      <c r="F2" s="244"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="244"/>
-      <c r="I2" s="244"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="258"/>
     </row>
     <row r="3" spans="2:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="245" t="s">
+      <c r="B3" s="377" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="246"/>
+      <c r="C3" s="378"/>
       <c r="D3" s="183" t="s">
         <v>117</v>
       </c>
@@ -22665,16 +22663,16 @@
       </c>
     </row>
     <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="255" t="s">
+      <c r="B4" s="249" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="256"/>
-      <c r="D4" s="256"/>
-      <c r="E4" s="256"/>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="256"/>
-      <c r="I4" s="257"/>
+      <c r="C4" s="250"/>
+      <c r="D4" s="250"/>
+      <c r="E4" s="250"/>
+      <c r="F4" s="250"/>
+      <c r="G4" s="250"/>
+      <c r="H4" s="250"/>
+      <c r="I4" s="251"/>
       <c r="L4" s="225"/>
       <c r="M4" s="215" t="s">
         <v>686</v>
@@ -22689,10 +22687,10 @@
       <c r="T4" s="190"/>
     </row>
     <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="249" t="s">
+      <c r="B5" s="379" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="250"/>
+      <c r="C5" s="380"/>
       <c r="D5" s="21"/>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
@@ -22713,10 +22711,10 @@
       <c r="T5" s="208"/>
     </row>
     <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="249" t="s">
+      <c r="B6" s="379" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="250"/>
+      <c r="C6" s="380"/>
       <c r="D6" s="21"/>
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
@@ -22724,16 +22722,16 @@
       <c r="H6" s="21"/>
       <c r="I6" s="32"/>
       <c r="L6" s="194"/>
-      <c r="M6" s="243" t="s">
+      <c r="M6" s="247" t="s">
         <v>107</v>
       </c>
-      <c r="N6" s="243"/>
+      <c r="N6" s="247"/>
       <c r="O6" s="193"/>
       <c r="Q6" s="194"/>
-      <c r="R6" s="243" t="s">
+      <c r="R6" s="247" t="s">
         <v>107</v>
       </c>
-      <c r="S6" s="243"/>
+      <c r="S6" s="247"/>
       <c r="T6" s="193"/>
     </row>
     <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -22761,10 +22759,10 @@
       <c r="T7" s="193"/>
     </row>
     <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="249" t="s">
+      <c r="B8" s="379" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="250"/>
+      <c r="C8" s="380"/>
       <c r="D8" s="21"/>
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
@@ -22785,16 +22783,16 @@
       <c r="T8" s="193"/>
     </row>
     <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="255" t="s">
+      <c r="B9" s="249" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="256"/>
-      <c r="D9" s="256"/>
-      <c r="E9" s="256"/>
-      <c r="F9" s="256"/>
-      <c r="G9" s="256"/>
-      <c r="H9" s="256"/>
-      <c r="I9" s="257"/>
+      <c r="C9" s="250"/>
+      <c r="D9" s="250"/>
+      <c r="E9" s="250"/>
+      <c r="F9" s="250"/>
+      <c r="G9" s="250"/>
+      <c r="H9" s="250"/>
+      <c r="I9" s="251"/>
       <c r="L9" s="194"/>
       <c r="M9" s="227" t="s">
         <v>634</v>
@@ -22809,7 +22807,7 @@
       <c r="T9" s="193"/>
     </row>
     <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="264" t="s">
+      <c r="B10" s="389" t="s">
         <v>73</v>
       </c>
       <c r="C10" s="35" t="s">
@@ -22835,7 +22833,7 @@
       <c r="T10" s="193"/>
     </row>
     <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="265"/>
+      <c r="B11" s="390"/>
       <c r="C11" s="35" t="s">
         <v>12</v>
       </c>
@@ -22846,20 +22844,20 @@
       <c r="H11" s="19"/>
       <c r="I11" s="24"/>
       <c r="L11" s="194"/>
-      <c r="M11" s="243" t="s">
+      <c r="M11" s="247" t="s">
         <v>663</v>
       </c>
-      <c r="N11" s="243"/>
+      <c r="N11" s="247"/>
       <c r="O11" s="193"/>
       <c r="Q11" s="194"/>
-      <c r="R11" s="243" t="s">
+      <c r="R11" s="247" t="s">
         <v>663</v>
       </c>
-      <c r="S11" s="243"/>
+      <c r="S11" s="247"/>
       <c r="T11" s="193"/>
     </row>
     <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="264" t="s">
+      <c r="B12" s="389" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="35" t="s">
@@ -22885,7 +22883,7 @@
       <c r="T12" s="193"/>
     </row>
     <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="265"/>
+      <c r="B13" s="390"/>
       <c r="C13" s="35" t="s">
         <v>12</v>
       </c>
@@ -22958,16 +22956,16 @@
     </row>
     <row r="17" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
-      <c r="B17" s="244" t="s">
+      <c r="B17" s="258" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="244"/>
-      <c r="D17" s="244"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
-      <c r="G17" s="244"/>
-      <c r="H17" s="244"/>
-      <c r="I17" s="244"/>
+      <c r="C17" s="258"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="258"/>
+      <c r="F17" s="258"/>
+      <c r="G17" s="258"/>
+      <c r="H17" s="258"/>
+      <c r="I17" s="258"/>
       <c r="K17"/>
       <c r="L17" s="238"/>
       <c r="M17" s="239"/>
@@ -22981,10 +22979,10 @@
     </row>
     <row r="18" spans="1:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
-      <c r="B18" s="245" t="s">
+      <c r="B18" s="377" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="246"/>
+      <c r="C18" s="378"/>
       <c r="D18" s="183" t="s">
         <v>117</v>
       </c>
@@ -23015,16 +23013,16 @@
     </row>
     <row r="19" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
-      <c r="B19" s="255" t="s">
+      <c r="B19" s="249" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="256"/>
-      <c r="D19" s="256"/>
-      <c r="E19" s="256"/>
-      <c r="F19" s="256"/>
-      <c r="G19" s="256"/>
-      <c r="H19" s="256"/>
-      <c r="I19" s="257"/>
+      <c r="C19" s="250"/>
+      <c r="D19" s="250"/>
+      <c r="E19" s="250"/>
+      <c r="F19" s="250"/>
+      <c r="G19" s="250"/>
+      <c r="H19" s="250"/>
+      <c r="I19" s="251"/>
       <c r="K19"/>
       <c r="L19"/>
       <c r="M19"/>
@@ -23037,10 +23035,10 @@
     </row>
     <row r="20" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
-      <c r="B20" s="249" t="s">
+      <c r="B20" s="379" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="250"/>
+      <c r="C20" s="380"/>
       <c r="D20" s="21"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
@@ -23059,10 +23057,10 @@
     </row>
     <row r="21" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
-      <c r="B21" s="249" t="s">
+      <c r="B21" s="379" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="250"/>
+      <c r="C21" s="380"/>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
@@ -23103,10 +23101,10 @@
     </row>
     <row r="23" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
-      <c r="B23" s="253" t="s">
+      <c r="B23" s="384" t="s">
         <v>244</v>
       </c>
-      <c r="C23" s="268"/>
+      <c r="C23" s="393"/>
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
@@ -23125,16 +23123,16 @@
     </row>
     <row r="24" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
-      <c r="B24" s="255" t="s">
+      <c r="B24" s="249" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="256"/>
-      <c r="D24" s="256"/>
-      <c r="E24" s="256"/>
-      <c r="F24" s="256"/>
-      <c r="G24" s="256"/>
-      <c r="H24" s="256"/>
-      <c r="I24" s="257"/>
+      <c r="C24" s="250"/>
+      <c r="D24" s="250"/>
+      <c r="E24" s="250"/>
+      <c r="F24" s="250"/>
+      <c r="G24" s="250"/>
+      <c r="H24" s="250"/>
+      <c r="I24" s="251"/>
       <c r="K24"/>
       <c r="L24"/>
       <c r="M24"/>
@@ -23147,10 +23145,10 @@
     </row>
     <row r="25" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
-      <c r="B25" s="266" t="s">
+      <c r="B25" s="391" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="267"/>
+      <c r="C25" s="392"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
@@ -23169,10 +23167,10 @@
     </row>
     <row r="26" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
-      <c r="B26" s="266" t="s">
+      <c r="B26" s="391" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="267"/>
+      <c r="C26" s="392"/>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
@@ -23191,10 +23189,10 @@
     </row>
     <row r="27" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
-      <c r="B27" s="266" t="s">
+      <c r="B27" s="391" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="267"/>
+      <c r="C27" s="392"/>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
@@ -23213,8 +23211,8 @@
     </row>
     <row r="28" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
-      <c r="B28" s="262"/>
-      <c r="C28" s="263"/>
+      <c r="B28" s="387"/>
+      <c r="C28" s="388"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="19"/>
@@ -23244,23 +23242,23 @@
       <c r="S29"/>
     </row>
     <row r="30" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="244" t="s">
+      <c r="B30" s="258" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="244"/>
-      <c r="D30" s="244"/>
-      <c r="E30" s="244"/>
-      <c r="F30" s="244"/>
-      <c r="G30" s="244"/>
-      <c r="H30" s="244"/>
-      <c r="I30" s="244"/>
+      <c r="C30" s="258"/>
+      <c r="D30" s="258"/>
+      <c r="E30" s="258"/>
+      <c r="F30" s="258"/>
+      <c r="G30" s="258"/>
+      <c r="H30" s="258"/>
+      <c r="I30" s="258"/>
       <c r="J30"/>
     </row>
     <row r="31" spans="1:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="245" t="s">
+      <c r="B31" s="377" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="246"/>
+      <c r="C31" s="378"/>
       <c r="D31" s="183" t="s">
         <v>117</v>
       </c>
@@ -23282,10 +23280,10 @@
       <c r="J31"/>
     </row>
     <row r="32" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="247" t="s">
+      <c r="B32" s="381" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="248"/>
+      <c r="C32" s="382"/>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -23301,16 +23299,16 @@
       <c r="O32" s="190"/>
     </row>
     <row r="33" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="255" t="s">
+      <c r="B33" s="249" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="256"/>
-      <c r="D33" s="256"/>
-      <c r="E33" s="256"/>
-      <c r="F33" s="256"/>
-      <c r="G33" s="256"/>
-      <c r="H33" s="256"/>
-      <c r="I33" s="257"/>
+      <c r="C33" s="250"/>
+      <c r="D33" s="250"/>
+      <c r="E33" s="250"/>
+      <c r="F33" s="250"/>
+      <c r="G33" s="250"/>
+      <c r="H33" s="250"/>
+      <c r="I33" s="251"/>
       <c r="J33"/>
       <c r="L33" s="194"/>
       <c r="M33" s="216" t="s">
@@ -23320,7 +23318,7 @@
       <c r="O33" s="208"/>
     </row>
     <row r="34" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="258" t="s">
+      <c r="B34" s="357" t="s">
         <v>83</v>
       </c>
       <c r="C34" s="35" t="s">
@@ -23341,7 +23339,7 @@
       <c r="O34" s="193"/>
     </row>
     <row r="35" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="258"/>
+      <c r="B35" s="357"/>
       <c r="C35" s="35" t="s">
         <v>12</v>
       </c>
@@ -23353,14 +23351,14 @@
       <c r="I35" s="24"/>
       <c r="J35"/>
       <c r="L35" s="194"/>
-      <c r="M35" s="241" t="s">
+      <c r="M35" s="285" t="s">
         <v>663</v>
       </c>
-      <c r="N35" s="242"/>
+      <c r="N35" s="287"/>
       <c r="O35" s="193"/>
     </row>
     <row r="36" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="258" t="s">
+      <c r="B36" s="357" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="35" t="s">
@@ -23381,7 +23379,7 @@
       <c r="O36" s="193"/>
     </row>
     <row r="37" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="258"/>
+      <c r="B37" s="357"/>
       <c r="C37" s="35" t="s">
         <v>12</v>
       </c>
@@ -23400,10 +23398,10 @@
       <c r="O37" s="193"/>
     </row>
     <row r="38" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="249" t="s">
+      <c r="B38" s="379" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="250"/>
+      <c r="C38" s="380"/>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
@@ -23419,16 +23417,16 @@
       <c r="O38" s="193"/>
     </row>
     <row r="39" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="260" t="s">
+      <c r="B39" s="386" t="s">
         <v>65</v>
       </c>
-      <c r="C39" s="261"/>
-      <c r="D39" s="256"/>
-      <c r="E39" s="256"/>
-      <c r="F39" s="256"/>
-      <c r="G39" s="256"/>
-      <c r="H39" s="256"/>
-      <c r="I39" s="257"/>
+      <c r="C39" s="373"/>
+      <c r="D39" s="250"/>
+      <c r="E39" s="250"/>
+      <c r="F39" s="250"/>
+      <c r="G39" s="250"/>
+      <c r="H39" s="250"/>
+      <c r="I39" s="251"/>
       <c r="J39"/>
       <c r="L39" s="194"/>
       <c r="M39" s="227" t="s">
@@ -23438,10 +23436,10 @@
       <c r="O39" s="193"/>
     </row>
     <row r="40" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="258" t="s">
+      <c r="B40" s="357" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="258"/>
+      <c r="C40" s="357"/>
       <c r="D40" s="33"/>
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
@@ -23457,10 +23455,10 @@
       <c r="O40" s="193"/>
     </row>
     <row r="41" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="258" t="s">
+      <c r="B41" s="357" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="258"/>
+      <c r="C41" s="357"/>
       <c r="D41" s="33"/>
       <c r="E41" s="19"/>
       <c r="F41" s="19"/>
@@ -23469,17 +23467,17 @@
       <c r="I41" s="24"/>
       <c r="J41"/>
       <c r="L41" s="194"/>
-      <c r="M41" s="241" t="s">
+      <c r="M41" s="285" t="s">
         <v>65</v>
       </c>
-      <c r="N41" s="242"/>
+      <c r="N41" s="287"/>
       <c r="O41" s="193"/>
     </row>
     <row r="42" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="251" t="s">
+      <c r="B42" s="311" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="259"/>
+      <c r="C42" s="312"/>
       <c r="D42" s="33"/>
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
@@ -23495,10 +23493,10 @@
       <c r="O42" s="193"/>
     </row>
     <row r="43" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="258" t="s">
+      <c r="B43" s="357" t="s">
         <v>85</v>
       </c>
-      <c r="C43" s="258"/>
+      <c r="C43" s="357"/>
       <c r="D43" s="33"/>
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
@@ -23557,22 +23555,22 @@
       <c r="J48"/>
     </row>
     <row r="49" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="244" t="s">
+      <c r="B49" s="258" t="s">
         <v>89</v>
       </c>
-      <c r="C49" s="244"/>
-      <c r="D49" s="244"/>
-      <c r="E49" s="244"/>
-      <c r="F49" s="244"/>
-      <c r="G49" s="244"/>
-      <c r="H49" s="244"/>
-      <c r="I49" s="244"/>
+      <c r="C49" s="258"/>
+      <c r="D49" s="258"/>
+      <c r="E49" s="258"/>
+      <c r="F49" s="258"/>
+      <c r="G49" s="258"/>
+      <c r="H49" s="258"/>
+      <c r="I49" s="258"/>
     </row>
     <row r="50" spans="2:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="245" t="s">
+      <c r="B50" s="377" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="246"/>
+      <c r="C50" s="378"/>
       <c r="D50" s="183" t="s">
         <v>117</v>
       </c>
@@ -23593,10 +23591,10 @@
       </c>
     </row>
     <row r="51" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="247" t="s">
+      <c r="B51" s="381" t="s">
         <v>86</v>
       </c>
-      <c r="C51" s="248"/>
+      <c r="C51" s="382"/>
       <c r="D51" s="22"/>
       <c r="E51" s="22"/>
       <c r="F51" s="22"/>
@@ -23605,10 +23603,10 @@
       <c r="I51" s="27"/>
     </row>
     <row r="52" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="249" t="s">
+      <c r="B52" s="379" t="s">
         <v>87</v>
       </c>
-      <c r="C52" s="250"/>
+      <c r="C52" s="380"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
       <c r="F52" s="21"/>
@@ -23617,10 +23615,10 @@
       <c r="I52" s="32"/>
     </row>
     <row r="53" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="249" t="s">
+      <c r="B53" s="379" t="s">
         <v>88</v>
       </c>
-      <c r="C53" s="250"/>
+      <c r="C53" s="380"/>
       <c r="D53" s="25"/>
       <c r="E53" s="25"/>
       <c r="F53" s="25"/>
@@ -23629,22 +23627,22 @@
       <c r="I53" s="26"/>
     </row>
     <row r="55" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="244" t="s">
+      <c r="B55" s="258" t="s">
         <v>308</v>
       </c>
-      <c r="C55" s="244"/>
-      <c r="D55" s="244"/>
-      <c r="E55" s="244"/>
-      <c r="F55" s="244"/>
-      <c r="G55" s="244"/>
-      <c r="H55" s="244"/>
-      <c r="I55" s="244"/>
+      <c r="C55" s="258"/>
+      <c r="D55" s="258"/>
+      <c r="E55" s="258"/>
+      <c r="F55" s="258"/>
+      <c r="G55" s="258"/>
+      <c r="H55" s="258"/>
+      <c r="I55" s="258"/>
     </row>
     <row r="56" spans="2:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="245" t="s">
+      <c r="B56" s="377" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="246"/>
+      <c r="C56" s="378"/>
       <c r="D56" s="183" t="s">
         <v>117</v>
       </c>
@@ -23665,10 +23663,10 @@
       </c>
     </row>
     <row r="57" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="247" t="s">
+      <c r="B57" s="381" t="s">
         <v>309</v>
       </c>
-      <c r="C57" s="248"/>
+      <c r="C57" s="382"/>
       <c r="D57" s="109"/>
       <c r="E57" s="109"/>
       <c r="F57" s="109"/>
@@ -23689,10 +23687,10 @@
       <c r="T57" s="190"/>
     </row>
     <row r="58" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="251" t="s">
+      <c r="B58" s="311" t="s">
         <v>310</v>
       </c>
-      <c r="C58" s="252"/>
+      <c r="C58" s="383"/>
       <c r="D58" s="23"/>
       <c r="E58" s="23"/>
       <c r="F58" s="23"/>
@@ -23713,10 +23711,10 @@
       <c r="T58" s="208"/>
     </row>
     <row r="59" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="253" t="s">
+      <c r="B59" s="384" t="s">
         <v>311</v>
       </c>
-      <c r="C59" s="254"/>
+      <c r="C59" s="385"/>
       <c r="D59" s="23"/>
       <c r="E59" s="23"/>
       <c r="F59" s="23"/>
@@ -23737,10 +23735,10 @@
       <c r="T59" s="193"/>
     </row>
     <row r="60" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="249" t="s">
+      <c r="B60" s="379" t="s">
         <v>312</v>
       </c>
-      <c r="C60" s="250"/>
+      <c r="C60" s="380"/>
       <c r="D60" s="109"/>
       <c r="E60" s="109"/>
       <c r="F60" s="109"/>
@@ -23761,10 +23759,10 @@
       <c r="T60" s="193"/>
     </row>
     <row r="61" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="249" t="s">
+      <c r="B61" s="379" t="s">
         <v>313</v>
       </c>
-      <c r="C61" s="250"/>
+      <c r="C61" s="380"/>
       <c r="D61" s="25"/>
       <c r="E61" s="25"/>
       <c r="F61" s="25"/>
@@ -23892,12 +23890,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="244" t="s">
+      <c r="A1" s="258" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="244"/>
-      <c r="C1" s="244"/>
-      <c r="D1" s="244"/>
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
     </row>
     <row r="2" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -24000,13 +23998,13 @@
       <c r="D15" s="43"/>
     </row>
     <row r="16" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F16" s="244" t="s">
+      <c r="F16" s="258" t="s">
         <v>142</v>
       </c>
-      <c r="G16" s="244"/>
-      <c r="H16" s="244"/>
-      <c r="I16" s="244"/>
-      <c r="J16" s="244"/>
+      <c r="G16" s="258"/>
+      <c r="H16" s="258"/>
+      <c r="I16" s="258"/>
+      <c r="J16" s="258"/>
     </row>
     <row r="17" spans="6:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F17" s="3"/>
@@ -24069,23 +24067,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="244" t="s">
+      <c r="A1" s="258" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="244"/>
-      <c r="C1" s="244"/>
-      <c r="D1" s="244"/>
-      <c r="E1" s="244"/>
-      <c r="F1" s="244"/>
-      <c r="G1" s="244"/>
-      <c r="H1" s="244"/>
-      <c r="I1" s="244"/>
-      <c r="J1" s="244"/>
-      <c r="K1" s="244"/>
-      <c r="L1" s="244"/>
-      <c r="M1" s="244"/>
-      <c r="N1" s="244"/>
-      <c r="O1" s="244"/>
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
+      <c r="E1" s="258"/>
+      <c r="F1" s="258"/>
+      <c r="G1" s="258"/>
+      <c r="H1" s="258"/>
+      <c r="I1" s="258"/>
+      <c r="J1" s="258"/>
+      <c r="K1" s="258"/>
+      <c r="L1" s="258"/>
+      <c r="M1" s="258"/>
+      <c r="N1" s="258"/>
+      <c r="O1" s="258"/>
     </row>
     <row r="2" spans="1:15" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="s">
@@ -24135,7 +24133,7 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="392" t="s">
+      <c r="A3" s="375" t="s">
         <v>150</v>
       </c>
       <c r="B3" s="44" t="s">
@@ -24182,7 +24180,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="392"/>
+      <c r="A4" s="375"/>
       <c r="B4" s="57" t="s">
         <v>22</v>
       </c>
@@ -24227,7 +24225,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="392" t="s">
+      <c r="A5" s="375" t="s">
         <v>151</v>
       </c>
       <c r="B5" s="44" t="s">
@@ -24248,7 +24246,7 @@
       <c r="O5" s="43"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="392"/>
+      <c r="A6" s="375"/>
       <c r="B6" s="57" t="s">
         <v>22</v>
       </c>
@@ -24267,7 +24265,7 @@
       <c r="O6" s="43"/>
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="392" t="s">
+      <c r="A7" s="375" t="s">
         <v>152</v>
       </c>
       <c r="B7" s="44" t="s">
@@ -24288,7 +24286,7 @@
       <c r="O7" s="43"/>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="392"/>
+      <c r="A8" s="375"/>
       <c r="B8" s="57" t="s">
         <v>22</v>
       </c>
@@ -24307,7 +24305,7 @@
       <c r="O8" s="43"/>
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="392" t="s">
+      <c r="A9" s="375" t="s">
         <v>153</v>
       </c>
       <c r="B9" s="44" t="s">
@@ -24328,7 +24326,7 @@
       <c r="O9" s="43"/>
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="392"/>
+      <c r="A10" s="375"/>
       <c r="B10" s="57" t="s">
         <v>22</v>
       </c>
@@ -24347,7 +24345,7 @@
       <c r="O10" s="43"/>
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="392" t="s">
+      <c r="A11" s="375" t="s">
         <v>154</v>
       </c>
       <c r="B11" s="44" t="s">
@@ -24368,7 +24366,7 @@
       <c r="O11" s="43"/>
     </row>
     <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="392"/>
+      <c r="A12" s="375"/>
       <c r="B12" s="57" t="s">
         <v>22</v>
       </c>
@@ -24387,7 +24385,7 @@
       <c r="O12" s="43"/>
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="392" t="s">
+      <c r="A13" s="375" t="s">
         <v>155</v>
       </c>
       <c r="B13" s="44" t="s">
@@ -24408,7 +24406,7 @@
       <c r="O13" s="43"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="392"/>
+      <c r="A14" s="375"/>
       <c r="B14" s="57" t="s">
         <v>22</v>
       </c>
@@ -24427,7 +24425,7 @@
       <c r="O14" s="43"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="392" t="s">
+      <c r="A15" s="375" t="s">
         <v>156</v>
       </c>
       <c r="B15" s="44" t="s">
@@ -24448,7 +24446,7 @@
       <c r="O15" s="43"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="392"/>
+      <c r="A16" s="375"/>
       <c r="B16" s="57" t="s">
         <v>22</v>
       </c>
@@ -24487,7 +24485,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="392" t="s">
+      <c r="A19" s="375" t="s">
         <v>174</v>
       </c>
       <c r="B19" s="44" t="s">
@@ -24507,7 +24505,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="392"/>
+      <c r="A20" s="375"/>
       <c r="B20" s="57" t="s">
         <v>22</v>
       </c>
@@ -24525,7 +24523,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="392" t="s">
+      <c r="A21" s="375" t="s">
         <v>175</v>
       </c>
       <c r="B21" s="44" t="s">
@@ -24537,7 +24535,7 @@
       <c r="F21" s="43"/>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="392"/>
+      <c r="A22" s="375"/>
       <c r="B22" s="57" t="s">
         <v>22</v>
       </c>
@@ -24547,7 +24545,7 @@
       <c r="F22" s="58"/>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="392" t="s">
+      <c r="A23" s="375" t="s">
         <v>173</v>
       </c>
       <c r="B23" s="44" t="s">
@@ -24559,7 +24557,7 @@
       <c r="F23" s="43"/>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="392"/>
+      <c r="A24" s="375"/>
       <c r="B24" s="57" t="s">
         <v>22</v>
       </c>
@@ -24595,7 +24593,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="392" t="s">
+      <c r="A27" s="375" t="s">
         <v>182</v>
       </c>
       <c r="B27" s="44" t="s">
@@ -24621,7 +24619,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="392"/>
+      <c r="A28" s="375"/>
       <c r="B28" s="57" t="s">
         <v>22</v>
       </c>
@@ -24645,7 +24643,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="392" t="s">
+      <c r="A29" s="375" t="s">
         <v>183</v>
       </c>
       <c r="B29" s="44" t="s">
@@ -24659,7 +24657,7 @@
       <c r="H29" s="43"/>
     </row>
     <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="392"/>
+      <c r="A30" s="375"/>
       <c r="B30" s="57" t="s">
         <v>22</v>
       </c>
@@ -24671,7 +24669,7 @@
       <c r="H30" s="58"/>
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="392" t="s">
+      <c r="A31" s="375" t="s">
         <v>184</v>
       </c>
       <c r="B31" s="44" t="s">
@@ -24685,7 +24683,7 @@
       <c r="H31" s="43"/>
     </row>
     <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="392"/>
+      <c r="A32" s="375"/>
       <c r="B32" s="57" t="s">
         <v>22</v>
       </c>
@@ -24697,7 +24695,7 @@
       <c r="H32" s="43"/>
     </row>
     <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="392" t="s">
+      <c r="A33" s="375" t="s">
         <v>185</v>
       </c>
       <c r="B33" s="44" t="s">
@@ -24711,7 +24709,7 @@
       <c r="H33" s="43"/>
     </row>
     <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="392"/>
+      <c r="A34" s="375"/>
       <c r="B34" s="57" t="s">
         <v>22</v>
       </c>
@@ -24743,7 +24741,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="392" t="s">
+      <c r="A37" s="375" t="s">
         <v>192</v>
       </c>
       <c r="B37" s="44" t="s">
@@ -24763,7 +24761,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="392"/>
+      <c r="A38" s="375"/>
       <c r="B38" s="57" t="s">
         <v>22</v>
       </c>
@@ -24781,7 +24779,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="392" t="s">
+      <c r="A39" s="375" t="s">
         <v>193</v>
       </c>
       <c r="B39" s="44" t="s">
@@ -24793,7 +24791,7 @@
       <c r="F39" s="43"/>
     </row>
     <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="392"/>
+      <c r="A40" s="375"/>
       <c r="B40" s="57" t="s">
         <v>22</v>
       </c>
@@ -24803,7 +24801,7 @@
       <c r="F40" s="58"/>
     </row>
     <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="392" t="s">
+      <c r="A41" s="375" t="s">
         <v>194</v>
       </c>
       <c r="B41" s="44" t="s">
@@ -24815,7 +24813,7 @@
       <c r="F41" s="43"/>
     </row>
     <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="392"/>
+      <c r="A42" s="375"/>
       <c r="B42" s="57" t="s">
         <v>22</v>
       </c>
@@ -24862,13 +24860,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="244" t="s">
+      <c r="A1" s="258" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="244"/>
-      <c r="C1" s="244"/>
-      <c r="D1" s="244"/>
-      <c r="E1" s="244"/>
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
+      <c r="E1" s="258"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="59" t="s">
@@ -24967,10 +24965,10 @@
         <v>207</v>
       </c>
       <c r="B10" s="43"/>
-      <c r="C10" s="251" t="s">
+      <c r="C10" s="311" t="s">
         <v>222</v>
       </c>
-      <c r="D10" s="259"/>
+      <c r="D10" s="312"/>
       <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -24978,10 +24976,10 @@
         <v>208</v>
       </c>
       <c r="B11" s="43"/>
-      <c r="C11" s="251" t="s">
+      <c r="C11" s="311" t="s">
         <v>226</v>
       </c>
-      <c r="D11" s="259"/>
+      <c r="D11" s="312"/>
       <c r="E11" s="43"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -25076,228 +25074,228 @@
   <sheetData>
     <row r="1" spans="2:16" ht="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="276" t="s">
+      <c r="B2" s="298" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="276"/>
-      <c r="D2" s="276"/>
-      <c r="E2" s="276"/>
-      <c r="F2" s="276"/>
-      <c r="G2" s="276"/>
-      <c r="H2" s="276"/>
-      <c r="J2" s="284" t="s">
+      <c r="C2" s="298"/>
+      <c r="D2" s="298"/>
+      <c r="E2" s="298"/>
+      <c r="F2" s="298"/>
+      <c r="G2" s="298"/>
+      <c r="H2" s="298"/>
+      <c r="J2" s="306" t="s">
         <v>425</v>
       </c>
-      <c r="K2" s="285"/>
-      <c r="L2" s="285"/>
-      <c r="M2" s="285"/>
-      <c r="N2" s="285"/>
-      <c r="O2" s="285"/>
-      <c r="P2" s="286"/>
+      <c r="K2" s="307"/>
+      <c r="L2" s="307"/>
+      <c r="M2" s="307"/>
+      <c r="N2" s="307"/>
+      <c r="O2" s="307"/>
+      <c r="P2" s="308"/>
     </row>
     <row r="3" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="280" t="s">
+      <c r="B3" s="302" t="s">
         <v>419</v>
       </c>
       <c r="C3" s="117" t="s">
         <v>415</v>
       </c>
       <c r="D3" s="118"/>
-      <c r="E3" s="280" t="s">
+      <c r="E3" s="302" t="s">
         <v>420</v>
       </c>
-      <c r="F3" s="274" t="s">
+      <c r="F3" s="296" t="s">
         <v>342</v>
       </c>
-      <c r="G3" s="275"/>
+      <c r="G3" s="297"/>
       <c r="H3" s="123"/>
-      <c r="J3" s="277" t="s">
+      <c r="J3" s="299" t="s">
         <v>424</v>
       </c>
       <c r="K3" s="41" t="s">
         <v>421</v>
       </c>
       <c r="L3" s="118"/>
-      <c r="M3" s="280" t="s">
+      <c r="M3" s="302" t="s">
         <v>427</v>
       </c>
-      <c r="N3" s="274" t="s">
+      <c r="N3" s="296" t="s">
         <v>416</v>
       </c>
-      <c r="O3" s="275"/>
+      <c r="O3" s="297"/>
       <c r="P3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="280"/>
+      <c r="B4" s="302"/>
       <c r="C4" s="117" t="s">
         <v>414</v>
       </c>
       <c r="D4" s="123"/>
-      <c r="E4" s="280"/>
-      <c r="F4" s="274" t="s">
+      <c r="E4" s="302"/>
+      <c r="F4" s="296" t="s">
         <v>413</v>
       </c>
-      <c r="G4" s="275"/>
+      <c r="G4" s="297"/>
       <c r="H4" s="123"/>
-      <c r="J4" s="278"/>
+      <c r="J4" s="300"/>
       <c r="K4" s="41" t="s">
         <v>422</v>
       </c>
       <c r="L4" s="118"/>
-      <c r="M4" s="280"/>
-      <c r="N4" s="274" t="s">
+      <c r="M4" s="302"/>
+      <c r="N4" s="296" t="s">
         <v>417</v>
       </c>
-      <c r="O4" s="275"/>
+      <c r="O4" s="297"/>
       <c r="P4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="280"/>
+      <c r="B5" s="302"/>
       <c r="C5" s="117" t="s">
         <v>340</v>
       </c>
       <c r="D5" s="123"/>
-      <c r="E5" s="280"/>
-      <c r="F5" s="274" t="s">
+      <c r="E5" s="302"/>
+      <c r="F5" s="296" t="s">
         <v>343</v>
       </c>
-      <c r="G5" s="275"/>
+      <c r="G5" s="297"/>
       <c r="H5" s="123"/>
-      <c r="J5" s="279"/>
+      <c r="J5" s="301"/>
       <c r="K5" s="41" t="s">
         <v>423</v>
       </c>
       <c r="L5" s="118"/>
-      <c r="M5" s="280"/>
-      <c r="N5" s="274" t="s">
+      <c r="M5" s="302"/>
+      <c r="N5" s="296" t="s">
         <v>418</v>
       </c>
-      <c r="O5" s="275"/>
+      <c r="O5" s="297"/>
       <c r="P5" s="118"/>
     </row>
     <row r="6" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="280"/>
+      <c r="B6" s="302"/>
       <c r="C6" s="117" t="s">
         <v>341</v>
       </c>
       <c r="D6" s="118"/>
-      <c r="E6" s="280"/>
-      <c r="F6" s="274" t="s">
+      <c r="E6" s="302"/>
+      <c r="F6" s="296" t="s">
         <v>113</v>
       </c>
-      <c r="G6" s="275"/>
+      <c r="G6" s="297"/>
       <c r="H6" s="123"/>
-      <c r="J6" s="280" t="s">
+      <c r="J6" s="302" t="s">
         <v>366</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>385</v>
       </c>
       <c r="L6" s="23"/>
-      <c r="M6" s="280" t="s">
+      <c r="M6" s="302" t="s">
         <v>366</v>
       </c>
-      <c r="N6" s="251" t="s">
+      <c r="N6" s="311" t="s">
         <v>410</v>
       </c>
-      <c r="O6" s="259"/>
+      <c r="O6" s="312"/>
       <c r="P6" s="23"/>
     </row>
     <row r="7" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="276" t="s">
+      <c r="B7" s="298" t="s">
         <v>238</v>
       </c>
-      <c r="C7" s="276"/>
-      <c r="D7" s="276"/>
-      <c r="E7" s="276"/>
-      <c r="F7" s="276"/>
-      <c r="G7" s="276"/>
-      <c r="H7" s="276"/>
-      <c r="J7" s="280"/>
+      <c r="C7" s="298"/>
+      <c r="D7" s="298"/>
+      <c r="E7" s="298"/>
+      <c r="F7" s="298"/>
+      <c r="G7" s="298"/>
+      <c r="H7" s="298"/>
+      <c r="J7" s="302"/>
       <c r="K7" s="3" t="s">
         <v>386</v>
       </c>
       <c r="L7" s="23"/>
-      <c r="M7" s="280"/>
-      <c r="N7" s="251" t="s">
+      <c r="M7" s="302"/>
+      <c r="N7" s="311" t="s">
         <v>411</v>
       </c>
-      <c r="O7" s="259"/>
+      <c r="O7" s="312"/>
       <c r="P7" s="23"/>
     </row>
     <row r="8" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="277" t="s">
+      <c r="B8" s="299" t="s">
         <v>389</v>
       </c>
       <c r="C8" s="117" t="s">
         <v>57</v>
       </c>
       <c r="D8" s="118"/>
-      <c r="E8" s="280" t="s">
+      <c r="E8" s="302" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="274" t="s">
+      <c r="F8" s="296" t="s">
         <v>388</v>
       </c>
-      <c r="G8" s="275"/>
+      <c r="G8" s="297"/>
       <c r="H8" s="118"/>
-      <c r="J8" s="280"/>
+      <c r="J8" s="302"/>
       <c r="K8" s="3" t="s">
         <v>409</v>
       </c>
       <c r="L8" s="23"/>
-      <c r="M8" s="280"/>
-      <c r="N8" s="287"/>
-      <c r="O8" s="288"/>
+      <c r="M8" s="302"/>
+      <c r="N8" s="309"/>
+      <c r="O8" s="310"/>
       <c r="P8" s="118"/>
     </row>
     <row r="9" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="278"/>
+      <c r="B9" s="300"/>
       <c r="C9" s="117" t="s">
         <v>356</v>
       </c>
       <c r="D9" s="118"/>
-      <c r="E9" s="280"/>
-      <c r="F9" s="274" t="s">
+      <c r="E9" s="302"/>
+      <c r="F9" s="296" t="s">
         <v>364</v>
       </c>
-      <c r="G9" s="275"/>
+      <c r="G9" s="297"/>
       <c r="H9" s="118"/>
-      <c r="J9" s="276" t="s">
+      <c r="J9" s="298" t="s">
         <v>431</v>
       </c>
-      <c r="K9" s="276"/>
-      <c r="L9" s="276"/>
-      <c r="M9" s="276"/>
-      <c r="N9" s="276"/>
-      <c r="O9" s="276"/>
-      <c r="P9" s="276"/>
+      <c r="K9" s="298"/>
+      <c r="L9" s="298"/>
+      <c r="M9" s="298"/>
+      <c r="N9" s="298"/>
+      <c r="O9" s="298"/>
+      <c r="P9" s="298"/>
     </row>
     <row r="10" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="278"/>
+      <c r="B10" s="300"/>
       <c r="C10" s="117" t="s">
         <v>357</v>
       </c>
       <c r="D10" s="118" t="s">
         <v>358</v>
       </c>
-      <c r="E10" s="280"/>
-      <c r="F10" s="274" t="s">
+      <c r="E10" s="302"/>
+      <c r="F10" s="296" t="s">
         <v>365</v>
       </c>
-      <c r="G10" s="275"/>
+      <c r="G10" s="297"/>
       <c r="H10" s="118"/>
-      <c r="J10" s="290" t="s">
+      <c r="J10" s="314" t="s">
         <v>323</v>
       </c>
-      <c r="K10" s="290"/>
+      <c r="K10" s="314"/>
       <c r="L10" s="99" t="s">
         <v>344</v>
       </c>
-      <c r="M10" s="291" t="s">
+      <c r="M10" s="315" t="s">
         <v>345</v>
       </c>
-      <c r="N10" s="291"/>
+      <c r="N10" s="315"/>
       <c r="O10" s="99" t="s">
         <v>346</v>
       </c>
@@ -25306,186 +25304,186 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="278"/>
+      <c r="B11" s="300"/>
       <c r="C11" s="117" t="s">
         <v>112</v>
       </c>
       <c r="D11" s="118"/>
-      <c r="E11" s="280"/>
-      <c r="F11" s="274" t="s">
+      <c r="E11" s="302"/>
+      <c r="F11" s="296" t="s">
         <v>396</v>
       </c>
-      <c r="G11" s="275"/>
+      <c r="G11" s="297"/>
       <c r="H11" s="118"/>
-      <c r="J11" s="292" t="s">
+      <c r="J11" s="316" t="s">
         <v>348</v>
       </c>
-      <c r="K11" s="292"/>
+      <c r="K11" s="316"/>
       <c r="L11" s="62"/>
-      <c r="M11" s="289"/>
-      <c r="N11" s="289"/>
+      <c r="M11" s="313"/>
+      <c r="N11" s="313"/>
       <c r="O11" s="62"/>
       <c r="P11" s="127"/>
     </row>
     <row r="12" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="278"/>
+      <c r="B12" s="300"/>
       <c r="C12" s="117" t="s">
         <v>360</v>
       </c>
       <c r="D12" s="118"/>
-      <c r="E12" s="280"/>
-      <c r="F12" s="274" t="s">
+      <c r="E12" s="302"/>
+      <c r="F12" s="296" t="s">
         <v>392</v>
       </c>
-      <c r="G12" s="275"/>
+      <c r="G12" s="297"/>
       <c r="H12" s="118"/>
-      <c r="J12" s="292" t="s">
+      <c r="J12" s="316" t="s">
         <v>350</v>
       </c>
-      <c r="K12" s="292"/>
+      <c r="K12" s="316"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="289"/>
-      <c r="N12" s="289"/>
+      <c r="M12" s="313"/>
+      <c r="N12" s="313"/>
       <c r="O12" s="62"/>
       <c r="P12" s="127"/>
     </row>
     <row r="13" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="278"/>
+      <c r="B13" s="300"/>
       <c r="C13" s="117" t="s">
         <v>391</v>
       </c>
       <c r="D13" s="118"/>
-      <c r="E13" s="280"/>
-      <c r="F13" s="274" t="s">
+      <c r="E13" s="302"/>
+      <c r="F13" s="296" t="s">
         <v>367</v>
       </c>
-      <c r="G13" s="275"/>
+      <c r="G13" s="297"/>
       <c r="H13" s="118"/>
-      <c r="J13" s="292" t="s">
+      <c r="J13" s="316" t="s">
         <v>352</v>
       </c>
-      <c r="K13" s="292"/>
+      <c r="K13" s="316"/>
       <c r="L13" s="127"/>
-      <c r="M13" s="289"/>
-      <c r="N13" s="289"/>
+      <c r="M13" s="313"/>
+      <c r="N13" s="313"/>
       <c r="O13" s="127"/>
       <c r="P13" s="127"/>
     </row>
     <row r="14" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="278"/>
+      <c r="B14" s="300"/>
       <c r="C14" s="117" t="s">
         <v>361</v>
       </c>
       <c r="D14" s="118"/>
-      <c r="E14" s="277" t="s">
+      <c r="E14" s="299" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="274" t="s">
+      <c r="F14" s="296" t="s">
         <v>368</v>
       </c>
-      <c r="G14" s="275"/>
+      <c r="G14" s="297"/>
       <c r="H14" s="118"/>
-      <c r="J14" s="292" t="s">
+      <c r="J14" s="316" t="s">
         <v>353</v>
       </c>
-      <c r="K14" s="292"/>
+      <c r="K14" s="316"/>
       <c r="L14" s="127"/>
-      <c r="M14" s="289"/>
-      <c r="N14" s="289"/>
+      <c r="M14" s="313"/>
+      <c r="N14" s="313"/>
       <c r="O14" s="127"/>
       <c r="P14" s="127"/>
     </row>
     <row r="15" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="278"/>
+      <c r="B15" s="300"/>
       <c r="C15" s="117" t="s">
         <v>362</v>
       </c>
       <c r="D15" s="118"/>
-      <c r="E15" s="278"/>
-      <c r="F15" s="274" t="s">
+      <c r="E15" s="300"/>
+      <c r="F15" s="296" t="s">
         <v>369</v>
       </c>
-      <c r="G15" s="275"/>
+      <c r="G15" s="297"/>
       <c r="H15" s="118"/>
-      <c r="J15" s="292" t="s">
+      <c r="J15" s="316" t="s">
         <v>354</v>
       </c>
-      <c r="K15" s="292"/>
+      <c r="K15" s="316"/>
       <c r="L15" s="127"/>
-      <c r="M15" s="289"/>
-      <c r="N15" s="289"/>
+      <c r="M15" s="313"/>
+      <c r="N15" s="313"/>
       <c r="O15" s="127"/>
       <c r="P15" s="127"/>
     </row>
     <row r="16" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="279"/>
+      <c r="B16" s="301"/>
       <c r="C16" s="147"/>
       <c r="D16" s="118"/>
-      <c r="E16" s="279"/>
-      <c r="F16" s="274" t="s">
+      <c r="E16" s="301"/>
+      <c r="F16" s="296" t="s">
         <v>370</v>
       </c>
-      <c r="G16" s="275"/>
+      <c r="G16" s="297"/>
       <c r="H16" s="118"/>
-      <c r="J16" s="292" t="s">
+      <c r="J16" s="316" t="s">
         <v>355</v>
       </c>
-      <c r="K16" s="292"/>
+      <c r="K16" s="316"/>
       <c r="L16" s="127"/>
-      <c r="M16" s="289"/>
-      <c r="N16" s="289"/>
+      <c r="M16" s="313"/>
+      <c r="N16" s="313"/>
       <c r="O16" s="127"/>
       <c r="P16" s="127"/>
     </row>
     <row r="17" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="277" t="s">
+      <c r="B17" s="299" t="s">
         <v>412</v>
       </c>
       <c r="C17" s="146" t="s">
         <v>347</v>
       </c>
       <c r="D17" s="118"/>
-      <c r="E17" s="277" t="s">
+      <c r="E17" s="299" t="s">
         <v>390</v>
       </c>
-      <c r="F17" s="274" t="s">
+      <c r="F17" s="296" t="s">
         <v>393</v>
       </c>
-      <c r="G17" s="275"/>
+      <c r="G17" s="297"/>
       <c r="H17" s="118"/>
-      <c r="J17" s="276" t="s">
+      <c r="J17" s="298" t="s">
         <v>432</v>
       </c>
-      <c r="K17" s="276"/>
-      <c r="L17" s="276"/>
-      <c r="M17" s="276"/>
-      <c r="N17" s="276"/>
-      <c r="O17" s="276"/>
-      <c r="P17" s="276"/>
+      <c r="K17" s="298"/>
+      <c r="L17" s="298"/>
+      <c r="M17" s="298"/>
+      <c r="N17" s="298"/>
+      <c r="O17" s="298"/>
+      <c r="P17" s="298"/>
     </row>
     <row r="18" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="278"/>
+      <c r="B18" s="300"/>
       <c r="C18" s="146" t="s">
         <v>349</v>
       </c>
       <c r="D18" s="118"/>
-      <c r="E18" s="278"/>
-      <c r="F18" s="274" t="s">
+      <c r="E18" s="300"/>
+      <c r="F18" s="296" t="s">
         <v>395</v>
       </c>
-      <c r="G18" s="275"/>
+      <c r="G18" s="297"/>
       <c r="H18" s="118"/>
-      <c r="J18" s="290" t="s">
+      <c r="J18" s="314" t="s">
         <v>323</v>
       </c>
-      <c r="K18" s="290"/>
+      <c r="K18" s="314"/>
       <c r="L18" s="99" t="s">
         <v>344</v>
       </c>
-      <c r="M18" s="291" t="s">
+      <c r="M18" s="315" t="s">
         <v>110</v>
       </c>
-      <c r="N18" s="291"/>
+      <c r="N18" s="315"/>
       <c r="O18" s="99" t="s">
         <v>359</v>
       </c>
@@ -25494,44 +25492,44 @@
       </c>
     </row>
     <row r="19" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="278"/>
+      <c r="B19" s="300"/>
       <c r="C19" s="146" t="s">
         <v>351</v>
       </c>
       <c r="D19" s="118"/>
-      <c r="E19" s="279"/>
-      <c r="F19" s="274" t="s">
+      <c r="E19" s="301"/>
+      <c r="F19" s="296" t="s">
         <v>394</v>
       </c>
-      <c r="G19" s="275"/>
+      <c r="G19" s="297"/>
       <c r="H19" s="118"/>
-      <c r="J19" s="292" t="s">
+      <c r="J19" s="316" t="s">
         <v>405</v>
       </c>
-      <c r="K19" s="292"/>
+      <c r="K19" s="316"/>
       <c r="L19" s="62"/>
-      <c r="M19" s="289"/>
-      <c r="N19" s="289"/>
+      <c r="M19" s="313"/>
+      <c r="N19" s="313"/>
       <c r="O19" s="62"/>
       <c r="P19" s="62"/>
     </row>
     <row r="20" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="276" t="s">
+      <c r="B20" s="298" t="s">
         <v>428</v>
       </c>
-      <c r="C20" s="276"/>
-      <c r="D20" s="276"/>
-      <c r="E20" s="276"/>
-      <c r="F20" s="276"/>
-      <c r="G20" s="276"/>
-      <c r="H20" s="276"/>
-      <c r="J20" s="292" t="s">
+      <c r="C20" s="298"/>
+      <c r="D20" s="298"/>
+      <c r="E20" s="298"/>
+      <c r="F20" s="298"/>
+      <c r="G20" s="298"/>
+      <c r="H20" s="298"/>
+      <c r="J20" s="316" t="s">
         <v>406</v>
       </c>
-      <c r="K20" s="292"/>
+      <c r="K20" s="316"/>
       <c r="L20" s="62"/>
-      <c r="M20" s="289"/>
-      <c r="N20" s="289"/>
+      <c r="M20" s="313"/>
+      <c r="N20" s="313"/>
       <c r="O20" s="62"/>
       <c r="P20" s="62"/>
       <c r="Q20" s="119"/>
@@ -25540,28 +25538,28 @@
       <c r="T20" s="119"/>
     </row>
     <row r="21" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="279" t="s">
+      <c r="B21" s="301" t="s">
         <v>429</v>
       </c>
       <c r="C21" s="41" t="s">
         <v>371</v>
       </c>
       <c r="D21" s="128"/>
-      <c r="E21" s="280" t="s">
+      <c r="E21" s="302" t="s">
         <v>426</v>
       </c>
-      <c r="F21" s="251" t="s">
+      <c r="F21" s="311" t="s">
         <v>371</v>
       </c>
-      <c r="G21" s="259"/>
+      <c r="G21" s="312"/>
       <c r="H21" s="118"/>
-      <c r="J21" s="292" t="s">
+      <c r="J21" s="316" t="s">
         <v>407</v>
       </c>
-      <c r="K21" s="292"/>
+      <c r="K21" s="316"/>
       <c r="L21" s="62"/>
-      <c r="M21" s="289"/>
-      <c r="N21" s="289"/>
+      <c r="M21" s="313"/>
+      <c r="N21" s="313"/>
       <c r="O21" s="62"/>
       <c r="P21" s="62"/>
       <c r="Q21" s="119"/>
@@ -25570,24 +25568,24 @@
       <c r="T21" s="119"/>
     </row>
     <row r="22" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="280"/>
+      <c r="B22" s="302"/>
       <c r="C22" s="41" t="s">
         <v>384</v>
       </c>
       <c r="D22" s="128"/>
-      <c r="E22" s="280"/>
-      <c r="F22" s="251" t="s">
+      <c r="E22" s="302"/>
+      <c r="F22" s="311" t="s">
         <v>384</v>
       </c>
-      <c r="G22" s="259"/>
+      <c r="G22" s="312"/>
       <c r="H22" s="118"/>
-      <c r="J22" s="292" t="s">
+      <c r="J22" s="316" t="s">
         <v>408</v>
       </c>
-      <c r="K22" s="292"/>
+      <c r="K22" s="316"/>
       <c r="L22" s="62"/>
-      <c r="M22" s="289"/>
-      <c r="N22" s="289"/>
+      <c r="M22" s="313"/>
+      <c r="N22" s="313"/>
       <c r="O22" s="62"/>
       <c r="P22" s="62"/>
       <c r="Q22" s="119"/>
@@ -25596,13 +25594,13 @@
       <c r="T22" s="119"/>
     </row>
     <row r="23" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J23" s="293" t="s">
+      <c r="J23" s="317" t="s">
         <v>363</v>
       </c>
-      <c r="K23" s="293"/>
+      <c r="K23" s="317"/>
       <c r="L23" s="62"/>
-      <c r="M23" s="294"/>
-      <c r="N23" s="295"/>
+      <c r="M23" s="318"/>
+      <c r="N23" s="319"/>
       <c r="O23" s="124"/>
       <c r="P23" s="124"/>
       <c r="Q23" s="119"/>
@@ -25669,42 +25667,42 @@
       <c r="M27"/>
       <c r="N27"/>
       <c r="O27"/>
-      <c r="U27" s="283" t="s">
+      <c r="U27" s="305" t="s">
         <v>64</v>
       </c>
-      <c r="V27" s="281" t="s">
+      <c r="V27" s="303" t="s">
         <v>344</v>
       </c>
-      <c r="W27" s="282" t="s">
+      <c r="W27" s="304" t="s">
         <v>372</v>
       </c>
-      <c r="X27" s="282"/>
-      <c r="Y27" s="282"/>
-      <c r="Z27" s="282"/>
-      <c r="AA27" s="282"/>
-      <c r="AB27" s="282"/>
-      <c r="AC27" s="282"/>
-      <c r="AD27" s="282"/>
-      <c r="AE27" s="282" t="s">
+      <c r="X27" s="304"/>
+      <c r="Y27" s="304"/>
+      <c r="Z27" s="304"/>
+      <c r="AA27" s="304"/>
+      <c r="AB27" s="304"/>
+      <c r="AC27" s="304"/>
+      <c r="AD27" s="304"/>
+      <c r="AE27" s="304" t="s">
         <v>373</v>
       </c>
-      <c r="AF27" s="282"/>
-      <c r="AG27" s="282"/>
-      <c r="AH27" s="282"/>
-      <c r="AI27" s="282"/>
-      <c r="AJ27" s="282"/>
-      <c r="AK27" s="282"/>
-      <c r="AL27" s="282"/>
-      <c r="AM27" s="281" t="s">
+      <c r="AF27" s="304"/>
+      <c r="AG27" s="304"/>
+      <c r="AH27" s="304"/>
+      <c r="AI27" s="304"/>
+      <c r="AJ27" s="304"/>
+      <c r="AK27" s="304"/>
+      <c r="AL27" s="304"/>
+      <c r="AM27" s="303" t="s">
         <v>345</v>
       </c>
-      <c r="AN27" s="281" t="s">
+      <c r="AN27" s="303" t="s">
         <v>374</v>
       </c>
-      <c r="AO27" s="281" t="s">
+      <c r="AO27" s="303" t="s">
         <v>346</v>
       </c>
-      <c r="AP27" s="281" t="s">
+      <c r="AP27" s="303" t="s">
         <v>375</v>
       </c>
     </row>
@@ -25715,8 +25713,8 @@
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28"/>
-      <c r="U28" s="283"/>
-      <c r="V28" s="281"/>
+      <c r="U28" s="305"/>
+      <c r="V28" s="303"/>
       <c r="W28" s="125" t="s">
         <v>143</v>
       </c>
@@ -25765,10 +25763,10 @@
       <c r="AL28" s="125" t="s">
         <v>382</v>
       </c>
-      <c r="AM28" s="281"/>
-      <c r="AN28" s="281"/>
-      <c r="AO28" s="281"/>
-      <c r="AP28" s="281"/>
+      <c r="AM28" s="303"/>
+      <c r="AN28" s="303"/>
+      <c r="AO28" s="303"/>
+      <c r="AP28" s="303"/>
     </row>
     <row r="29" spans="2:42" x14ac:dyDescent="0.25">
       <c r="J29"/>
@@ -26115,16 +26113,16 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="296" t="s">
+      <c r="F1" s="320" t="s">
         <v>329</v>
       </c>
-      <c r="G1" s="296"/>
-      <c r="H1" s="296"/>
+      <c r="G1" s="320"/>
+      <c r="H1" s="320"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="298" t="s">
+      <c r="J1" s="322" t="s">
         <v>339</v>
       </c>
-      <c r="K1" s="298"/>
+      <c r="K1" s="322"/>
     </row>
     <row r="2" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="114" t="s">
@@ -26133,12 +26131,12 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="296"/>
-      <c r="G2" s="296"/>
-      <c r="H2" s="296"/>
+      <c r="F2" s="320"/>
+      <c r="G2" s="320"/>
+      <c r="H2" s="320"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="298"/>
-      <c r="K2" s="298"/>
+      <c r="J2" s="322"/>
+      <c r="K2" s="322"/>
     </row>
     <row r="3" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="104"/>
@@ -26148,9 +26146,9 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="297"/>
-      <c r="G3" s="297"/>
-      <c r="H3" s="297"/>
+      <c r="F3" s="321"/>
+      <c r="G3" s="321"/>
+      <c r="H3" s="321"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="116" t="s">
@@ -26234,16 +26232,16 @@
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="296" t="s">
+      <c r="F56" s="320" t="s">
         <v>329</v>
       </c>
-      <c r="G56" s="296"/>
-      <c r="H56" s="296"/>
+      <c r="G56" s="320"/>
+      <c r="H56" s="320"/>
       <c r="I56" s="1"/>
-      <c r="J56" s="298" t="s">
+      <c r="J56" s="322" t="s">
         <v>339</v>
       </c>
-      <c r="K56" s="298"/>
+      <c r="K56" s="322"/>
     </row>
     <row r="57" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="114" t="s">
@@ -26252,12 +26250,12 @@
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="296"/>
-      <c r="G57" s="296"/>
-      <c r="H57" s="296"/>
+      <c r="F57" s="320"/>
+      <c r="G57" s="320"/>
+      <c r="H57" s="320"/>
       <c r="I57" s="1"/>
-      <c r="J57" s="298"/>
-      <c r="K57" s="298"/>
+      <c r="J57" s="322"/>
+      <c r="K57" s="322"/>
     </row>
     <row r="58" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="104"/>
@@ -26267,9 +26265,9 @@
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
-      <c r="F58" s="297"/>
-      <c r="G58" s="297"/>
-      <c r="H58" s="297"/>
+      <c r="F58" s="321"/>
+      <c r="G58" s="321"/>
+      <c r="H58" s="321"/>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
       <c r="K58" s="116" t="s">
@@ -26353,16 +26351,16 @@
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="296" t="s">
+      <c r="F111" s="320" t="s">
         <v>329</v>
       </c>
-      <c r="G111" s="296"/>
-      <c r="H111" s="296"/>
+      <c r="G111" s="320"/>
+      <c r="H111" s="320"/>
       <c r="I111" s="1"/>
-      <c r="J111" s="298" t="s">
+      <c r="J111" s="322" t="s">
         <v>339</v>
       </c>
-      <c r="K111" s="298"/>
+      <c r="K111" s="322"/>
     </row>
     <row r="112" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="114" t="s">
@@ -26371,12 +26369,12 @@
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
-      <c r="F112" s="296"/>
-      <c r="G112" s="296"/>
-      <c r="H112" s="296"/>
+      <c r="F112" s="320"/>
+      <c r="G112" s="320"/>
+      <c r="H112" s="320"/>
       <c r="I112" s="1"/>
-      <c r="J112" s="298"/>
-      <c r="K112" s="298"/>
+      <c r="J112" s="322"/>
+      <c r="K112" s="322"/>
     </row>
     <row r="113" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="104"/>
@@ -26386,9 +26384,9 @@
       <c r="C113" s="8"/>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
-      <c r="F113" s="297"/>
-      <c r="G113" s="297"/>
-      <c r="H113" s="297"/>
+      <c r="F113" s="321"/>
+      <c r="G113" s="321"/>
+      <c r="H113" s="321"/>
       <c r="I113" s="8"/>
       <c r="J113" s="8"/>
       <c r="K113" s="116" t="s">
@@ -26472,16 +26470,16 @@
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
-      <c r="F166" s="296" t="s">
+      <c r="F166" s="320" t="s">
         <v>329</v>
       </c>
-      <c r="G166" s="296"/>
-      <c r="H166" s="296"/>
+      <c r="G166" s="320"/>
+      <c r="H166" s="320"/>
       <c r="I166" s="1"/>
-      <c r="J166" s="298" t="s">
+      <c r="J166" s="322" t="s">
         <v>339</v>
       </c>
-      <c r="K166" s="298"/>
+      <c r="K166" s="322"/>
     </row>
     <row r="167" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B167" s="114" t="s">
@@ -26490,12 +26488,12 @@
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
-      <c r="F167" s="296"/>
-      <c r="G167" s="296"/>
-      <c r="H167" s="296"/>
+      <c r="F167" s="320"/>
+      <c r="G167" s="320"/>
+      <c r="H167" s="320"/>
       <c r="I167" s="1"/>
-      <c r="J167" s="298"/>
-      <c r="K167" s="298"/>
+      <c r="J167" s="322"/>
+      <c r="K167" s="322"/>
     </row>
     <row r="168" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="104"/>
@@ -26505,9 +26503,9 @@
       <c r="C168" s="8"/>
       <c r="D168" s="8"/>
       <c r="E168" s="8"/>
-      <c r="F168" s="297"/>
-      <c r="G168" s="297"/>
-      <c r="H168" s="297"/>
+      <c r="F168" s="321"/>
+      <c r="G168" s="321"/>
+      <c r="H168" s="321"/>
       <c r="I168" s="8"/>
       <c r="J168" s="8"/>
       <c r="K168" s="116" t="s">
@@ -26661,32 +26659,32 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="304" t="s">
+      <c r="A3" s="328" t="s">
         <v>544</v>
       </c>
-      <c r="B3" s="305"/>
-      <c r="C3" s="306"/>
-      <c r="H3" s="283" t="s">
+      <c r="B3" s="329"/>
+      <c r="C3" s="330"/>
+      <c r="H3" s="305" t="s">
         <v>256</v>
       </c>
-      <c r="I3" s="283" t="s">
+      <c r="I3" s="305" t="s">
         <v>323</v>
       </c>
-      <c r="J3" s="283" t="s">
+      <c r="J3" s="305" t="s">
         <v>459</v>
       </c>
-      <c r="K3" s="283" t="s">
+      <c r="K3" s="305" t="s">
         <v>471</v>
       </c>
-      <c r="L3" s="283" t="s">
+      <c r="L3" s="305" t="s">
         <v>478</v>
       </c>
-      <c r="M3" s="283"/>
-      <c r="N3" s="302" t="s">
+      <c r="M3" s="305"/>
+      <c r="N3" s="326" t="s">
         <v>477</v>
       </c>
-      <c r="O3" s="303"/>
-      <c r="P3" s="282" t="s">
+      <c r="O3" s="327"/>
+      <c r="P3" s="304" t="s">
         <v>498</v>
       </c>
     </row>
@@ -26694,12 +26692,12 @@
       <c r="A4" s="132" t="s">
         <v>545</v>
       </c>
-      <c r="B4" s="272"/>
-      <c r="C4" s="272"/>
-      <c r="H4" s="283"/>
-      <c r="I4" s="283"/>
-      <c r="J4" s="283"/>
-      <c r="K4" s="283"/>
+      <c r="B4" s="294"/>
+      <c r="C4" s="294"/>
+      <c r="H4" s="305"/>
+      <c r="I4" s="305"/>
+      <c r="J4" s="305"/>
+      <c r="K4" s="305"/>
       <c r="L4" s="100" t="s">
         <v>61</v>
       </c>
@@ -26712,14 +26710,14 @@
       <c r="O4" s="100" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="299"/>
+      <c r="P4" s="323"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="132" t="s">
         <v>548</v>
       </c>
-      <c r="B5" s="300"/>
-      <c r="C5" s="301"/>
+      <c r="B5" s="324"/>
+      <c r="C5" s="325"/>
       <c r="H5" s="132" t="s">
         <v>465</v>
       </c>
@@ -26748,8 +26746,8 @@
       <c r="A6" s="132" t="s">
         <v>546</v>
       </c>
-      <c r="B6" s="300"/>
-      <c r="C6" s="301"/>
+      <c r="B6" s="324"/>
+      <c r="C6" s="325"/>
       <c r="H6" s="132" t="s">
         <v>464</v>
       </c>
@@ -26778,8 +26776,8 @@
       <c r="A7" s="132" t="s">
         <v>549</v>
       </c>
-      <c r="B7" s="300"/>
-      <c r="C7" s="301"/>
+      <c r="B7" s="324"/>
+      <c r="C7" s="325"/>
       <c r="H7" s="132" t="s">
         <v>463</v>
       </c>
@@ -26808,8 +26806,8 @@
       <c r="A8" s="132" t="s">
         <v>550</v>
       </c>
-      <c r="B8" s="300"/>
-      <c r="C8" s="301"/>
+      <c r="B8" s="324"/>
+      <c r="C8" s="325"/>
       <c r="H8" s="132" t="s">
         <v>494</v>
       </c>
@@ -26838,8 +26836,8 @@
       <c r="A9" s="132" t="s">
         <v>551</v>
       </c>
-      <c r="B9" s="300"/>
-      <c r="C9" s="301"/>
+      <c r="B9" s="324"/>
+      <c r="C9" s="325"/>
       <c r="H9" s="132" t="s">
         <v>495</v>
       </c>
@@ -26852,10 +26850,10 @@
       <c r="K9" s="133" t="s">
         <v>251</v>
       </c>
-      <c r="L9" s="300" t="s">
+      <c r="L9" s="324" t="s">
         <v>469</v>
       </c>
-      <c r="M9" s="301"/>
+      <c r="M9" s="325"/>
       <c r="N9" s="95"/>
       <c r="O9" s="95"/>
       <c r="P9" s="99" t="s">
@@ -26949,10 +26947,10 @@
       <c r="K12" s="134" t="s">
         <v>251</v>
       </c>
-      <c r="L12" s="300" t="s">
+      <c r="L12" s="324" t="s">
         <v>470</v>
       </c>
-      <c r="M12" s="301"/>
+      <c r="M12" s="325"/>
       <c r="N12" s="95"/>
       <c r="O12" s="95"/>
       <c r="P12" s="99" t="s">
@@ -27992,39 +27990,39 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="312" t="s">
+      <c r="B2" s="241" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="313"/>
-      <c r="D2" s="313"/>
-      <c r="E2" s="313"/>
-      <c r="F2" s="313"/>
-      <c r="G2" s="313"/>
-      <c r="H2" s="313"/>
-      <c r="I2" s="313"/>
-      <c r="J2" s="313"/>
-      <c r="K2" s="313"/>
-      <c r="L2" s="313"/>
-      <c r="M2" s="314"/>
-      <c r="N2" s="315" t="s">
+      <c r="C2" s="242"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="242"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="M2" s="243"/>
+      <c r="N2" s="336" t="s">
         <v>552</v>
       </c>
-      <c r="O2" s="316"/>
-      <c r="Q2" s="321" t="s">
+      <c r="O2" s="337"/>
+      <c r="Q2" s="342" t="s">
         <v>583</v>
       </c>
-      <c r="R2" s="322"/>
-      <c r="S2" s="322"/>
-      <c r="T2" s="322"/>
-      <c r="U2" s="322"/>
-      <c r="V2" s="322"/>
-      <c r="W2" s="322"/>
-      <c r="X2" s="322"/>
-      <c r="Y2" s="322"/>
-      <c r="Z2" s="322"/>
-      <c r="AA2" s="322"/>
-      <c r="AB2" s="322"/>
-      <c r="AC2" s="323"/>
+      <c r="R2" s="343"/>
+      <c r="S2" s="343"/>
+      <c r="T2" s="343"/>
+      <c r="U2" s="343"/>
+      <c r="V2" s="343"/>
+      <c r="W2" s="343"/>
+      <c r="X2" s="343"/>
+      <c r="Y2" s="343"/>
+      <c r="Z2" s="343"/>
+      <c r="AA2" s="343"/>
+      <c r="AB2" s="343"/>
+      <c r="AC2" s="344"/>
     </row>
     <row r="3" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5"/>
@@ -28039,10 +28037,10 @@
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="7"/>
-      <c r="N3" s="307" t="s">
+      <c r="N3" s="331" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="309"/>
+      <c r="O3" s="333"/>
       <c r="Q3" s="200" t="s">
         <v>569</v>
       </c>
@@ -28074,8 +28072,8 @@
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="7"/>
-      <c r="N4" s="310"/>
-      <c r="O4" s="311"/>
+      <c r="N4" s="334"/>
+      <c r="O4" s="335"/>
       <c r="Q4" s="194"/>
       <c r="R4" s="195"/>
       <c r="S4" s="192"/>
@@ -28110,19 +28108,19 @@
       <c r="Q5" s="191" t="s">
         <v>579</v>
       </c>
-      <c r="R5" s="326" t="s">
+      <c r="R5" s="347" t="s">
         <v>584</v>
       </c>
-      <c r="S5" s="327"/>
-      <c r="T5" s="327"/>
-      <c r="U5" s="327"/>
-      <c r="V5" s="327"/>
-      <c r="W5" s="327"/>
-      <c r="X5" s="327"/>
-      <c r="Y5" s="327"/>
-      <c r="Z5" s="327"/>
-      <c r="AA5" s="327"/>
-      <c r="AB5" s="328"/>
+      <c r="S5" s="348"/>
+      <c r="T5" s="348"/>
+      <c r="U5" s="348"/>
+      <c r="V5" s="348"/>
+      <c r="W5" s="348"/>
+      <c r="X5" s="348"/>
+      <c r="Y5" s="348"/>
+      <c r="Z5" s="348"/>
+      <c r="AA5" s="348"/>
+      <c r="AB5" s="349"/>
       <c r="AC5" s="193"/>
     </row>
     <row r="6" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28145,17 +28143,17 @@
       <c r="Q6" s="191" t="s">
         <v>580</v>
       </c>
-      <c r="R6" s="329"/>
-      <c r="S6" s="330"/>
-      <c r="T6" s="330"/>
-      <c r="U6" s="330"/>
-      <c r="V6" s="330"/>
-      <c r="W6" s="330"/>
-      <c r="X6" s="330"/>
-      <c r="Y6" s="330"/>
-      <c r="Z6" s="330"/>
-      <c r="AA6" s="330"/>
-      <c r="AB6" s="331"/>
+      <c r="R6" s="350"/>
+      <c r="S6" s="351"/>
+      <c r="T6" s="351"/>
+      <c r="U6" s="351"/>
+      <c r="V6" s="351"/>
+      <c r="W6" s="351"/>
+      <c r="X6" s="351"/>
+      <c r="Y6" s="351"/>
+      <c r="Z6" s="351"/>
+      <c r="AA6" s="351"/>
+      <c r="AB6" s="352"/>
       <c r="AC6" s="193"/>
     </row>
     <row r="7" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28176,17 +28174,17 @@
       <c r="Q7" s="191" t="s">
         <v>581</v>
       </c>
-      <c r="R7" s="329"/>
-      <c r="S7" s="330"/>
-      <c r="T7" s="330"/>
-      <c r="U7" s="330"/>
-      <c r="V7" s="330"/>
-      <c r="W7" s="330"/>
-      <c r="X7" s="330"/>
-      <c r="Y7" s="330"/>
-      <c r="Z7" s="330"/>
-      <c r="AA7" s="330"/>
-      <c r="AB7" s="331"/>
+      <c r="R7" s="350"/>
+      <c r="S7" s="351"/>
+      <c r="T7" s="351"/>
+      <c r="U7" s="351"/>
+      <c r="V7" s="351"/>
+      <c r="W7" s="351"/>
+      <c r="X7" s="351"/>
+      <c r="Y7" s="351"/>
+      <c r="Z7" s="351"/>
+      <c r="AA7" s="351"/>
+      <c r="AB7" s="352"/>
       <c r="AC7" s="193"/>
     </row>
     <row r="8" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28207,17 +28205,17 @@
       <c r="Q8" s="191" t="s">
         <v>582</v>
       </c>
-      <c r="R8" s="329"/>
-      <c r="S8" s="330"/>
-      <c r="T8" s="330"/>
-      <c r="U8" s="330"/>
-      <c r="V8" s="330"/>
-      <c r="W8" s="330"/>
-      <c r="X8" s="330"/>
-      <c r="Y8" s="330"/>
-      <c r="Z8" s="330"/>
-      <c r="AA8" s="330"/>
-      <c r="AB8" s="331"/>
+      <c r="R8" s="350"/>
+      <c r="S8" s="351"/>
+      <c r="T8" s="351"/>
+      <c r="U8" s="351"/>
+      <c r="V8" s="351"/>
+      <c r="W8" s="351"/>
+      <c r="X8" s="351"/>
+      <c r="Y8" s="351"/>
+      <c r="Z8" s="351"/>
+      <c r="AA8" s="351"/>
+      <c r="AB8" s="352"/>
       <c r="AC8" s="193"/>
     </row>
     <row r="9" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28253,23 +28251,23 @@
       <c r="B12" s="182" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="312" t="s">
+      <c r="C12" s="241" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="313"/>
-      <c r="E12" s="313"/>
-      <c r="F12" s="313"/>
-      <c r="G12" s="313"/>
-      <c r="H12" s="313"/>
-      <c r="I12" s="313"/>
-      <c r="J12" s="313"/>
-      <c r="K12" s="313"/>
-      <c r="L12" s="313"/>
-      <c r="M12" s="314"/>
-      <c r="N12" s="317" t="s">
+      <c r="D12" s="242"/>
+      <c r="E12" s="242"/>
+      <c r="F12" s="242"/>
+      <c r="G12" s="242"/>
+      <c r="H12" s="242"/>
+      <c r="I12" s="242"/>
+      <c r="J12" s="242"/>
+      <c r="K12" s="242"/>
+      <c r="L12" s="242"/>
+      <c r="M12" s="243"/>
+      <c r="N12" s="338" t="s">
         <v>103</v>
       </c>
-      <c r="O12" s="318"/>
+      <c r="O12" s="339"/>
       <c r="Q12" s="204" t="s">
         <v>631</v>
       </c>
@@ -28299,10 +28297,10 @@
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
-      <c r="N13" s="319" t="s">
+      <c r="N13" s="340" t="s">
         <v>21</v>
       </c>
-      <c r="O13" s="320"/>
+      <c r="O13" s="341"/>
       <c r="Q13" s="200" t="s">
         <v>568</v>
       </c>
@@ -28417,19 +28415,19 @@
       <c r="Q16" s="191" t="s">
         <v>579</v>
       </c>
-      <c r="R16" s="325" t="s">
+      <c r="R16" s="346" t="s">
         <v>578</v>
       </c>
-      <c r="S16" s="325"/>
-      <c r="T16" s="325"/>
-      <c r="U16" s="325"/>
-      <c r="V16" s="325"/>
-      <c r="W16" s="325"/>
-      <c r="X16" s="325"/>
-      <c r="Y16" s="325"/>
-      <c r="Z16" s="325"/>
-      <c r="AA16" s="325"/>
-      <c r="AB16" s="325"/>
+      <c r="S16" s="346"/>
+      <c r="T16" s="346"/>
+      <c r="U16" s="346"/>
+      <c r="V16" s="346"/>
+      <c r="W16" s="346"/>
+      <c r="X16" s="346"/>
+      <c r="Y16" s="346"/>
+      <c r="Z16" s="346"/>
+      <c r="AA16" s="346"/>
+      <c r="AB16" s="346"/>
       <c r="AC16" s="193"/>
     </row>
     <row r="17" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28445,24 +28443,24 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
-      <c r="N17" s="307" t="s">
+      <c r="N17" s="331" t="s">
         <v>21</v>
       </c>
-      <c r="O17" s="308"/>
+      <c r="O17" s="332"/>
       <c r="Q17" s="191" t="s">
         <v>580</v>
       </c>
-      <c r="R17" s="324"/>
-      <c r="S17" s="324"/>
-      <c r="T17" s="324"/>
-      <c r="U17" s="324"/>
-      <c r="V17" s="324"/>
-      <c r="W17" s="324"/>
-      <c r="X17" s="324"/>
-      <c r="Y17" s="324"/>
-      <c r="Z17" s="324"/>
-      <c r="AA17" s="324"/>
-      <c r="AB17" s="324"/>
+      <c r="R17" s="345"/>
+      <c r="S17" s="345"/>
+      <c r="T17" s="345"/>
+      <c r="U17" s="345"/>
+      <c r="V17" s="345"/>
+      <c r="W17" s="345"/>
+      <c r="X17" s="345"/>
+      <c r="Y17" s="345"/>
+      <c r="Z17" s="345"/>
+      <c r="AA17" s="345"/>
+      <c r="AB17" s="345"/>
       <c r="AC17" s="193"/>
     </row>
     <row r="18" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28487,17 +28485,17 @@
       <c r="Q18" s="191" t="s">
         <v>581</v>
       </c>
-      <c r="R18" s="324"/>
-      <c r="S18" s="324"/>
-      <c r="T18" s="324"/>
-      <c r="U18" s="324"/>
-      <c r="V18" s="324"/>
-      <c r="W18" s="324"/>
-      <c r="X18" s="324"/>
-      <c r="Y18" s="324"/>
-      <c r="Z18" s="324"/>
-      <c r="AA18" s="324"/>
-      <c r="AB18" s="324"/>
+      <c r="R18" s="345"/>
+      <c r="S18" s="345"/>
+      <c r="T18" s="345"/>
+      <c r="U18" s="345"/>
+      <c r="V18" s="345"/>
+      <c r="W18" s="345"/>
+      <c r="X18" s="345"/>
+      <c r="Y18" s="345"/>
+      <c r="Z18" s="345"/>
+      <c r="AA18" s="345"/>
+      <c r="AB18" s="345"/>
       <c r="AC18" s="193"/>
     </row>
     <row r="19" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28522,17 +28520,17 @@
       <c r="Q19" s="191" t="s">
         <v>582</v>
       </c>
-      <c r="R19" s="324"/>
-      <c r="S19" s="324"/>
-      <c r="T19" s="324"/>
-      <c r="U19" s="324"/>
-      <c r="V19" s="324"/>
-      <c r="W19" s="324"/>
-      <c r="X19" s="324"/>
-      <c r="Y19" s="324"/>
-      <c r="Z19" s="324"/>
-      <c r="AA19" s="324"/>
-      <c r="AB19" s="324"/>
+      <c r="R19" s="345"/>
+      <c r="S19" s="345"/>
+      <c r="T19" s="345"/>
+      <c r="U19" s="345"/>
+      <c r="V19" s="345"/>
+      <c r="W19" s="345"/>
+      <c r="X19" s="345"/>
+      <c r="Y19" s="345"/>
+      <c r="Z19" s="345"/>
+      <c r="AA19" s="345"/>
+      <c r="AB19" s="345"/>
       <c r="AC19" s="193"/>
     </row>
     <row r="20" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28579,10 +28577,10 @@
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
-      <c r="N21" s="307" t="s">
+      <c r="N21" s="331" t="s">
         <v>21</v>
       </c>
-      <c r="O21" s="308"/>
+      <c r="O21" s="332"/>
     </row>
     <row r="22" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="188" t="s">
@@ -28655,10 +28653,10 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
-      <c r="N25" s="307" t="s">
+      <c r="N25" s="331" t="s">
         <v>21</v>
       </c>
-      <c r="O25" s="308"/>
+      <c r="O25" s="332"/>
     </row>
     <row r="26" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="188" t="s">
@@ -28731,10 +28729,10 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
-      <c r="N29" s="307" t="s">
+      <c r="N29" s="331" t="s">
         <v>21</v>
       </c>
-      <c r="O29" s="308"/>
+      <c r="O29" s="332"/>
     </row>
     <row r="30" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="188" t="s">
@@ -28807,10 +28805,10 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
-      <c r="N33" s="307" t="s">
+      <c r="N33" s="331" t="s">
         <v>21</v>
       </c>
-      <c r="O33" s="308"/>
+      <c r="O33" s="332"/>
     </row>
     <row r="34" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="188" t="s">
@@ -29456,15 +29454,15 @@
       <c r="V2" s="190"/>
     </row>
     <row r="3" spans="2:23" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G3" s="312" t="s">
+      <c r="G3" s="241" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="313"/>
-      <c r="I3" s="313"/>
-      <c r="J3" s="313"/>
-      <c r="K3" s="313"/>
-      <c r="L3" s="313"/>
-      <c r="M3" s="314"/>
+      <c r="H3" s="242"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="M3" s="243"/>
       <c r="N3" s="213"/>
       <c r="O3" s="213"/>
       <c r="P3" s="213"/>
@@ -29504,39 +29502,39 @@
       <c r="O4" s="214"/>
       <c r="P4" s="214"/>
       <c r="Q4" s="194"/>
-      <c r="R4" s="333" t="s">
+      <c r="R4" s="244" t="s">
         <v>618</v>
       </c>
-      <c r="S4" s="243" t="s">
+      <c r="S4" s="247" t="s">
         <v>617</v>
       </c>
-      <c r="T4" s="332" t="s">
+      <c r="T4" s="248" t="s">
         <v>619</v>
       </c>
-      <c r="U4" s="332" t="s">
+      <c r="U4" s="248" t="s">
         <v>10</v>
       </c>
       <c r="V4" s="193"/>
       <c r="W4" s="39"/>
     </row>
     <row r="5" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G5" s="255" t="s">
+      <c r="G5" s="249" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="256"/>
-      <c r="I5" s="256"/>
-      <c r="J5" s="256"/>
-      <c r="K5" s="256"/>
-      <c r="L5" s="256"/>
-      <c r="M5" s="257"/>
+      <c r="H5" s="250"/>
+      <c r="I5" s="250"/>
+      <c r="J5" s="250"/>
+      <c r="K5" s="250"/>
+      <c r="L5" s="250"/>
+      <c r="M5" s="251"/>
       <c r="N5" s="91"/>
       <c r="O5" s="91"/>
       <c r="P5" s="91"/>
       <c r="Q5" s="194"/>
-      <c r="R5" s="334"/>
-      <c r="S5" s="243"/>
-      <c r="T5" s="332"/>
-      <c r="U5" s="332"/>
+      <c r="R5" s="245"/>
+      <c r="S5" s="247"/>
+      <c r="T5" s="248"/>
+      <c r="U5" s="248"/>
       <c r="V5" s="193"/>
       <c r="W5" s="39"/>
     </row>
@@ -29562,7 +29560,7 @@
       <c r="O6" s="91"/>
       <c r="P6" s="91"/>
       <c r="Q6" s="194"/>
-      <c r="R6" s="335"/>
+      <c r="R6" s="246"/>
       <c r="S6" s="234" t="s">
         <v>620</v>
       </c>
@@ -29609,15 +29607,15 @@
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="193"/>
-      <c r="G8" s="336" t="s">
+      <c r="G8" s="255" t="s">
         <v>0</v>
       </c>
-      <c r="H8" s="337"/>
-      <c r="I8" s="337"/>
-      <c r="J8" s="337"/>
-      <c r="K8" s="337"/>
-      <c r="L8" s="337"/>
-      <c r="M8" s="338"/>
+      <c r="H8" s="256"/>
+      <c r="I8" s="256"/>
+      <c r="J8" s="256"/>
+      <c r="K8" s="256"/>
+      <c r="L8" s="256"/>
+      <c r="M8" s="257"/>
       <c r="N8" s="91"/>
       <c r="O8" s="91"/>
       <c r="P8" s="91"/>
@@ -29700,15 +29698,15 @@
       </c>
       <c r="D11" s="38"/>
       <c r="E11" s="193"/>
-      <c r="G11" s="336" t="s">
+      <c r="G11" s="255" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="337"/>
-      <c r="I11" s="337"/>
-      <c r="J11" s="337"/>
-      <c r="K11" s="337"/>
-      <c r="L11" s="337"/>
-      <c r="M11" s="338"/>
+      <c r="H11" s="256"/>
+      <c r="I11" s="256"/>
+      <c r="J11" s="256"/>
+      <c r="K11" s="256"/>
+      <c r="L11" s="256"/>
+      <c r="M11" s="257"/>
       <c r="N11" s="91"/>
       <c r="O11" s="91"/>
       <c r="P11" s="91"/>
@@ -29791,15 +29789,15 @@
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="193"/>
-      <c r="G14" s="336" t="s">
+      <c r="G14" s="255" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="337"/>
-      <c r="I14" s="337"/>
-      <c r="J14" s="337"/>
-      <c r="K14" s="337"/>
-      <c r="L14" s="337"/>
-      <c r="M14" s="338"/>
+      <c r="H14" s="256"/>
+      <c r="I14" s="256"/>
+      <c r="J14" s="256"/>
+      <c r="K14" s="256"/>
+      <c r="L14" s="256"/>
+      <c r="M14" s="257"/>
       <c r="N14" s="91"/>
       <c r="O14" s="91"/>
       <c r="P14" s="91"/>
@@ -29944,15 +29942,15 @@
       </c>
       <c r="D19" s="38"/>
       <c r="E19" s="193"/>
-      <c r="G19" s="336" t="s">
+      <c r="G19" s="255" t="s">
         <v>114</v>
       </c>
-      <c r="H19" s="337"/>
-      <c r="I19" s="337"/>
-      <c r="J19" s="337"/>
-      <c r="K19" s="337"/>
-      <c r="L19" s="337"/>
-      <c r="M19" s="338"/>
+      <c r="H19" s="256"/>
+      <c r="I19" s="256"/>
+      <c r="J19" s="256"/>
+      <c r="K19" s="256"/>
+      <c r="L19" s="256"/>
+      <c r="M19" s="257"/>
       <c r="N19" s="91"/>
       <c r="O19" s="91"/>
       <c r="P19" s="91"/>
@@ -30059,27 +30057,27 @@
       <c r="T23" s="192"/>
       <c r="U23" s="192"/>
       <c r="V23" s="193"/>
-      <c r="X23" s="244" t="s">
+      <c r="X23" s="258" t="s">
         <v>227</v>
       </c>
-      <c r="Y23" s="244"/>
-      <c r="Z23" s="244"/>
-      <c r="AA23" s="244"/>
-      <c r="AB23" s="244"/>
-      <c r="AC23" s="244"/>
-      <c r="AD23" s="244"/>
-      <c r="AE23" s="244"/>
-      <c r="AF23" s="244"/>
-      <c r="AG23" s="244"/>
-      <c r="AH23" s="244"/>
-      <c r="AI23" s="244"/>
-      <c r="AJ23" s="244"/>
-      <c r="AK23" s="244"/>
-      <c r="AL23" s="244"/>
-      <c r="AM23" s="244"/>
-      <c r="AN23" s="244"/>
-      <c r="AO23" s="244"/>
-      <c r="AP23" s="244"/>
+      <c r="Y23" s="258"/>
+      <c r="Z23" s="258"/>
+      <c r="AA23" s="258"/>
+      <c r="AB23" s="258"/>
+      <c r="AC23" s="258"/>
+      <c r="AD23" s="258"/>
+      <c r="AE23" s="258"/>
+      <c r="AF23" s="258"/>
+      <c r="AG23" s="258"/>
+      <c r="AH23" s="258"/>
+      <c r="AI23" s="258"/>
+      <c r="AJ23" s="258"/>
+      <c r="AK23" s="258"/>
+      <c r="AL23" s="258"/>
+      <c r="AM23" s="258"/>
+      <c r="AN23" s="258"/>
+      <c r="AO23" s="258"/>
+      <c r="AP23" s="258"/>
     </row>
     <row r="24" spans="2:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q24" s="196"/>
@@ -30091,36 +30089,36 @@
       <c r="X24" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Y24" s="339" t="s">
+      <c r="Y24" s="259" t="s">
         <v>18</v>
       </c>
-      <c r="Z24" s="340"/>
-      <c r="AA24" s="341"/>
-      <c r="AB24" s="339" t="s">
+      <c r="Z24" s="260"/>
+      <c r="AA24" s="261"/>
+      <c r="AB24" s="259" t="s">
         <v>17</v>
       </c>
-      <c r="AC24" s="340"/>
-      <c r="AD24" s="341"/>
-      <c r="AE24" s="339" t="s">
+      <c r="AC24" s="260"/>
+      <c r="AD24" s="261"/>
+      <c r="AE24" s="259" t="s">
         <v>16</v>
       </c>
-      <c r="AF24" s="340"/>
-      <c r="AG24" s="341"/>
-      <c r="AH24" s="339" t="s">
+      <c r="AF24" s="260"/>
+      <c r="AG24" s="261"/>
+      <c r="AH24" s="259" t="s">
         <v>13</v>
       </c>
-      <c r="AI24" s="340"/>
-      <c r="AJ24" s="341"/>
-      <c r="AK24" s="339" t="s">
+      <c r="AI24" s="260"/>
+      <c r="AJ24" s="261"/>
+      <c r="AK24" s="259" t="s">
         <v>20</v>
       </c>
-      <c r="AL24" s="340"/>
-      <c r="AM24" s="341"/>
-      <c r="AN24" s="339" t="s">
+      <c r="AL24" s="260"/>
+      <c r="AM24" s="261"/>
+      <c r="AN24" s="259" t="s">
         <v>553</v>
       </c>
-      <c r="AO24" s="340"/>
-      <c r="AP24" s="341"/>
+      <c r="AO24" s="260"/>
+      <c r="AP24" s="261"/>
     </row>
     <row r="25" spans="2:42" ht="81.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="X25" s="64" t="s">
@@ -30183,35 +30181,35 @@
     </row>
     <row r="26" spans="2:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="X26" s="212" t="s">
-        <v>229</v>
+        <v>711</v>
       </c>
       <c r="Y26" s="63" t="s">
-        <v>230</v>
+        <v>712</v>
       </c>
       <c r="Z26" s="62"/>
       <c r="AA26" s="62"/>
       <c r="AB26" s="63" t="s">
-        <v>228</v>
+        <v>712</v>
       </c>
       <c r="AC26" s="62"/>
       <c r="AD26" s="62"/>
       <c r="AE26" s="63" t="s">
-        <v>228</v>
+        <v>712</v>
       </c>
       <c r="AF26" s="62"/>
       <c r="AG26" s="62"/>
       <c r="AH26" s="63" t="s">
-        <v>228</v>
+        <v>712</v>
       </c>
       <c r="AI26" s="62"/>
       <c r="AJ26" s="62"/>
       <c r="AK26" s="63" t="s">
-        <v>228</v>
+        <v>712</v>
       </c>
       <c r="AL26" s="62"/>
       <c r="AM26" s="62"/>
       <c r="AN26" s="63" t="s">
-        <v>228</v>
+        <v>712</v>
       </c>
       <c r="AO26" s="62"/>
       <c r="AP26" s="62"/>
@@ -30634,48 +30632,48 @@
       <c r="P43" s="39"/>
     </row>
     <row r="44" spans="7:49" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X44" s="342" t="s">
+      <c r="X44" s="252" t="s">
         <v>238</v>
       </c>
-      <c r="Y44" s="343"/>
-      <c r="Z44" s="342" t="s">
+      <c r="Y44" s="254"/>
+      <c r="Z44" s="252" t="s">
         <v>237</v>
       </c>
-      <c r="AA44" s="344"/>
-      <c r="AB44" s="344"/>
-      <c r="AC44" s="344"/>
-      <c r="AD44" s="344"/>
-      <c r="AE44" s="343"/>
-      <c r="AF44" s="342" t="s">
+      <c r="AA44" s="253"/>
+      <c r="AB44" s="253"/>
+      <c r="AC44" s="253"/>
+      <c r="AD44" s="253"/>
+      <c r="AE44" s="254"/>
+      <c r="AF44" s="252" t="s">
         <v>239</v>
       </c>
-      <c r="AG44" s="344"/>
-      <c r="AH44" s="344"/>
-      <c r="AI44" s="344"/>
-      <c r="AJ44" s="344"/>
-      <c r="AK44" s="343"/>
-      <c r="AL44" s="342" t="s">
+      <c r="AG44" s="253"/>
+      <c r="AH44" s="253"/>
+      <c r="AI44" s="253"/>
+      <c r="AJ44" s="253"/>
+      <c r="AK44" s="254"/>
+      <c r="AL44" s="252" t="s">
         <v>240</v>
       </c>
-      <c r="AM44" s="344"/>
-      <c r="AN44" s="344"/>
-      <c r="AO44" s="344"/>
-      <c r="AP44" s="344"/>
-      <c r="AQ44" s="343"/>
-      <c r="AR44" s="342" t="s">
+      <c r="AM44" s="253"/>
+      <c r="AN44" s="253"/>
+      <c r="AO44" s="253"/>
+      <c r="AP44" s="253"/>
+      <c r="AQ44" s="254"/>
+      <c r="AR44" s="252" t="s">
         <v>241</v>
       </c>
-      <c r="AS44" s="344"/>
-      <c r="AT44" s="344"/>
-      <c r="AU44" s="344"/>
-      <c r="AV44" s="344"/>
-      <c r="AW44" s="343"/>
+      <c r="AS44" s="253"/>
+      <c r="AT44" s="253"/>
+      <c r="AU44" s="253"/>
+      <c r="AV44" s="253"/>
+      <c r="AW44" s="254"/>
     </row>
     <row r="45" spans="7:49" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X45" s="345" t="s">
+      <c r="X45" s="262" t="s">
         <v>40</v>
       </c>
-      <c r="Y45" s="346"/>
+      <c r="Y45" s="263"/>
       <c r="Z45" s="184" t="s">
         <v>117</v>
       </c>
@@ -30760,10 +30758,10 @@
       <c r="T46" s="215"/>
       <c r="U46" s="189"/>
       <c r="V46" s="190"/>
-      <c r="X46" s="347" t="s">
+      <c r="X46" s="264" t="s">
         <v>31</v>
       </c>
-      <c r="Y46" s="348"/>
+      <c r="Y46" s="265"/>
       <c r="Z46" s="66"/>
       <c r="AA46" s="22"/>
       <c r="AB46" s="22"/>
@@ -30800,47 +30798,47 @@
       <c r="T47" s="216"/>
       <c r="U47" s="211"/>
       <c r="V47" s="208"/>
-      <c r="X47" s="349"/>
-      <c r="Y47" s="350"/>
-      <c r="Z47" s="351" t="s">
+      <c r="X47" s="266"/>
+      <c r="Y47" s="267"/>
+      <c r="Z47" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="AA47" s="337"/>
-      <c r="AB47" s="337"/>
-      <c r="AC47" s="337"/>
-      <c r="AD47" s="337"/>
-      <c r="AE47" s="352"/>
-      <c r="AF47" s="351" t="s">
+      <c r="AA47" s="256"/>
+      <c r="AB47" s="256"/>
+      <c r="AC47" s="256"/>
+      <c r="AD47" s="256"/>
+      <c r="AE47" s="269"/>
+      <c r="AF47" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="AG47" s="337"/>
-      <c r="AH47" s="337"/>
-      <c r="AI47" s="337"/>
-      <c r="AJ47" s="337"/>
-      <c r="AK47" s="352"/>
-      <c r="AL47" s="351" t="s">
+      <c r="AG47" s="256"/>
+      <c r="AH47" s="256"/>
+      <c r="AI47" s="256"/>
+      <c r="AJ47" s="256"/>
+      <c r="AK47" s="269"/>
+      <c r="AL47" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="AM47" s="337"/>
-      <c r="AN47" s="337"/>
-      <c r="AO47" s="337"/>
-      <c r="AP47" s="337"/>
-      <c r="AQ47" s="352"/>
-      <c r="AR47" s="351" t="s">
+      <c r="AM47" s="256"/>
+      <c r="AN47" s="256"/>
+      <c r="AO47" s="256"/>
+      <c r="AP47" s="256"/>
+      <c r="AQ47" s="269"/>
+      <c r="AR47" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="AS47" s="337"/>
-      <c r="AT47" s="337"/>
-      <c r="AU47" s="337"/>
-      <c r="AV47" s="337"/>
-      <c r="AW47" s="352"/>
+      <c r="AS47" s="256"/>
+      <c r="AT47" s="256"/>
+      <c r="AU47" s="256"/>
+      <c r="AV47" s="256"/>
+      <c r="AW47" s="269"/>
     </row>
     <row r="48" spans="7:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O48" s="194"/>
-      <c r="P48" s="370" t="s">
+      <c r="P48" s="270" t="s">
         <v>621</v>
       </c>
-      <c r="Q48" s="371"/>
+      <c r="Q48" s="271"/>
       <c r="R48" s="151" t="s">
         <v>223</v>
       </c>
@@ -30854,7 +30852,7 @@
         <v>622</v>
       </c>
       <c r="V48" s="193"/>
-      <c r="X48" s="353" t="s">
+      <c r="X48" s="272" t="s">
         <v>1</v>
       </c>
       <c r="Y48" s="72" t="s">
@@ -30887,16 +30885,16 @@
     </row>
     <row r="49" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O49" s="194"/>
-      <c r="P49" s="370" t="s">
+      <c r="P49" s="270" t="s">
         <v>31</v>
       </c>
-      <c r="Q49" s="371"/>
+      <c r="Q49" s="271"/>
       <c r="R49" s="31"/>
       <c r="S49" s="89"/>
       <c r="T49" s="224"/>
       <c r="U49" s="224"/>
       <c r="V49" s="193"/>
-      <c r="X49" s="353"/>
+      <c r="X49" s="272"/>
       <c r="Y49" s="72" t="s">
         <v>12</v>
       </c>
@@ -30927,16 +30925,16 @@
     </row>
     <row r="50" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O50" s="194"/>
-      <c r="P50" s="243" t="s">
+      <c r="P50" s="247" t="s">
         <v>30</v>
       </c>
-      <c r="Q50" s="243"/>
-      <c r="R50" s="243"/>
-      <c r="S50" s="243"/>
-      <c r="T50" s="243"/>
-      <c r="U50" s="243"/>
+      <c r="Q50" s="247"/>
+      <c r="R50" s="247"/>
+      <c r="S50" s="247"/>
+      <c r="T50" s="247"/>
+      <c r="U50" s="247"/>
       <c r="V50" s="193"/>
-      <c r="X50" s="353" t="s">
+      <c r="X50" s="272" t="s">
         <v>32</v>
       </c>
       <c r="Y50" s="72" t="s">
@@ -30969,7 +30967,7 @@
     </row>
     <row r="51" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O51" s="194"/>
-      <c r="P51" s="369" t="s">
+      <c r="P51" s="273" t="s">
         <v>1</v>
       </c>
       <c r="Q51" s="151" t="s">
@@ -30980,7 +30978,7 @@
       <c r="T51" s="219"/>
       <c r="U51" s="220"/>
       <c r="V51" s="193"/>
-      <c r="X51" s="353"/>
+      <c r="X51" s="272"/>
       <c r="Y51" s="72" t="s">
         <v>12</v>
       </c>
@@ -31011,7 +31009,7 @@
     </row>
     <row r="52" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O52" s="194"/>
-      <c r="P52" s="369"/>
+      <c r="P52" s="273"/>
       <c r="Q52" s="151" t="s">
         <v>12</v>
       </c>
@@ -31020,7 +31018,7 @@
       <c r="T52" s="219"/>
       <c r="U52" s="220"/>
       <c r="V52" s="193"/>
-      <c r="X52" s="354" t="s">
+      <c r="X52" s="274" t="s">
         <v>33</v>
       </c>
       <c r="Y52" s="72" t="s">
@@ -31053,7 +31051,7 @@
     </row>
     <row r="53" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O53" s="194"/>
-      <c r="P53" s="369" t="s">
+      <c r="P53" s="273" t="s">
         <v>623</v>
       </c>
       <c r="Q53" s="151" t="s">
@@ -31064,7 +31062,7 @@
       <c r="T53" s="219"/>
       <c r="U53" s="220"/>
       <c r="V53" s="193"/>
-      <c r="X53" s="355"/>
+      <c r="X53" s="275"/>
       <c r="Y53" s="72" t="s">
         <v>12</v>
       </c>
@@ -31095,7 +31093,7 @@
     </row>
     <row r="54" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O54" s="194"/>
-      <c r="P54" s="369"/>
+      <c r="P54" s="273"/>
       <c r="Q54" s="151" t="s">
         <v>12</v>
       </c>
@@ -31104,10 +31102,10 @@
       <c r="T54" s="219"/>
       <c r="U54" s="220"/>
       <c r="V54" s="193"/>
-      <c r="X54" s="356" t="s">
+      <c r="X54" s="276" t="s">
         <v>34</v>
       </c>
-      <c r="Y54" s="357"/>
+      <c r="Y54" s="277"/>
       <c r="Z54" s="70"/>
       <c r="AA54" s="25"/>
       <c r="AB54" s="25"/>
@@ -31135,7 +31133,7 @@
     </row>
     <row r="55" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O55" s="194"/>
-      <c r="P55" s="369" t="s">
+      <c r="P55" s="273" t="s">
         <v>624</v>
       </c>
       <c r="Q55" s="151" t="s">
@@ -31146,44 +31144,44 @@
       <c r="T55" s="219"/>
       <c r="U55" s="220"/>
       <c r="V55" s="193"/>
-      <c r="X55" s="358"/>
-      <c r="Y55" s="350"/>
-      <c r="Z55" s="358" t="s">
+      <c r="X55" s="278"/>
+      <c r="Y55" s="267"/>
+      <c r="Z55" s="278" t="s">
         <v>107</v>
       </c>
-      <c r="AA55" s="256"/>
-      <c r="AB55" s="256"/>
-      <c r="AC55" s="256"/>
-      <c r="AD55" s="256"/>
-      <c r="AE55" s="350"/>
-      <c r="AF55" s="358" t="s">
+      <c r="AA55" s="250"/>
+      <c r="AB55" s="250"/>
+      <c r="AC55" s="250"/>
+      <c r="AD55" s="250"/>
+      <c r="AE55" s="267"/>
+      <c r="AF55" s="278" t="s">
         <v>107</v>
       </c>
-      <c r="AG55" s="256"/>
-      <c r="AH55" s="256"/>
-      <c r="AI55" s="256"/>
-      <c r="AJ55" s="256"/>
-      <c r="AK55" s="350"/>
-      <c r="AL55" s="358" t="s">
+      <c r="AG55" s="250"/>
+      <c r="AH55" s="250"/>
+      <c r="AI55" s="250"/>
+      <c r="AJ55" s="250"/>
+      <c r="AK55" s="267"/>
+      <c r="AL55" s="278" t="s">
         <v>107</v>
       </c>
-      <c r="AM55" s="256"/>
-      <c r="AN55" s="256"/>
-      <c r="AO55" s="256"/>
-      <c r="AP55" s="256"/>
-      <c r="AQ55" s="350"/>
-      <c r="AR55" s="358" t="s">
+      <c r="AM55" s="250"/>
+      <c r="AN55" s="250"/>
+      <c r="AO55" s="250"/>
+      <c r="AP55" s="250"/>
+      <c r="AQ55" s="267"/>
+      <c r="AR55" s="278" t="s">
         <v>107</v>
       </c>
-      <c r="AS55" s="256"/>
-      <c r="AT55" s="256"/>
-      <c r="AU55" s="256"/>
-      <c r="AV55" s="256"/>
-      <c r="AW55" s="350"/>
+      <c r="AS55" s="250"/>
+      <c r="AT55" s="250"/>
+      <c r="AU55" s="250"/>
+      <c r="AV55" s="250"/>
+      <c r="AW55" s="267"/>
     </row>
     <row r="56" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O56" s="194"/>
-      <c r="P56" s="369"/>
+      <c r="P56" s="273"/>
       <c r="Q56" s="151" t="s">
         <v>12</v>
       </c>
@@ -31192,10 +31190,10 @@
       <c r="T56" s="219"/>
       <c r="U56" s="220"/>
       <c r="V56" s="193"/>
-      <c r="X56" s="359" t="s">
+      <c r="X56" s="279" t="s">
         <v>37</v>
       </c>
-      <c r="Y56" s="360"/>
+      <c r="Y56" s="280"/>
       <c r="Z56" s="68"/>
       <c r="AA56" s="19"/>
       <c r="AB56" s="19"/>
@@ -31223,65 +31221,65 @@
     </row>
     <row r="57" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O57" s="194"/>
-      <c r="P57" s="367" t="s">
+      <c r="P57" s="281" t="s">
         <v>625</v>
       </c>
-      <c r="Q57" s="367"/>
+      <c r="Q57" s="281"/>
       <c r="R57" s="218"/>
       <c r="S57" s="218"/>
       <c r="T57" s="219"/>
       <c r="U57" s="221"/>
       <c r="V57" s="210"/>
-      <c r="X57" s="364"/>
-      <c r="Y57" s="365"/>
-      <c r="Z57" s="351" t="s">
+      <c r="X57" s="282"/>
+      <c r="Y57" s="283"/>
+      <c r="Z57" s="268" t="s">
         <v>108</v>
       </c>
-      <c r="AA57" s="337"/>
-      <c r="AB57" s="337"/>
-      <c r="AC57" s="337"/>
-      <c r="AD57" s="337"/>
-      <c r="AE57" s="352"/>
-      <c r="AF57" s="351" t="s">
+      <c r="AA57" s="256"/>
+      <c r="AB57" s="256"/>
+      <c r="AC57" s="256"/>
+      <c r="AD57" s="256"/>
+      <c r="AE57" s="269"/>
+      <c r="AF57" s="268" t="s">
         <v>108</v>
       </c>
-      <c r="AG57" s="337"/>
-      <c r="AH57" s="337"/>
-      <c r="AI57" s="337"/>
-      <c r="AJ57" s="337"/>
-      <c r="AK57" s="352"/>
-      <c r="AL57" s="351" t="s">
+      <c r="AG57" s="256"/>
+      <c r="AH57" s="256"/>
+      <c r="AI57" s="256"/>
+      <c r="AJ57" s="256"/>
+      <c r="AK57" s="269"/>
+      <c r="AL57" s="268" t="s">
         <v>108</v>
       </c>
-      <c r="AM57" s="337"/>
-      <c r="AN57" s="337"/>
-      <c r="AO57" s="337"/>
-      <c r="AP57" s="337"/>
-      <c r="AQ57" s="352"/>
-      <c r="AR57" s="351" t="s">
+      <c r="AM57" s="256"/>
+      <c r="AN57" s="256"/>
+      <c r="AO57" s="256"/>
+      <c r="AP57" s="256"/>
+      <c r="AQ57" s="269"/>
+      <c r="AR57" s="268" t="s">
         <v>108</v>
       </c>
-      <c r="AS57" s="337"/>
-      <c r="AT57" s="337"/>
-      <c r="AU57" s="337"/>
-      <c r="AV57" s="337"/>
-      <c r="AW57" s="352"/>
+      <c r="AS57" s="256"/>
+      <c r="AT57" s="256"/>
+      <c r="AU57" s="256"/>
+      <c r="AV57" s="256"/>
+      <c r="AW57" s="269"/>
     </row>
     <row r="58" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O58" s="194"/>
-      <c r="P58" s="241" t="s">
+      <c r="P58" s="285" t="s">
         <v>107</v>
       </c>
-      <c r="Q58" s="368"/>
-      <c r="R58" s="368"/>
-      <c r="S58" s="368"/>
-      <c r="T58" s="368"/>
-      <c r="U58" s="242"/>
+      <c r="Q58" s="286"/>
+      <c r="R58" s="286"/>
+      <c r="S58" s="286"/>
+      <c r="T58" s="286"/>
+      <c r="U58" s="287"/>
       <c r="V58" s="210"/>
-      <c r="X58" s="353" t="s">
+      <c r="X58" s="272" t="s">
         <v>38</v>
       </c>
-      <c r="Y58" s="361"/>
+      <c r="Y58" s="288"/>
       <c r="Z58" s="68"/>
       <c r="AA58" s="19"/>
       <c r="AB58" s="19"/>
@@ -31309,19 +31307,19 @@
     </row>
     <row r="59" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O59" s="194"/>
-      <c r="P59" s="367" t="s">
+      <c r="P59" s="281" t="s">
         <v>626</v>
       </c>
-      <c r="Q59" s="367"/>
+      <c r="Q59" s="281"/>
       <c r="R59" s="218"/>
       <c r="S59" s="218"/>
       <c r="T59" s="219"/>
       <c r="U59" s="221"/>
       <c r="V59" s="210"/>
-      <c r="X59" s="353" t="s">
+      <c r="X59" s="272" t="s">
         <v>36</v>
       </c>
-      <c r="Y59" s="361"/>
+      <c r="Y59" s="288"/>
       <c r="Z59" s="68"/>
       <c r="AA59" s="19"/>
       <c r="AB59" s="19"/>
@@ -31349,19 +31347,19 @@
     </row>
     <row r="60" spans="15:49" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O60" s="194"/>
-      <c r="P60" s="241" t="s">
+      <c r="P60" s="285" t="s">
         <v>627</v>
       </c>
-      <c r="Q60" s="368"/>
-      <c r="R60" s="368"/>
-      <c r="S60" s="368"/>
-      <c r="T60" s="368"/>
-      <c r="U60" s="242"/>
+      <c r="Q60" s="286"/>
+      <c r="R60" s="286"/>
+      <c r="S60" s="286"/>
+      <c r="T60" s="286"/>
+      <c r="U60" s="287"/>
       <c r="V60" s="193"/>
-      <c r="X60" s="362" t="s">
+      <c r="X60" s="289" t="s">
         <v>39</v>
       </c>
-      <c r="Y60" s="363"/>
+      <c r="Y60" s="290"/>
       <c r="Z60" s="73"/>
       <c r="AA60" s="74"/>
       <c r="AB60" s="74"/>
@@ -31389,10 +31387,10 @@
     </row>
     <row r="61" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O61" s="194"/>
-      <c r="P61" s="369" t="s">
+      <c r="P61" s="273" t="s">
         <v>628</v>
       </c>
-      <c r="Q61" s="369"/>
+      <c r="Q61" s="273"/>
       <c r="R61" s="218"/>
       <c r="S61" s="218"/>
       <c r="T61" s="219"/>
@@ -31401,10 +31399,10 @@
     </row>
     <row r="62" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O62" s="194"/>
-      <c r="P62" s="369" t="s">
+      <c r="P62" s="273" t="s">
         <v>629</v>
       </c>
-      <c r="Q62" s="369"/>
+      <c r="Q62" s="273"/>
       <c r="R62" s="218"/>
       <c r="S62" s="218"/>
       <c r="T62" s="219"/>
@@ -31413,10 +31411,10 @@
     </row>
     <row r="63" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O63" s="194"/>
-      <c r="P63" s="366" t="s">
+      <c r="P63" s="284" t="s">
         <v>39</v>
       </c>
-      <c r="Q63" s="366"/>
+      <c r="Q63" s="284"/>
       <c r="R63" s="218"/>
       <c r="S63" s="218"/>
       <c r="T63" s="219"/>
@@ -31472,11 +31470,6 @@
     <mergeCell ref="X59:Y59"/>
     <mergeCell ref="P60:U60"/>
     <mergeCell ref="X60:Y60"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="X57:Y57"/>
-    <mergeCell ref="Z57:AE57"/>
-    <mergeCell ref="AF57:AK57"/>
-    <mergeCell ref="AL57:AQ57"/>
     <mergeCell ref="AR57:AW57"/>
     <mergeCell ref="P55:P56"/>
     <mergeCell ref="X55:Y55"/>
@@ -31485,6 +31478,11 @@
     <mergeCell ref="AL55:AQ55"/>
     <mergeCell ref="AR55:AW55"/>
     <mergeCell ref="X56:Y56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="X57:Y57"/>
+    <mergeCell ref="Z57:AE57"/>
+    <mergeCell ref="AF57:AK57"/>
+    <mergeCell ref="AL57:AQ57"/>
     <mergeCell ref="AR47:AW47"/>
     <mergeCell ref="P48:Q48"/>
     <mergeCell ref="X48:X49"/>
@@ -31495,17 +31493,12 @@
     <mergeCell ref="X52:X53"/>
     <mergeCell ref="P53:P54"/>
     <mergeCell ref="X54:Y54"/>
+    <mergeCell ref="AL47:AQ47"/>
     <mergeCell ref="X45:Y45"/>
     <mergeCell ref="X46:Y46"/>
     <mergeCell ref="X47:Y47"/>
     <mergeCell ref="Z47:AE47"/>
     <mergeCell ref="AF47:AK47"/>
-    <mergeCell ref="AL47:AQ47"/>
-    <mergeCell ref="AN24:AP24"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="Z44:AE44"/>
-    <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="AL44:AQ44"/>
     <mergeCell ref="AR44:AW44"/>
     <mergeCell ref="G8:M8"/>
     <mergeCell ref="G11:M11"/>
@@ -31517,6 +31510,11 @@
     <mergeCell ref="AE24:AG24"/>
     <mergeCell ref="AH24:AJ24"/>
     <mergeCell ref="AK24:AM24"/>
+    <mergeCell ref="AN24:AP24"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="Z44:AE44"/>
+    <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="AL44:AQ44"/>
     <mergeCell ref="G3:M3"/>
     <mergeCell ref="R4:R6"/>
     <mergeCell ref="S4:S5"/>
@@ -31564,15 +31562,15 @@
       <c r="V2" s="190"/>
     </row>
     <row r="3" spans="2:23" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G3" s="312" t="s">
+      <c r="G3" s="241" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="313"/>
-      <c r="I3" s="313"/>
-      <c r="J3" s="313"/>
-      <c r="K3" s="313"/>
-      <c r="L3" s="313"/>
-      <c r="M3" s="314"/>
+      <c r="H3" s="242"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="M3" s="243"/>
       <c r="N3" s="213"/>
       <c r="O3" s="213"/>
       <c r="P3" s="213"/>
@@ -31612,39 +31610,39 @@
       <c r="O4" s="214"/>
       <c r="P4" s="214"/>
       <c r="Q4" s="194"/>
-      <c r="R4" s="333" t="s">
+      <c r="R4" s="244" t="s">
         <v>618</v>
       </c>
-      <c r="S4" s="243" t="s">
+      <c r="S4" s="247" t="s">
         <v>617</v>
       </c>
-      <c r="T4" s="332" t="s">
+      <c r="T4" s="248" t="s">
         <v>619</v>
       </c>
-      <c r="U4" s="332" t="s">
+      <c r="U4" s="248" t="s">
         <v>10</v>
       </c>
       <c r="V4" s="193"/>
       <c r="W4" s="39"/>
     </row>
     <row r="5" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G5" s="255" t="s">
+      <c r="G5" s="249" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="256"/>
-      <c r="I5" s="256"/>
-      <c r="J5" s="256"/>
-      <c r="K5" s="256"/>
-      <c r="L5" s="256"/>
-      <c r="M5" s="257"/>
+      <c r="H5" s="250"/>
+      <c r="I5" s="250"/>
+      <c r="J5" s="250"/>
+      <c r="K5" s="250"/>
+      <c r="L5" s="250"/>
+      <c r="M5" s="251"/>
       <c r="N5" s="91"/>
       <c r="O5" s="91"/>
       <c r="P5" s="91"/>
       <c r="Q5" s="194"/>
-      <c r="R5" s="334"/>
-      <c r="S5" s="243"/>
-      <c r="T5" s="332"/>
-      <c r="U5" s="332"/>
+      <c r="R5" s="245"/>
+      <c r="S5" s="247"/>
+      <c r="T5" s="248"/>
+      <c r="U5" s="248"/>
       <c r="V5" s="193"/>
       <c r="W5" s="39"/>
     </row>
@@ -31670,7 +31668,7 @@
       <c r="O6" s="91"/>
       <c r="P6" s="91"/>
       <c r="Q6" s="194"/>
-      <c r="R6" s="335"/>
+      <c r="R6" s="246"/>
       <c r="S6" s="234" t="s">
         <v>620</v>
       </c>
@@ -31717,15 +31715,15 @@
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="193"/>
-      <c r="G8" s="336" t="s">
+      <c r="G8" s="255" t="s">
         <v>0</v>
       </c>
-      <c r="H8" s="337"/>
-      <c r="I8" s="337"/>
-      <c r="J8" s="337"/>
-      <c r="K8" s="337"/>
-      <c r="L8" s="337"/>
-      <c r="M8" s="338"/>
+      <c r="H8" s="256"/>
+      <c r="I8" s="256"/>
+      <c r="J8" s="256"/>
+      <c r="K8" s="256"/>
+      <c r="L8" s="256"/>
+      <c r="M8" s="257"/>
       <c r="N8" s="91"/>
       <c r="O8" s="91"/>
       <c r="P8" s="91"/>
@@ -31808,15 +31806,15 @@
       </c>
       <c r="D11" s="38"/>
       <c r="E11" s="193"/>
-      <c r="G11" s="336" t="s">
+      <c r="G11" s="255" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="337"/>
-      <c r="I11" s="337"/>
-      <c r="J11" s="337"/>
-      <c r="K11" s="337"/>
-      <c r="L11" s="337"/>
-      <c r="M11" s="338"/>
+      <c r="H11" s="256"/>
+      <c r="I11" s="256"/>
+      <c r="J11" s="256"/>
+      <c r="K11" s="256"/>
+      <c r="L11" s="256"/>
+      <c r="M11" s="257"/>
       <c r="N11" s="91"/>
       <c r="O11" s="91"/>
       <c r="P11" s="91"/>
@@ -31899,15 +31897,15 @@
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="193"/>
-      <c r="G14" s="336" t="s">
+      <c r="G14" s="255" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="337"/>
-      <c r="I14" s="337"/>
-      <c r="J14" s="337"/>
-      <c r="K14" s="337"/>
-      <c r="L14" s="337"/>
-      <c r="M14" s="338"/>
+      <c r="H14" s="256"/>
+      <c r="I14" s="256"/>
+      <c r="J14" s="256"/>
+      <c r="K14" s="256"/>
+      <c r="L14" s="256"/>
+      <c r="M14" s="257"/>
       <c r="N14" s="91"/>
       <c r="O14" s="91"/>
       <c r="P14" s="91"/>
@@ -32052,15 +32050,15 @@
       </c>
       <c r="D19" s="38"/>
       <c r="E19" s="193"/>
-      <c r="G19" s="336" t="s">
+      <c r="G19" s="255" t="s">
         <v>114</v>
       </c>
-      <c r="H19" s="337"/>
-      <c r="I19" s="337"/>
-      <c r="J19" s="337"/>
-      <c r="K19" s="337"/>
-      <c r="L19" s="337"/>
-      <c r="M19" s="338"/>
+      <c r="H19" s="256"/>
+      <c r="I19" s="256"/>
+      <c r="J19" s="256"/>
+      <c r="K19" s="256"/>
+      <c r="L19" s="256"/>
+      <c r="M19" s="257"/>
       <c r="N19" s="91"/>
       <c r="O19" s="91"/>
       <c r="P19" s="91"/>
@@ -32167,27 +32165,27 @@
       <c r="T23" s="192"/>
       <c r="U23" s="192"/>
       <c r="V23" s="193"/>
-      <c r="X23" s="244" t="s">
+      <c r="X23" s="258" t="s">
         <v>227</v>
       </c>
-      <c r="Y23" s="244"/>
-      <c r="Z23" s="244"/>
-      <c r="AA23" s="244"/>
-      <c r="AB23" s="244"/>
-      <c r="AC23" s="244"/>
-      <c r="AD23" s="244"/>
-      <c r="AE23" s="244"/>
-      <c r="AF23" s="244"/>
-      <c r="AG23" s="244"/>
-      <c r="AH23" s="244"/>
-      <c r="AI23" s="244"/>
-      <c r="AJ23" s="244"/>
-      <c r="AK23" s="244"/>
-      <c r="AL23" s="244"/>
-      <c r="AM23" s="244"/>
-      <c r="AN23" s="244"/>
-      <c r="AO23" s="244"/>
-      <c r="AP23" s="244"/>
+      <c r="Y23" s="258"/>
+      <c r="Z23" s="258"/>
+      <c r="AA23" s="258"/>
+      <c r="AB23" s="258"/>
+      <c r="AC23" s="258"/>
+      <c r="AD23" s="258"/>
+      <c r="AE23" s="258"/>
+      <c r="AF23" s="258"/>
+      <c r="AG23" s="258"/>
+      <c r="AH23" s="258"/>
+      <c r="AI23" s="258"/>
+      <c r="AJ23" s="258"/>
+      <c r="AK23" s="258"/>
+      <c r="AL23" s="258"/>
+      <c r="AM23" s="258"/>
+      <c r="AN23" s="258"/>
+      <c r="AO23" s="258"/>
+      <c r="AP23" s="258"/>
     </row>
     <row r="24" spans="2:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q24" s="196"/>
@@ -32199,36 +32197,36 @@
       <c r="X24" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Y24" s="339" t="s">
+      <c r="Y24" s="259" t="s">
         <v>18</v>
       </c>
-      <c r="Z24" s="340"/>
-      <c r="AA24" s="341"/>
-      <c r="AB24" s="339" t="s">
+      <c r="Z24" s="260"/>
+      <c r="AA24" s="261"/>
+      <c r="AB24" s="259" t="s">
         <v>17</v>
       </c>
-      <c r="AC24" s="340"/>
-      <c r="AD24" s="341"/>
-      <c r="AE24" s="339" t="s">
+      <c r="AC24" s="260"/>
+      <c r="AD24" s="261"/>
+      <c r="AE24" s="259" t="s">
         <v>16</v>
       </c>
-      <c r="AF24" s="340"/>
-      <c r="AG24" s="341"/>
-      <c r="AH24" s="339" t="s">
+      <c r="AF24" s="260"/>
+      <c r="AG24" s="261"/>
+      <c r="AH24" s="259" t="s">
         <v>13</v>
       </c>
-      <c r="AI24" s="340"/>
-      <c r="AJ24" s="341"/>
-      <c r="AK24" s="339" t="s">
+      <c r="AI24" s="260"/>
+      <c r="AJ24" s="261"/>
+      <c r="AK24" s="259" t="s">
         <v>20</v>
       </c>
-      <c r="AL24" s="340"/>
-      <c r="AM24" s="341"/>
-      <c r="AN24" s="339" t="s">
+      <c r="AL24" s="260"/>
+      <c r="AM24" s="261"/>
+      <c r="AN24" s="259" t="s">
         <v>553</v>
       </c>
-      <c r="AO24" s="340"/>
-      <c r="AP24" s="341"/>
+      <c r="AO24" s="260"/>
+      <c r="AP24" s="261"/>
     </row>
     <row r="25" spans="2:42" ht="81.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="X25" s="64" t="s">
@@ -32742,48 +32740,48 @@
       <c r="P43" s="39"/>
     </row>
     <row r="44" spans="7:49" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X44" s="342" t="s">
+      <c r="X44" s="252" t="s">
         <v>238</v>
       </c>
-      <c r="Y44" s="343"/>
-      <c r="Z44" s="342" t="s">
+      <c r="Y44" s="254"/>
+      <c r="Z44" s="252" t="s">
         <v>237</v>
       </c>
-      <c r="AA44" s="344"/>
-      <c r="AB44" s="344"/>
-      <c r="AC44" s="344"/>
-      <c r="AD44" s="344"/>
-      <c r="AE44" s="343"/>
-      <c r="AF44" s="342" t="s">
+      <c r="AA44" s="253"/>
+      <c r="AB44" s="253"/>
+      <c r="AC44" s="253"/>
+      <c r="AD44" s="253"/>
+      <c r="AE44" s="254"/>
+      <c r="AF44" s="252" t="s">
         <v>239</v>
       </c>
-      <c r="AG44" s="344"/>
-      <c r="AH44" s="344"/>
-      <c r="AI44" s="344"/>
-      <c r="AJ44" s="344"/>
-      <c r="AK44" s="343"/>
-      <c r="AL44" s="342" t="s">
+      <c r="AG44" s="253"/>
+      <c r="AH44" s="253"/>
+      <c r="AI44" s="253"/>
+      <c r="AJ44" s="253"/>
+      <c r="AK44" s="254"/>
+      <c r="AL44" s="252" t="s">
         <v>240</v>
       </c>
-      <c r="AM44" s="344"/>
-      <c r="AN44" s="344"/>
-      <c r="AO44" s="344"/>
-      <c r="AP44" s="344"/>
-      <c r="AQ44" s="343"/>
-      <c r="AR44" s="342" t="s">
+      <c r="AM44" s="253"/>
+      <c r="AN44" s="253"/>
+      <c r="AO44" s="253"/>
+      <c r="AP44" s="253"/>
+      <c r="AQ44" s="254"/>
+      <c r="AR44" s="252" t="s">
         <v>241</v>
       </c>
-      <c r="AS44" s="344"/>
-      <c r="AT44" s="344"/>
-      <c r="AU44" s="344"/>
-      <c r="AV44" s="344"/>
-      <c r="AW44" s="343"/>
+      <c r="AS44" s="253"/>
+      <c r="AT44" s="253"/>
+      <c r="AU44" s="253"/>
+      <c r="AV44" s="253"/>
+      <c r="AW44" s="254"/>
     </row>
     <row r="45" spans="7:49" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X45" s="345" t="s">
+      <c r="X45" s="262" t="s">
         <v>40</v>
       </c>
-      <c r="Y45" s="346"/>
+      <c r="Y45" s="263"/>
       <c r="Z45" s="184" t="s">
         <v>117</v>
       </c>
@@ -32868,10 +32866,10 @@
       <c r="T46" s="215"/>
       <c r="U46" s="189"/>
       <c r="V46" s="190"/>
-      <c r="X46" s="347" t="s">
+      <c r="X46" s="264" t="s">
         <v>31</v>
       </c>
-      <c r="Y46" s="348"/>
+      <c r="Y46" s="265"/>
       <c r="Z46" s="66"/>
       <c r="AA46" s="22"/>
       <c r="AB46" s="22"/>
@@ -32908,47 +32906,47 @@
       <c r="T47" s="216"/>
       <c r="U47" s="211"/>
       <c r="V47" s="208"/>
-      <c r="X47" s="349"/>
-      <c r="Y47" s="350"/>
-      <c r="Z47" s="351" t="s">
+      <c r="X47" s="266"/>
+      <c r="Y47" s="267"/>
+      <c r="Z47" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="AA47" s="337"/>
-      <c r="AB47" s="337"/>
-      <c r="AC47" s="337"/>
-      <c r="AD47" s="337"/>
-      <c r="AE47" s="352"/>
-      <c r="AF47" s="351" t="s">
+      <c r="AA47" s="256"/>
+      <c r="AB47" s="256"/>
+      <c r="AC47" s="256"/>
+      <c r="AD47" s="256"/>
+      <c r="AE47" s="269"/>
+      <c r="AF47" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="AG47" s="337"/>
-      <c r="AH47" s="337"/>
-      <c r="AI47" s="337"/>
-      <c r="AJ47" s="337"/>
-      <c r="AK47" s="352"/>
-      <c r="AL47" s="351" t="s">
+      <c r="AG47" s="256"/>
+      <c r="AH47" s="256"/>
+      <c r="AI47" s="256"/>
+      <c r="AJ47" s="256"/>
+      <c r="AK47" s="269"/>
+      <c r="AL47" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="AM47" s="337"/>
-      <c r="AN47" s="337"/>
-      <c r="AO47" s="337"/>
-      <c r="AP47" s="337"/>
-      <c r="AQ47" s="352"/>
-      <c r="AR47" s="351" t="s">
+      <c r="AM47" s="256"/>
+      <c r="AN47" s="256"/>
+      <c r="AO47" s="256"/>
+      <c r="AP47" s="256"/>
+      <c r="AQ47" s="269"/>
+      <c r="AR47" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="AS47" s="337"/>
-      <c r="AT47" s="337"/>
-      <c r="AU47" s="337"/>
-      <c r="AV47" s="337"/>
-      <c r="AW47" s="352"/>
+      <c r="AS47" s="256"/>
+      <c r="AT47" s="256"/>
+      <c r="AU47" s="256"/>
+      <c r="AV47" s="256"/>
+      <c r="AW47" s="269"/>
     </row>
     <row r="48" spans="7:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O48" s="194"/>
-      <c r="P48" s="370" t="s">
+      <c r="P48" s="270" t="s">
         <v>621</v>
       </c>
-      <c r="Q48" s="371"/>
+      <c r="Q48" s="271"/>
       <c r="R48" s="151" t="s">
         <v>223</v>
       </c>
@@ -32962,7 +32960,7 @@
         <v>622</v>
       </c>
       <c r="V48" s="193"/>
-      <c r="X48" s="353" t="s">
+      <c r="X48" s="272" t="s">
         <v>1</v>
       </c>
       <c r="Y48" s="72" t="s">
@@ -32995,16 +32993,16 @@
     </row>
     <row r="49" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O49" s="194"/>
-      <c r="P49" s="370" t="s">
+      <c r="P49" s="270" t="s">
         <v>31</v>
       </c>
-      <c r="Q49" s="371"/>
+      <c r="Q49" s="271"/>
       <c r="R49" s="31"/>
       <c r="S49" s="89"/>
       <c r="T49" s="224"/>
       <c r="U49" s="224"/>
       <c r="V49" s="193"/>
-      <c r="X49" s="353"/>
+      <c r="X49" s="272"/>
       <c r="Y49" s="72" t="s">
         <v>12</v>
       </c>
@@ -33035,16 +33033,16 @@
     </row>
     <row r="50" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O50" s="194"/>
-      <c r="P50" s="243" t="s">
+      <c r="P50" s="247" t="s">
         <v>30</v>
       </c>
-      <c r="Q50" s="243"/>
-      <c r="R50" s="243"/>
-      <c r="S50" s="243"/>
-      <c r="T50" s="243"/>
-      <c r="U50" s="243"/>
+      <c r="Q50" s="247"/>
+      <c r="R50" s="247"/>
+      <c r="S50" s="247"/>
+      <c r="T50" s="247"/>
+      <c r="U50" s="247"/>
       <c r="V50" s="193"/>
-      <c r="X50" s="353" t="s">
+      <c r="X50" s="272" t="s">
         <v>32</v>
       </c>
       <c r="Y50" s="72" t="s">
@@ -33077,7 +33075,7 @@
     </row>
     <row r="51" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O51" s="194"/>
-      <c r="P51" s="369" t="s">
+      <c r="P51" s="273" t="s">
         <v>1</v>
       </c>
       <c r="Q51" s="151" t="s">
@@ -33088,7 +33086,7 @@
       <c r="T51" s="219"/>
       <c r="U51" s="220"/>
       <c r="V51" s="193"/>
-      <c r="X51" s="353"/>
+      <c r="X51" s="272"/>
       <c r="Y51" s="72" t="s">
         <v>12</v>
       </c>
@@ -33119,7 +33117,7 @@
     </row>
     <row r="52" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O52" s="194"/>
-      <c r="P52" s="369"/>
+      <c r="P52" s="273"/>
       <c r="Q52" s="151" t="s">
         <v>12</v>
       </c>
@@ -33128,7 +33126,7 @@
       <c r="T52" s="219"/>
       <c r="U52" s="220"/>
       <c r="V52" s="193"/>
-      <c r="X52" s="354" t="s">
+      <c r="X52" s="274" t="s">
         <v>33</v>
       </c>
       <c r="Y52" s="72" t="s">
@@ -33161,7 +33159,7 @@
     </row>
     <row r="53" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O53" s="194"/>
-      <c r="P53" s="369" t="s">
+      <c r="P53" s="273" t="s">
         <v>623</v>
       </c>
       <c r="Q53" s="151" t="s">
@@ -33172,7 +33170,7 @@
       <c r="T53" s="219"/>
       <c r="U53" s="220"/>
       <c r="V53" s="193"/>
-      <c r="X53" s="355"/>
+      <c r="X53" s="275"/>
       <c r="Y53" s="72" t="s">
         <v>12</v>
       </c>
@@ -33203,7 +33201,7 @@
     </row>
     <row r="54" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O54" s="194"/>
-      <c r="P54" s="369"/>
+      <c r="P54" s="273"/>
       <c r="Q54" s="151" t="s">
         <v>12</v>
       </c>
@@ -33212,10 +33210,10 @@
       <c r="T54" s="219"/>
       <c r="U54" s="220"/>
       <c r="V54" s="193"/>
-      <c r="X54" s="356" t="s">
+      <c r="X54" s="276" t="s">
         <v>34</v>
       </c>
-      <c r="Y54" s="357"/>
+      <c r="Y54" s="277"/>
       <c r="Z54" s="70"/>
       <c r="AA54" s="25"/>
       <c r="AB54" s="25"/>
@@ -33243,7 +33241,7 @@
     </row>
     <row r="55" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O55" s="194"/>
-      <c r="P55" s="369" t="s">
+      <c r="P55" s="273" t="s">
         <v>624</v>
       </c>
       <c r="Q55" s="151" t="s">
@@ -33254,44 +33252,44 @@
       <c r="T55" s="219"/>
       <c r="U55" s="220"/>
       <c r="V55" s="193"/>
-      <c r="X55" s="358"/>
-      <c r="Y55" s="350"/>
-      <c r="Z55" s="358" t="s">
+      <c r="X55" s="278"/>
+      <c r="Y55" s="267"/>
+      <c r="Z55" s="278" t="s">
         <v>107</v>
       </c>
-      <c r="AA55" s="256"/>
-      <c r="AB55" s="256"/>
-      <c r="AC55" s="256"/>
-      <c r="AD55" s="256"/>
-      <c r="AE55" s="350"/>
-      <c r="AF55" s="358" t="s">
+      <c r="AA55" s="250"/>
+      <c r="AB55" s="250"/>
+      <c r="AC55" s="250"/>
+      <c r="AD55" s="250"/>
+      <c r="AE55" s="267"/>
+      <c r="AF55" s="278" t="s">
         <v>107</v>
       </c>
-      <c r="AG55" s="256"/>
-      <c r="AH55" s="256"/>
-      <c r="AI55" s="256"/>
-      <c r="AJ55" s="256"/>
-      <c r="AK55" s="350"/>
-      <c r="AL55" s="358" t="s">
+      <c r="AG55" s="250"/>
+      <c r="AH55" s="250"/>
+      <c r="AI55" s="250"/>
+      <c r="AJ55" s="250"/>
+      <c r="AK55" s="267"/>
+      <c r="AL55" s="278" t="s">
         <v>107</v>
       </c>
-      <c r="AM55" s="256"/>
-      <c r="AN55" s="256"/>
-      <c r="AO55" s="256"/>
-      <c r="AP55" s="256"/>
-      <c r="AQ55" s="350"/>
-      <c r="AR55" s="358" t="s">
+      <c r="AM55" s="250"/>
+      <c r="AN55" s="250"/>
+      <c r="AO55" s="250"/>
+      <c r="AP55" s="250"/>
+      <c r="AQ55" s="267"/>
+      <c r="AR55" s="278" t="s">
         <v>107</v>
       </c>
-      <c r="AS55" s="256"/>
-      <c r="AT55" s="256"/>
-      <c r="AU55" s="256"/>
-      <c r="AV55" s="256"/>
-      <c r="AW55" s="350"/>
+      <c r="AS55" s="250"/>
+      <c r="AT55" s="250"/>
+      <c r="AU55" s="250"/>
+      <c r="AV55" s="250"/>
+      <c r="AW55" s="267"/>
     </row>
     <row r="56" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O56" s="194"/>
-      <c r="P56" s="369"/>
+      <c r="P56" s="273"/>
       <c r="Q56" s="151" t="s">
         <v>12</v>
       </c>
@@ -33300,10 +33298,10 @@
       <c r="T56" s="219"/>
       <c r="U56" s="220"/>
       <c r="V56" s="193"/>
-      <c r="X56" s="359" t="s">
+      <c r="X56" s="279" t="s">
         <v>37</v>
       </c>
-      <c r="Y56" s="360"/>
+      <c r="Y56" s="280"/>
       <c r="Z56" s="68"/>
       <c r="AA56" s="19"/>
       <c r="AB56" s="19"/>
@@ -33331,65 +33329,65 @@
     </row>
     <row r="57" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O57" s="194"/>
-      <c r="P57" s="367" t="s">
+      <c r="P57" s="281" t="s">
         <v>625</v>
       </c>
-      <c r="Q57" s="367"/>
+      <c r="Q57" s="281"/>
       <c r="R57" s="218"/>
       <c r="S57" s="218"/>
       <c r="T57" s="219"/>
       <c r="U57" s="221"/>
       <c r="V57" s="210"/>
-      <c r="X57" s="364"/>
-      <c r="Y57" s="365"/>
-      <c r="Z57" s="351" t="s">
+      <c r="X57" s="282"/>
+      <c r="Y57" s="283"/>
+      <c r="Z57" s="268" t="s">
         <v>108</v>
       </c>
-      <c r="AA57" s="337"/>
-      <c r="AB57" s="337"/>
-      <c r="AC57" s="337"/>
-      <c r="AD57" s="337"/>
-      <c r="AE57" s="352"/>
-      <c r="AF57" s="351" t="s">
+      <c r="AA57" s="256"/>
+      <c r="AB57" s="256"/>
+      <c r="AC57" s="256"/>
+      <c r="AD57" s="256"/>
+      <c r="AE57" s="269"/>
+      <c r="AF57" s="268" t="s">
         <v>108</v>
       </c>
-      <c r="AG57" s="337"/>
-      <c r="AH57" s="337"/>
-      <c r="AI57" s="337"/>
-      <c r="AJ57" s="337"/>
-      <c r="AK57" s="352"/>
-      <c r="AL57" s="351" t="s">
+      <c r="AG57" s="256"/>
+      <c r="AH57" s="256"/>
+      <c r="AI57" s="256"/>
+      <c r="AJ57" s="256"/>
+      <c r="AK57" s="269"/>
+      <c r="AL57" s="268" t="s">
         <v>108</v>
       </c>
-      <c r="AM57" s="337"/>
-      <c r="AN57" s="337"/>
-      <c r="AO57" s="337"/>
-      <c r="AP57" s="337"/>
-      <c r="AQ57" s="352"/>
-      <c r="AR57" s="351" t="s">
+      <c r="AM57" s="256"/>
+      <c r="AN57" s="256"/>
+      <c r="AO57" s="256"/>
+      <c r="AP57" s="256"/>
+      <c r="AQ57" s="269"/>
+      <c r="AR57" s="268" t="s">
         <v>108</v>
       </c>
-      <c r="AS57" s="337"/>
-      <c r="AT57" s="337"/>
-      <c r="AU57" s="337"/>
-      <c r="AV57" s="337"/>
-      <c r="AW57" s="352"/>
+      <c r="AS57" s="256"/>
+      <c r="AT57" s="256"/>
+      <c r="AU57" s="256"/>
+      <c r="AV57" s="256"/>
+      <c r="AW57" s="269"/>
     </row>
     <row r="58" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O58" s="194"/>
-      <c r="P58" s="241" t="s">
+      <c r="P58" s="285" t="s">
         <v>107</v>
       </c>
-      <c r="Q58" s="368"/>
-      <c r="R58" s="368"/>
-      <c r="S58" s="368"/>
-      <c r="T58" s="368"/>
-      <c r="U58" s="242"/>
+      <c r="Q58" s="286"/>
+      <c r="R58" s="286"/>
+      <c r="S58" s="286"/>
+      <c r="T58" s="286"/>
+      <c r="U58" s="287"/>
       <c r="V58" s="210"/>
-      <c r="X58" s="353" t="s">
+      <c r="X58" s="272" t="s">
         <v>38</v>
       </c>
-      <c r="Y58" s="361"/>
+      <c r="Y58" s="288"/>
       <c r="Z58" s="68"/>
       <c r="AA58" s="19"/>
       <c r="AB58" s="19"/>
@@ -33417,19 +33415,19 @@
     </row>
     <row r="59" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O59" s="194"/>
-      <c r="P59" s="367" t="s">
+      <c r="P59" s="281" t="s">
         <v>626</v>
       </c>
-      <c r="Q59" s="367"/>
+      <c r="Q59" s="281"/>
       <c r="R59" s="218"/>
       <c r="S59" s="218"/>
       <c r="T59" s="219"/>
       <c r="U59" s="221"/>
       <c r="V59" s="210"/>
-      <c r="X59" s="353" t="s">
+      <c r="X59" s="272" t="s">
         <v>36</v>
       </c>
-      <c r="Y59" s="361"/>
+      <c r="Y59" s="288"/>
       <c r="Z59" s="68"/>
       <c r="AA59" s="19"/>
       <c r="AB59" s="19"/>
@@ -33457,19 +33455,19 @@
     </row>
     <row r="60" spans="15:49" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O60" s="194"/>
-      <c r="P60" s="241" t="s">
+      <c r="P60" s="285" t="s">
         <v>627</v>
       </c>
-      <c r="Q60" s="368"/>
-      <c r="R60" s="368"/>
-      <c r="S60" s="368"/>
-      <c r="T60" s="368"/>
-      <c r="U60" s="242"/>
+      <c r="Q60" s="286"/>
+      <c r="R60" s="286"/>
+      <c r="S60" s="286"/>
+      <c r="T60" s="286"/>
+      <c r="U60" s="287"/>
       <c r="V60" s="193"/>
-      <c r="X60" s="362" t="s">
+      <c r="X60" s="289" t="s">
         <v>39</v>
       </c>
-      <c r="Y60" s="363"/>
+      <c r="Y60" s="290"/>
       <c r="Z60" s="73"/>
       <c r="AA60" s="74"/>
       <c r="AB60" s="74"/>
@@ -33497,10 +33495,10 @@
     </row>
     <row r="61" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O61" s="194"/>
-      <c r="P61" s="369" t="s">
+      <c r="P61" s="273" t="s">
         <v>628</v>
       </c>
-      <c r="Q61" s="369"/>
+      <c r="Q61" s="273"/>
       <c r="R61" s="218"/>
       <c r="S61" s="218"/>
       <c r="T61" s="219"/>
@@ -33509,10 +33507,10 @@
     </row>
     <row r="62" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O62" s="194"/>
-      <c r="P62" s="369" t="s">
+      <c r="P62" s="273" t="s">
         <v>629</v>
       </c>
-      <c r="Q62" s="369"/>
+      <c r="Q62" s="273"/>
       <c r="R62" s="218"/>
       <c r="S62" s="218"/>
       <c r="T62" s="219"/>
@@ -33521,10 +33519,10 @@
     </row>
     <row r="63" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O63" s="194"/>
-      <c r="P63" s="366" t="s">
+      <c r="P63" s="284" t="s">
         <v>39</v>
       </c>
-      <c r="Q63" s="366"/>
+      <c r="Q63" s="284"/>
       <c r="R63" s="218"/>
       <c r="S63" s="218"/>
       <c r="T63" s="219"/>

--- a/erlb.xlsx
+++ b/erlb.xlsx
@@ -4787,6 +4787,129 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="79" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4806,137 +4929,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="79" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4961,16 +4961,49 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4991,39 +5024,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5033,29 +5033,62 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5090,38 +5123,41 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="77" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5136,39 +5172,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="77" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5177,34 +5207,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5213,37 +5237,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -19605,42 +19605,42 @@
   <sheetData>
     <row r="1" spans="2:27" ht="11.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="252" t="s">
+      <c r="B2" s="273" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="254"/>
-      <c r="D2" s="252" t="s">
+      <c r="C2" s="275"/>
+      <c r="D2" s="273" t="s">
         <v>235</v>
       </c>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="254"/>
-      <c r="J2" s="252" t="s">
+      <c r="E2" s="274"/>
+      <c r="F2" s="274"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="274"/>
+      <c r="I2" s="275"/>
+      <c r="J2" s="273" t="s">
         <v>236</v>
       </c>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
-      <c r="M2" s="253"/>
-      <c r="N2" s="253"/>
-      <c r="O2" s="254"/>
-      <c r="P2" s="252" t="s">
+      <c r="K2" s="274"/>
+      <c r="L2" s="274"/>
+      <c r="M2" s="274"/>
+      <c r="N2" s="274"/>
+      <c r="O2" s="275"/>
+      <c r="P2" s="273" t="s">
         <v>235</v>
       </c>
-      <c r="Q2" s="253"/>
-      <c r="R2" s="253"/>
-      <c r="S2" s="253"/>
-      <c r="T2" s="253"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="252" t="s">
+      <c r="Q2" s="274"/>
+      <c r="R2" s="274"/>
+      <c r="S2" s="274"/>
+      <c r="T2" s="274"/>
+      <c r="U2" s="275"/>
+      <c r="V2" s="273" t="s">
         <v>236</v>
       </c>
-      <c r="W2" s="253"/>
-      <c r="X2" s="253"/>
-      <c r="Y2" s="253"/>
-      <c r="Z2" s="253"/>
-      <c r="AA2" s="254"/>
+      <c r="W2" s="274"/>
+      <c r="X2" s="274"/>
+      <c r="Y2" s="274"/>
+      <c r="Z2" s="274"/>
+      <c r="AA2" s="275"/>
     </row>
     <row r="3" spans="2:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="362" t="s">
@@ -19721,10 +19721,10 @@
       </c>
     </row>
     <row r="4" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="264" t="s">
+      <c r="B4" s="270" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="265"/>
+      <c r="C4" s="271"/>
       <c r="D4" s="141" t="s">
         <v>234</v>
       </c>
@@ -19753,43 +19753,43 @@
       <c r="AA4" s="158"/>
     </row>
     <row r="5" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="266"/>
-      <c r="C5" s="365"/>
-      <c r="D5" s="268" t="s">
+      <c r="B5" s="272"/>
+      <c r="C5" s="357"/>
+      <c r="D5" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="256"/>
-      <c r="F5" s="256"/>
-      <c r="G5" s="256"/>
-      <c r="H5" s="256"/>
-      <c r="I5" s="269"/>
-      <c r="J5" s="268" t="s">
+      <c r="E5" s="252"/>
+      <c r="F5" s="252"/>
+      <c r="G5" s="252"/>
+      <c r="H5" s="252"/>
+      <c r="I5" s="253"/>
+      <c r="J5" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="256"/>
-      <c r="L5" s="256"/>
-      <c r="M5" s="256"/>
-      <c r="N5" s="256"/>
-      <c r="O5" s="269"/>
-      <c r="P5" s="268" t="s">
+      <c r="K5" s="252"/>
+      <c r="L5" s="252"/>
+      <c r="M5" s="252"/>
+      <c r="N5" s="252"/>
+      <c r="O5" s="253"/>
+      <c r="P5" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="256"/>
-      <c r="R5" s="256"/>
-      <c r="S5" s="256"/>
-      <c r="T5" s="256"/>
-      <c r="U5" s="269"/>
-      <c r="V5" s="268" t="s">
+      <c r="Q5" s="252"/>
+      <c r="R5" s="252"/>
+      <c r="S5" s="252"/>
+      <c r="T5" s="252"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="W5" s="256"/>
-      <c r="X5" s="256"/>
-      <c r="Y5" s="256"/>
-      <c r="Z5" s="256"/>
-      <c r="AA5" s="269"/>
+      <c r="W5" s="252"/>
+      <c r="X5" s="252"/>
+      <c r="Y5" s="252"/>
+      <c r="Z5" s="252"/>
+      <c r="AA5" s="253"/>
     </row>
     <row r="6" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="364" t="s">
+      <c r="B6" s="356" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="72" t="s">
@@ -19823,7 +19823,7 @@
       <c r="AA6" s="161"/>
     </row>
     <row r="7" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="364"/>
+      <c r="B7" s="356"/>
       <c r="C7" s="72" t="s">
         <v>61</v>
       </c>
@@ -19987,10 +19987,10 @@
       <c r="AA11" s="161"/>
     </row>
     <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="276" t="s">
+      <c r="B12" s="266" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="277"/>
+      <c r="C12" s="267"/>
       <c r="D12" s="142" t="s">
         <v>122</v>
       </c>
@@ -20051,46 +20051,46 @@
       <c r="AA13" s="165"/>
     </row>
     <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="279"/>
-      <c r="C14" s="280"/>
-      <c r="D14" s="278" t="s">
+      <c r="B14" s="257"/>
+      <c r="C14" s="258"/>
+      <c r="D14" s="254" t="s">
         <v>105</v>
       </c>
-      <c r="E14" s="250"/>
-      <c r="F14" s="250"/>
-      <c r="G14" s="250"/>
-      <c r="H14" s="250"/>
-      <c r="I14" s="267"/>
-      <c r="J14" s="278" t="s">
+      <c r="E14" s="256"/>
+      <c r="F14" s="256"/>
+      <c r="G14" s="256"/>
+      <c r="H14" s="256"/>
+      <c r="I14" s="255"/>
+      <c r="J14" s="254" t="s">
         <v>232</v>
       </c>
-      <c r="K14" s="250"/>
-      <c r="L14" s="250"/>
-      <c r="M14" s="250"/>
-      <c r="N14" s="250"/>
-      <c r="O14" s="267"/>
-      <c r="P14" s="278" t="s">
+      <c r="K14" s="256"/>
+      <c r="L14" s="256"/>
+      <c r="M14" s="256"/>
+      <c r="N14" s="256"/>
+      <c r="O14" s="255"/>
+      <c r="P14" s="254" t="s">
         <v>232</v>
       </c>
-      <c r="Q14" s="250"/>
-      <c r="R14" s="250"/>
-      <c r="S14" s="250"/>
-      <c r="T14" s="250"/>
-      <c r="U14" s="267"/>
-      <c r="V14" s="278" t="s">
+      <c r="Q14" s="256"/>
+      <c r="R14" s="256"/>
+      <c r="S14" s="256"/>
+      <c r="T14" s="256"/>
+      <c r="U14" s="255"/>
+      <c r="V14" s="254" t="s">
         <v>232</v>
       </c>
-      <c r="W14" s="250"/>
-      <c r="X14" s="250"/>
-      <c r="Y14" s="250"/>
-      <c r="Z14" s="250"/>
-      <c r="AA14" s="267"/>
+      <c r="W14" s="256"/>
+      <c r="X14" s="256"/>
+      <c r="Y14" s="256"/>
+      <c r="Z14" s="256"/>
+      <c r="AA14" s="255"/>
     </row>
     <row r="15" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="279" t="s">
+      <c r="B15" s="257" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="280"/>
+      <c r="C15" s="258"/>
       <c r="D15" s="143" t="s">
         <v>135</v>
       </c>
@@ -20119,10 +20119,10 @@
       <c r="AA15" s="161"/>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="279" t="s">
+      <c r="B16" s="257" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="280"/>
+      <c r="C16" s="258"/>
       <c r="D16" s="142" t="s">
         <v>135</v>
       </c>
@@ -20151,10 +20151,10 @@
       <c r="AA16" s="161"/>
     </row>
     <row r="17" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="279" t="s">
+      <c r="B17" s="257" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="280"/>
+      <c r="C17" s="258"/>
       <c r="D17" s="142" t="s">
         <v>135</v>
       </c>
@@ -20183,10 +20183,10 @@
       <c r="AA17" s="161"/>
     </row>
     <row r="18" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="279" t="s">
+      <c r="B18" s="257" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="280"/>
+      <c r="C18" s="258"/>
       <c r="D18" s="142" t="s">
         <v>135</v>
       </c>
@@ -20215,46 +20215,46 @@
       <c r="AA18" s="161"/>
     </row>
     <row r="19" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="279"/>
-      <c r="C19" s="280"/>
-      <c r="D19" s="366" t="s">
+      <c r="B19" s="257"/>
+      <c r="C19" s="258"/>
+      <c r="D19" s="353" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
-      <c r="G19" s="367"/>
-      <c r="H19" s="367"/>
-      <c r="I19" s="368"/>
-      <c r="J19" s="268" t="s">
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
+      <c r="G19" s="354"/>
+      <c r="H19" s="354"/>
+      <c r="I19" s="355"/>
+      <c r="J19" s="251" t="s">
         <v>65</v>
       </c>
-      <c r="K19" s="256"/>
-      <c r="L19" s="256"/>
-      <c r="M19" s="256"/>
-      <c r="N19" s="256"/>
-      <c r="O19" s="269"/>
-      <c r="P19" s="268" t="s">
+      <c r="K19" s="252"/>
+      <c r="L19" s="252"/>
+      <c r="M19" s="252"/>
+      <c r="N19" s="252"/>
+      <c r="O19" s="253"/>
+      <c r="P19" s="251" t="s">
         <v>65</v>
       </c>
-      <c r="Q19" s="256"/>
-      <c r="R19" s="256"/>
-      <c r="S19" s="256"/>
-      <c r="T19" s="256"/>
-      <c r="U19" s="269"/>
-      <c r="V19" s="268" t="s">
+      <c r="Q19" s="252"/>
+      <c r="R19" s="252"/>
+      <c r="S19" s="252"/>
+      <c r="T19" s="252"/>
+      <c r="U19" s="253"/>
+      <c r="V19" s="251" t="s">
         <v>65</v>
       </c>
-      <c r="W19" s="256"/>
-      <c r="X19" s="256"/>
-      <c r="Y19" s="256"/>
-      <c r="Z19" s="256"/>
-      <c r="AA19" s="269"/>
+      <c r="W19" s="252"/>
+      <c r="X19" s="252"/>
+      <c r="Y19" s="252"/>
+      <c r="Z19" s="252"/>
+      <c r="AA19" s="253"/>
     </row>
     <row r="20" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="272" t="s">
+      <c r="B20" s="246" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="288"/>
+      <c r="C20" s="247"/>
       <c r="D20" s="142" t="s">
         <v>233</v>
       </c>
@@ -20283,10 +20283,10 @@
       <c r="AA20" s="161"/>
     </row>
     <row r="21" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="272" t="s">
+      <c r="B21" s="246" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="288"/>
+      <c r="C21" s="247"/>
       <c r="D21" s="142" t="s">
         <v>233</v>
       </c>
@@ -20315,10 +20315,10 @@
       <c r="AA21" s="161"/>
     </row>
     <row r="22" spans="2:37" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="289" t="s">
+      <c r="B22" s="249" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="290"/>
+      <c r="C22" s="250"/>
       <c r="D22" s="145" t="s">
         <v>121</v>
       </c>
@@ -20381,52 +20381,52 @@
       <c r="AA29"/>
     </row>
     <row r="30" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="356" t="s">
+      <c r="B30" s="368" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="356"/>
-      <c r="D30" s="353" t="s">
+      <c r="C30" s="368"/>
+      <c r="D30" s="365" t="s">
         <v>644</v>
       </c>
-      <c r="E30" s="353"/>
-      <c r="F30" s="353"/>
-      <c r="G30" s="353"/>
-      <c r="H30" s="353" t="s">
+      <c r="E30" s="365"/>
+      <c r="F30" s="365"/>
+      <c r="G30" s="365"/>
+      <c r="H30" s="365" t="s">
         <v>17</v>
       </c>
-      <c r="I30" s="353"/>
-      <c r="J30" s="353"/>
-      <c r="K30" s="353"/>
-      <c r="L30" s="353" t="s">
+      <c r="I30" s="365"/>
+      <c r="J30" s="365"/>
+      <c r="K30" s="365"/>
+      <c r="L30" s="365" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="353"/>
-      <c r="N30" s="353"/>
-      <c r="O30" s="353"/>
-      <c r="P30" s="353" t="s">
+      <c r="M30" s="365"/>
+      <c r="N30" s="365"/>
+      <c r="O30" s="365"/>
+      <c r="P30" s="365" t="s">
         <v>13</v>
       </c>
-      <c r="Q30" s="353"/>
-      <c r="R30" s="353"/>
-      <c r="S30" s="353"/>
-      <c r="T30" s="353" t="s">
+      <c r="Q30" s="365"/>
+      <c r="R30" s="365"/>
+      <c r="S30" s="365"/>
+      <c r="T30" s="365" t="s">
         <v>20</v>
       </c>
-      <c r="U30" s="353"/>
-      <c r="V30" s="353"/>
-      <c r="W30" s="353"/>
-      <c r="X30" s="353" t="s">
+      <c r="U30" s="365"/>
+      <c r="V30" s="365"/>
+      <c r="W30" s="365"/>
+      <c r="X30" s="365" t="s">
         <v>553</v>
       </c>
-      <c r="Y30" s="353"/>
-      <c r="Z30" s="353"/>
-      <c r="AA30" s="353"/>
+      <c r="Y30" s="365"/>
+      <c r="Z30" s="365"/>
+      <c r="AA30" s="365"/>
     </row>
     <row r="31" spans="2:37" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="354" t="s">
+      <c r="B31" s="366" t="s">
         <v>632</v>
       </c>
-      <c r="C31" s="355"/>
+      <c r="C31" s="367"/>
       <c r="D31" s="232" t="s">
         <v>641</v>
       </c>
@@ -20501,10 +20501,10 @@
       </c>
     </row>
     <row r="32" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="314" t="s">
+      <c r="B32" s="309" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="314"/>
+      <c r="C32" s="309"/>
       <c r="D32" s="231" t="s">
         <v>234</v>
       </c>
@@ -20543,34 +20543,34 @@
       <c r="AK32" s="190"/>
     </row>
     <row r="33" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="306" t="s">
+      <c r="B33" s="317" t="s">
         <v>646</v>
       </c>
-      <c r="C33" s="307"/>
-      <c r="D33" s="307"/>
-      <c r="E33" s="307"/>
-      <c r="F33" s="307"/>
-      <c r="G33" s="307"/>
-      <c r="H33" s="307"/>
-      <c r="I33" s="307"/>
-      <c r="J33" s="307"/>
-      <c r="K33" s="307"/>
-      <c r="L33" s="307"/>
-      <c r="M33" s="307"/>
-      <c r="N33" s="307"/>
-      <c r="O33" s="307"/>
-      <c r="P33" s="307"/>
-      <c r="Q33" s="307"/>
-      <c r="R33" s="307"/>
-      <c r="S33" s="307"/>
-      <c r="T33" s="307"/>
-      <c r="U33" s="307"/>
-      <c r="V33" s="307"/>
-      <c r="W33" s="307"/>
-      <c r="X33" s="307"/>
-      <c r="Y33" s="307"/>
-      <c r="Z33" s="307"/>
-      <c r="AA33" s="308"/>
+      <c r="C33" s="318"/>
+      <c r="D33" s="318"/>
+      <c r="E33" s="318"/>
+      <c r="F33" s="318"/>
+      <c r="G33" s="318"/>
+      <c r="H33" s="318"/>
+      <c r="I33" s="318"/>
+      <c r="J33" s="318"/>
+      <c r="K33" s="318"/>
+      <c r="L33" s="318"/>
+      <c r="M33" s="318"/>
+      <c r="N33" s="318"/>
+      <c r="O33" s="318"/>
+      <c r="P33" s="318"/>
+      <c r="Q33" s="318"/>
+      <c r="R33" s="318"/>
+      <c r="S33" s="318"/>
+      <c r="T33" s="318"/>
+      <c r="U33" s="318"/>
+      <c r="V33" s="318"/>
+      <c r="W33" s="318"/>
+      <c r="X33" s="318"/>
+      <c r="Y33" s="318"/>
+      <c r="Z33" s="318"/>
+      <c r="AA33" s="319"/>
       <c r="AD33" s="194"/>
       <c r="AE33" s="216" t="s">
         <v>585</v>
@@ -20583,7 +20583,7 @@
       <c r="AK33" s="208"/>
     </row>
     <row r="34" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="316" t="s">
+      <c r="B34" s="303" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="111" t="s">
@@ -20616,10 +20616,10 @@
       <c r="Z34" s="62"/>
       <c r="AA34" s="148"/>
       <c r="AD34" s="194"/>
-      <c r="AE34" s="270" t="s">
+      <c r="AE34" s="261" t="s">
         <v>632</v>
       </c>
-      <c r="AF34" s="271"/>
+      <c r="AF34" s="262"/>
       <c r="AG34" s="151" t="s">
         <v>223</v>
       </c>
@@ -20635,7 +20635,7 @@
       <c r="AK34" s="193"/>
     </row>
     <row r="35" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="316"/>
+      <c r="B35" s="303"/>
       <c r="C35" s="111" t="s">
         <v>61</v>
       </c>
@@ -20666,10 +20666,10 @@
       <c r="Z35" s="62"/>
       <c r="AA35" s="148"/>
       <c r="AD35" s="194"/>
-      <c r="AE35" s="270" t="s">
+      <c r="AE35" s="261" t="s">
         <v>31</v>
       </c>
-      <c r="AF35" s="271"/>
+      <c r="AF35" s="262"/>
       <c r="AG35" s="31"/>
       <c r="AH35" s="89"/>
       <c r="AI35" s="89"/>
@@ -20677,7 +20677,7 @@
       <c r="AK35" s="193"/>
     </row>
     <row r="36" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="316" t="s">
+      <c r="B36" s="303" t="s">
         <v>33</v>
       </c>
       <c r="C36" s="111" t="s">
@@ -20710,18 +20710,18 @@
       <c r="Z36" s="62"/>
       <c r="AA36" s="148"/>
       <c r="AD36" s="194"/>
-      <c r="AE36" s="247" t="s">
+      <c r="AE36" s="263" t="s">
         <v>30</v>
       </c>
-      <c r="AF36" s="247"/>
-      <c r="AG36" s="247"/>
-      <c r="AH36" s="247"/>
-      <c r="AI36" s="247"/>
-      <c r="AJ36" s="247"/>
+      <c r="AF36" s="263"/>
+      <c r="AG36" s="263"/>
+      <c r="AH36" s="263"/>
+      <c r="AI36" s="263"/>
+      <c r="AJ36" s="263"/>
       <c r="AK36" s="193"/>
     </row>
     <row r="37" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="316"/>
+      <c r="B37" s="303"/>
       <c r="C37" s="111" t="s">
         <v>12</v>
       </c>
@@ -20752,7 +20752,7 @@
       <c r="Z37" s="62"/>
       <c r="AA37" s="148"/>
       <c r="AD37" s="194"/>
-      <c r="AE37" s="273" t="s">
+      <c r="AE37" s="241" t="s">
         <v>1</v>
       </c>
       <c r="AF37" s="151" t="s">
@@ -20765,7 +20765,7 @@
       <c r="AK37" s="193"/>
     </row>
     <row r="38" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="316" t="s">
+      <c r="B38" s="303" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="111" t="s">
@@ -20798,7 +20798,7 @@
       <c r="Z38" s="62"/>
       <c r="AA38" s="148"/>
       <c r="AD38" s="194"/>
-      <c r="AE38" s="273"/>
+      <c r="AE38" s="241"/>
       <c r="AF38" s="151" t="s">
         <v>61</v>
       </c>
@@ -20809,7 +20809,7 @@
       <c r="AK38" s="193"/>
     </row>
     <row r="39" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="316"/>
+      <c r="B39" s="303"/>
       <c r="C39" s="111" t="s">
         <v>12</v>
       </c>
@@ -20840,7 +20840,7 @@
       <c r="Z39" s="62"/>
       <c r="AA39" s="148"/>
       <c r="AD39" s="194"/>
-      <c r="AE39" s="273" t="s">
+      <c r="AE39" s="241" t="s">
         <v>624</v>
       </c>
       <c r="AF39" s="151" t="s">
@@ -20853,10 +20853,10 @@
       <c r="AK39" s="193"/>
     </row>
     <row r="40" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="316" t="s">
+      <c r="B40" s="303" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="316"/>
+      <c r="C40" s="303"/>
       <c r="D40" s="2" t="s">
         <v>122</v>
       </c>
@@ -20884,7 +20884,7 @@
       <c r="Z40" s="62"/>
       <c r="AA40" s="148"/>
       <c r="AD40" s="194"/>
-      <c r="AE40" s="273"/>
+      <c r="AE40" s="241"/>
       <c r="AF40" s="151" t="s">
         <v>12</v>
       </c>
@@ -20895,10 +20895,10 @@
       <c r="AK40" s="193"/>
     </row>
     <row r="41" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="316" t="s">
+      <c r="B41" s="303" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="316"/>
+      <c r="C41" s="303"/>
       <c r="D41" s="2" t="s">
         <v>122</v>
       </c>
@@ -20926,7 +20926,7 @@
       <c r="Z41" s="62"/>
       <c r="AA41" s="148"/>
       <c r="AD41" s="194"/>
-      <c r="AE41" s="273" t="s">
+      <c r="AE41" s="241" t="s">
         <v>634</v>
       </c>
       <c r="AF41" s="151" t="s">
@@ -20939,36 +20939,36 @@
       <c r="AK41" s="193"/>
     </row>
     <row r="42" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="306" t="s">
+      <c r="B42" s="317" t="s">
         <v>647</v>
       </c>
-      <c r="C42" s="307"/>
-      <c r="D42" s="307"/>
-      <c r="E42" s="307"/>
-      <c r="F42" s="307"/>
-      <c r="G42" s="307"/>
-      <c r="H42" s="307"/>
-      <c r="I42" s="307"/>
-      <c r="J42" s="307"/>
-      <c r="K42" s="307"/>
-      <c r="L42" s="307"/>
-      <c r="M42" s="307"/>
-      <c r="N42" s="307"/>
-      <c r="O42" s="307"/>
-      <c r="P42" s="307"/>
-      <c r="Q42" s="307"/>
-      <c r="R42" s="307"/>
-      <c r="S42" s="307"/>
-      <c r="T42" s="307"/>
-      <c r="U42" s="307"/>
-      <c r="V42" s="307"/>
-      <c r="W42" s="307"/>
-      <c r="X42" s="307"/>
-      <c r="Y42" s="307"/>
-      <c r="Z42" s="307"/>
-      <c r="AA42" s="308"/>
+      <c r="C42" s="318"/>
+      <c r="D42" s="318"/>
+      <c r="E42" s="318"/>
+      <c r="F42" s="318"/>
+      <c r="G42" s="318"/>
+      <c r="H42" s="318"/>
+      <c r="I42" s="318"/>
+      <c r="J42" s="318"/>
+      <c r="K42" s="318"/>
+      <c r="L42" s="318"/>
+      <c r="M42" s="318"/>
+      <c r="N42" s="318"/>
+      <c r="O42" s="318"/>
+      <c r="P42" s="318"/>
+      <c r="Q42" s="318"/>
+      <c r="R42" s="318"/>
+      <c r="S42" s="318"/>
+      <c r="T42" s="318"/>
+      <c r="U42" s="318"/>
+      <c r="V42" s="318"/>
+      <c r="W42" s="318"/>
+      <c r="X42" s="318"/>
+      <c r="Y42" s="318"/>
+      <c r="Z42" s="318"/>
+      <c r="AA42" s="319"/>
       <c r="AD42" s="194"/>
-      <c r="AE42" s="273"/>
+      <c r="AE42" s="241"/>
       <c r="AF42" s="151" t="s">
         <v>12</v>
       </c>
@@ -20979,10 +20979,10 @@
       <c r="AK42" s="193"/>
     </row>
     <row r="43" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="364" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="357"/>
+      <c r="C43" s="364"/>
       <c r="D43" s="2" t="s">
         <v>135</v>
       </c>
@@ -21010,10 +21010,10 @@
       <c r="Z43" s="62"/>
       <c r="AA43" s="148"/>
       <c r="AD43" s="194"/>
-      <c r="AE43" s="281" t="s">
+      <c r="AE43" s="248" t="s">
         <v>635</v>
       </c>
-      <c r="AF43" s="281"/>
+      <c r="AF43" s="248"/>
       <c r="AG43" s="218"/>
       <c r="AH43" s="218"/>
       <c r="AI43" s="218"/>
@@ -21021,10 +21021,10 @@
       <c r="AK43" s="210"/>
     </row>
     <row r="44" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="357" t="s">
+      <c r="B44" s="364" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="357"/>
+      <c r="C44" s="364"/>
       <c r="D44" s="2" t="s">
         <v>135</v>
       </c>
@@ -21052,10 +21052,10 @@
       <c r="Z44" s="62"/>
       <c r="AA44" s="148"/>
       <c r="AD44" s="194"/>
-      <c r="AE44" s="281" t="s">
+      <c r="AE44" s="248" t="s">
         <v>636</v>
       </c>
-      <c r="AF44" s="281"/>
+      <c r="AF44" s="248"/>
       <c r="AG44" s="218"/>
       <c r="AH44" s="218"/>
       <c r="AI44" s="218"/>
@@ -21063,10 +21063,10 @@
       <c r="AK44" s="210"/>
     </row>
     <row r="45" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="357" t="s">
+      <c r="B45" s="364" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="357"/>
+      <c r="C45" s="364"/>
       <c r="D45" s="2" t="s">
         <v>135</v>
       </c>
@@ -21094,21 +21094,21 @@
       <c r="Z45" s="62"/>
       <c r="AA45" s="148"/>
       <c r="AD45" s="194"/>
-      <c r="AE45" s="285" t="s">
+      <c r="AE45" s="243" t="s">
         <v>107</v>
       </c>
-      <c r="AF45" s="286"/>
-      <c r="AG45" s="286"/>
-      <c r="AH45" s="286"/>
-      <c r="AI45" s="286"/>
-      <c r="AJ45" s="287"/>
+      <c r="AF45" s="244"/>
+      <c r="AG45" s="244"/>
+      <c r="AH45" s="244"/>
+      <c r="AI45" s="244"/>
+      <c r="AJ45" s="245"/>
       <c r="AK45" s="210"/>
     </row>
     <row r="46" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="357" t="s">
+      <c r="B46" s="364" t="s">
         <v>64</v>
       </c>
-      <c r="C46" s="357"/>
+      <c r="C46" s="364"/>
       <c r="D46" s="2" t="s">
         <v>135</v>
       </c>
@@ -21136,10 +21136,10 @@
       <c r="Z46" s="62"/>
       <c r="AA46" s="148"/>
       <c r="AD46" s="194"/>
-      <c r="AE46" s="285" t="s">
+      <c r="AE46" s="243" t="s">
         <v>634</v>
       </c>
-      <c r="AF46" s="287"/>
+      <c r="AF46" s="245"/>
       <c r="AG46" s="218"/>
       <c r="AH46" s="218"/>
       <c r="AI46" s="218"/>
@@ -21147,39 +21147,39 @@
       <c r="AK46" s="210"/>
     </row>
     <row r="47" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="306" t="s">
+      <c r="B47" s="317" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="307"/>
-      <c r="D47" s="307"/>
-      <c r="E47" s="307"/>
-      <c r="F47" s="307"/>
-      <c r="G47" s="307"/>
-      <c r="H47" s="307"/>
-      <c r="I47" s="307"/>
-      <c r="J47" s="307"/>
-      <c r="K47" s="307"/>
-      <c r="L47" s="307"/>
-      <c r="M47" s="307"/>
-      <c r="N47" s="307"/>
-      <c r="O47" s="307"/>
-      <c r="P47" s="307"/>
-      <c r="Q47" s="307"/>
-      <c r="R47" s="307"/>
-      <c r="S47" s="307"/>
-      <c r="T47" s="307"/>
-      <c r="U47" s="307"/>
-      <c r="V47" s="307"/>
-      <c r="W47" s="307"/>
-      <c r="X47" s="307"/>
-      <c r="Y47" s="307"/>
-      <c r="Z47" s="307"/>
-      <c r="AA47" s="308"/>
+      <c r="C47" s="318"/>
+      <c r="D47" s="318"/>
+      <c r="E47" s="318"/>
+      <c r="F47" s="318"/>
+      <c r="G47" s="318"/>
+      <c r="H47" s="318"/>
+      <c r="I47" s="318"/>
+      <c r="J47" s="318"/>
+      <c r="K47" s="318"/>
+      <c r="L47" s="318"/>
+      <c r="M47" s="318"/>
+      <c r="N47" s="318"/>
+      <c r="O47" s="318"/>
+      <c r="P47" s="318"/>
+      <c r="Q47" s="318"/>
+      <c r="R47" s="318"/>
+      <c r="S47" s="318"/>
+      <c r="T47" s="318"/>
+      <c r="U47" s="318"/>
+      <c r="V47" s="318"/>
+      <c r="W47" s="318"/>
+      <c r="X47" s="318"/>
+      <c r="Y47" s="318"/>
+      <c r="Z47" s="318"/>
+      <c r="AA47" s="319"/>
       <c r="AD47" s="194"/>
-      <c r="AE47" s="285" t="s">
+      <c r="AE47" s="243" t="s">
         <v>624</v>
       </c>
-      <c r="AF47" s="287"/>
+      <c r="AF47" s="245"/>
       <c r="AG47" s="218"/>
       <c r="AH47" s="218"/>
       <c r="AI47" s="218"/>
@@ -21187,10 +21187,10 @@
       <c r="AK47" s="193"/>
     </row>
     <row r="48" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="357" t="s">
+      <c r="B48" s="364" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="357"/>
+      <c r="C48" s="364"/>
       <c r="D48" s="2" t="s">
         <v>233</v>
       </c>
@@ -21218,10 +21218,10 @@
       <c r="Z48" s="62"/>
       <c r="AA48" s="148"/>
       <c r="AD48" s="194"/>
-      <c r="AE48" s="285" t="s">
+      <c r="AE48" s="243" t="s">
         <v>635</v>
       </c>
-      <c r="AF48" s="287"/>
+      <c r="AF48" s="245"/>
       <c r="AG48" s="218"/>
       <c r="AH48" s="218"/>
       <c r="AI48" s="218"/>
@@ -21229,10 +21229,10 @@
       <c r="AK48" s="193"/>
     </row>
     <row r="49" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="357" t="s">
+      <c r="B49" s="364" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="357"/>
+      <c r="C49" s="364"/>
       <c r="D49" s="2" t="s">
         <v>233</v>
       </c>
@@ -21260,10 +21260,10 @@
       <c r="Z49" s="62"/>
       <c r="AA49" s="148"/>
       <c r="AD49" s="194"/>
-      <c r="AE49" s="285" t="s">
+      <c r="AE49" s="243" t="s">
         <v>637</v>
       </c>
-      <c r="AF49" s="287"/>
+      <c r="AF49" s="245"/>
       <c r="AG49" s="218"/>
       <c r="AH49" s="218"/>
       <c r="AI49" s="218"/>
@@ -21271,10 +21271,10 @@
       <c r="AK49" s="193"/>
     </row>
     <row r="50" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="364" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="357"/>
+      <c r="C50" s="364"/>
       <c r="D50" s="2" t="s">
         <v>121</v>
       </c>
@@ -21302,22 +21302,22 @@
       <c r="Z50" s="62"/>
       <c r="AA50" s="148"/>
       <c r="AD50" s="194"/>
-      <c r="AE50" s="285" t="s">
+      <c r="AE50" s="243" t="s">
         <v>65</v>
       </c>
-      <c r="AF50" s="286"/>
-      <c r="AG50" s="286"/>
-      <c r="AH50" s="286"/>
-      <c r="AI50" s="286"/>
-      <c r="AJ50" s="287"/>
+      <c r="AF50" s="244"/>
+      <c r="AG50" s="244"/>
+      <c r="AH50" s="244"/>
+      <c r="AI50" s="244"/>
+      <c r="AJ50" s="245"/>
       <c r="AK50" s="193"/>
     </row>
     <row r="51" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AD51" s="194"/>
-      <c r="AE51" s="285" t="s">
+      <c r="AE51" s="243" t="s">
         <v>639</v>
       </c>
-      <c r="AF51" s="287"/>
+      <c r="AF51" s="245"/>
       <c r="AG51" s="218"/>
       <c r="AH51" s="218"/>
       <c r="AI51" s="218"/>
@@ -21326,10 +21326,10 @@
     </row>
     <row r="52" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AD52" s="194"/>
-      <c r="AE52" s="285" t="s">
+      <c r="AE52" s="243" t="s">
         <v>638</v>
       </c>
-      <c r="AF52" s="287"/>
+      <c r="AF52" s="245"/>
       <c r="AG52" s="218"/>
       <c r="AH52" s="218"/>
       <c r="AI52" s="218"/>
@@ -21338,10 +21338,10 @@
     </row>
     <row r="53" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AD53" s="194"/>
-      <c r="AE53" s="285" t="s">
+      <c r="AE53" s="243" t="s">
         <v>640</v>
       </c>
-      <c r="AF53" s="287"/>
+      <c r="AF53" s="245"/>
       <c r="AG53" s="218"/>
       <c r="AH53" s="218"/>
       <c r="AI53" s="218"/>
@@ -21370,16 +21370,55 @@
     </row>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="P30:S30"/>
+    <mergeCell ref="T30:W30"/>
+    <mergeCell ref="X30:AA30"/>
+    <mergeCell ref="B42:AA42"/>
+    <mergeCell ref="B33:AA33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B47:AA47"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="AE50:AJ50"/>
+    <mergeCell ref="AE46:AF46"/>
+    <mergeCell ref="AE51:AF51"/>
+    <mergeCell ref="AE52:AF52"/>
+    <mergeCell ref="AE53:AF53"/>
+    <mergeCell ref="AE47:AF47"/>
+    <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AE49:AF49"/>
+    <mergeCell ref="AE44:AF44"/>
+    <mergeCell ref="AE45:AJ45"/>
+    <mergeCell ref="AE41:AE42"/>
+    <mergeCell ref="AE43:AF43"/>
+    <mergeCell ref="AE34:AF34"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AE36:AJ36"/>
+    <mergeCell ref="AE37:AE38"/>
+    <mergeCell ref="AE39:AE40"/>
+    <mergeCell ref="V2:AA2"/>
+    <mergeCell ref="V5:AA5"/>
+    <mergeCell ref="V14:AA14"/>
+    <mergeCell ref="V19:AA19"/>
+    <mergeCell ref="P2:U2"/>
+    <mergeCell ref="P5:U5"/>
+    <mergeCell ref="P14:U14"/>
+    <mergeCell ref="P19:U19"/>
     <mergeCell ref="J2:O2"/>
     <mergeCell ref="J5:O5"/>
     <mergeCell ref="J19:O19"/>
@@ -21396,55 +21435,16 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="V2:AA2"/>
-    <mergeCell ref="V5:AA5"/>
-    <mergeCell ref="V14:AA14"/>
-    <mergeCell ref="V19:AA19"/>
-    <mergeCell ref="P2:U2"/>
-    <mergeCell ref="P5:U5"/>
-    <mergeCell ref="P14:U14"/>
-    <mergeCell ref="P19:U19"/>
-    <mergeCell ref="AE44:AF44"/>
-    <mergeCell ref="AE45:AJ45"/>
-    <mergeCell ref="AE41:AE42"/>
-    <mergeCell ref="AE43:AF43"/>
-    <mergeCell ref="AE34:AF34"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AE36:AJ36"/>
-    <mergeCell ref="AE37:AE38"/>
-    <mergeCell ref="AE39:AE40"/>
-    <mergeCell ref="AE50:AJ50"/>
-    <mergeCell ref="AE46:AF46"/>
-    <mergeCell ref="AE51:AF51"/>
-    <mergeCell ref="AE52:AF52"/>
-    <mergeCell ref="AE53:AF53"/>
-    <mergeCell ref="AE47:AF47"/>
-    <mergeCell ref="AE48:AF48"/>
-    <mergeCell ref="AE49:AF49"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B47:AA47"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="P30:S30"/>
-    <mergeCell ref="T30:W30"/>
-    <mergeCell ref="X30:AA30"/>
-    <mergeCell ref="B42:AA42"/>
-    <mergeCell ref="B33:AA33"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21476,15 +21476,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="374" t="s">
+      <c r="B2" s="373" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="374"/>
-      <c r="D2" s="374"/>
-      <c r="E2" s="374"/>
-      <c r="F2" s="374"/>
-      <c r="G2" s="374"/>
-      <c r="H2" s="374"/>
+      <c r="C2" s="373"/>
+      <c r="D2" s="373"/>
+      <c r="E2" s="373"/>
+      <c r="F2" s="373"/>
+      <c r="G2" s="373"/>
+      <c r="H2" s="373"/>
     </row>
     <row r="3" spans="2:28" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -21510,15 +21510,15 @@
       </c>
     </row>
     <row r="4" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="289" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="250"/>
-      <c r="D4" s="250"/>
-      <c r="E4" s="250"/>
-      <c r="F4" s="250"/>
-      <c r="G4" s="250"/>
-      <c r="H4" s="251"/>
+      <c r="C4" s="256"/>
+      <c r="D4" s="256"/>
+      <c r="E4" s="256"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="290"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
@@ -21570,10 +21570,10 @@
       <c r="L6"/>
       <c r="M6"/>
       <c r="Y6" s="194"/>
-      <c r="Z6" s="285" t="s">
+      <c r="Z6" s="243" t="s">
         <v>663</v>
       </c>
-      <c r="AA6" s="287"/>
+      <c r="AA6" s="245"/>
       <c r="AB6" s="193"/>
     </row>
     <row r="7" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -21669,15 +21669,15 @@
       <c r="AB10" s="193"/>
     </row>
     <row r="11" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="249" t="s">
+      <c r="B11" s="289" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="373"/>
-      <c r="D11" s="373"/>
-      <c r="E11" s="373"/>
-      <c r="F11" s="373"/>
-      <c r="G11" s="373"/>
-      <c r="H11" s="333"/>
+      <c r="C11" s="378"/>
+      <c r="D11" s="378"/>
+      <c r="E11" s="378"/>
+      <c r="F11" s="378"/>
+      <c r="G11" s="378"/>
+      <c r="H11" s="344"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11"/>
@@ -21729,22 +21729,22 @@
       <c r="L13"/>
       <c r="M13"/>
       <c r="Y13" s="194"/>
-      <c r="Z13" s="285" t="s">
+      <c r="Z13" s="243" t="s">
         <v>107</v>
       </c>
-      <c r="AA13" s="287"/>
+      <c r="AA13" s="245"/>
       <c r="AB13" s="193"/>
     </row>
     <row r="14" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="249" t="s">
+      <c r="B14" s="289" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="373"/>
-      <c r="D14" s="373"/>
-      <c r="E14" s="373"/>
-      <c r="F14" s="373"/>
-      <c r="G14" s="373"/>
-      <c r="H14" s="333"/>
+      <c r="C14" s="378"/>
+      <c r="D14" s="378"/>
+      <c r="E14" s="378"/>
+      <c r="F14" s="378"/>
+      <c r="G14" s="378"/>
+      <c r="H14" s="344"/>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14"/>
@@ -21803,15 +21803,15 @@
       <c r="AB16" s="210"/>
     </row>
     <row r="17" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="249" t="s">
+      <c r="B17" s="289" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="373"/>
-      <c r="D17" s="373"/>
-      <c r="E17" s="373"/>
-      <c r="F17" s="373"/>
-      <c r="G17" s="373"/>
-      <c r="H17" s="333"/>
+      <c r="C17" s="378"/>
+      <c r="D17" s="378"/>
+      <c r="E17" s="378"/>
+      <c r="F17" s="378"/>
+      <c r="G17" s="378"/>
+      <c r="H17" s="344"/>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17"/>
@@ -21863,10 +21863,10 @@
       <c r="L19"/>
       <c r="M19"/>
       <c r="Y19" s="194"/>
-      <c r="Z19" s="285" t="s">
+      <c r="Z19" s="243" t="s">
         <v>50</v>
       </c>
-      <c r="AA19" s="287"/>
+      <c r="AA19" s="245"/>
       <c r="AB19" s="193"/>
     </row>
     <row r="20" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -21958,16 +21958,16 @@
       <c r="AB24" s="193"/>
     </row>
     <row r="25" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J25" s="374" t="s">
+      <c r="J25" s="373" t="s">
         <v>90</v>
       </c>
-      <c r="K25" s="374"/>
-      <c r="L25" s="374"/>
-      <c r="M25" s="374"/>
-      <c r="N25" s="374"/>
-      <c r="O25" s="374"/>
-      <c r="P25" s="374"/>
-      <c r="Q25" s="374"/>
+      <c r="K25" s="373"/>
+      <c r="L25" s="373"/>
+      <c r="M25" s="373"/>
+      <c r="N25" s="373"/>
+      <c r="O25" s="373"/>
+      <c r="P25" s="373"/>
+      <c r="Q25" s="373"/>
       <c r="Y25" s="194"/>
       <c r="Z25" s="230" t="s">
         <v>662</v>
@@ -21976,10 +21976,10 @@
       <c r="AB25" s="193"/>
     </row>
     <row r="26" spans="2:28" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J26" s="377" t="s">
+      <c r="J26" s="374" t="s">
         <v>40</v>
       </c>
-      <c r="K26" s="378"/>
+      <c r="K26" s="375"/>
       <c r="L26" s="184" t="s">
         <v>117</v>
       </c>
@@ -22004,26 +22004,26 @@
       <c r="AB26" s="193"/>
     </row>
     <row r="27" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J27" s="249" t="s">
+      <c r="J27" s="289" t="s">
         <v>30</v>
       </c>
-      <c r="K27" s="250"/>
-      <c r="L27" s="250"/>
-      <c r="M27" s="250"/>
-      <c r="N27" s="250"/>
-      <c r="O27" s="250"/>
-      <c r="P27" s="250"/>
-      <c r="Q27" s="251"/>
+      <c r="K27" s="256"/>
+      <c r="L27" s="256"/>
+      <c r="M27" s="256"/>
+      <c r="N27" s="256"/>
+      <c r="O27" s="256"/>
+      <c r="P27" s="256"/>
+      <c r="Q27" s="290"/>
       <c r="Y27" s="196"/>
       <c r="Z27" s="197"/>
       <c r="AA27" s="223"/>
       <c r="AB27" s="198"/>
     </row>
     <row r="28" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J28" s="379" t="s">
+      <c r="J28" s="376" t="s">
         <v>91</v>
       </c>
-      <c r="K28" s="380"/>
+      <c r="K28" s="377"/>
       <c r="L28" s="36"/>
       <c r="M28" s="36"/>
       <c r="N28" s="36"/>
@@ -22032,7 +22032,7 @@
       <c r="Q28" s="37"/>
     </row>
     <row r="29" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J29" s="371" t="s">
+      <c r="J29" s="370" t="s">
         <v>92</v>
       </c>
       <c r="K29" s="34" t="s">
@@ -22046,7 +22046,7 @@
       <c r="Q29" s="45"/>
     </row>
     <row r="30" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J30" s="376"/>
+      <c r="J30" s="371"/>
       <c r="K30" s="34" t="s">
         <v>94</v>
       </c>
@@ -22084,7 +22084,7 @@
       <c r="W31" s="208"/>
     </row>
     <row r="32" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J32" s="371" t="s">
+      <c r="J32" s="370" t="s">
         <v>100</v>
       </c>
       <c r="K32" s="34" t="s">
@@ -22097,15 +22097,15 @@
       <c r="P32" s="40"/>
       <c r="Q32" s="45"/>
       <c r="S32" s="194"/>
-      <c r="T32" s="247" t="s">
+      <c r="T32" s="263" t="s">
         <v>663</v>
       </c>
-      <c r="U32" s="247"/>
-      <c r="V32" s="247"/>
+      <c r="U32" s="263"/>
+      <c r="V32" s="263"/>
       <c r="W32" s="193"/>
     </row>
     <row r="33" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J33" s="376"/>
+      <c r="J33" s="371"/>
       <c r="K33" s="34" t="s">
         <v>93</v>
       </c>
@@ -22124,7 +22124,7 @@
       <c r="W33" s="193"/>
     </row>
     <row r="34" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J34" s="376"/>
+      <c r="J34" s="371"/>
       <c r="K34" s="34" t="s">
         <v>97</v>
       </c>
@@ -22166,7 +22166,7 @@
       <c r="W35" s="193"/>
     </row>
     <row r="36" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J36" s="371" t="s">
+      <c r="J36" s="370" t="s">
         <v>319</v>
       </c>
       <c r="K36" s="34" t="s">
@@ -22187,7 +22187,7 @@
       <c r="W36" s="193"/>
     </row>
     <row r="37" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J37" s="376"/>
+      <c r="J37" s="371"/>
       <c r="K37" s="34" t="s">
         <v>93</v>
       </c>
@@ -22206,7 +22206,7 @@
       <c r="W37" s="193"/>
     </row>
     <row r="38" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J38" s="376"/>
+      <c r="J38" s="371"/>
       <c r="K38" s="34" t="s">
         <v>94</v>
       </c>
@@ -22244,7 +22244,7 @@
       <c r="W39" s="193"/>
     </row>
     <row r="40" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J40" s="371" t="s">
+      <c r="J40" s="370" t="s">
         <v>99</v>
       </c>
       <c r="K40" s="34" t="s">
@@ -22267,7 +22267,7 @@
       <c r="X40"/>
     </row>
     <row r="41" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J41" s="376"/>
+      <c r="J41" s="371"/>
       <c r="K41" s="34" t="s">
         <v>93</v>
       </c>
@@ -22288,7 +22288,7 @@
       <c r="X41"/>
     </row>
     <row r="42" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J42" s="376"/>
+      <c r="J42" s="371"/>
       <c r="K42" s="34" t="s">
         <v>97</v>
       </c>
@@ -22309,7 +22309,7 @@
       <c r="X42"/>
     </row>
     <row r="43" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J43" s="376"/>
+      <c r="J43" s="371"/>
       <c r="K43" s="102" t="s">
         <v>98</v>
       </c>
@@ -22321,25 +22321,25 @@
       <c r="Q43" s="37"/>
       <c r="R43"/>
       <c r="S43" s="194"/>
-      <c r="T43" s="247" t="s">
+      <c r="T43" s="263" t="s">
         <v>107</v>
       </c>
-      <c r="U43" s="247"/>
+      <c r="U43" s="263"/>
       <c r="V43" s="235"/>
       <c r="W43" s="193"/>
       <c r="X43"/>
     </row>
     <row r="44" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J44" s="375" t="s">
+      <c r="J44" s="369" t="s">
         <v>107</v>
       </c>
-      <c r="K44" s="375"/>
-      <c r="L44" s="375"/>
-      <c r="M44" s="375"/>
-      <c r="N44" s="375"/>
-      <c r="O44" s="375"/>
-      <c r="P44" s="375"/>
-      <c r="Q44" s="375"/>
+      <c r="K44" s="369"/>
+      <c r="L44" s="369"/>
+      <c r="M44" s="369"/>
+      <c r="N44" s="369"/>
+      <c r="O44" s="369"/>
+      <c r="P44" s="369"/>
+      <c r="Q44" s="369"/>
       <c r="S44" s="194"/>
       <c r="T44" s="227" t="s">
         <v>649</v>
@@ -22349,10 +22349,10 @@
       <c r="W44" s="193"/>
     </row>
     <row r="45" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J45" s="316" t="s">
+      <c r="J45" s="303" t="s">
         <v>42</v>
       </c>
-      <c r="K45" s="316"/>
+      <c r="K45" s="303"/>
       <c r="L45" s="62"/>
       <c r="M45" s="62"/>
       <c r="N45" s="62"/>
@@ -22368,10 +22368,10 @@
       <c r="W45" s="193"/>
     </row>
     <row r="46" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J46" s="369" t="s">
+      <c r="J46" s="379" t="s">
         <v>314</v>
       </c>
-      <c r="K46" s="370"/>
+      <c r="K46" s="380"/>
       <c r="L46" s="62"/>
       <c r="M46" s="62"/>
       <c r="N46" s="62"/>
@@ -22387,10 +22387,10 @@
       <c r="W46" s="193"/>
     </row>
     <row r="47" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J47" s="369" t="s">
+      <c r="J47" s="379" t="s">
         <v>322</v>
       </c>
-      <c r="K47" s="370"/>
+      <c r="K47" s="380"/>
       <c r="L47" s="62"/>
       <c r="M47" s="62"/>
       <c r="N47" s="62"/>
@@ -22406,10 +22406,10 @@
       <c r="W47" s="193"/>
     </row>
     <row r="48" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J48" s="369" t="s">
+      <c r="J48" s="379" t="s">
         <v>321</v>
       </c>
-      <c r="K48" s="370"/>
+      <c r="K48" s="380"/>
       <c r="L48" s="62"/>
       <c r="M48" s="62"/>
       <c r="N48" s="62"/>
@@ -22425,10 +22425,10 @@
       <c r="W48" s="193"/>
     </row>
     <row r="49" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J49" s="369" t="s">
+      <c r="J49" s="379" t="s">
         <v>320</v>
       </c>
-      <c r="K49" s="370"/>
+      <c r="K49" s="380"/>
       <c r="L49" s="62"/>
       <c r="M49" s="62"/>
       <c r="N49" s="62"/>
@@ -22444,7 +22444,7 @@
       <c r="W49" s="193"/>
     </row>
     <row r="50" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J50" s="371" t="s">
+      <c r="J50" s="370" t="s">
         <v>37</v>
       </c>
       <c r="K50" s="111" t="s">
@@ -22484,10 +22484,10 @@
       <c r="W51" s="193"/>
     </row>
     <row r="52" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J52" s="369" t="s">
+      <c r="J52" s="379" t="s">
         <v>64</v>
       </c>
-      <c r="K52" s="370"/>
+      <c r="K52" s="380"/>
       <c r="L52" s="62"/>
       <c r="M52" s="62"/>
       <c r="N52" s="62"/>
@@ -22503,10 +22503,10 @@
       <c r="W52" s="193"/>
     </row>
     <row r="53" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J53" s="369" t="s">
+      <c r="J53" s="379" t="s">
         <v>10</v>
       </c>
-      <c r="K53" s="370"/>
+      <c r="K53" s="380"/>
       <c r="L53" s="62"/>
       <c r="M53" s="62"/>
       <c r="N53" s="62"/>
@@ -22522,10 +22522,10 @@
       <c r="W53" s="193"/>
     </row>
     <row r="54" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J54" s="369" t="s">
+      <c r="J54" s="379" t="s">
         <v>315</v>
       </c>
-      <c r="K54" s="370"/>
+      <c r="K54" s="380"/>
       <c r="L54" s="62"/>
       <c r="M54" s="62"/>
       <c r="N54" s="62"/>
@@ -22541,10 +22541,10 @@
       <c r="W54" s="193"/>
     </row>
     <row r="55" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J55" s="369" t="s">
+      <c r="J55" s="379" t="s">
         <v>316</v>
       </c>
-      <c r="K55" s="370"/>
+      <c r="K55" s="380"/>
       <c r="L55" s="62"/>
       <c r="M55" s="62"/>
       <c r="N55" s="62"/>
@@ -22566,20 +22566,11 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="J44:Q44"/>
-    <mergeCell ref="J32:J35"/>
-    <mergeCell ref="J36:J39"/>
-    <mergeCell ref="J40:J43"/>
-    <mergeCell ref="J25:Q25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:Q27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:J31"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="T32:V32"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="Z19:AA19"/>
     <mergeCell ref="J55:K55"/>
     <mergeCell ref="J49:K49"/>
     <mergeCell ref="J48:K48"/>
@@ -22590,11 +22581,20 @@
     <mergeCell ref="J53:K53"/>
     <mergeCell ref="J52:K52"/>
     <mergeCell ref="J54:K54"/>
-    <mergeCell ref="T32:V32"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="J44:Q44"/>
+    <mergeCell ref="J32:J35"/>
+    <mergeCell ref="J36:J39"/>
+    <mergeCell ref="J40:J43"/>
+    <mergeCell ref="J25:Q25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:Q27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:J31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22627,22 +22627,22 @@
   <sheetData>
     <row r="1" spans="2:20" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="258" t="s">
+      <c r="B2" s="278" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="258"/>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="258"/>
+      <c r="C2" s="278"/>
+      <c r="D2" s="278"/>
+      <c r="E2" s="278"/>
+      <c r="F2" s="278"/>
+      <c r="G2" s="278"/>
+      <c r="H2" s="278"/>
+      <c r="I2" s="278"/>
     </row>
     <row r="3" spans="2:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="377" t="s">
+      <c r="B3" s="374" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="378"/>
+      <c r="C3" s="375"/>
       <c r="D3" s="183" t="s">
         <v>117</v>
       </c>
@@ -22663,16 +22663,16 @@
       </c>
     </row>
     <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="249" t="s">
+      <c r="B4" s="289" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="250"/>
-      <c r="D4" s="250"/>
-      <c r="E4" s="250"/>
-      <c r="F4" s="250"/>
-      <c r="G4" s="250"/>
-      <c r="H4" s="250"/>
-      <c r="I4" s="251"/>
+      <c r="C4" s="256"/>
+      <c r="D4" s="256"/>
+      <c r="E4" s="256"/>
+      <c r="F4" s="256"/>
+      <c r="G4" s="256"/>
+      <c r="H4" s="256"/>
+      <c r="I4" s="290"/>
       <c r="L4" s="225"/>
       <c r="M4" s="215" t="s">
         <v>686</v>
@@ -22687,10 +22687,10 @@
       <c r="T4" s="190"/>
     </row>
     <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="379" t="s">
+      <c r="B5" s="376" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="380"/>
+      <c r="C5" s="377"/>
       <c r="D5" s="21"/>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
@@ -22711,10 +22711,10 @@
       <c r="T5" s="208"/>
     </row>
     <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="379" t="s">
+      <c r="B6" s="376" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="380"/>
+      <c r="C6" s="377"/>
       <c r="D6" s="21"/>
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
@@ -22722,16 +22722,16 @@
       <c r="H6" s="21"/>
       <c r="I6" s="32"/>
       <c r="L6" s="194"/>
-      <c r="M6" s="247" t="s">
+      <c r="M6" s="263" t="s">
         <v>107</v>
       </c>
-      <c r="N6" s="247"/>
+      <c r="N6" s="263"/>
       <c r="O6" s="193"/>
       <c r="Q6" s="194"/>
-      <c r="R6" s="247" t="s">
+      <c r="R6" s="263" t="s">
         <v>107</v>
       </c>
-      <c r="S6" s="247"/>
+      <c r="S6" s="263"/>
       <c r="T6" s="193"/>
     </row>
     <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -22759,10 +22759,10 @@
       <c r="T7" s="193"/>
     </row>
     <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="379" t="s">
+      <c r="B8" s="376" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="380"/>
+      <c r="C8" s="377"/>
       <c r="D8" s="21"/>
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
@@ -22783,16 +22783,16 @@
       <c r="T8" s="193"/>
     </row>
     <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="249" t="s">
+      <c r="B9" s="289" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="250"/>
-      <c r="D9" s="250"/>
-      <c r="E9" s="250"/>
-      <c r="F9" s="250"/>
-      <c r="G9" s="250"/>
-      <c r="H9" s="250"/>
-      <c r="I9" s="251"/>
+      <c r="C9" s="256"/>
+      <c r="D9" s="256"/>
+      <c r="E9" s="256"/>
+      <c r="F9" s="256"/>
+      <c r="G9" s="256"/>
+      <c r="H9" s="256"/>
+      <c r="I9" s="290"/>
       <c r="L9" s="194"/>
       <c r="M9" s="227" t="s">
         <v>634</v>
@@ -22807,7 +22807,7 @@
       <c r="T9" s="193"/>
     </row>
     <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="389" t="s">
+      <c r="B10" s="383" t="s">
         <v>73</v>
       </c>
       <c r="C10" s="35" t="s">
@@ -22833,7 +22833,7 @@
       <c r="T10" s="193"/>
     </row>
     <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="390"/>
+      <c r="B11" s="384"/>
       <c r="C11" s="35" t="s">
         <v>12</v>
       </c>
@@ -22844,20 +22844,20 @@
       <c r="H11" s="19"/>
       <c r="I11" s="24"/>
       <c r="L11" s="194"/>
-      <c r="M11" s="247" t="s">
+      <c r="M11" s="263" t="s">
         <v>663</v>
       </c>
-      <c r="N11" s="247"/>
+      <c r="N11" s="263"/>
       <c r="O11" s="193"/>
       <c r="Q11" s="194"/>
-      <c r="R11" s="247" t="s">
+      <c r="R11" s="263" t="s">
         <v>663</v>
       </c>
-      <c r="S11" s="247"/>
+      <c r="S11" s="263"/>
       <c r="T11" s="193"/>
     </row>
     <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="389" t="s">
+      <c r="B12" s="383" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="35" t="s">
@@ -22883,7 +22883,7 @@
       <c r="T12" s="193"/>
     </row>
     <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="390"/>
+      <c r="B13" s="384"/>
       <c r="C13" s="35" t="s">
         <v>12</v>
       </c>
@@ -22956,16 +22956,16 @@
     </row>
     <row r="17" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
-      <c r="B17" s="258" t="s">
+      <c r="B17" s="278" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="258"/>
-      <c r="D17" s="258"/>
-      <c r="E17" s="258"/>
-      <c r="F17" s="258"/>
-      <c r="G17" s="258"/>
-      <c r="H17" s="258"/>
-      <c r="I17" s="258"/>
+      <c r="C17" s="278"/>
+      <c r="D17" s="278"/>
+      <c r="E17" s="278"/>
+      <c r="F17" s="278"/>
+      <c r="G17" s="278"/>
+      <c r="H17" s="278"/>
+      <c r="I17" s="278"/>
       <c r="K17"/>
       <c r="L17" s="238"/>
       <c r="M17" s="239"/>
@@ -22979,10 +22979,10 @@
     </row>
     <row r="18" spans="1:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
-      <c r="B18" s="377" t="s">
+      <c r="B18" s="374" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="378"/>
+      <c r="C18" s="375"/>
       <c r="D18" s="183" t="s">
         <v>117</v>
       </c>
@@ -23013,16 +23013,16 @@
     </row>
     <row r="19" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
-      <c r="B19" s="249" t="s">
+      <c r="B19" s="289" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="250"/>
-      <c r="D19" s="250"/>
-      <c r="E19" s="250"/>
-      <c r="F19" s="250"/>
-      <c r="G19" s="250"/>
-      <c r="H19" s="250"/>
-      <c r="I19" s="251"/>
+      <c r="C19" s="256"/>
+      <c r="D19" s="256"/>
+      <c r="E19" s="256"/>
+      <c r="F19" s="256"/>
+      <c r="G19" s="256"/>
+      <c r="H19" s="256"/>
+      <c r="I19" s="290"/>
       <c r="K19"/>
       <c r="L19"/>
       <c r="M19"/>
@@ -23035,10 +23035,10 @@
     </row>
     <row r="20" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
-      <c r="B20" s="379" t="s">
+      <c r="B20" s="376" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="380"/>
+      <c r="C20" s="377"/>
       <c r="D20" s="21"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
@@ -23057,10 +23057,10 @@
     </row>
     <row r="21" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
-      <c r="B21" s="379" t="s">
+      <c r="B21" s="376" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="380"/>
+      <c r="C21" s="377"/>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
@@ -23101,10 +23101,10 @@
     </row>
     <row r="23" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
-      <c r="B23" s="384" t="s">
+      <c r="B23" s="387" t="s">
         <v>244</v>
       </c>
-      <c r="C23" s="393"/>
+      <c r="C23" s="388"/>
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
@@ -23123,16 +23123,16 @@
     </row>
     <row r="24" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
-      <c r="B24" s="249" t="s">
+      <c r="B24" s="289" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="250"/>
-      <c r="D24" s="250"/>
-      <c r="E24" s="250"/>
-      <c r="F24" s="250"/>
-      <c r="G24" s="250"/>
-      <c r="H24" s="250"/>
-      <c r="I24" s="251"/>
+      <c r="C24" s="256"/>
+      <c r="D24" s="256"/>
+      <c r="E24" s="256"/>
+      <c r="F24" s="256"/>
+      <c r="G24" s="256"/>
+      <c r="H24" s="256"/>
+      <c r="I24" s="290"/>
       <c r="K24"/>
       <c r="L24"/>
       <c r="M24"/>
@@ -23145,10 +23145,10 @@
     </row>
     <row r="25" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
-      <c r="B25" s="391" t="s">
+      <c r="B25" s="385" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="392"/>
+      <c r="C25" s="386"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
@@ -23167,10 +23167,10 @@
     </row>
     <row r="26" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
-      <c r="B26" s="391" t="s">
+      <c r="B26" s="385" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="392"/>
+      <c r="C26" s="386"/>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
@@ -23189,10 +23189,10 @@
     </row>
     <row r="27" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
-      <c r="B27" s="391" t="s">
+      <c r="B27" s="385" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="392"/>
+      <c r="C27" s="386"/>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
@@ -23211,8 +23211,8 @@
     </row>
     <row r="28" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
-      <c r="B28" s="387"/>
-      <c r="C28" s="388"/>
+      <c r="B28" s="381"/>
+      <c r="C28" s="382"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="19"/>
@@ -23242,23 +23242,23 @@
       <c r="S29"/>
     </row>
     <row r="30" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="258" t="s">
+      <c r="B30" s="278" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="258"/>
-      <c r="D30" s="258"/>
-      <c r="E30" s="258"/>
-      <c r="F30" s="258"/>
-      <c r="G30" s="258"/>
-      <c r="H30" s="258"/>
-      <c r="I30" s="258"/>
+      <c r="C30" s="278"/>
+      <c r="D30" s="278"/>
+      <c r="E30" s="278"/>
+      <c r="F30" s="278"/>
+      <c r="G30" s="278"/>
+      <c r="H30" s="278"/>
+      <c r="I30" s="278"/>
       <c r="J30"/>
     </row>
     <row r="31" spans="1:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="377" t="s">
+      <c r="B31" s="374" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="378"/>
+      <c r="C31" s="375"/>
       <c r="D31" s="183" t="s">
         <v>117</v>
       </c>
@@ -23280,10 +23280,10 @@
       <c r="J31"/>
     </row>
     <row r="32" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="381" t="s">
+      <c r="B32" s="389" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="382"/>
+      <c r="C32" s="390"/>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -23299,16 +23299,16 @@
       <c r="O32" s="190"/>
     </row>
     <row r="33" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="249" t="s">
+      <c r="B33" s="289" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="250"/>
-      <c r="D33" s="250"/>
-      <c r="E33" s="250"/>
-      <c r="F33" s="250"/>
-      <c r="G33" s="250"/>
-      <c r="H33" s="250"/>
-      <c r="I33" s="251"/>
+      <c r="C33" s="256"/>
+      <c r="D33" s="256"/>
+      <c r="E33" s="256"/>
+      <c r="F33" s="256"/>
+      <c r="G33" s="256"/>
+      <c r="H33" s="256"/>
+      <c r="I33" s="290"/>
       <c r="J33"/>
       <c r="L33" s="194"/>
       <c r="M33" s="216" t="s">
@@ -23318,7 +23318,7 @@
       <c r="O33" s="208"/>
     </row>
     <row r="34" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="357" t="s">
+      <c r="B34" s="364" t="s">
         <v>83</v>
       </c>
       <c r="C34" s="35" t="s">
@@ -23339,7 +23339,7 @@
       <c r="O34" s="193"/>
     </row>
     <row r="35" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="357"/>
+      <c r="B35" s="364"/>
       <c r="C35" s="35" t="s">
         <v>12</v>
       </c>
@@ -23351,14 +23351,14 @@
       <c r="I35" s="24"/>
       <c r="J35"/>
       <c r="L35" s="194"/>
-      <c r="M35" s="285" t="s">
+      <c r="M35" s="243" t="s">
         <v>663</v>
       </c>
-      <c r="N35" s="287"/>
+      <c r="N35" s="245"/>
       <c r="O35" s="193"/>
     </row>
     <row r="36" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="364" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="35" t="s">
@@ -23379,7 +23379,7 @@
       <c r="O36" s="193"/>
     </row>
     <row r="37" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="357"/>
+      <c r="B37" s="364"/>
       <c r="C37" s="35" t="s">
         <v>12</v>
       </c>
@@ -23398,10 +23398,10 @@
       <c r="O37" s="193"/>
     </row>
     <row r="38" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="379" t="s">
+      <c r="B38" s="376" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="380"/>
+      <c r="C38" s="377"/>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
@@ -23417,16 +23417,16 @@
       <c r="O38" s="193"/>
     </row>
     <row r="39" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="386" t="s">
+      <c r="B39" s="391" t="s">
         <v>65</v>
       </c>
-      <c r="C39" s="373"/>
-      <c r="D39" s="250"/>
-      <c r="E39" s="250"/>
-      <c r="F39" s="250"/>
-      <c r="G39" s="250"/>
-      <c r="H39" s="250"/>
-      <c r="I39" s="251"/>
+      <c r="C39" s="378"/>
+      <c r="D39" s="256"/>
+      <c r="E39" s="256"/>
+      <c r="F39" s="256"/>
+      <c r="G39" s="256"/>
+      <c r="H39" s="256"/>
+      <c r="I39" s="290"/>
       <c r="J39"/>
       <c r="L39" s="194"/>
       <c r="M39" s="227" t="s">
@@ -23436,10 +23436,10 @@
       <c r="O39" s="193"/>
     </row>
     <row r="40" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="364" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="357"/>
+      <c r="C40" s="364"/>
       <c r="D40" s="33"/>
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
@@ -23455,10 +23455,10 @@
       <c r="O40" s="193"/>
     </row>
     <row r="41" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="357" t="s">
+      <c r="B41" s="364" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="357"/>
+      <c r="C41" s="364"/>
       <c r="D41" s="33"/>
       <c r="E41" s="19"/>
       <c r="F41" s="19"/>
@@ -23467,17 +23467,17 @@
       <c r="I41" s="24"/>
       <c r="J41"/>
       <c r="L41" s="194"/>
-      <c r="M41" s="285" t="s">
+      <c r="M41" s="243" t="s">
         <v>65</v>
       </c>
-      <c r="N41" s="287"/>
+      <c r="N41" s="245"/>
       <c r="O41" s="193"/>
     </row>
     <row r="42" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="311" t="s">
+      <c r="B42" s="301" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="312"/>
+      <c r="C42" s="302"/>
       <c r="D42" s="33"/>
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
@@ -23493,10 +23493,10 @@
       <c r="O42" s="193"/>
     </row>
     <row r="43" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="364" t="s">
         <v>85</v>
       </c>
-      <c r="C43" s="357"/>
+      <c r="C43" s="364"/>
       <c r="D43" s="33"/>
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
@@ -23555,22 +23555,22 @@
       <c r="J48"/>
     </row>
     <row r="49" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="258" t="s">
+      <c r="B49" s="278" t="s">
         <v>89</v>
       </c>
-      <c r="C49" s="258"/>
-      <c r="D49" s="258"/>
-      <c r="E49" s="258"/>
-      <c r="F49" s="258"/>
-      <c r="G49" s="258"/>
-      <c r="H49" s="258"/>
-      <c r="I49" s="258"/>
+      <c r="C49" s="278"/>
+      <c r="D49" s="278"/>
+      <c r="E49" s="278"/>
+      <c r="F49" s="278"/>
+      <c r="G49" s="278"/>
+      <c r="H49" s="278"/>
+      <c r="I49" s="278"/>
     </row>
     <row r="50" spans="2:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="377" t="s">
+      <c r="B50" s="374" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="378"/>
+      <c r="C50" s="375"/>
       <c r="D50" s="183" t="s">
         <v>117</v>
       </c>
@@ -23591,10 +23591,10 @@
       </c>
     </row>
     <row r="51" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="381" t="s">
+      <c r="B51" s="389" t="s">
         <v>86</v>
       </c>
-      <c r="C51" s="382"/>
+      <c r="C51" s="390"/>
       <c r="D51" s="22"/>
       <c r="E51" s="22"/>
       <c r="F51" s="22"/>
@@ -23603,10 +23603,10 @@
       <c r="I51" s="27"/>
     </row>
     <row r="52" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="379" t="s">
+      <c r="B52" s="376" t="s">
         <v>87</v>
       </c>
-      <c r="C52" s="380"/>
+      <c r="C52" s="377"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
       <c r="F52" s="21"/>
@@ -23615,10 +23615,10 @@
       <c r="I52" s="32"/>
     </row>
     <row r="53" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="379" t="s">
+      <c r="B53" s="376" t="s">
         <v>88</v>
       </c>
-      <c r="C53" s="380"/>
+      <c r="C53" s="377"/>
       <c r="D53" s="25"/>
       <c r="E53" s="25"/>
       <c r="F53" s="25"/>
@@ -23627,22 +23627,22 @@
       <c r="I53" s="26"/>
     </row>
     <row r="55" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="258" t="s">
+      <c r="B55" s="278" t="s">
         <v>308</v>
       </c>
-      <c r="C55" s="258"/>
-      <c r="D55" s="258"/>
-      <c r="E55" s="258"/>
-      <c r="F55" s="258"/>
-      <c r="G55" s="258"/>
-      <c r="H55" s="258"/>
-      <c r="I55" s="258"/>
+      <c r="C55" s="278"/>
+      <c r="D55" s="278"/>
+      <c r="E55" s="278"/>
+      <c r="F55" s="278"/>
+      <c r="G55" s="278"/>
+      <c r="H55" s="278"/>
+      <c r="I55" s="278"/>
     </row>
     <row r="56" spans="2:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="377" t="s">
+      <c r="B56" s="374" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="378"/>
+      <c r="C56" s="375"/>
       <c r="D56" s="183" t="s">
         <v>117</v>
       </c>
@@ -23663,10 +23663,10 @@
       </c>
     </row>
     <row r="57" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="381" t="s">
+      <c r="B57" s="389" t="s">
         <v>309</v>
       </c>
-      <c r="C57" s="382"/>
+      <c r="C57" s="390"/>
       <c r="D57" s="109"/>
       <c r="E57" s="109"/>
       <c r="F57" s="109"/>
@@ -23687,10 +23687,10 @@
       <c r="T57" s="190"/>
     </row>
     <row r="58" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="311" t="s">
+      <c r="B58" s="301" t="s">
         <v>310</v>
       </c>
-      <c r="C58" s="383"/>
+      <c r="C58" s="392"/>
       <c r="D58" s="23"/>
       <c r="E58" s="23"/>
       <c r="F58" s="23"/>
@@ -23711,10 +23711,10 @@
       <c r="T58" s="208"/>
     </row>
     <row r="59" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="384" t="s">
+      <c r="B59" s="387" t="s">
         <v>311</v>
       </c>
-      <c r="C59" s="385"/>
+      <c r="C59" s="393"/>
       <c r="D59" s="23"/>
       <c r="E59" s="23"/>
       <c r="F59" s="23"/>
@@ -23735,10 +23735,10 @@
       <c r="T59" s="193"/>
     </row>
     <row r="60" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="379" t="s">
+      <c r="B60" s="376" t="s">
         <v>312</v>
       </c>
-      <c r="C60" s="380"/>
+      <c r="C60" s="377"/>
       <c r="D60" s="109"/>
       <c r="E60" s="109"/>
       <c r="F60" s="109"/>
@@ -23759,10 +23759,10 @@
       <c r="T60" s="193"/>
     </row>
     <row r="61" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="379" t="s">
+      <c r="B61" s="376" t="s">
         <v>313</v>
       </c>
-      <c r="C61" s="380"/>
+      <c r="C61" s="377"/>
       <c r="D61" s="25"/>
       <c r="E61" s="25"/>
       <c r="F61" s="25"/>
@@ -23820,12 +23820,36 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B4:I4"/>
@@ -23840,36 +23864,12 @@
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B39:I39"/>
-    <mergeCell ref="B55:I55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23890,12 +23890,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="278" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="258"/>
+      <c r="B1" s="278"/>
+      <c r="C1" s="278"/>
+      <c r="D1" s="278"/>
     </row>
     <row r="2" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -23998,13 +23998,13 @@
       <c r="D15" s="43"/>
     </row>
     <row r="16" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F16" s="258" t="s">
+      <c r="F16" s="278" t="s">
         <v>142</v>
       </c>
-      <c r="G16" s="258"/>
-      <c r="H16" s="258"/>
-      <c r="I16" s="258"/>
-      <c r="J16" s="258"/>
+      <c r="G16" s="278"/>
+      <c r="H16" s="278"/>
+      <c r="I16" s="278"/>
+      <c r="J16" s="278"/>
     </row>
     <row r="17" spans="6:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F17" s="3"/>
@@ -24067,23 +24067,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="278" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="258"/>
-      <c r="E1" s="258"/>
-      <c r="F1" s="258"/>
-      <c r="G1" s="258"/>
-      <c r="H1" s="258"/>
-      <c r="I1" s="258"/>
-      <c r="J1" s="258"/>
-      <c r="K1" s="258"/>
-      <c r="L1" s="258"/>
-      <c r="M1" s="258"/>
-      <c r="N1" s="258"/>
-      <c r="O1" s="258"/>
+      <c r="B1" s="278"/>
+      <c r="C1" s="278"/>
+      <c r="D1" s="278"/>
+      <c r="E1" s="278"/>
+      <c r="F1" s="278"/>
+      <c r="G1" s="278"/>
+      <c r="H1" s="278"/>
+      <c r="I1" s="278"/>
+      <c r="J1" s="278"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="278"/>
+      <c r="M1" s="278"/>
+      <c r="N1" s="278"/>
+      <c r="O1" s="278"/>
     </row>
     <row r="2" spans="1:15" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="s">
@@ -24133,7 +24133,7 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="375" t="s">
+      <c r="A3" s="369" t="s">
         <v>150</v>
       </c>
       <c r="B3" s="44" t="s">
@@ -24180,7 +24180,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="375"/>
+      <c r="A4" s="369"/>
       <c r="B4" s="57" t="s">
         <v>22</v>
       </c>
@@ -24225,7 +24225,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="375" t="s">
+      <c r="A5" s="369" t="s">
         <v>151</v>
       </c>
       <c r="B5" s="44" t="s">
@@ -24246,7 +24246,7 @@
       <c r="O5" s="43"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="375"/>
+      <c r="A6" s="369"/>
       <c r="B6" s="57" t="s">
         <v>22</v>
       </c>
@@ -24265,7 +24265,7 @@
       <c r="O6" s="43"/>
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="375" t="s">
+      <c r="A7" s="369" t="s">
         <v>152</v>
       </c>
       <c r="B7" s="44" t="s">
@@ -24286,7 +24286,7 @@
       <c r="O7" s="43"/>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="375"/>
+      <c r="A8" s="369"/>
       <c r="B8" s="57" t="s">
         <v>22</v>
       </c>
@@ -24305,7 +24305,7 @@
       <c r="O8" s="43"/>
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="375" t="s">
+      <c r="A9" s="369" t="s">
         <v>153</v>
       </c>
       <c r="B9" s="44" t="s">
@@ -24326,7 +24326,7 @@
       <c r="O9" s="43"/>
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="375"/>
+      <c r="A10" s="369"/>
       <c r="B10" s="57" t="s">
         <v>22</v>
       </c>
@@ -24345,7 +24345,7 @@
       <c r="O10" s="43"/>
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="375" t="s">
+      <c r="A11" s="369" t="s">
         <v>154</v>
       </c>
       <c r="B11" s="44" t="s">
@@ -24366,7 +24366,7 @@
       <c r="O11" s="43"/>
     </row>
     <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="375"/>
+      <c r="A12" s="369"/>
       <c r="B12" s="57" t="s">
         <v>22</v>
       </c>
@@ -24385,7 +24385,7 @@
       <c r="O12" s="43"/>
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="375" t="s">
+      <c r="A13" s="369" t="s">
         <v>155</v>
       </c>
       <c r="B13" s="44" t="s">
@@ -24406,7 +24406,7 @@
       <c r="O13" s="43"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="375"/>
+      <c r="A14" s="369"/>
       <c r="B14" s="57" t="s">
         <v>22</v>
       </c>
@@ -24425,7 +24425,7 @@
       <c r="O14" s="43"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="375" t="s">
+      <c r="A15" s="369" t="s">
         <v>156</v>
       </c>
       <c r="B15" s="44" t="s">
@@ -24446,7 +24446,7 @@
       <c r="O15" s="43"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="375"/>
+      <c r="A16" s="369"/>
       <c r="B16" s="57" t="s">
         <v>22</v>
       </c>
@@ -24485,7 +24485,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="375" t="s">
+      <c r="A19" s="369" t="s">
         <v>174</v>
       </c>
       <c r="B19" s="44" t="s">
@@ -24505,7 +24505,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="375"/>
+      <c r="A20" s="369"/>
       <c r="B20" s="57" t="s">
         <v>22</v>
       </c>
@@ -24523,7 +24523,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="375" t="s">
+      <c r="A21" s="369" t="s">
         <v>175</v>
       </c>
       <c r="B21" s="44" t="s">
@@ -24535,7 +24535,7 @@
       <c r="F21" s="43"/>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="375"/>
+      <c r="A22" s="369"/>
       <c r="B22" s="57" t="s">
         <v>22</v>
       </c>
@@ -24545,7 +24545,7 @@
       <c r="F22" s="58"/>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="375" t="s">
+      <c r="A23" s="369" t="s">
         <v>173</v>
       </c>
       <c r="B23" s="44" t="s">
@@ -24557,7 +24557,7 @@
       <c r="F23" s="43"/>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="375"/>
+      <c r="A24" s="369"/>
       <c r="B24" s="57" t="s">
         <v>22</v>
       </c>
@@ -24593,7 +24593,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="375" t="s">
+      <c r="A27" s="369" t="s">
         <v>182</v>
       </c>
       <c r="B27" s="44" t="s">
@@ -24619,7 +24619,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="375"/>
+      <c r="A28" s="369"/>
       <c r="B28" s="57" t="s">
         <v>22</v>
       </c>
@@ -24643,7 +24643,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="375" t="s">
+      <c r="A29" s="369" t="s">
         <v>183</v>
       </c>
       <c r="B29" s="44" t="s">
@@ -24657,7 +24657,7 @@
       <c r="H29" s="43"/>
     </row>
     <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="375"/>
+      <c r="A30" s="369"/>
       <c r="B30" s="57" t="s">
         <v>22</v>
       </c>
@@ -24669,7 +24669,7 @@
       <c r="H30" s="58"/>
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="375" t="s">
+      <c r="A31" s="369" t="s">
         <v>184</v>
       </c>
       <c r="B31" s="44" t="s">
@@ -24683,7 +24683,7 @@
       <c r="H31" s="43"/>
     </row>
     <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="375"/>
+      <c r="A32" s="369"/>
       <c r="B32" s="57" t="s">
         <v>22</v>
       </c>
@@ -24695,7 +24695,7 @@
       <c r="H32" s="43"/>
     </row>
     <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="375" t="s">
+      <c r="A33" s="369" t="s">
         <v>185</v>
       </c>
       <c r="B33" s="44" t="s">
@@ -24709,7 +24709,7 @@
       <c r="H33" s="43"/>
     </row>
     <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="375"/>
+      <c r="A34" s="369"/>
       <c r="B34" s="57" t="s">
         <v>22</v>
       </c>
@@ -24741,7 +24741,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="375" t="s">
+      <c r="A37" s="369" t="s">
         <v>192</v>
       </c>
       <c r="B37" s="44" t="s">
@@ -24761,7 +24761,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="375"/>
+      <c r="A38" s="369"/>
       <c r="B38" s="57" t="s">
         <v>22</v>
       </c>
@@ -24779,7 +24779,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="375" t="s">
+      <c r="A39" s="369" t="s">
         <v>193</v>
       </c>
       <c r="B39" s="44" t="s">
@@ -24791,7 +24791,7 @@
       <c r="F39" s="43"/>
     </row>
     <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="375"/>
+      <c r="A40" s="369"/>
       <c r="B40" s="57" t="s">
         <v>22</v>
       </c>
@@ -24801,7 +24801,7 @@
       <c r="F40" s="58"/>
     </row>
     <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="375" t="s">
+      <c r="A41" s="369" t="s">
         <v>194</v>
       </c>
       <c r="B41" s="44" t="s">
@@ -24813,7 +24813,7 @@
       <c r="F41" s="43"/>
     </row>
     <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="375"/>
+      <c r="A42" s="369"/>
       <c r="B42" s="57" t="s">
         <v>22</v>
       </c>
@@ -24824,14 +24824,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="A37:A38"/>
     <mergeCell ref="A39:A40"/>
@@ -24842,6 +24834,14 @@
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24860,13 +24860,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="278" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="258"/>
-      <c r="E1" s="258"/>
+      <c r="B1" s="278"/>
+      <c r="C1" s="278"/>
+      <c r="D1" s="278"/>
+      <c r="E1" s="278"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="59" t="s">
@@ -24965,10 +24965,10 @@
         <v>207</v>
       </c>
       <c r="B10" s="43"/>
-      <c r="C10" s="311" t="s">
+      <c r="C10" s="301" t="s">
         <v>222</v>
       </c>
-      <c r="D10" s="312"/>
+      <c r="D10" s="302"/>
       <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -24976,10 +24976,10 @@
         <v>208</v>
       </c>
       <c r="B11" s="43"/>
-      <c r="C11" s="311" t="s">
+      <c r="C11" s="301" t="s">
         <v>226</v>
       </c>
-      <c r="D11" s="312"/>
+      <c r="D11" s="302"/>
       <c r="E11" s="43"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -25083,25 +25083,25 @@
       <c r="F2" s="298"/>
       <c r="G2" s="298"/>
       <c r="H2" s="298"/>
-      <c r="J2" s="306" t="s">
+      <c r="J2" s="317" t="s">
         <v>425</v>
       </c>
-      <c r="K2" s="307"/>
-      <c r="L2" s="307"/>
-      <c r="M2" s="307"/>
-      <c r="N2" s="307"/>
-      <c r="O2" s="307"/>
-      <c r="P2" s="308"/>
+      <c r="K2" s="318"/>
+      <c r="L2" s="318"/>
+      <c r="M2" s="318"/>
+      <c r="N2" s="318"/>
+      <c r="O2" s="318"/>
+      <c r="P2" s="319"/>
     </row>
     <row r="3" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="302" t="s">
+      <c r="B3" s="300" t="s">
         <v>419</v>
       </c>
       <c r="C3" s="117" t="s">
         <v>415</v>
       </c>
       <c r="D3" s="118"/>
-      <c r="E3" s="302" t="s">
+      <c r="E3" s="300" t="s">
         <v>420</v>
       </c>
       <c r="F3" s="296" t="s">
@@ -25109,14 +25109,14 @@
       </c>
       <c r="G3" s="297"/>
       <c r="H3" s="123"/>
-      <c r="J3" s="299" t="s">
+      <c r="J3" s="310" t="s">
         <v>424</v>
       </c>
       <c r="K3" s="41" t="s">
         <v>421</v>
       </c>
       <c r="L3" s="118"/>
-      <c r="M3" s="302" t="s">
+      <c r="M3" s="300" t="s">
         <v>427</v>
       </c>
       <c r="N3" s="296" t="s">
@@ -25126,23 +25126,23 @@
       <c r="P3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="302"/>
+      <c r="B4" s="300"/>
       <c r="C4" s="117" t="s">
         <v>414</v>
       </c>
       <c r="D4" s="123"/>
-      <c r="E4" s="302"/>
+      <c r="E4" s="300"/>
       <c r="F4" s="296" t="s">
         <v>413</v>
       </c>
       <c r="G4" s="297"/>
       <c r="H4" s="123"/>
-      <c r="J4" s="300"/>
+      <c r="J4" s="311"/>
       <c r="K4" s="41" t="s">
         <v>422</v>
       </c>
       <c r="L4" s="118"/>
-      <c r="M4" s="302"/>
+      <c r="M4" s="300"/>
       <c r="N4" s="296" t="s">
         <v>417</v>
       </c>
@@ -25150,23 +25150,23 @@
       <c r="P4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="302"/>
+      <c r="B5" s="300"/>
       <c r="C5" s="117" t="s">
         <v>340</v>
       </c>
       <c r="D5" s="123"/>
-      <c r="E5" s="302"/>
+      <c r="E5" s="300"/>
       <c r="F5" s="296" t="s">
         <v>343</v>
       </c>
       <c r="G5" s="297"/>
       <c r="H5" s="123"/>
-      <c r="J5" s="301"/>
+      <c r="J5" s="299"/>
       <c r="K5" s="41" t="s">
         <v>423</v>
       </c>
       <c r="L5" s="118"/>
-      <c r="M5" s="302"/>
+      <c r="M5" s="300"/>
       <c r="N5" s="296" t="s">
         <v>418</v>
       </c>
@@ -25174,31 +25174,31 @@
       <c r="P5" s="118"/>
     </row>
     <row r="6" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="302"/>
+      <c r="B6" s="300"/>
       <c r="C6" s="117" t="s">
         <v>341</v>
       </c>
       <c r="D6" s="118"/>
-      <c r="E6" s="302"/>
+      <c r="E6" s="300"/>
       <c r="F6" s="296" t="s">
         <v>113</v>
       </c>
       <c r="G6" s="297"/>
       <c r="H6" s="123"/>
-      <c r="J6" s="302" t="s">
+      <c r="J6" s="300" t="s">
         <v>366</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>385</v>
       </c>
       <c r="L6" s="23"/>
-      <c r="M6" s="302" t="s">
+      <c r="M6" s="300" t="s">
         <v>366</v>
       </c>
-      <c r="N6" s="311" t="s">
+      <c r="N6" s="301" t="s">
         <v>410</v>
       </c>
-      <c r="O6" s="312"/>
+      <c r="O6" s="302"/>
       <c r="P6" s="23"/>
     </row>
     <row r="7" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -25211,27 +25211,27 @@
       <c r="F7" s="298"/>
       <c r="G7" s="298"/>
       <c r="H7" s="298"/>
-      <c r="J7" s="302"/>
+      <c r="J7" s="300"/>
       <c r="K7" s="3" t="s">
         <v>386</v>
       </c>
       <c r="L7" s="23"/>
-      <c r="M7" s="302"/>
-      <c r="N7" s="311" t="s">
+      <c r="M7" s="300"/>
+      <c r="N7" s="301" t="s">
         <v>411</v>
       </c>
-      <c r="O7" s="312"/>
+      <c r="O7" s="302"/>
       <c r="P7" s="23"/>
     </row>
     <row r="8" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="299" t="s">
+      <c r="B8" s="310" t="s">
         <v>389</v>
       </c>
       <c r="C8" s="117" t="s">
         <v>57</v>
       </c>
       <c r="D8" s="118"/>
-      <c r="E8" s="302" t="s">
+      <c r="E8" s="300" t="s">
         <v>64</v>
       </c>
       <c r="F8" s="296" t="s">
@@ -25239,23 +25239,23 @@
       </c>
       <c r="G8" s="297"/>
       <c r="H8" s="118"/>
-      <c r="J8" s="302"/>
+      <c r="J8" s="300"/>
       <c r="K8" s="3" t="s">
         <v>409</v>
       </c>
       <c r="L8" s="23"/>
-      <c r="M8" s="302"/>
-      <c r="N8" s="309"/>
-      <c r="O8" s="310"/>
+      <c r="M8" s="300"/>
+      <c r="N8" s="312"/>
+      <c r="O8" s="313"/>
       <c r="P8" s="118"/>
     </row>
     <row r="9" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="300"/>
+      <c r="B9" s="311"/>
       <c r="C9" s="117" t="s">
         <v>356</v>
       </c>
       <c r="D9" s="118"/>
-      <c r="E9" s="302"/>
+      <c r="E9" s="300"/>
       <c r="F9" s="296" t="s">
         <v>364</v>
       </c>
@@ -25272,30 +25272,30 @@
       <c r="P9" s="298"/>
     </row>
     <row r="10" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="300"/>
+      <c r="B10" s="311"/>
       <c r="C10" s="117" t="s">
         <v>357</v>
       </c>
       <c r="D10" s="118" t="s">
         <v>358</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="300"/>
       <c r="F10" s="296" t="s">
         <v>365</v>
       </c>
       <c r="G10" s="297"/>
       <c r="H10" s="118"/>
-      <c r="J10" s="314" t="s">
+      <c r="J10" s="309" t="s">
         <v>323</v>
       </c>
-      <c r="K10" s="314"/>
+      <c r="K10" s="309"/>
       <c r="L10" s="99" t="s">
         <v>344</v>
       </c>
-      <c r="M10" s="315" t="s">
+      <c r="M10" s="308" t="s">
         <v>345</v>
       </c>
-      <c r="N10" s="315"/>
+      <c r="N10" s="308"/>
       <c r="O10" s="99" t="s">
         <v>346</v>
       </c>
@@ -25304,78 +25304,78 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="300"/>
+      <c r="B11" s="311"/>
       <c r="C11" s="117" t="s">
         <v>112</v>
       </c>
       <c r="D11" s="118"/>
-      <c r="E11" s="302"/>
+      <c r="E11" s="300"/>
       <c r="F11" s="296" t="s">
         <v>396</v>
       </c>
       <c r="G11" s="297"/>
       <c r="H11" s="118"/>
-      <c r="J11" s="316" t="s">
+      <c r="J11" s="303" t="s">
         <v>348</v>
       </c>
-      <c r="K11" s="316"/>
+      <c r="K11" s="303"/>
       <c r="L11" s="62"/>
-      <c r="M11" s="313"/>
-      <c r="N11" s="313"/>
+      <c r="M11" s="305"/>
+      <c r="N11" s="305"/>
       <c r="O11" s="62"/>
       <c r="P11" s="127"/>
     </row>
     <row r="12" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="300"/>
+      <c r="B12" s="311"/>
       <c r="C12" s="117" t="s">
         <v>360</v>
       </c>
       <c r="D12" s="118"/>
-      <c r="E12" s="302"/>
+      <c r="E12" s="300"/>
       <c r="F12" s="296" t="s">
         <v>392</v>
       </c>
       <c r="G12" s="297"/>
       <c r="H12" s="118"/>
-      <c r="J12" s="316" t="s">
+      <c r="J12" s="303" t="s">
         <v>350</v>
       </c>
-      <c r="K12" s="316"/>
+      <c r="K12" s="303"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="313"/>
-      <c r="N12" s="313"/>
+      <c r="M12" s="305"/>
+      <c r="N12" s="305"/>
       <c r="O12" s="62"/>
       <c r="P12" s="127"/>
     </row>
     <row r="13" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="300"/>
+      <c r="B13" s="311"/>
       <c r="C13" s="117" t="s">
         <v>391</v>
       </c>
       <c r="D13" s="118"/>
-      <c r="E13" s="302"/>
+      <c r="E13" s="300"/>
       <c r="F13" s="296" t="s">
         <v>367</v>
       </c>
       <c r="G13" s="297"/>
       <c r="H13" s="118"/>
-      <c r="J13" s="316" t="s">
+      <c r="J13" s="303" t="s">
         <v>352</v>
       </c>
-      <c r="K13" s="316"/>
+      <c r="K13" s="303"/>
       <c r="L13" s="127"/>
-      <c r="M13" s="313"/>
-      <c r="N13" s="313"/>
+      <c r="M13" s="305"/>
+      <c r="N13" s="305"/>
       <c r="O13" s="127"/>
       <c r="P13" s="127"/>
     </row>
     <row r="14" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="300"/>
+      <c r="B14" s="311"/>
       <c r="C14" s="117" t="s">
         <v>361</v>
       </c>
       <c r="D14" s="118"/>
-      <c r="E14" s="299" t="s">
+      <c r="E14" s="310" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="296" t="s">
@@ -25383,67 +25383,67 @@
       </c>
       <c r="G14" s="297"/>
       <c r="H14" s="118"/>
-      <c r="J14" s="316" t="s">
+      <c r="J14" s="303" t="s">
         <v>353</v>
       </c>
-      <c r="K14" s="316"/>
+      <c r="K14" s="303"/>
       <c r="L14" s="127"/>
-      <c r="M14" s="313"/>
-      <c r="N14" s="313"/>
+      <c r="M14" s="305"/>
+      <c r="N14" s="305"/>
       <c r="O14" s="127"/>
       <c r="P14" s="127"/>
     </row>
     <row r="15" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="300"/>
+      <c r="B15" s="311"/>
       <c r="C15" s="117" t="s">
         <v>362</v>
       </c>
       <c r="D15" s="118"/>
-      <c r="E15" s="300"/>
+      <c r="E15" s="311"/>
       <c r="F15" s="296" t="s">
         <v>369</v>
       </c>
       <c r="G15" s="297"/>
       <c r="H15" s="118"/>
-      <c r="J15" s="316" t="s">
+      <c r="J15" s="303" t="s">
         <v>354</v>
       </c>
-      <c r="K15" s="316"/>
+      <c r="K15" s="303"/>
       <c r="L15" s="127"/>
-      <c r="M15" s="313"/>
-      <c r="N15" s="313"/>
+      <c r="M15" s="305"/>
+      <c r="N15" s="305"/>
       <c r="O15" s="127"/>
       <c r="P15" s="127"/>
     </row>
     <row r="16" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="301"/>
+      <c r="B16" s="299"/>
       <c r="C16" s="147"/>
       <c r="D16" s="118"/>
-      <c r="E16" s="301"/>
+      <c r="E16" s="299"/>
       <c r="F16" s="296" t="s">
         <v>370</v>
       </c>
       <c r="G16" s="297"/>
       <c r="H16" s="118"/>
-      <c r="J16" s="316" t="s">
+      <c r="J16" s="303" t="s">
         <v>355</v>
       </c>
-      <c r="K16" s="316"/>
+      <c r="K16" s="303"/>
       <c r="L16" s="127"/>
-      <c r="M16" s="313"/>
-      <c r="N16" s="313"/>
+      <c r="M16" s="305"/>
+      <c r="N16" s="305"/>
       <c r="O16" s="127"/>
       <c r="P16" s="127"/>
     </row>
     <row r="17" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="299" t="s">
+      <c r="B17" s="310" t="s">
         <v>412</v>
       </c>
       <c r="C17" s="146" t="s">
         <v>347</v>
       </c>
       <c r="D17" s="118"/>
-      <c r="E17" s="299" t="s">
+      <c r="E17" s="310" t="s">
         <v>390</v>
       </c>
       <c r="F17" s="296" t="s">
@@ -25462,28 +25462,28 @@
       <c r="P17" s="298"/>
     </row>
     <row r="18" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="300"/>
+      <c r="B18" s="311"/>
       <c r="C18" s="146" t="s">
         <v>349</v>
       </c>
       <c r="D18" s="118"/>
-      <c r="E18" s="300"/>
+      <c r="E18" s="311"/>
       <c r="F18" s="296" t="s">
         <v>395</v>
       </c>
       <c r="G18" s="297"/>
       <c r="H18" s="118"/>
-      <c r="J18" s="314" t="s">
+      <c r="J18" s="309" t="s">
         <v>323</v>
       </c>
-      <c r="K18" s="314"/>
+      <c r="K18" s="309"/>
       <c r="L18" s="99" t="s">
         <v>344</v>
       </c>
-      <c r="M18" s="315" t="s">
+      <c r="M18" s="308" t="s">
         <v>110</v>
       </c>
-      <c r="N18" s="315"/>
+      <c r="N18" s="308"/>
       <c r="O18" s="99" t="s">
         <v>359</v>
       </c>
@@ -25492,24 +25492,24 @@
       </c>
     </row>
     <row r="19" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="300"/>
+      <c r="B19" s="311"/>
       <c r="C19" s="146" t="s">
         <v>351</v>
       </c>
       <c r="D19" s="118"/>
-      <c r="E19" s="301"/>
+      <c r="E19" s="299"/>
       <c r="F19" s="296" t="s">
         <v>394</v>
       </c>
       <c r="G19" s="297"/>
       <c r="H19" s="118"/>
-      <c r="J19" s="316" t="s">
+      <c r="J19" s="303" t="s">
         <v>405</v>
       </c>
-      <c r="K19" s="316"/>
+      <c r="K19" s="303"/>
       <c r="L19" s="62"/>
-      <c r="M19" s="313"/>
-      <c r="N19" s="313"/>
+      <c r="M19" s="305"/>
+      <c r="N19" s="305"/>
       <c r="O19" s="62"/>
       <c r="P19" s="62"/>
     </row>
@@ -25523,13 +25523,13 @@
       <c r="F20" s="298"/>
       <c r="G20" s="298"/>
       <c r="H20" s="298"/>
-      <c r="J20" s="316" t="s">
+      <c r="J20" s="303" t="s">
         <v>406</v>
       </c>
-      <c r="K20" s="316"/>
+      <c r="K20" s="303"/>
       <c r="L20" s="62"/>
-      <c r="M20" s="313"/>
-      <c r="N20" s="313"/>
+      <c r="M20" s="305"/>
+      <c r="N20" s="305"/>
       <c r="O20" s="62"/>
       <c r="P20" s="62"/>
       <c r="Q20" s="119"/>
@@ -25538,28 +25538,28 @@
       <c r="T20" s="119"/>
     </row>
     <row r="21" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="301" t="s">
+      <c r="B21" s="299" t="s">
         <v>429</v>
       </c>
       <c r="C21" s="41" t="s">
         <v>371</v>
       </c>
       <c r="D21" s="128"/>
-      <c r="E21" s="302" t="s">
+      <c r="E21" s="300" t="s">
         <v>426</v>
       </c>
-      <c r="F21" s="311" t="s">
+      <c r="F21" s="301" t="s">
         <v>371</v>
       </c>
-      <c r="G21" s="312"/>
+      <c r="G21" s="302"/>
       <c r="H21" s="118"/>
-      <c r="J21" s="316" t="s">
+      <c r="J21" s="303" t="s">
         <v>407</v>
       </c>
-      <c r="K21" s="316"/>
+      <c r="K21" s="303"/>
       <c r="L21" s="62"/>
-      <c r="M21" s="313"/>
-      <c r="N21" s="313"/>
+      <c r="M21" s="305"/>
+      <c r="N21" s="305"/>
       <c r="O21" s="62"/>
       <c r="P21" s="62"/>
       <c r="Q21" s="119"/>
@@ -25568,24 +25568,24 @@
       <c r="T21" s="119"/>
     </row>
     <row r="22" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="302"/>
+      <c r="B22" s="300"/>
       <c r="C22" s="41" t="s">
         <v>384</v>
       </c>
       <c r="D22" s="128"/>
-      <c r="E22" s="302"/>
-      <c r="F22" s="311" t="s">
+      <c r="E22" s="300"/>
+      <c r="F22" s="301" t="s">
         <v>384</v>
       </c>
-      <c r="G22" s="312"/>
+      <c r="G22" s="302"/>
       <c r="H22" s="118"/>
-      <c r="J22" s="316" t="s">
+      <c r="J22" s="303" t="s">
         <v>408</v>
       </c>
-      <c r="K22" s="316"/>
+      <c r="K22" s="303"/>
       <c r="L22" s="62"/>
-      <c r="M22" s="313"/>
-      <c r="N22" s="313"/>
+      <c r="M22" s="305"/>
+      <c r="N22" s="305"/>
       <c r="O22" s="62"/>
       <c r="P22" s="62"/>
       <c r="Q22" s="119"/>
@@ -25594,13 +25594,13 @@
       <c r="T22" s="119"/>
     </row>
     <row r="23" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J23" s="317" t="s">
+      <c r="J23" s="304" t="s">
         <v>363</v>
       </c>
-      <c r="K23" s="317"/>
+      <c r="K23" s="304"/>
       <c r="L23" s="62"/>
-      <c r="M23" s="318"/>
-      <c r="N23" s="319"/>
+      <c r="M23" s="306"/>
+      <c r="N23" s="307"/>
       <c r="O23" s="124"/>
       <c r="P23" s="124"/>
       <c r="Q23" s="119"/>
@@ -25667,42 +25667,42 @@
       <c r="M27"/>
       <c r="N27"/>
       <c r="O27"/>
-      <c r="U27" s="305" t="s">
+      <c r="U27" s="316" t="s">
         <v>64</v>
       </c>
-      <c r="V27" s="303" t="s">
+      <c r="V27" s="314" t="s">
         <v>344</v>
       </c>
-      <c r="W27" s="304" t="s">
+      <c r="W27" s="315" t="s">
         <v>372</v>
       </c>
-      <c r="X27" s="304"/>
-      <c r="Y27" s="304"/>
-      <c r="Z27" s="304"/>
-      <c r="AA27" s="304"/>
-      <c r="AB27" s="304"/>
-      <c r="AC27" s="304"/>
-      <c r="AD27" s="304"/>
-      <c r="AE27" s="304" t="s">
+      <c r="X27" s="315"/>
+      <c r="Y27" s="315"/>
+      <c r="Z27" s="315"/>
+      <c r="AA27" s="315"/>
+      <c r="AB27" s="315"/>
+      <c r="AC27" s="315"/>
+      <c r="AD27" s="315"/>
+      <c r="AE27" s="315" t="s">
         <v>373</v>
       </c>
-      <c r="AF27" s="304"/>
-      <c r="AG27" s="304"/>
-      <c r="AH27" s="304"/>
-      <c r="AI27" s="304"/>
-      <c r="AJ27" s="304"/>
-      <c r="AK27" s="304"/>
-      <c r="AL27" s="304"/>
-      <c r="AM27" s="303" t="s">
+      <c r="AF27" s="315"/>
+      <c r="AG27" s="315"/>
+      <c r="AH27" s="315"/>
+      <c r="AI27" s="315"/>
+      <c r="AJ27" s="315"/>
+      <c r="AK27" s="315"/>
+      <c r="AL27" s="315"/>
+      <c r="AM27" s="314" t="s">
         <v>345</v>
       </c>
-      <c r="AN27" s="303" t="s">
+      <c r="AN27" s="314" t="s">
         <v>374</v>
       </c>
-      <c r="AO27" s="303" t="s">
+      <c r="AO27" s="314" t="s">
         <v>346</v>
       </c>
-      <c r="AP27" s="303" t="s">
+      <c r="AP27" s="314" t="s">
         <v>375</v>
       </c>
     </row>
@@ -25713,8 +25713,8 @@
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28"/>
-      <c r="U28" s="305"/>
-      <c r="V28" s="303"/>
+      <c r="U28" s="316"/>
+      <c r="V28" s="314"/>
       <c r="W28" s="125" t="s">
         <v>143</v>
       </c>
@@ -25763,10 +25763,10 @@
       <c r="AL28" s="125" t="s">
         <v>382</v>
       </c>
-      <c r="AM28" s="303"/>
-      <c r="AN28" s="303"/>
-      <c r="AO28" s="303"/>
-      <c r="AP28" s="303"/>
+      <c r="AM28" s="314"/>
+      <c r="AN28" s="314"/>
+      <c r="AO28" s="314"/>
+      <c r="AP28" s="314"/>
     </row>
     <row r="29" spans="2:42" x14ac:dyDescent="0.25">
       <c r="J29"/>
@@ -26008,51 +26008,22 @@
     </row>
   </sheetData>
   <mergeCells count="77">
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B8:B16"/>
+    <mergeCell ref="E8:E13"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="E3:E6"/>
@@ -26069,22 +26040,51 @@
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="J2:P2"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B8:B16"/>
-    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -26659,32 +26659,32 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="328" t="s">
+      <c r="A3" s="325" t="s">
         <v>544</v>
       </c>
-      <c r="B3" s="329"/>
-      <c r="C3" s="330"/>
-      <c r="H3" s="305" t="s">
+      <c r="B3" s="326"/>
+      <c r="C3" s="327"/>
+      <c r="H3" s="316" t="s">
         <v>256</v>
       </c>
-      <c r="I3" s="305" t="s">
+      <c r="I3" s="316" t="s">
         <v>323</v>
       </c>
-      <c r="J3" s="305" t="s">
+      <c r="J3" s="316" t="s">
         <v>459</v>
       </c>
-      <c r="K3" s="305" t="s">
+      <c r="K3" s="316" t="s">
         <v>471</v>
       </c>
-      <c r="L3" s="305" t="s">
+      <c r="L3" s="316" t="s">
         <v>478</v>
       </c>
-      <c r="M3" s="305"/>
-      <c r="N3" s="326" t="s">
+      <c r="M3" s="316"/>
+      <c r="N3" s="329" t="s">
         <v>477</v>
       </c>
-      <c r="O3" s="327"/>
-      <c r="P3" s="304" t="s">
+      <c r="O3" s="330"/>
+      <c r="P3" s="315" t="s">
         <v>498</v>
       </c>
     </row>
@@ -26694,10 +26694,10 @@
       </c>
       <c r="B4" s="294"/>
       <c r="C4" s="294"/>
-      <c r="H4" s="305"/>
-      <c r="I4" s="305"/>
-      <c r="J4" s="305"/>
-      <c r="K4" s="305"/>
+      <c r="H4" s="316"/>
+      <c r="I4" s="316"/>
+      <c r="J4" s="316"/>
+      <c r="K4" s="316"/>
       <c r="L4" s="100" t="s">
         <v>61</v>
       </c>
@@ -26710,14 +26710,14 @@
       <c r="O4" s="100" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="323"/>
+      <c r="P4" s="328"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="132" t="s">
         <v>548</v>
       </c>
-      <c r="B5" s="324"/>
-      <c r="C5" s="325"/>
+      <c r="B5" s="323"/>
+      <c r="C5" s="324"/>
       <c r="H5" s="132" t="s">
         <v>465</v>
       </c>
@@ -26746,8 +26746,8 @@
       <c r="A6" s="132" t="s">
         <v>546</v>
       </c>
-      <c r="B6" s="324"/>
-      <c r="C6" s="325"/>
+      <c r="B6" s="323"/>
+      <c r="C6" s="324"/>
       <c r="H6" s="132" t="s">
         <v>464</v>
       </c>
@@ -26776,8 +26776,8 @@
       <c r="A7" s="132" t="s">
         <v>549</v>
       </c>
-      <c r="B7" s="324"/>
-      <c r="C7" s="325"/>
+      <c r="B7" s="323"/>
+      <c r="C7" s="324"/>
       <c r="H7" s="132" t="s">
         <v>463</v>
       </c>
@@ -26806,8 +26806,8 @@
       <c r="A8" s="132" t="s">
         <v>550</v>
       </c>
-      <c r="B8" s="324"/>
-      <c r="C8" s="325"/>
+      <c r="B8" s="323"/>
+      <c r="C8" s="324"/>
       <c r="H8" s="132" t="s">
         <v>494</v>
       </c>
@@ -26836,8 +26836,8 @@
       <c r="A9" s="132" t="s">
         <v>551</v>
       </c>
-      <c r="B9" s="324"/>
-      <c r="C9" s="325"/>
+      <c r="B9" s="323"/>
+      <c r="C9" s="324"/>
       <c r="H9" s="132" t="s">
         <v>495</v>
       </c>
@@ -26850,10 +26850,10 @@
       <c r="K9" s="133" t="s">
         <v>251</v>
       </c>
-      <c r="L9" s="324" t="s">
+      <c r="L9" s="323" t="s">
         <v>469</v>
       </c>
-      <c r="M9" s="325"/>
+      <c r="M9" s="324"/>
       <c r="N9" s="95"/>
       <c r="O9" s="95"/>
       <c r="P9" s="99" t="s">
@@ -26947,10 +26947,10 @@
       <c r="K12" s="134" t="s">
         <v>251</v>
       </c>
-      <c r="L12" s="324" t="s">
+      <c r="L12" s="323" t="s">
         <v>470</v>
       </c>
-      <c r="M12" s="325"/>
+      <c r="M12" s="324"/>
       <c r="N12" s="95"/>
       <c r="O12" s="95"/>
       <c r="P12" s="99" t="s">
@@ -27950,13 +27950,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="L12:M12"/>
@@ -27966,6 +27959,13 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="N3:O3"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -27990,39 +27990,39 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="241" t="s">
+      <c r="B2" s="282" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="242"/>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="242"/>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="M2" s="243"/>
-      <c r="N2" s="336" t="s">
+      <c r="C2" s="283"/>
+      <c r="D2" s="283"/>
+      <c r="E2" s="283"/>
+      <c r="F2" s="283"/>
+      <c r="G2" s="283"/>
+      <c r="H2" s="283"/>
+      <c r="I2" s="283"/>
+      <c r="J2" s="283"/>
+      <c r="K2" s="283"/>
+      <c r="L2" s="283"/>
+      <c r="M2" s="284"/>
+      <c r="N2" s="347" t="s">
         <v>552</v>
       </c>
-      <c r="O2" s="337"/>
-      <c r="Q2" s="342" t="s">
+      <c r="O2" s="348"/>
+      <c r="Q2" s="331" t="s">
         <v>583</v>
       </c>
-      <c r="R2" s="343"/>
-      <c r="S2" s="343"/>
-      <c r="T2" s="343"/>
-      <c r="U2" s="343"/>
-      <c r="V2" s="343"/>
-      <c r="W2" s="343"/>
-      <c r="X2" s="343"/>
-      <c r="Y2" s="343"/>
-      <c r="Z2" s="343"/>
-      <c r="AA2" s="343"/>
-      <c r="AB2" s="343"/>
-      <c r="AC2" s="344"/>
+      <c r="R2" s="332"/>
+      <c r="S2" s="332"/>
+      <c r="T2" s="332"/>
+      <c r="U2" s="332"/>
+      <c r="V2" s="332"/>
+      <c r="W2" s="332"/>
+      <c r="X2" s="332"/>
+      <c r="Y2" s="332"/>
+      <c r="Z2" s="332"/>
+      <c r="AA2" s="332"/>
+      <c r="AB2" s="332"/>
+      <c r="AC2" s="333"/>
     </row>
     <row r="3" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5"/>
@@ -28037,10 +28037,10 @@
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="7"/>
-      <c r="N3" s="331" t="s">
+      <c r="N3" s="342" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="333"/>
+      <c r="O3" s="344"/>
       <c r="Q3" s="200" t="s">
         <v>569</v>
       </c>
@@ -28072,8 +28072,8 @@
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="7"/>
-      <c r="N4" s="334"/>
-      <c r="O4" s="335"/>
+      <c r="N4" s="345"/>
+      <c r="O4" s="346"/>
       <c r="Q4" s="194"/>
       <c r="R4" s="195"/>
       <c r="S4" s="192"/>
@@ -28108,19 +28108,19 @@
       <c r="Q5" s="191" t="s">
         <v>579</v>
       </c>
-      <c r="R5" s="347" t="s">
+      <c r="R5" s="336" t="s">
         <v>584</v>
       </c>
-      <c r="S5" s="348"/>
-      <c r="T5" s="348"/>
-      <c r="U5" s="348"/>
-      <c r="V5" s="348"/>
-      <c r="W5" s="348"/>
-      <c r="X5" s="348"/>
-      <c r="Y5" s="348"/>
-      <c r="Z5" s="348"/>
-      <c r="AA5" s="348"/>
-      <c r="AB5" s="349"/>
+      <c r="S5" s="337"/>
+      <c r="T5" s="337"/>
+      <c r="U5" s="337"/>
+      <c r="V5" s="337"/>
+      <c r="W5" s="337"/>
+      <c r="X5" s="337"/>
+      <c r="Y5" s="337"/>
+      <c r="Z5" s="337"/>
+      <c r="AA5" s="337"/>
+      <c r="AB5" s="338"/>
       <c r="AC5" s="193"/>
     </row>
     <row r="6" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28143,17 +28143,17 @@
       <c r="Q6" s="191" t="s">
         <v>580</v>
       </c>
-      <c r="R6" s="350"/>
-      <c r="S6" s="351"/>
-      <c r="T6" s="351"/>
-      <c r="U6" s="351"/>
-      <c r="V6" s="351"/>
-      <c r="W6" s="351"/>
-      <c r="X6" s="351"/>
-      <c r="Y6" s="351"/>
-      <c r="Z6" s="351"/>
-      <c r="AA6" s="351"/>
-      <c r="AB6" s="352"/>
+      <c r="R6" s="339"/>
+      <c r="S6" s="340"/>
+      <c r="T6" s="340"/>
+      <c r="U6" s="340"/>
+      <c r="V6" s="340"/>
+      <c r="W6" s="340"/>
+      <c r="X6" s="340"/>
+      <c r="Y6" s="340"/>
+      <c r="Z6" s="340"/>
+      <c r="AA6" s="340"/>
+      <c r="AB6" s="341"/>
       <c r="AC6" s="193"/>
     </row>
     <row r="7" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28174,17 +28174,17 @@
       <c r="Q7" s="191" t="s">
         <v>581</v>
       </c>
-      <c r="R7" s="350"/>
-      <c r="S7" s="351"/>
-      <c r="T7" s="351"/>
-      <c r="U7" s="351"/>
-      <c r="V7" s="351"/>
-      <c r="W7" s="351"/>
-      <c r="X7" s="351"/>
-      <c r="Y7" s="351"/>
-      <c r="Z7" s="351"/>
-      <c r="AA7" s="351"/>
-      <c r="AB7" s="352"/>
+      <c r="R7" s="339"/>
+      <c r="S7" s="340"/>
+      <c r="T7" s="340"/>
+      <c r="U7" s="340"/>
+      <c r="V7" s="340"/>
+      <c r="W7" s="340"/>
+      <c r="X7" s="340"/>
+      <c r="Y7" s="340"/>
+      <c r="Z7" s="340"/>
+      <c r="AA7" s="340"/>
+      <c r="AB7" s="341"/>
       <c r="AC7" s="193"/>
     </row>
     <row r="8" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28205,17 +28205,17 @@
       <c r="Q8" s="191" t="s">
         <v>582</v>
       </c>
-      <c r="R8" s="350"/>
-      <c r="S8" s="351"/>
-      <c r="T8" s="351"/>
-      <c r="U8" s="351"/>
-      <c r="V8" s="351"/>
-      <c r="W8" s="351"/>
-      <c r="X8" s="351"/>
-      <c r="Y8" s="351"/>
-      <c r="Z8" s="351"/>
-      <c r="AA8" s="351"/>
-      <c r="AB8" s="352"/>
+      <c r="R8" s="339"/>
+      <c r="S8" s="340"/>
+      <c r="T8" s="340"/>
+      <c r="U8" s="340"/>
+      <c r="V8" s="340"/>
+      <c r="W8" s="340"/>
+      <c r="X8" s="340"/>
+      <c r="Y8" s="340"/>
+      <c r="Z8" s="340"/>
+      <c r="AA8" s="340"/>
+      <c r="AB8" s="341"/>
       <c r="AC8" s="193"/>
     </row>
     <row r="9" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28251,23 +28251,23 @@
       <c r="B12" s="182" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="241" t="s">
+      <c r="C12" s="282" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="242"/>
-      <c r="E12" s="242"/>
-      <c r="F12" s="242"/>
-      <c r="G12" s="242"/>
-      <c r="H12" s="242"/>
-      <c r="I12" s="242"/>
-      <c r="J12" s="242"/>
-      <c r="K12" s="242"/>
-      <c r="L12" s="242"/>
-      <c r="M12" s="243"/>
-      <c r="N12" s="338" t="s">
+      <c r="D12" s="283"/>
+      <c r="E12" s="283"/>
+      <c r="F12" s="283"/>
+      <c r="G12" s="283"/>
+      <c r="H12" s="283"/>
+      <c r="I12" s="283"/>
+      <c r="J12" s="283"/>
+      <c r="K12" s="283"/>
+      <c r="L12" s="283"/>
+      <c r="M12" s="284"/>
+      <c r="N12" s="349" t="s">
         <v>103</v>
       </c>
-      <c r="O12" s="339"/>
+      <c r="O12" s="350"/>
       <c r="Q12" s="204" t="s">
         <v>631</v>
       </c>
@@ -28297,10 +28297,10 @@
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
-      <c r="N13" s="340" t="s">
+      <c r="N13" s="351" t="s">
         <v>21</v>
       </c>
-      <c r="O13" s="341"/>
+      <c r="O13" s="352"/>
       <c r="Q13" s="200" t="s">
         <v>568</v>
       </c>
@@ -28415,19 +28415,19 @@
       <c r="Q16" s="191" t="s">
         <v>579</v>
       </c>
-      <c r="R16" s="346" t="s">
+      <c r="R16" s="335" t="s">
         <v>578</v>
       </c>
-      <c r="S16" s="346"/>
-      <c r="T16" s="346"/>
-      <c r="U16" s="346"/>
-      <c r="V16" s="346"/>
-      <c r="W16" s="346"/>
-      <c r="X16" s="346"/>
-      <c r="Y16" s="346"/>
-      <c r="Z16" s="346"/>
-      <c r="AA16" s="346"/>
-      <c r="AB16" s="346"/>
+      <c r="S16" s="335"/>
+      <c r="T16" s="335"/>
+      <c r="U16" s="335"/>
+      <c r="V16" s="335"/>
+      <c r="W16" s="335"/>
+      <c r="X16" s="335"/>
+      <c r="Y16" s="335"/>
+      <c r="Z16" s="335"/>
+      <c r="AA16" s="335"/>
+      <c r="AB16" s="335"/>
       <c r="AC16" s="193"/>
     </row>
     <row r="17" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28443,24 +28443,24 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
-      <c r="N17" s="331" t="s">
+      <c r="N17" s="342" t="s">
         <v>21</v>
       </c>
-      <c r="O17" s="332"/>
+      <c r="O17" s="343"/>
       <c r="Q17" s="191" t="s">
         <v>580</v>
       </c>
-      <c r="R17" s="345"/>
-      <c r="S17" s="345"/>
-      <c r="T17" s="345"/>
-      <c r="U17" s="345"/>
-      <c r="V17" s="345"/>
-      <c r="W17" s="345"/>
-      <c r="X17" s="345"/>
-      <c r="Y17" s="345"/>
-      <c r="Z17" s="345"/>
-      <c r="AA17" s="345"/>
-      <c r="AB17" s="345"/>
+      <c r="R17" s="334"/>
+      <c r="S17" s="334"/>
+      <c r="T17" s="334"/>
+      <c r="U17" s="334"/>
+      <c r="V17" s="334"/>
+      <c r="W17" s="334"/>
+      <c r="X17" s="334"/>
+      <c r="Y17" s="334"/>
+      <c r="Z17" s="334"/>
+      <c r="AA17" s="334"/>
+      <c r="AB17" s="334"/>
       <c r="AC17" s="193"/>
     </row>
     <row r="18" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28485,17 +28485,17 @@
       <c r="Q18" s="191" t="s">
         <v>581</v>
       </c>
-      <c r="R18" s="345"/>
-      <c r="S18" s="345"/>
-      <c r="T18" s="345"/>
-      <c r="U18" s="345"/>
-      <c r="V18" s="345"/>
-      <c r="W18" s="345"/>
-      <c r="X18" s="345"/>
-      <c r="Y18" s="345"/>
-      <c r="Z18" s="345"/>
-      <c r="AA18" s="345"/>
-      <c r="AB18" s="345"/>
+      <c r="R18" s="334"/>
+      <c r="S18" s="334"/>
+      <c r="T18" s="334"/>
+      <c r="U18" s="334"/>
+      <c r="V18" s="334"/>
+      <c r="W18" s="334"/>
+      <c r="X18" s="334"/>
+      <c r="Y18" s="334"/>
+      <c r="Z18" s="334"/>
+      <c r="AA18" s="334"/>
+      <c r="AB18" s="334"/>
       <c r="AC18" s="193"/>
     </row>
     <row r="19" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28520,17 +28520,17 @@
       <c r="Q19" s="191" t="s">
         <v>582</v>
       </c>
-      <c r="R19" s="345"/>
-      <c r="S19" s="345"/>
-      <c r="T19" s="345"/>
-      <c r="U19" s="345"/>
-      <c r="V19" s="345"/>
-      <c r="W19" s="345"/>
-      <c r="X19" s="345"/>
-      <c r="Y19" s="345"/>
-      <c r="Z19" s="345"/>
-      <c r="AA19" s="345"/>
-      <c r="AB19" s="345"/>
+      <c r="R19" s="334"/>
+      <c r="S19" s="334"/>
+      <c r="T19" s="334"/>
+      <c r="U19" s="334"/>
+      <c r="V19" s="334"/>
+      <c r="W19" s="334"/>
+      <c r="X19" s="334"/>
+      <c r="Y19" s="334"/>
+      <c r="Z19" s="334"/>
+      <c r="AA19" s="334"/>
+      <c r="AB19" s="334"/>
       <c r="AC19" s="193"/>
     </row>
     <row r="20" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28577,10 +28577,10 @@
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
-      <c r="N21" s="331" t="s">
+      <c r="N21" s="342" t="s">
         <v>21</v>
       </c>
-      <c r="O21" s="332"/>
+      <c r="O21" s="343"/>
     </row>
     <row r="22" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="188" t="s">
@@ -28653,10 +28653,10 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
-      <c r="N25" s="331" t="s">
+      <c r="N25" s="342" t="s">
         <v>21</v>
       </c>
-      <c r="O25" s="332"/>
+      <c r="O25" s="343"/>
     </row>
     <row r="26" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="188" t="s">
@@ -28729,10 +28729,10 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
-      <c r="N29" s="331" t="s">
+      <c r="N29" s="342" t="s">
         <v>21</v>
       </c>
-      <c r="O29" s="332"/>
+      <c r="O29" s="343"/>
     </row>
     <row r="30" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="188" t="s">
@@ -28805,10 +28805,10 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
-      <c r="N33" s="331" t="s">
+      <c r="N33" s="342" t="s">
         <v>21</v>
       </c>
-      <c r="O33" s="332"/>
+      <c r="O33" s="343"/>
     </row>
     <row r="34" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="188" t="s">
@@ -28870,15 +28870,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="Q2:AC2"/>
-    <mergeCell ref="R19:AB19"/>
-    <mergeCell ref="R16:AB16"/>
-    <mergeCell ref="R17:AB17"/>
-    <mergeCell ref="R18:AB18"/>
-    <mergeCell ref="R5:AB5"/>
-    <mergeCell ref="R6:AB6"/>
-    <mergeCell ref="R7:AB7"/>
-    <mergeCell ref="R8:AB8"/>
     <mergeCell ref="N33:O33"/>
     <mergeCell ref="N3:O4"/>
     <mergeCell ref="B2:M2"/>
@@ -28890,6 +28881,15 @@
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="N12:O12"/>
     <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q2:AC2"/>
+    <mergeCell ref="R19:AB19"/>
+    <mergeCell ref="R16:AB16"/>
+    <mergeCell ref="R17:AB17"/>
+    <mergeCell ref="R18:AB18"/>
+    <mergeCell ref="R5:AB5"/>
+    <mergeCell ref="R6:AB6"/>
+    <mergeCell ref="R7:AB7"/>
+    <mergeCell ref="R8:AB8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -29454,15 +29454,15 @@
       <c r="V2" s="190"/>
     </row>
     <row r="3" spans="2:23" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G3" s="241" t="s">
+      <c r="G3" s="282" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="242"/>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="M3" s="243"/>
+      <c r="H3" s="283"/>
+      <c r="I3" s="283"/>
+      <c r="J3" s="283"/>
+      <c r="K3" s="283"/>
+      <c r="L3" s="283"/>
+      <c r="M3" s="284"/>
       <c r="N3" s="213"/>
       <c r="O3" s="213"/>
       <c r="P3" s="213"/>
@@ -29502,39 +29502,39 @@
       <c r="O4" s="214"/>
       <c r="P4" s="214"/>
       <c r="Q4" s="194"/>
-      <c r="R4" s="244" t="s">
+      <c r="R4" s="285" t="s">
         <v>618</v>
       </c>
-      <c r="S4" s="247" t="s">
+      <c r="S4" s="263" t="s">
         <v>617</v>
       </c>
-      <c r="T4" s="248" t="s">
+      <c r="T4" s="288" t="s">
         <v>619</v>
       </c>
-      <c r="U4" s="248" t="s">
+      <c r="U4" s="288" t="s">
         <v>10</v>
       </c>
       <c r="V4" s="193"/>
       <c r="W4" s="39"/>
     </row>
     <row r="5" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G5" s="249" t="s">
+      <c r="G5" s="289" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="250"/>
-      <c r="I5" s="250"/>
-      <c r="J5" s="250"/>
-      <c r="K5" s="250"/>
-      <c r="L5" s="250"/>
-      <c r="M5" s="251"/>
+      <c r="H5" s="256"/>
+      <c r="I5" s="256"/>
+      <c r="J5" s="256"/>
+      <c r="K5" s="256"/>
+      <c r="L5" s="256"/>
+      <c r="M5" s="290"/>
       <c r="N5" s="91"/>
       <c r="O5" s="91"/>
       <c r="P5" s="91"/>
       <c r="Q5" s="194"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="247"/>
-      <c r="T5" s="248"/>
-      <c r="U5" s="248"/>
+      <c r="R5" s="286"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="288"/>
+      <c r="U5" s="288"/>
       <c r="V5" s="193"/>
       <c r="W5" s="39"/>
     </row>
@@ -29560,7 +29560,7 @@
       <c r="O6" s="91"/>
       <c r="P6" s="91"/>
       <c r="Q6" s="194"/>
-      <c r="R6" s="246"/>
+      <c r="R6" s="287"/>
       <c r="S6" s="234" t="s">
         <v>620</v>
       </c>
@@ -29607,15 +29607,15 @@
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="193"/>
-      <c r="G8" s="255" t="s">
+      <c r="G8" s="276" t="s">
         <v>0</v>
       </c>
-      <c r="H8" s="256"/>
-      <c r="I8" s="256"/>
-      <c r="J8" s="256"/>
-      <c r="K8" s="256"/>
-      <c r="L8" s="256"/>
-      <c r="M8" s="257"/>
+      <c r="H8" s="252"/>
+      <c r="I8" s="252"/>
+      <c r="J8" s="252"/>
+      <c r="K8" s="252"/>
+      <c r="L8" s="252"/>
+      <c r="M8" s="277"/>
       <c r="N8" s="91"/>
       <c r="O8" s="91"/>
       <c r="P8" s="91"/>
@@ -29698,15 +29698,15 @@
       </c>
       <c r="D11" s="38"/>
       <c r="E11" s="193"/>
-      <c r="G11" s="255" t="s">
+      <c r="G11" s="276" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="256"/>
-      <c r="I11" s="256"/>
-      <c r="J11" s="256"/>
-      <c r="K11" s="256"/>
-      <c r="L11" s="256"/>
-      <c r="M11" s="257"/>
+      <c r="H11" s="252"/>
+      <c r="I11" s="252"/>
+      <c r="J11" s="252"/>
+      <c r="K11" s="252"/>
+      <c r="L11" s="252"/>
+      <c r="M11" s="277"/>
       <c r="N11" s="91"/>
       <c r="O11" s="91"/>
       <c r="P11" s="91"/>
@@ -29789,15 +29789,15 @@
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="193"/>
-      <c r="G14" s="255" t="s">
+      <c r="G14" s="276" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="256"/>
-      <c r="I14" s="256"/>
-      <c r="J14" s="256"/>
-      <c r="K14" s="256"/>
-      <c r="L14" s="256"/>
-      <c r="M14" s="257"/>
+      <c r="H14" s="252"/>
+      <c r="I14" s="252"/>
+      <c r="J14" s="252"/>
+      <c r="K14" s="252"/>
+      <c r="L14" s="252"/>
+      <c r="M14" s="277"/>
       <c r="N14" s="91"/>
       <c r="O14" s="91"/>
       <c r="P14" s="91"/>
@@ -29942,15 +29942,15 @@
       </c>
       <c r="D19" s="38"/>
       <c r="E19" s="193"/>
-      <c r="G19" s="255" t="s">
+      <c r="G19" s="276" t="s">
         <v>114</v>
       </c>
-      <c r="H19" s="256"/>
-      <c r="I19" s="256"/>
-      <c r="J19" s="256"/>
-      <c r="K19" s="256"/>
-      <c r="L19" s="256"/>
-      <c r="M19" s="257"/>
+      <c r="H19" s="252"/>
+      <c r="I19" s="252"/>
+      <c r="J19" s="252"/>
+      <c r="K19" s="252"/>
+      <c r="L19" s="252"/>
+      <c r="M19" s="277"/>
       <c r="N19" s="91"/>
       <c r="O19" s="91"/>
       <c r="P19" s="91"/>
@@ -30057,27 +30057,27 @@
       <c r="T23" s="192"/>
       <c r="U23" s="192"/>
       <c r="V23" s="193"/>
-      <c r="X23" s="258" t="s">
+      <c r="X23" s="278" t="s">
         <v>227</v>
       </c>
-      <c r="Y23" s="258"/>
-      <c r="Z23" s="258"/>
-      <c r="AA23" s="258"/>
-      <c r="AB23" s="258"/>
-      <c r="AC23" s="258"/>
-      <c r="AD23" s="258"/>
-      <c r="AE23" s="258"/>
-      <c r="AF23" s="258"/>
-      <c r="AG23" s="258"/>
-      <c r="AH23" s="258"/>
-      <c r="AI23" s="258"/>
-      <c r="AJ23" s="258"/>
-      <c r="AK23" s="258"/>
-      <c r="AL23" s="258"/>
-      <c r="AM23" s="258"/>
-      <c r="AN23" s="258"/>
-      <c r="AO23" s="258"/>
-      <c r="AP23" s="258"/>
+      <c r="Y23" s="278"/>
+      <c r="Z23" s="278"/>
+      <c r="AA23" s="278"/>
+      <c r="AB23" s="278"/>
+      <c r="AC23" s="278"/>
+      <c r="AD23" s="278"/>
+      <c r="AE23" s="278"/>
+      <c r="AF23" s="278"/>
+      <c r="AG23" s="278"/>
+      <c r="AH23" s="278"/>
+      <c r="AI23" s="278"/>
+      <c r="AJ23" s="278"/>
+      <c r="AK23" s="278"/>
+      <c r="AL23" s="278"/>
+      <c r="AM23" s="278"/>
+      <c r="AN23" s="278"/>
+      <c r="AO23" s="278"/>
+      <c r="AP23" s="278"/>
     </row>
     <row r="24" spans="2:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q24" s="196"/>
@@ -30089,36 +30089,36 @@
       <c r="X24" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Y24" s="259" t="s">
+      <c r="Y24" s="279" t="s">
         <v>18</v>
       </c>
-      <c r="Z24" s="260"/>
-      <c r="AA24" s="261"/>
-      <c r="AB24" s="259" t="s">
+      <c r="Z24" s="280"/>
+      <c r="AA24" s="281"/>
+      <c r="AB24" s="279" t="s">
         <v>17</v>
       </c>
-      <c r="AC24" s="260"/>
-      <c r="AD24" s="261"/>
-      <c r="AE24" s="259" t="s">
+      <c r="AC24" s="280"/>
+      <c r="AD24" s="281"/>
+      <c r="AE24" s="279" t="s">
         <v>16</v>
       </c>
-      <c r="AF24" s="260"/>
-      <c r="AG24" s="261"/>
-      <c r="AH24" s="259" t="s">
+      <c r="AF24" s="280"/>
+      <c r="AG24" s="281"/>
+      <c r="AH24" s="279" t="s">
         <v>13</v>
       </c>
-      <c r="AI24" s="260"/>
-      <c r="AJ24" s="261"/>
-      <c r="AK24" s="259" t="s">
+      <c r="AI24" s="280"/>
+      <c r="AJ24" s="281"/>
+      <c r="AK24" s="279" t="s">
         <v>20</v>
       </c>
-      <c r="AL24" s="260"/>
-      <c r="AM24" s="261"/>
-      <c r="AN24" s="259" t="s">
+      <c r="AL24" s="280"/>
+      <c r="AM24" s="281"/>
+      <c r="AN24" s="279" t="s">
         <v>553</v>
       </c>
-      <c r="AO24" s="260"/>
-      <c r="AP24" s="261"/>
+      <c r="AO24" s="280"/>
+      <c r="AP24" s="281"/>
     </row>
     <row r="25" spans="2:42" ht="81.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="X25" s="64" t="s">
@@ -30632,48 +30632,48 @@
       <c r="P43" s="39"/>
     </row>
     <row r="44" spans="7:49" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X44" s="252" t="s">
+      <c r="X44" s="273" t="s">
         <v>238</v>
       </c>
-      <c r="Y44" s="254"/>
-      <c r="Z44" s="252" t="s">
+      <c r="Y44" s="275"/>
+      <c r="Z44" s="273" t="s">
         <v>237</v>
       </c>
-      <c r="AA44" s="253"/>
-      <c r="AB44" s="253"/>
-      <c r="AC44" s="253"/>
-      <c r="AD44" s="253"/>
-      <c r="AE44" s="254"/>
-      <c r="AF44" s="252" t="s">
+      <c r="AA44" s="274"/>
+      <c r="AB44" s="274"/>
+      <c r="AC44" s="274"/>
+      <c r="AD44" s="274"/>
+      <c r="AE44" s="275"/>
+      <c r="AF44" s="273" t="s">
         <v>239</v>
       </c>
-      <c r="AG44" s="253"/>
-      <c r="AH44" s="253"/>
-      <c r="AI44" s="253"/>
-      <c r="AJ44" s="253"/>
-      <c r="AK44" s="254"/>
-      <c r="AL44" s="252" t="s">
+      <c r="AG44" s="274"/>
+      <c r="AH44" s="274"/>
+      <c r="AI44" s="274"/>
+      <c r="AJ44" s="274"/>
+      <c r="AK44" s="275"/>
+      <c r="AL44" s="273" t="s">
         <v>240</v>
       </c>
-      <c r="AM44" s="253"/>
-      <c r="AN44" s="253"/>
-      <c r="AO44" s="253"/>
-      <c r="AP44" s="253"/>
-      <c r="AQ44" s="254"/>
-      <c r="AR44" s="252" t="s">
+      <c r="AM44" s="274"/>
+      <c r="AN44" s="274"/>
+      <c r="AO44" s="274"/>
+      <c r="AP44" s="274"/>
+      <c r="AQ44" s="275"/>
+      <c r="AR44" s="273" t="s">
         <v>241</v>
       </c>
-      <c r="AS44" s="253"/>
-      <c r="AT44" s="253"/>
-      <c r="AU44" s="253"/>
-      <c r="AV44" s="253"/>
-      <c r="AW44" s="254"/>
+      <c r="AS44" s="274"/>
+      <c r="AT44" s="274"/>
+      <c r="AU44" s="274"/>
+      <c r="AV44" s="274"/>
+      <c r="AW44" s="275"/>
     </row>
     <row r="45" spans="7:49" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X45" s="262" t="s">
+      <c r="X45" s="268" t="s">
         <v>40</v>
       </c>
-      <c r="Y45" s="263"/>
+      <c r="Y45" s="269"/>
       <c r="Z45" s="184" t="s">
         <v>117</v>
       </c>
@@ -30758,10 +30758,10 @@
       <c r="T46" s="215"/>
       <c r="U46" s="189"/>
       <c r="V46" s="190"/>
-      <c r="X46" s="264" t="s">
+      <c r="X46" s="270" t="s">
         <v>31</v>
       </c>
-      <c r="Y46" s="265"/>
+      <c r="Y46" s="271"/>
       <c r="Z46" s="66"/>
       <c r="AA46" s="22"/>
       <c r="AB46" s="22"/>
@@ -30798,47 +30798,47 @@
       <c r="T47" s="216"/>
       <c r="U47" s="211"/>
       <c r="V47" s="208"/>
-      <c r="X47" s="266"/>
-      <c r="Y47" s="267"/>
-      <c r="Z47" s="268" t="s">
+      <c r="X47" s="272"/>
+      <c r="Y47" s="255"/>
+      <c r="Z47" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="AA47" s="256"/>
-      <c r="AB47" s="256"/>
-      <c r="AC47" s="256"/>
-      <c r="AD47" s="256"/>
-      <c r="AE47" s="269"/>
-      <c r="AF47" s="268" t="s">
+      <c r="AA47" s="252"/>
+      <c r="AB47" s="252"/>
+      <c r="AC47" s="252"/>
+      <c r="AD47" s="252"/>
+      <c r="AE47" s="253"/>
+      <c r="AF47" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="AG47" s="256"/>
-      <c r="AH47" s="256"/>
-      <c r="AI47" s="256"/>
-      <c r="AJ47" s="256"/>
-      <c r="AK47" s="269"/>
-      <c r="AL47" s="268" t="s">
+      <c r="AG47" s="252"/>
+      <c r="AH47" s="252"/>
+      <c r="AI47" s="252"/>
+      <c r="AJ47" s="252"/>
+      <c r="AK47" s="253"/>
+      <c r="AL47" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="AM47" s="256"/>
-      <c r="AN47" s="256"/>
-      <c r="AO47" s="256"/>
-      <c r="AP47" s="256"/>
-      <c r="AQ47" s="269"/>
-      <c r="AR47" s="268" t="s">
+      <c r="AM47" s="252"/>
+      <c r="AN47" s="252"/>
+      <c r="AO47" s="252"/>
+      <c r="AP47" s="252"/>
+      <c r="AQ47" s="253"/>
+      <c r="AR47" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="AS47" s="256"/>
-      <c r="AT47" s="256"/>
-      <c r="AU47" s="256"/>
-      <c r="AV47" s="256"/>
-      <c r="AW47" s="269"/>
+      <c r="AS47" s="252"/>
+      <c r="AT47" s="252"/>
+      <c r="AU47" s="252"/>
+      <c r="AV47" s="252"/>
+      <c r="AW47" s="253"/>
     </row>
     <row r="48" spans="7:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O48" s="194"/>
-      <c r="P48" s="270" t="s">
+      <c r="P48" s="261" t="s">
         <v>621</v>
       </c>
-      <c r="Q48" s="271"/>
+      <c r="Q48" s="262"/>
       <c r="R48" s="151" t="s">
         <v>223</v>
       </c>
@@ -30852,7 +30852,7 @@
         <v>622</v>
       </c>
       <c r="V48" s="193"/>
-      <c r="X48" s="272" t="s">
+      <c r="X48" s="246" t="s">
         <v>1</v>
       </c>
       <c r="Y48" s="72" t="s">
@@ -30885,16 +30885,16 @@
     </row>
     <row r="49" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O49" s="194"/>
-      <c r="P49" s="270" t="s">
+      <c r="P49" s="261" t="s">
         <v>31</v>
       </c>
-      <c r="Q49" s="271"/>
+      <c r="Q49" s="262"/>
       <c r="R49" s="31"/>
       <c r="S49" s="89"/>
       <c r="T49" s="224"/>
       <c r="U49" s="224"/>
       <c r="V49" s="193"/>
-      <c r="X49" s="272"/>
+      <c r="X49" s="246"/>
       <c r="Y49" s="72" t="s">
         <v>12</v>
       </c>
@@ -30925,16 +30925,16 @@
     </row>
     <row r="50" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O50" s="194"/>
-      <c r="P50" s="247" t="s">
+      <c r="P50" s="263" t="s">
         <v>30</v>
       </c>
-      <c r="Q50" s="247"/>
-      <c r="R50" s="247"/>
-      <c r="S50" s="247"/>
-      <c r="T50" s="247"/>
-      <c r="U50" s="247"/>
+      <c r="Q50" s="263"/>
+      <c r="R50" s="263"/>
+      <c r="S50" s="263"/>
+      <c r="T50" s="263"/>
+      <c r="U50" s="263"/>
       <c r="V50" s="193"/>
-      <c r="X50" s="272" t="s">
+      <c r="X50" s="246" t="s">
         <v>32</v>
       </c>
       <c r="Y50" s="72" t="s">
@@ -30967,7 +30967,7 @@
     </row>
     <row r="51" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O51" s="194"/>
-      <c r="P51" s="273" t="s">
+      <c r="P51" s="241" t="s">
         <v>1</v>
       </c>
       <c r="Q51" s="151" t="s">
@@ -30978,7 +30978,7 @@
       <c r="T51" s="219"/>
       <c r="U51" s="220"/>
       <c r="V51" s="193"/>
-      <c r="X51" s="272"/>
+      <c r="X51" s="246"/>
       <c r="Y51" s="72" t="s">
         <v>12</v>
       </c>
@@ -31009,7 +31009,7 @@
     </row>
     <row r="52" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O52" s="194"/>
-      <c r="P52" s="273"/>
+      <c r="P52" s="241"/>
       <c r="Q52" s="151" t="s">
         <v>12</v>
       </c>
@@ -31018,7 +31018,7 @@
       <c r="T52" s="219"/>
       <c r="U52" s="220"/>
       <c r="V52" s="193"/>
-      <c r="X52" s="274" t="s">
+      <c r="X52" s="264" t="s">
         <v>33</v>
       </c>
       <c r="Y52" s="72" t="s">
@@ -31051,7 +31051,7 @@
     </row>
     <row r="53" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O53" s="194"/>
-      <c r="P53" s="273" t="s">
+      <c r="P53" s="241" t="s">
         <v>623</v>
       </c>
       <c r="Q53" s="151" t="s">
@@ -31062,7 +31062,7 @@
       <c r="T53" s="219"/>
       <c r="U53" s="220"/>
       <c r="V53" s="193"/>
-      <c r="X53" s="275"/>
+      <c r="X53" s="265"/>
       <c r="Y53" s="72" t="s">
         <v>12</v>
       </c>
@@ -31093,7 +31093,7 @@
     </row>
     <row r="54" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O54" s="194"/>
-      <c r="P54" s="273"/>
+      <c r="P54" s="241"/>
       <c r="Q54" s="151" t="s">
         <v>12</v>
       </c>
@@ -31102,10 +31102,10 @@
       <c r="T54" s="219"/>
       <c r="U54" s="220"/>
       <c r="V54" s="193"/>
-      <c r="X54" s="276" t="s">
+      <c r="X54" s="266" t="s">
         <v>34</v>
       </c>
-      <c r="Y54" s="277"/>
+      <c r="Y54" s="267"/>
       <c r="Z54" s="70"/>
       <c r="AA54" s="25"/>
       <c r="AB54" s="25"/>
@@ -31133,7 +31133,7 @@
     </row>
     <row r="55" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O55" s="194"/>
-      <c r="P55" s="273" t="s">
+      <c r="P55" s="241" t="s">
         <v>624</v>
       </c>
       <c r="Q55" s="151" t="s">
@@ -31144,44 +31144,44 @@
       <c r="T55" s="219"/>
       <c r="U55" s="220"/>
       <c r="V55" s="193"/>
-      <c r="X55" s="278"/>
-      <c r="Y55" s="267"/>
-      <c r="Z55" s="278" t="s">
+      <c r="X55" s="254"/>
+      <c r="Y55" s="255"/>
+      <c r="Z55" s="254" t="s">
         <v>107</v>
       </c>
-      <c r="AA55" s="250"/>
-      <c r="AB55" s="250"/>
-      <c r="AC55" s="250"/>
-      <c r="AD55" s="250"/>
-      <c r="AE55" s="267"/>
-      <c r="AF55" s="278" t="s">
+      <c r="AA55" s="256"/>
+      <c r="AB55" s="256"/>
+      <c r="AC55" s="256"/>
+      <c r="AD55" s="256"/>
+      <c r="AE55" s="255"/>
+      <c r="AF55" s="254" t="s">
         <v>107</v>
       </c>
-      <c r="AG55" s="250"/>
-      <c r="AH55" s="250"/>
-      <c r="AI55" s="250"/>
-      <c r="AJ55" s="250"/>
-      <c r="AK55" s="267"/>
-      <c r="AL55" s="278" t="s">
+      <c r="AG55" s="256"/>
+      <c r="AH55" s="256"/>
+      <c r="AI55" s="256"/>
+      <c r="AJ55" s="256"/>
+      <c r="AK55" s="255"/>
+      <c r="AL55" s="254" t="s">
         <v>107</v>
       </c>
-      <c r="AM55" s="250"/>
-      <c r="AN55" s="250"/>
-      <c r="AO55" s="250"/>
-      <c r="AP55" s="250"/>
-      <c r="AQ55" s="267"/>
-      <c r="AR55" s="278" t="s">
+      <c r="AM55" s="256"/>
+      <c r="AN55" s="256"/>
+      <c r="AO55" s="256"/>
+      <c r="AP55" s="256"/>
+      <c r="AQ55" s="255"/>
+      <c r="AR55" s="254" t="s">
         <v>107</v>
       </c>
-      <c r="AS55" s="250"/>
-      <c r="AT55" s="250"/>
-      <c r="AU55" s="250"/>
-      <c r="AV55" s="250"/>
-      <c r="AW55" s="267"/>
+      <c r="AS55" s="256"/>
+      <c r="AT55" s="256"/>
+      <c r="AU55" s="256"/>
+      <c r="AV55" s="256"/>
+      <c r="AW55" s="255"/>
     </row>
     <row r="56" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O56" s="194"/>
-      <c r="P56" s="273"/>
+      <c r="P56" s="241"/>
       <c r="Q56" s="151" t="s">
         <v>12</v>
       </c>
@@ -31190,10 +31190,10 @@
       <c r="T56" s="219"/>
       <c r="U56" s="220"/>
       <c r="V56" s="193"/>
-      <c r="X56" s="279" t="s">
+      <c r="X56" s="257" t="s">
         <v>37</v>
       </c>
-      <c r="Y56" s="280"/>
+      <c r="Y56" s="258"/>
       <c r="Z56" s="68"/>
       <c r="AA56" s="19"/>
       <c r="AB56" s="19"/>
@@ -31221,65 +31221,65 @@
     </row>
     <row r="57" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O57" s="194"/>
-      <c r="P57" s="281" t="s">
+      <c r="P57" s="248" t="s">
         <v>625</v>
       </c>
-      <c r="Q57" s="281"/>
+      <c r="Q57" s="248"/>
       <c r="R57" s="218"/>
       <c r="S57" s="218"/>
       <c r="T57" s="219"/>
       <c r="U57" s="221"/>
       <c r="V57" s="210"/>
-      <c r="X57" s="282"/>
-      <c r="Y57" s="283"/>
-      <c r="Z57" s="268" t="s">
+      <c r="X57" s="259"/>
+      <c r="Y57" s="260"/>
+      <c r="Z57" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="AA57" s="256"/>
-      <c r="AB57" s="256"/>
-      <c r="AC57" s="256"/>
-      <c r="AD57" s="256"/>
-      <c r="AE57" s="269"/>
-      <c r="AF57" s="268" t="s">
+      <c r="AA57" s="252"/>
+      <c r="AB57" s="252"/>
+      <c r="AC57" s="252"/>
+      <c r="AD57" s="252"/>
+      <c r="AE57" s="253"/>
+      <c r="AF57" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="AG57" s="256"/>
-      <c r="AH57" s="256"/>
-      <c r="AI57" s="256"/>
-      <c r="AJ57" s="256"/>
-      <c r="AK57" s="269"/>
-      <c r="AL57" s="268" t="s">
+      <c r="AG57" s="252"/>
+      <c r="AH57" s="252"/>
+      <c r="AI57" s="252"/>
+      <c r="AJ57" s="252"/>
+      <c r="AK57" s="253"/>
+      <c r="AL57" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="AM57" s="256"/>
-      <c r="AN57" s="256"/>
-      <c r="AO57" s="256"/>
-      <c r="AP57" s="256"/>
-      <c r="AQ57" s="269"/>
-      <c r="AR57" s="268" t="s">
+      <c r="AM57" s="252"/>
+      <c r="AN57" s="252"/>
+      <c r="AO57" s="252"/>
+      <c r="AP57" s="252"/>
+      <c r="AQ57" s="253"/>
+      <c r="AR57" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="AS57" s="256"/>
-      <c r="AT57" s="256"/>
-      <c r="AU57" s="256"/>
-      <c r="AV57" s="256"/>
-      <c r="AW57" s="269"/>
+      <c r="AS57" s="252"/>
+      <c r="AT57" s="252"/>
+      <c r="AU57" s="252"/>
+      <c r="AV57" s="252"/>
+      <c r="AW57" s="253"/>
     </row>
     <row r="58" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O58" s="194"/>
-      <c r="P58" s="285" t="s">
+      <c r="P58" s="243" t="s">
         <v>107</v>
       </c>
-      <c r="Q58" s="286"/>
-      <c r="R58" s="286"/>
-      <c r="S58" s="286"/>
-      <c r="T58" s="286"/>
-      <c r="U58" s="287"/>
+      <c r="Q58" s="244"/>
+      <c r="R58" s="244"/>
+      <c r="S58" s="244"/>
+      <c r="T58" s="244"/>
+      <c r="U58" s="245"/>
       <c r="V58" s="210"/>
-      <c r="X58" s="272" t="s">
+      <c r="X58" s="246" t="s">
         <v>38</v>
       </c>
-      <c r="Y58" s="288"/>
+      <c r="Y58" s="247"/>
       <c r="Z58" s="68"/>
       <c r="AA58" s="19"/>
       <c r="AB58" s="19"/>
@@ -31307,19 +31307,19 @@
     </row>
     <row r="59" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O59" s="194"/>
-      <c r="P59" s="281" t="s">
+      <c r="P59" s="248" t="s">
         <v>626</v>
       </c>
-      <c r="Q59" s="281"/>
+      <c r="Q59" s="248"/>
       <c r="R59" s="218"/>
       <c r="S59" s="218"/>
       <c r="T59" s="219"/>
       <c r="U59" s="221"/>
       <c r="V59" s="210"/>
-      <c r="X59" s="272" t="s">
+      <c r="X59" s="246" t="s">
         <v>36</v>
       </c>
-      <c r="Y59" s="288"/>
+      <c r="Y59" s="247"/>
       <c r="Z59" s="68"/>
       <c r="AA59" s="19"/>
       <c r="AB59" s="19"/>
@@ -31347,19 +31347,19 @@
     </row>
     <row r="60" spans="15:49" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O60" s="194"/>
-      <c r="P60" s="285" t="s">
+      <c r="P60" s="243" t="s">
         <v>627</v>
       </c>
-      <c r="Q60" s="286"/>
-      <c r="R60" s="286"/>
-      <c r="S60" s="286"/>
-      <c r="T60" s="286"/>
-      <c r="U60" s="287"/>
+      <c r="Q60" s="244"/>
+      <c r="R60" s="244"/>
+      <c r="S60" s="244"/>
+      <c r="T60" s="244"/>
+      <c r="U60" s="245"/>
       <c r="V60" s="193"/>
-      <c r="X60" s="289" t="s">
+      <c r="X60" s="249" t="s">
         <v>39</v>
       </c>
-      <c r="Y60" s="290"/>
+      <c r="Y60" s="250"/>
       <c r="Z60" s="73"/>
       <c r="AA60" s="74"/>
       <c r="AB60" s="74"/>
@@ -31387,10 +31387,10 @@
     </row>
     <row r="61" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O61" s="194"/>
-      <c r="P61" s="273" t="s">
+      <c r="P61" s="241" t="s">
         <v>628</v>
       </c>
-      <c r="Q61" s="273"/>
+      <c r="Q61" s="241"/>
       <c r="R61" s="218"/>
       <c r="S61" s="218"/>
       <c r="T61" s="219"/>
@@ -31399,10 +31399,10 @@
     </row>
     <row r="62" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O62" s="194"/>
-      <c r="P62" s="273" t="s">
+      <c r="P62" s="241" t="s">
         <v>629</v>
       </c>
-      <c r="Q62" s="273"/>
+      <c r="Q62" s="241"/>
       <c r="R62" s="218"/>
       <c r="S62" s="218"/>
       <c r="T62" s="219"/>
@@ -31411,10 +31411,10 @@
     </row>
     <row r="63" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O63" s="194"/>
-      <c r="P63" s="284" t="s">
+      <c r="P63" s="242" t="s">
         <v>39</v>
       </c>
-      <c r="Q63" s="284"/>
+      <c r="Q63" s="242"/>
       <c r="R63" s="218"/>
       <c r="S63" s="218"/>
       <c r="T63" s="219"/>
@@ -31461,44 +31461,12 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P58:U58"/>
-    <mergeCell ref="X58:Y58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="X59:Y59"/>
-    <mergeCell ref="P60:U60"/>
-    <mergeCell ref="X60:Y60"/>
-    <mergeCell ref="AR57:AW57"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="X55:Y55"/>
-    <mergeCell ref="Z55:AE55"/>
-    <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="AL55:AQ55"/>
-    <mergeCell ref="AR55:AW55"/>
-    <mergeCell ref="X56:Y56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="X57:Y57"/>
-    <mergeCell ref="Z57:AE57"/>
-    <mergeCell ref="AF57:AK57"/>
-    <mergeCell ref="AL57:AQ57"/>
-    <mergeCell ref="AR47:AW47"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P50:U50"/>
-    <mergeCell ref="X50:X51"/>
-    <mergeCell ref="P51:P52"/>
-    <mergeCell ref="X52:X53"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="X54:Y54"/>
-    <mergeCell ref="AL47:AQ47"/>
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="X46:Y46"/>
-    <mergeCell ref="X47:Y47"/>
-    <mergeCell ref="Z47:AE47"/>
-    <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="R4:R6"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="G5:M5"/>
     <mergeCell ref="AR44:AW44"/>
     <mergeCell ref="G8:M8"/>
     <mergeCell ref="G11:M11"/>
@@ -31515,12 +31483,44 @@
     <mergeCell ref="Z44:AE44"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="AL44:AQ44"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="R4:R6"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="G5:M5"/>
+    <mergeCell ref="X45:Y45"/>
+    <mergeCell ref="X46:Y46"/>
+    <mergeCell ref="X47:Y47"/>
+    <mergeCell ref="Z47:AE47"/>
+    <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="AR47:AW47"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P50:U50"/>
+    <mergeCell ref="X50:X51"/>
+    <mergeCell ref="P51:P52"/>
+    <mergeCell ref="X52:X53"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="X54:Y54"/>
+    <mergeCell ref="AL47:AQ47"/>
+    <mergeCell ref="AR57:AW57"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="X55:Y55"/>
+    <mergeCell ref="Z55:AE55"/>
+    <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="AL55:AQ55"/>
+    <mergeCell ref="AR55:AW55"/>
+    <mergeCell ref="X56:Y56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="X57:Y57"/>
+    <mergeCell ref="Z57:AE57"/>
+    <mergeCell ref="AF57:AK57"/>
+    <mergeCell ref="AL57:AQ57"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P58:U58"/>
+    <mergeCell ref="X58:Y58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="X59:Y59"/>
+    <mergeCell ref="P60:U60"/>
+    <mergeCell ref="X60:Y60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -31562,15 +31562,15 @@
       <c r="V2" s="190"/>
     </row>
     <row r="3" spans="2:23" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G3" s="241" t="s">
+      <c r="G3" s="282" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="242"/>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="M3" s="243"/>
+      <c r="H3" s="283"/>
+      <c r="I3" s="283"/>
+      <c r="J3" s="283"/>
+      <c r="K3" s="283"/>
+      <c r="L3" s="283"/>
+      <c r="M3" s="284"/>
       <c r="N3" s="213"/>
       <c r="O3" s="213"/>
       <c r="P3" s="213"/>
@@ -31610,39 +31610,39 @@
       <c r="O4" s="214"/>
       <c r="P4" s="214"/>
       <c r="Q4" s="194"/>
-      <c r="R4" s="244" t="s">
+      <c r="R4" s="285" t="s">
         <v>618</v>
       </c>
-      <c r="S4" s="247" t="s">
+      <c r="S4" s="263" t="s">
         <v>617</v>
       </c>
-      <c r="T4" s="248" t="s">
+      <c r="T4" s="288" t="s">
         <v>619</v>
       </c>
-      <c r="U4" s="248" t="s">
+      <c r="U4" s="288" t="s">
         <v>10</v>
       </c>
       <c r="V4" s="193"/>
       <c r="W4" s="39"/>
     </row>
     <row r="5" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G5" s="249" t="s">
+      <c r="G5" s="289" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="250"/>
-      <c r="I5" s="250"/>
-      <c r="J5" s="250"/>
-      <c r="K5" s="250"/>
-      <c r="L5" s="250"/>
-      <c r="M5" s="251"/>
+      <c r="H5" s="256"/>
+      <c r="I5" s="256"/>
+      <c r="J5" s="256"/>
+      <c r="K5" s="256"/>
+      <c r="L5" s="256"/>
+      <c r="M5" s="290"/>
       <c r="N5" s="91"/>
       <c r="O5" s="91"/>
       <c r="P5" s="91"/>
       <c r="Q5" s="194"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="247"/>
-      <c r="T5" s="248"/>
-      <c r="U5" s="248"/>
+      <c r="R5" s="286"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="288"/>
+      <c r="U5" s="288"/>
       <c r="V5" s="193"/>
       <c r="W5" s="39"/>
     </row>
@@ -31668,7 +31668,7 @@
       <c r="O6" s="91"/>
       <c r="P6" s="91"/>
       <c r="Q6" s="194"/>
-      <c r="R6" s="246"/>
+      <c r="R6" s="287"/>
       <c r="S6" s="234" t="s">
         <v>620</v>
       </c>
@@ -31715,15 +31715,15 @@
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="193"/>
-      <c r="G8" s="255" t="s">
+      <c r="G8" s="276" t="s">
         <v>0</v>
       </c>
-      <c r="H8" s="256"/>
-      <c r="I8" s="256"/>
-      <c r="J8" s="256"/>
-      <c r="K8" s="256"/>
-      <c r="L8" s="256"/>
-      <c r="M8" s="257"/>
+      <c r="H8" s="252"/>
+      <c r="I8" s="252"/>
+      <c r="J8" s="252"/>
+      <c r="K8" s="252"/>
+      <c r="L8" s="252"/>
+      <c r="M8" s="277"/>
       <c r="N8" s="91"/>
       <c r="O8" s="91"/>
       <c r="P8" s="91"/>
@@ -31806,15 +31806,15 @@
       </c>
       <c r="D11" s="38"/>
       <c r="E11" s="193"/>
-      <c r="G11" s="255" t="s">
+      <c r="G11" s="276" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="256"/>
-      <c r="I11" s="256"/>
-      <c r="J11" s="256"/>
-      <c r="K11" s="256"/>
-      <c r="L11" s="256"/>
-      <c r="M11" s="257"/>
+      <c r="H11" s="252"/>
+      <c r="I11" s="252"/>
+      <c r="J11" s="252"/>
+      <c r="K11" s="252"/>
+      <c r="L11" s="252"/>
+      <c r="M11" s="277"/>
       <c r="N11" s="91"/>
       <c r="O11" s="91"/>
       <c r="P11" s="91"/>
@@ -31897,15 +31897,15 @@
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="193"/>
-      <c r="G14" s="255" t="s">
+      <c r="G14" s="276" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="256"/>
-      <c r="I14" s="256"/>
-      <c r="J14" s="256"/>
-      <c r="K14" s="256"/>
-      <c r="L14" s="256"/>
-      <c r="M14" s="257"/>
+      <c r="H14" s="252"/>
+      <c r="I14" s="252"/>
+      <c r="J14" s="252"/>
+      <c r="K14" s="252"/>
+      <c r="L14" s="252"/>
+      <c r="M14" s="277"/>
       <c r="N14" s="91"/>
       <c r="O14" s="91"/>
       <c r="P14" s="91"/>
@@ -32050,15 +32050,15 @@
       </c>
       <c r="D19" s="38"/>
       <c r="E19" s="193"/>
-      <c r="G19" s="255" t="s">
+      <c r="G19" s="276" t="s">
         <v>114</v>
       </c>
-      <c r="H19" s="256"/>
-      <c r="I19" s="256"/>
-      <c r="J19" s="256"/>
-      <c r="K19" s="256"/>
-      <c r="L19" s="256"/>
-      <c r="M19" s="257"/>
+      <c r="H19" s="252"/>
+      <c r="I19" s="252"/>
+      <c r="J19" s="252"/>
+      <c r="K19" s="252"/>
+      <c r="L19" s="252"/>
+      <c r="M19" s="277"/>
       <c r="N19" s="91"/>
       <c r="O19" s="91"/>
       <c r="P19" s="91"/>
@@ -32165,27 +32165,27 @@
       <c r="T23" s="192"/>
       <c r="U23" s="192"/>
       <c r="V23" s="193"/>
-      <c r="X23" s="258" t="s">
+      <c r="X23" s="278" t="s">
         <v>227</v>
       </c>
-      <c r="Y23" s="258"/>
-      <c r="Z23" s="258"/>
-      <c r="AA23" s="258"/>
-      <c r="AB23" s="258"/>
-      <c r="AC23" s="258"/>
-      <c r="AD23" s="258"/>
-      <c r="AE23" s="258"/>
-      <c r="AF23" s="258"/>
-      <c r="AG23" s="258"/>
-      <c r="AH23" s="258"/>
-      <c r="AI23" s="258"/>
-      <c r="AJ23" s="258"/>
-      <c r="AK23" s="258"/>
-      <c r="AL23" s="258"/>
-      <c r="AM23" s="258"/>
-      <c r="AN23" s="258"/>
-      <c r="AO23" s="258"/>
-      <c r="AP23" s="258"/>
+      <c r="Y23" s="278"/>
+      <c r="Z23" s="278"/>
+      <c r="AA23" s="278"/>
+      <c r="AB23" s="278"/>
+      <c r="AC23" s="278"/>
+      <c r="AD23" s="278"/>
+      <c r="AE23" s="278"/>
+      <c r="AF23" s="278"/>
+      <c r="AG23" s="278"/>
+      <c r="AH23" s="278"/>
+      <c r="AI23" s="278"/>
+      <c r="AJ23" s="278"/>
+      <c r="AK23" s="278"/>
+      <c r="AL23" s="278"/>
+      <c r="AM23" s="278"/>
+      <c r="AN23" s="278"/>
+      <c r="AO23" s="278"/>
+      <c r="AP23" s="278"/>
     </row>
     <row r="24" spans="2:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q24" s="196"/>
@@ -32197,36 +32197,36 @@
       <c r="X24" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Y24" s="259" t="s">
+      <c r="Y24" s="279" t="s">
         <v>18</v>
       </c>
-      <c r="Z24" s="260"/>
-      <c r="AA24" s="261"/>
-      <c r="AB24" s="259" t="s">
+      <c r="Z24" s="280"/>
+      <c r="AA24" s="281"/>
+      <c r="AB24" s="279" t="s">
         <v>17</v>
       </c>
-      <c r="AC24" s="260"/>
-      <c r="AD24" s="261"/>
-      <c r="AE24" s="259" t="s">
+      <c r="AC24" s="280"/>
+      <c r="AD24" s="281"/>
+      <c r="AE24" s="279" t="s">
         <v>16</v>
       </c>
-      <c r="AF24" s="260"/>
-      <c r="AG24" s="261"/>
-      <c r="AH24" s="259" t="s">
+      <c r="AF24" s="280"/>
+      <c r="AG24" s="281"/>
+      <c r="AH24" s="279" t="s">
         <v>13</v>
       </c>
-      <c r="AI24" s="260"/>
-      <c r="AJ24" s="261"/>
-      <c r="AK24" s="259" t="s">
+      <c r="AI24" s="280"/>
+      <c r="AJ24" s="281"/>
+      <c r="AK24" s="279" t="s">
         <v>20</v>
       </c>
-      <c r="AL24" s="260"/>
-      <c r="AM24" s="261"/>
-      <c r="AN24" s="259" t="s">
+      <c r="AL24" s="280"/>
+      <c r="AM24" s="281"/>
+      <c r="AN24" s="279" t="s">
         <v>553</v>
       </c>
-      <c r="AO24" s="260"/>
-      <c r="AP24" s="261"/>
+      <c r="AO24" s="280"/>
+      <c r="AP24" s="281"/>
     </row>
     <row r="25" spans="2:42" ht="81.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="X25" s="64" t="s">
@@ -32740,48 +32740,48 @@
       <c r="P43" s="39"/>
     </row>
     <row r="44" spans="7:49" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X44" s="252" t="s">
+      <c r="X44" s="273" t="s">
         <v>238</v>
       </c>
-      <c r="Y44" s="254"/>
-      <c r="Z44" s="252" t="s">
+      <c r="Y44" s="275"/>
+      <c r="Z44" s="273" t="s">
         <v>237</v>
       </c>
-      <c r="AA44" s="253"/>
-      <c r="AB44" s="253"/>
-      <c r="AC44" s="253"/>
-      <c r="AD44" s="253"/>
-      <c r="AE44" s="254"/>
-      <c r="AF44" s="252" t="s">
+      <c r="AA44" s="274"/>
+      <c r="AB44" s="274"/>
+      <c r="AC44" s="274"/>
+      <c r="AD44" s="274"/>
+      <c r="AE44" s="275"/>
+      <c r="AF44" s="273" t="s">
         <v>239</v>
       </c>
-      <c r="AG44" s="253"/>
-      <c r="AH44" s="253"/>
-      <c r="AI44" s="253"/>
-      <c r="AJ44" s="253"/>
-      <c r="AK44" s="254"/>
-      <c r="AL44" s="252" t="s">
+      <c r="AG44" s="274"/>
+      <c r="AH44" s="274"/>
+      <c r="AI44" s="274"/>
+      <c r="AJ44" s="274"/>
+      <c r="AK44" s="275"/>
+      <c r="AL44" s="273" t="s">
         <v>240</v>
       </c>
-      <c r="AM44" s="253"/>
-      <c r="AN44" s="253"/>
-      <c r="AO44" s="253"/>
-      <c r="AP44" s="253"/>
-      <c r="AQ44" s="254"/>
-      <c r="AR44" s="252" t="s">
+      <c r="AM44" s="274"/>
+      <c r="AN44" s="274"/>
+      <c r="AO44" s="274"/>
+      <c r="AP44" s="274"/>
+      <c r="AQ44" s="275"/>
+      <c r="AR44" s="273" t="s">
         <v>241</v>
       </c>
-      <c r="AS44" s="253"/>
-      <c r="AT44" s="253"/>
-      <c r="AU44" s="253"/>
-      <c r="AV44" s="253"/>
-      <c r="AW44" s="254"/>
+      <c r="AS44" s="274"/>
+      <c r="AT44" s="274"/>
+      <c r="AU44" s="274"/>
+      <c r="AV44" s="274"/>
+      <c r="AW44" s="275"/>
     </row>
     <row r="45" spans="7:49" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X45" s="262" t="s">
+      <c r="X45" s="268" t="s">
         <v>40</v>
       </c>
-      <c r="Y45" s="263"/>
+      <c r="Y45" s="269"/>
       <c r="Z45" s="184" t="s">
         <v>117</v>
       </c>
@@ -32866,10 +32866,10 @@
       <c r="T46" s="215"/>
       <c r="U46" s="189"/>
       <c r="V46" s="190"/>
-      <c r="X46" s="264" t="s">
+      <c r="X46" s="270" t="s">
         <v>31</v>
       </c>
-      <c r="Y46" s="265"/>
+      <c r="Y46" s="271"/>
       <c r="Z46" s="66"/>
       <c r="AA46" s="22"/>
       <c r="AB46" s="22"/>
@@ -32906,47 +32906,47 @@
       <c r="T47" s="216"/>
       <c r="U47" s="211"/>
       <c r="V47" s="208"/>
-      <c r="X47" s="266"/>
-      <c r="Y47" s="267"/>
-      <c r="Z47" s="268" t="s">
+      <c r="X47" s="272"/>
+      <c r="Y47" s="255"/>
+      <c r="Z47" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="AA47" s="256"/>
-      <c r="AB47" s="256"/>
-      <c r="AC47" s="256"/>
-      <c r="AD47" s="256"/>
-      <c r="AE47" s="269"/>
-      <c r="AF47" s="268" t="s">
+      <c r="AA47" s="252"/>
+      <c r="AB47" s="252"/>
+      <c r="AC47" s="252"/>
+      <c r="AD47" s="252"/>
+      <c r="AE47" s="253"/>
+      <c r="AF47" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="AG47" s="256"/>
-      <c r="AH47" s="256"/>
-      <c r="AI47" s="256"/>
-      <c r="AJ47" s="256"/>
-      <c r="AK47" s="269"/>
-      <c r="AL47" s="268" t="s">
+      <c r="AG47" s="252"/>
+      <c r="AH47" s="252"/>
+      <c r="AI47" s="252"/>
+      <c r="AJ47" s="252"/>
+      <c r="AK47" s="253"/>
+      <c r="AL47" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="AM47" s="256"/>
-      <c r="AN47" s="256"/>
-      <c r="AO47" s="256"/>
-      <c r="AP47" s="256"/>
-      <c r="AQ47" s="269"/>
-      <c r="AR47" s="268" t="s">
+      <c r="AM47" s="252"/>
+      <c r="AN47" s="252"/>
+      <c r="AO47" s="252"/>
+      <c r="AP47" s="252"/>
+      <c r="AQ47" s="253"/>
+      <c r="AR47" s="251" t="s">
         <v>30</v>
       </c>
-      <c r="AS47" s="256"/>
-      <c r="AT47" s="256"/>
-      <c r="AU47" s="256"/>
-      <c r="AV47" s="256"/>
-      <c r="AW47" s="269"/>
+      <c r="AS47" s="252"/>
+      <c r="AT47" s="252"/>
+      <c r="AU47" s="252"/>
+      <c r="AV47" s="252"/>
+      <c r="AW47" s="253"/>
     </row>
     <row r="48" spans="7:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O48" s="194"/>
-      <c r="P48" s="270" t="s">
+      <c r="P48" s="261" t="s">
         <v>621</v>
       </c>
-      <c r="Q48" s="271"/>
+      <c r="Q48" s="262"/>
       <c r="R48" s="151" t="s">
         <v>223</v>
       </c>
@@ -32960,7 +32960,7 @@
         <v>622</v>
       </c>
       <c r="V48" s="193"/>
-      <c r="X48" s="272" t="s">
+      <c r="X48" s="246" t="s">
         <v>1</v>
       </c>
       <c r="Y48" s="72" t="s">
@@ -32993,16 +32993,16 @@
     </row>
     <row r="49" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O49" s="194"/>
-      <c r="P49" s="270" t="s">
+      <c r="P49" s="261" t="s">
         <v>31</v>
       </c>
-      <c r="Q49" s="271"/>
+      <c r="Q49" s="262"/>
       <c r="R49" s="31"/>
       <c r="S49" s="89"/>
       <c r="T49" s="224"/>
       <c r="U49" s="224"/>
       <c r="V49" s="193"/>
-      <c r="X49" s="272"/>
+      <c r="X49" s="246"/>
       <c r="Y49" s="72" t="s">
         <v>12</v>
       </c>
@@ -33033,16 +33033,16 @@
     </row>
     <row r="50" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O50" s="194"/>
-      <c r="P50" s="247" t="s">
+      <c r="P50" s="263" t="s">
         <v>30</v>
       </c>
-      <c r="Q50" s="247"/>
-      <c r="R50" s="247"/>
-      <c r="S50" s="247"/>
-      <c r="T50" s="247"/>
-      <c r="U50" s="247"/>
+      <c r="Q50" s="263"/>
+      <c r="R50" s="263"/>
+      <c r="S50" s="263"/>
+      <c r="T50" s="263"/>
+      <c r="U50" s="263"/>
       <c r="V50" s="193"/>
-      <c r="X50" s="272" t="s">
+      <c r="X50" s="246" t="s">
         <v>32</v>
       </c>
       <c r="Y50" s="72" t="s">
@@ -33075,7 +33075,7 @@
     </row>
     <row r="51" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O51" s="194"/>
-      <c r="P51" s="273" t="s">
+      <c r="P51" s="241" t="s">
         <v>1</v>
       </c>
       <c r="Q51" s="151" t="s">
@@ -33086,7 +33086,7 @@
       <c r="T51" s="219"/>
       <c r="U51" s="220"/>
       <c r="V51" s="193"/>
-      <c r="X51" s="272"/>
+      <c r="X51" s="246"/>
       <c r="Y51" s="72" t="s">
         <v>12</v>
       </c>
@@ -33117,7 +33117,7 @@
     </row>
     <row r="52" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O52" s="194"/>
-      <c r="P52" s="273"/>
+      <c r="P52" s="241"/>
       <c r="Q52" s="151" t="s">
         <v>12</v>
       </c>
@@ -33126,7 +33126,7 @@
       <c r="T52" s="219"/>
       <c r="U52" s="220"/>
       <c r="V52" s="193"/>
-      <c r="X52" s="274" t="s">
+      <c r="X52" s="264" t="s">
         <v>33</v>
       </c>
       <c r="Y52" s="72" t="s">
@@ -33159,7 +33159,7 @@
     </row>
     <row r="53" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O53" s="194"/>
-      <c r="P53" s="273" t="s">
+      <c r="P53" s="241" t="s">
         <v>623</v>
       </c>
       <c r="Q53" s="151" t="s">
@@ -33170,7 +33170,7 @@
       <c r="T53" s="219"/>
       <c r="U53" s="220"/>
       <c r="V53" s="193"/>
-      <c r="X53" s="275"/>
+      <c r="X53" s="265"/>
       <c r="Y53" s="72" t="s">
         <v>12</v>
       </c>
@@ -33201,7 +33201,7 @@
     </row>
     <row r="54" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O54" s="194"/>
-      <c r="P54" s="273"/>
+      <c r="P54" s="241"/>
       <c r="Q54" s="151" t="s">
         <v>12</v>
       </c>
@@ -33210,10 +33210,10 @@
       <c r="T54" s="219"/>
       <c r="U54" s="220"/>
       <c r="V54" s="193"/>
-      <c r="X54" s="276" t="s">
+      <c r="X54" s="266" t="s">
         <v>34</v>
       </c>
-      <c r="Y54" s="277"/>
+      <c r="Y54" s="267"/>
       <c r="Z54" s="70"/>
       <c r="AA54" s="25"/>
       <c r="AB54" s="25"/>
@@ -33241,7 +33241,7 @@
     </row>
     <row r="55" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O55" s="194"/>
-      <c r="P55" s="273" t="s">
+      <c r="P55" s="241" t="s">
         <v>624</v>
       </c>
       <c r="Q55" s="151" t="s">
@@ -33252,44 +33252,44 @@
       <c r="T55" s="219"/>
       <c r="U55" s="220"/>
       <c r="V55" s="193"/>
-      <c r="X55" s="278"/>
-      <c r="Y55" s="267"/>
-      <c r="Z55" s="278" t="s">
+      <c r="X55" s="254"/>
+      <c r="Y55" s="255"/>
+      <c r="Z55" s="254" t="s">
         <v>107</v>
       </c>
-      <c r="AA55" s="250"/>
-      <c r="AB55" s="250"/>
-      <c r="AC55" s="250"/>
-      <c r="AD55" s="250"/>
-      <c r="AE55" s="267"/>
-      <c r="AF55" s="278" t="s">
+      <c r="AA55" s="256"/>
+      <c r="AB55" s="256"/>
+      <c r="AC55" s="256"/>
+      <c r="AD55" s="256"/>
+      <c r="AE55" s="255"/>
+      <c r="AF55" s="254" t="s">
         <v>107</v>
       </c>
-      <c r="AG55" s="250"/>
-      <c r="AH55" s="250"/>
-      <c r="AI55" s="250"/>
-      <c r="AJ55" s="250"/>
-      <c r="AK55" s="267"/>
-      <c r="AL55" s="278" t="s">
+      <c r="AG55" s="256"/>
+      <c r="AH55" s="256"/>
+      <c r="AI55" s="256"/>
+      <c r="AJ55" s="256"/>
+      <c r="AK55" s="255"/>
+      <c r="AL55" s="254" t="s">
         <v>107</v>
       </c>
-      <c r="AM55" s="250"/>
-      <c r="AN55" s="250"/>
-      <c r="AO55" s="250"/>
-      <c r="AP55" s="250"/>
-      <c r="AQ55" s="267"/>
-      <c r="AR55" s="278" t="s">
+      <c r="AM55" s="256"/>
+      <c r="AN55" s="256"/>
+      <c r="AO55" s="256"/>
+      <c r="AP55" s="256"/>
+      <c r="AQ55" s="255"/>
+      <c r="AR55" s="254" t="s">
         <v>107</v>
       </c>
-      <c r="AS55" s="250"/>
-      <c r="AT55" s="250"/>
-      <c r="AU55" s="250"/>
-      <c r="AV55" s="250"/>
-      <c r="AW55" s="267"/>
+      <c r="AS55" s="256"/>
+      <c r="AT55" s="256"/>
+      <c r="AU55" s="256"/>
+      <c r="AV55" s="256"/>
+      <c r="AW55" s="255"/>
     </row>
     <row r="56" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O56" s="194"/>
-      <c r="P56" s="273"/>
+      <c r="P56" s="241"/>
       <c r="Q56" s="151" t="s">
         <v>12</v>
       </c>
@@ -33298,10 +33298,10 @@
       <c r="T56" s="219"/>
       <c r="U56" s="220"/>
       <c r="V56" s="193"/>
-      <c r="X56" s="279" t="s">
+      <c r="X56" s="257" t="s">
         <v>37</v>
       </c>
-      <c r="Y56" s="280"/>
+      <c r="Y56" s="258"/>
       <c r="Z56" s="68"/>
       <c r="AA56" s="19"/>
       <c r="AB56" s="19"/>
@@ -33329,65 +33329,65 @@
     </row>
     <row r="57" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O57" s="194"/>
-      <c r="P57" s="281" t="s">
+      <c r="P57" s="248" t="s">
         <v>625</v>
       </c>
-      <c r="Q57" s="281"/>
+      <c r="Q57" s="248"/>
       <c r="R57" s="218"/>
       <c r="S57" s="218"/>
       <c r="T57" s="219"/>
       <c r="U57" s="221"/>
       <c r="V57" s="210"/>
-      <c r="X57" s="282"/>
-      <c r="Y57" s="283"/>
-      <c r="Z57" s="268" t="s">
+      <c r="X57" s="259"/>
+      <c r="Y57" s="260"/>
+      <c r="Z57" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="AA57" s="256"/>
-      <c r="AB57" s="256"/>
-      <c r="AC57" s="256"/>
-      <c r="AD57" s="256"/>
-      <c r="AE57" s="269"/>
-      <c r="AF57" s="268" t="s">
+      <c r="AA57" s="252"/>
+      <c r="AB57" s="252"/>
+      <c r="AC57" s="252"/>
+      <c r="AD57" s="252"/>
+      <c r="AE57" s="253"/>
+      <c r="AF57" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="AG57" s="256"/>
-      <c r="AH57" s="256"/>
-      <c r="AI57" s="256"/>
-      <c r="AJ57" s="256"/>
-      <c r="AK57" s="269"/>
-      <c r="AL57" s="268" t="s">
+      <c r="AG57" s="252"/>
+      <c r="AH57" s="252"/>
+      <c r="AI57" s="252"/>
+      <c r="AJ57" s="252"/>
+      <c r="AK57" s="253"/>
+      <c r="AL57" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="AM57" s="256"/>
-      <c r="AN57" s="256"/>
-      <c r="AO57" s="256"/>
-      <c r="AP57" s="256"/>
-      <c r="AQ57" s="269"/>
-      <c r="AR57" s="268" t="s">
+      <c r="AM57" s="252"/>
+      <c r="AN57" s="252"/>
+      <c r="AO57" s="252"/>
+      <c r="AP57" s="252"/>
+      <c r="AQ57" s="253"/>
+      <c r="AR57" s="251" t="s">
         <v>108</v>
       </c>
-      <c r="AS57" s="256"/>
-      <c r="AT57" s="256"/>
-      <c r="AU57" s="256"/>
-      <c r="AV57" s="256"/>
-      <c r="AW57" s="269"/>
+      <c r="AS57" s="252"/>
+      <c r="AT57" s="252"/>
+      <c r="AU57" s="252"/>
+      <c r="AV57" s="252"/>
+      <c r="AW57" s="253"/>
     </row>
     <row r="58" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O58" s="194"/>
-      <c r="P58" s="285" t="s">
+      <c r="P58" s="243" t="s">
         <v>107</v>
       </c>
-      <c r="Q58" s="286"/>
-      <c r="R58" s="286"/>
-      <c r="S58" s="286"/>
-      <c r="T58" s="286"/>
-      <c r="U58" s="287"/>
+      <c r="Q58" s="244"/>
+      <c r="R58" s="244"/>
+      <c r="S58" s="244"/>
+      <c r="T58" s="244"/>
+      <c r="U58" s="245"/>
       <c r="V58" s="210"/>
-      <c r="X58" s="272" t="s">
+      <c r="X58" s="246" t="s">
         <v>38</v>
       </c>
-      <c r="Y58" s="288"/>
+      <c r="Y58" s="247"/>
       <c r="Z58" s="68"/>
       <c r="AA58" s="19"/>
       <c r="AB58" s="19"/>
@@ -33415,19 +33415,19 @@
     </row>
     <row r="59" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O59" s="194"/>
-      <c r="P59" s="281" t="s">
+      <c r="P59" s="248" t="s">
         <v>626</v>
       </c>
-      <c r="Q59" s="281"/>
+      <c r="Q59" s="248"/>
       <c r="R59" s="218"/>
       <c r="S59" s="218"/>
       <c r="T59" s="219"/>
       <c r="U59" s="221"/>
       <c r="V59" s="210"/>
-      <c r="X59" s="272" t="s">
+      <c r="X59" s="246" t="s">
         <v>36</v>
       </c>
-      <c r="Y59" s="288"/>
+      <c r="Y59" s="247"/>
       <c r="Z59" s="68"/>
       <c r="AA59" s="19"/>
       <c r="AB59" s="19"/>
@@ -33455,19 +33455,19 @@
     </row>
     <row r="60" spans="15:49" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O60" s="194"/>
-      <c r="P60" s="285" t="s">
+      <c r="P60" s="243" t="s">
         <v>627</v>
       </c>
-      <c r="Q60" s="286"/>
-      <c r="R60" s="286"/>
-      <c r="S60" s="286"/>
-      <c r="T60" s="286"/>
-      <c r="U60" s="287"/>
+      <c r="Q60" s="244"/>
+      <c r="R60" s="244"/>
+      <c r="S60" s="244"/>
+      <c r="T60" s="244"/>
+      <c r="U60" s="245"/>
       <c r="V60" s="193"/>
-      <c r="X60" s="289" t="s">
+      <c r="X60" s="249" t="s">
         <v>39</v>
       </c>
-      <c r="Y60" s="290"/>
+      <c r="Y60" s="250"/>
       <c r="Z60" s="73"/>
       <c r="AA60" s="74"/>
       <c r="AB60" s="74"/>
@@ -33495,10 +33495,10 @@
     </row>
     <row r="61" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O61" s="194"/>
-      <c r="P61" s="273" t="s">
+      <c r="P61" s="241" t="s">
         <v>628</v>
       </c>
-      <c r="Q61" s="273"/>
+      <c r="Q61" s="241"/>
       <c r="R61" s="218"/>
       <c r="S61" s="218"/>
       <c r="T61" s="219"/>
@@ -33507,10 +33507,10 @@
     </row>
     <row r="62" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O62" s="194"/>
-      <c r="P62" s="273" t="s">
+      <c r="P62" s="241" t="s">
         <v>629</v>
       </c>
-      <c r="Q62" s="273"/>
+      <c r="Q62" s="241"/>
       <c r="R62" s="218"/>
       <c r="S62" s="218"/>
       <c r="T62" s="219"/>
@@ -33519,10 +33519,10 @@
     </row>
     <row r="63" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O63" s="194"/>
-      <c r="P63" s="284" t="s">
+      <c r="P63" s="242" t="s">
         <v>39</v>
       </c>
-      <c r="Q63" s="284"/>
+      <c r="Q63" s="242"/>
       <c r="R63" s="218"/>
       <c r="S63" s="218"/>
       <c r="T63" s="219"/>
@@ -33569,24 +33569,38 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P60:U60"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P50:U50"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:U58"/>
-    <mergeCell ref="P51:P52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="X58:Y58"/>
-    <mergeCell ref="X59:Y59"/>
-    <mergeCell ref="X60:Y60"/>
-    <mergeCell ref="X57:Y57"/>
-    <mergeCell ref="Z57:AE57"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="R4:R6"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="G19:M19"/>
+    <mergeCell ref="G14:M14"/>
+    <mergeCell ref="G11:M11"/>
+    <mergeCell ref="G8:M8"/>
+    <mergeCell ref="G5:M5"/>
+    <mergeCell ref="X23:AP23"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="AB24:AD24"/>
+    <mergeCell ref="AE24:AG24"/>
+    <mergeCell ref="AH24:AJ24"/>
+    <mergeCell ref="AK24:AM24"/>
+    <mergeCell ref="AN24:AP24"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="Z44:AE44"/>
+    <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="AL44:AQ44"/>
+    <mergeCell ref="AR44:AW44"/>
+    <mergeCell ref="X45:Y45"/>
+    <mergeCell ref="X46:Y46"/>
+    <mergeCell ref="X47:Y47"/>
+    <mergeCell ref="Z47:AE47"/>
+    <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="AL47:AQ47"/>
+    <mergeCell ref="AR47:AW47"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="X50:X51"/>
+    <mergeCell ref="X52:X53"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="AL57:AQ57"/>
     <mergeCell ref="AR57:AW57"/>
@@ -33597,38 +33611,24 @@
     <mergeCell ref="X56:Y56"/>
     <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="AL55:AQ55"/>
-    <mergeCell ref="AL47:AQ47"/>
-    <mergeCell ref="AR47:AW47"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="X50:X51"/>
-    <mergeCell ref="X52:X53"/>
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="X46:Y46"/>
-    <mergeCell ref="X47:Y47"/>
-    <mergeCell ref="Z47:AE47"/>
-    <mergeCell ref="AF47:AK47"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="Z44:AE44"/>
-    <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="AL44:AQ44"/>
-    <mergeCell ref="AR44:AW44"/>
-    <mergeCell ref="X23:AP23"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="AB24:AD24"/>
-    <mergeCell ref="AE24:AG24"/>
-    <mergeCell ref="AH24:AJ24"/>
-    <mergeCell ref="AK24:AM24"/>
-    <mergeCell ref="AN24:AP24"/>
-    <mergeCell ref="G19:M19"/>
-    <mergeCell ref="G14:M14"/>
-    <mergeCell ref="G11:M11"/>
-    <mergeCell ref="G8:M8"/>
-    <mergeCell ref="G5:M5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="R4:R6"/>
-    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="X58:Y58"/>
+    <mergeCell ref="X59:Y59"/>
+    <mergeCell ref="X60:Y60"/>
+    <mergeCell ref="X57:Y57"/>
+    <mergeCell ref="Z57:AE57"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P50:U50"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:U58"/>
+    <mergeCell ref="P51:P52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P60:U60"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/erlb.xlsx
+++ b/erlb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Haw\logs\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846B8CE9-4092-4733-AA5F-3BC931361257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8FEE41-DAAC-4D1A-B214-45FCCDACA8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{54DBC823-74FD-41B1-B15F-EAE87DE01D59}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{54DBC823-74FD-41B1-B15F-EAE87DE01D59}"/>
   </bookViews>
   <sheets>
     <sheet name="ship" sheetId="28" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="764">
   <si>
     <t>Revolution</t>
   </si>
@@ -2957,6 +2957,9 @@
   </si>
   <si>
     <t>Units</t>
+  </si>
+  <si>
+    <t>(deg C)</t>
   </si>
 </sst>
 </file>
@@ -4973,9 +4976,300 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4985,24 +5279,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5015,275 +5294,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="79" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5291,23 +5318,44 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="77" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5318,60 +5366,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="77" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5384,14 +5402,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5411,27 +5438,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="75" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5443,12 +5452,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -19145,7 +19148,7 @@
       <c r="A8" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="B8" s="410">
+      <c r="B8" s="253">
         <f>1.8*B7</f>
         <v>39600</v>
       </c>
@@ -19157,7 +19160,7 @@
       <c r="A9" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="B9" s="409">
+      <c r="B9" s="252">
         <v>175</v>
       </c>
       <c r="C9" t="s">
@@ -19168,7 +19171,7 @@
       <c r="A10" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="B10" s="409">
+      <c r="B10" s="252">
         <v>143</v>
       </c>
       <c r="C10" t="s">
@@ -19179,7 +19182,7 @@
       <c r="A11" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="B11" s="409">
+      <c r="B11" s="252">
         <v>32.200000000000003</v>
       </c>
       <c r="C11" t="s">
@@ -19190,7 +19193,7 @@
       <c r="A12" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="B12" s="409">
+      <c r="B12" s="252">
         <v>11.2</v>
       </c>
       <c r="C12" t="s">
@@ -19201,7 +19204,7 @@
       <c r="A13" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="B13" s="409">
+      <c r="B13" s="252">
         <v>20</v>
       </c>
       <c r="C13" t="s">
@@ -19369,15 +19372,15 @@
       <c r="V2" s="190"/>
     </row>
     <row r="3" spans="2:23" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G3" s="284" t="s">
+      <c r="G3" s="299" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="285"/>
-      <c r="I3" s="285"/>
-      <c r="J3" s="285"/>
-      <c r="K3" s="285"/>
-      <c r="L3" s="285"/>
-      <c r="M3" s="286"/>
+      <c r="H3" s="300"/>
+      <c r="I3" s="300"/>
+      <c r="J3" s="300"/>
+      <c r="K3" s="300"/>
+      <c r="L3" s="300"/>
+      <c r="M3" s="301"/>
       <c r="N3" s="213"/>
       <c r="O3" s="213"/>
       <c r="P3" s="213"/>
@@ -19417,39 +19420,39 @@
       <c r="O4" s="214"/>
       <c r="P4" s="214"/>
       <c r="Q4" s="194"/>
-      <c r="R4" s="287" t="s">
+      <c r="R4" s="322" t="s">
         <v>618</v>
       </c>
-      <c r="S4" s="290" t="s">
+      <c r="S4" s="325" t="s">
         <v>617</v>
       </c>
-      <c r="T4" s="291" t="s">
+      <c r="T4" s="326" t="s">
         <v>619</v>
       </c>
-      <c r="U4" s="291" t="s">
+      <c r="U4" s="326" t="s">
         <v>10</v>
       </c>
       <c r="V4" s="193"/>
       <c r="W4" s="39"/>
     </row>
     <row r="5" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G5" s="292" t="s">
+      <c r="G5" s="327" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="261"/>
-      <c r="I5" s="261"/>
-      <c r="J5" s="261"/>
-      <c r="K5" s="261"/>
-      <c r="L5" s="261"/>
-      <c r="M5" s="293"/>
+      <c r="H5" s="328"/>
+      <c r="I5" s="328"/>
+      <c r="J5" s="328"/>
+      <c r="K5" s="328"/>
+      <c r="L5" s="328"/>
+      <c r="M5" s="329"/>
       <c r="N5" s="91"/>
       <c r="O5" s="91"/>
       <c r="P5" s="91"/>
       <c r="Q5" s="194"/>
-      <c r="R5" s="288"/>
-      <c r="S5" s="290"/>
-      <c r="T5" s="291"/>
-      <c r="U5" s="291"/>
+      <c r="R5" s="323"/>
+      <c r="S5" s="325"/>
+      <c r="T5" s="326"/>
+      <c r="U5" s="326"/>
       <c r="V5" s="193"/>
       <c r="W5" s="39"/>
     </row>
@@ -19475,7 +19478,7 @@
       <c r="O6" s="91"/>
       <c r="P6" s="91"/>
       <c r="Q6" s="194"/>
-      <c r="R6" s="289"/>
+      <c r="R6" s="324"/>
       <c r="S6" s="234" t="s">
         <v>620</v>
       </c>
@@ -19524,15 +19527,15 @@
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="193"/>
-      <c r="G8" s="278" t="s">
+      <c r="G8" s="333" t="s">
         <v>0</v>
       </c>
-      <c r="H8" s="257"/>
-      <c r="I8" s="257"/>
-      <c r="J8" s="257"/>
-      <c r="K8" s="257"/>
-      <c r="L8" s="257"/>
-      <c r="M8" s="279"/>
+      <c r="H8" s="334"/>
+      <c r="I8" s="334"/>
+      <c r="J8" s="334"/>
+      <c r="K8" s="334"/>
+      <c r="L8" s="334"/>
+      <c r="M8" s="335"/>
       <c r="N8" s="91"/>
       <c r="O8" s="91"/>
       <c r="P8" s="91"/>
@@ -19615,15 +19618,15 @@
       </c>
       <c r="D11" s="38"/>
       <c r="E11" s="193"/>
-      <c r="G11" s="278" t="s">
+      <c r="G11" s="333" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="257"/>
-      <c r="I11" s="257"/>
-      <c r="J11" s="257"/>
-      <c r="K11" s="257"/>
-      <c r="L11" s="257"/>
-      <c r="M11" s="279"/>
+      <c r="H11" s="334"/>
+      <c r="I11" s="334"/>
+      <c r="J11" s="334"/>
+      <c r="K11" s="334"/>
+      <c r="L11" s="334"/>
+      <c r="M11" s="335"/>
       <c r="N11" s="91"/>
       <c r="O11" s="91"/>
       <c r="P11" s="91"/>
@@ -19706,15 +19709,15 @@
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="193"/>
-      <c r="G14" s="278" t="s">
+      <c r="G14" s="333" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="257"/>
-      <c r="I14" s="257"/>
-      <c r="J14" s="257"/>
-      <c r="K14" s="257"/>
-      <c r="L14" s="257"/>
-      <c r="M14" s="279"/>
+      <c r="H14" s="334"/>
+      <c r="I14" s="334"/>
+      <c r="J14" s="334"/>
+      <c r="K14" s="334"/>
+      <c r="L14" s="334"/>
+      <c r="M14" s="335"/>
       <c r="N14" s="91"/>
       <c r="O14" s="91"/>
       <c r="P14" s="91"/>
@@ -19859,15 +19862,15 @@
       </c>
       <c r="D19" s="38"/>
       <c r="E19" s="193"/>
-      <c r="G19" s="278" t="s">
+      <c r="G19" s="333" t="s">
         <v>114</v>
       </c>
-      <c r="H19" s="257"/>
-      <c r="I19" s="257"/>
-      <c r="J19" s="257"/>
-      <c r="K19" s="257"/>
-      <c r="L19" s="257"/>
-      <c r="M19" s="279"/>
+      <c r="H19" s="334"/>
+      <c r="I19" s="334"/>
+      <c r="J19" s="334"/>
+      <c r="K19" s="334"/>
+      <c r="L19" s="334"/>
+      <c r="M19" s="335"/>
       <c r="N19" s="91"/>
       <c r="O19" s="91"/>
       <c r="P19" s="91"/>
@@ -19974,27 +19977,27 @@
       <c r="T23" s="192"/>
       <c r="U23" s="192"/>
       <c r="V23" s="193"/>
-      <c r="X23" s="280" t="s">
+      <c r="X23" s="336" t="s">
         <v>227</v>
       </c>
-      <c r="Y23" s="280"/>
-      <c r="Z23" s="280"/>
-      <c r="AA23" s="280"/>
-      <c r="AB23" s="280"/>
-      <c r="AC23" s="280"/>
-      <c r="AD23" s="280"/>
-      <c r="AE23" s="280"/>
-      <c r="AF23" s="280"/>
-      <c r="AG23" s="280"/>
-      <c r="AH23" s="280"/>
-      <c r="AI23" s="280"/>
-      <c r="AJ23" s="280"/>
-      <c r="AK23" s="280"/>
-      <c r="AL23" s="280"/>
-      <c r="AM23" s="280"/>
-      <c r="AN23" s="280"/>
-      <c r="AO23" s="280"/>
-      <c r="AP23" s="280"/>
+      <c r="Y23" s="336"/>
+      <c r="Z23" s="336"/>
+      <c r="AA23" s="336"/>
+      <c r="AB23" s="336"/>
+      <c r="AC23" s="336"/>
+      <c r="AD23" s="336"/>
+      <c r="AE23" s="336"/>
+      <c r="AF23" s="336"/>
+      <c r="AG23" s="336"/>
+      <c r="AH23" s="336"/>
+      <c r="AI23" s="336"/>
+      <c r="AJ23" s="336"/>
+      <c r="AK23" s="336"/>
+      <c r="AL23" s="336"/>
+      <c r="AM23" s="336"/>
+      <c r="AN23" s="336"/>
+      <c r="AO23" s="336"/>
+      <c r="AP23" s="336"/>
     </row>
     <row r="24" spans="2:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q24" s="196"/>
@@ -20006,36 +20009,36 @@
       <c r="X24" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Y24" s="281" t="s">
+      <c r="Y24" s="319" t="s">
         <v>18</v>
       </c>
-      <c r="Z24" s="282"/>
-      <c r="AA24" s="283"/>
-      <c r="AB24" s="281" t="s">
+      <c r="Z24" s="320"/>
+      <c r="AA24" s="321"/>
+      <c r="AB24" s="319" t="s">
         <v>17</v>
       </c>
-      <c r="AC24" s="282"/>
-      <c r="AD24" s="283"/>
-      <c r="AE24" s="281" t="s">
+      <c r="AC24" s="320"/>
+      <c r="AD24" s="321"/>
+      <c r="AE24" s="319" t="s">
         <v>16</v>
       </c>
-      <c r="AF24" s="282"/>
-      <c r="AG24" s="283"/>
-      <c r="AH24" s="281" t="s">
+      <c r="AF24" s="320"/>
+      <c r="AG24" s="321"/>
+      <c r="AH24" s="319" t="s">
         <v>13</v>
       </c>
-      <c r="AI24" s="282"/>
-      <c r="AJ24" s="283"/>
-      <c r="AK24" s="281" t="s">
+      <c r="AI24" s="320"/>
+      <c r="AJ24" s="321"/>
+      <c r="AK24" s="319" t="s">
         <v>20</v>
       </c>
-      <c r="AL24" s="282"/>
-      <c r="AM24" s="283"/>
-      <c r="AN24" s="281" t="s">
+      <c r="AL24" s="320"/>
+      <c r="AM24" s="321"/>
+      <c r="AN24" s="319" t="s">
         <v>553</v>
       </c>
-      <c r="AO24" s="282"/>
-      <c r="AP24" s="283"/>
+      <c r="AO24" s="320"/>
+      <c r="AP24" s="321"/>
     </row>
     <row r="25" spans="2:42" ht="81.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="X25" s="64" t="s">
@@ -20549,48 +20552,48 @@
       <c r="P43" s="39"/>
     </row>
     <row r="44" spans="7:49" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X44" s="275" t="s">
+      <c r="X44" s="330" t="s">
         <v>238</v>
       </c>
-      <c r="Y44" s="277"/>
-      <c r="Z44" s="275" t="s">
+      <c r="Y44" s="332"/>
+      <c r="Z44" s="330" t="s">
         <v>237</v>
       </c>
-      <c r="AA44" s="276"/>
-      <c r="AB44" s="276"/>
-      <c r="AC44" s="276"/>
-      <c r="AD44" s="276"/>
-      <c r="AE44" s="277"/>
-      <c r="AF44" s="275" t="s">
+      <c r="AA44" s="331"/>
+      <c r="AB44" s="331"/>
+      <c r="AC44" s="331"/>
+      <c r="AD44" s="331"/>
+      <c r="AE44" s="332"/>
+      <c r="AF44" s="330" t="s">
         <v>239</v>
       </c>
-      <c r="AG44" s="276"/>
-      <c r="AH44" s="276"/>
-      <c r="AI44" s="276"/>
-      <c r="AJ44" s="276"/>
-      <c r="AK44" s="277"/>
-      <c r="AL44" s="275" t="s">
+      <c r="AG44" s="331"/>
+      <c r="AH44" s="331"/>
+      <c r="AI44" s="331"/>
+      <c r="AJ44" s="331"/>
+      <c r="AK44" s="332"/>
+      <c r="AL44" s="330" t="s">
         <v>240</v>
       </c>
-      <c r="AM44" s="276"/>
-      <c r="AN44" s="276"/>
-      <c r="AO44" s="276"/>
-      <c r="AP44" s="276"/>
-      <c r="AQ44" s="277"/>
-      <c r="AR44" s="275" t="s">
+      <c r="AM44" s="331"/>
+      <c r="AN44" s="331"/>
+      <c r="AO44" s="331"/>
+      <c r="AP44" s="331"/>
+      <c r="AQ44" s="332"/>
+      <c r="AR44" s="330" t="s">
         <v>241</v>
       </c>
-      <c r="AS44" s="276"/>
-      <c r="AT44" s="276"/>
-      <c r="AU44" s="276"/>
-      <c r="AV44" s="276"/>
-      <c r="AW44" s="277"/>
+      <c r="AS44" s="331"/>
+      <c r="AT44" s="331"/>
+      <c r="AU44" s="331"/>
+      <c r="AV44" s="331"/>
+      <c r="AW44" s="332"/>
     </row>
     <row r="45" spans="7:49" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X45" s="270" t="s">
+      <c r="X45" s="337" t="s">
         <v>40</v>
       </c>
-      <c r="Y45" s="271"/>
+      <c r="Y45" s="338"/>
       <c r="Z45" s="184" t="s">
         <v>117</v>
       </c>
@@ -20673,10 +20676,10 @@
       <c r="S46" s="215"/>
       <c r="T46" s="215"/>
       <c r="U46" s="190"/>
-      <c r="X46" s="272" t="s">
+      <c r="X46" s="339" t="s">
         <v>31</v>
       </c>
-      <c r="Y46" s="273"/>
+      <c r="Y46" s="340"/>
       <c r="Z46" s="66"/>
       <c r="AA46" s="22"/>
       <c r="AB46" s="22"/>
@@ -20711,40 +20714,40 @@
       <c r="S47" s="216"/>
       <c r="T47" s="216"/>
       <c r="U47" s="208"/>
-      <c r="X47" s="274"/>
-      <c r="Y47" s="260"/>
-      <c r="Z47" s="256" t="s">
+      <c r="X47" s="341"/>
+      <c r="Y47" s="342"/>
+      <c r="Z47" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="AA47" s="257"/>
-      <c r="AB47" s="257"/>
-      <c r="AC47" s="257"/>
-      <c r="AD47" s="257"/>
-      <c r="AE47" s="258"/>
-      <c r="AF47" s="256" t="s">
+      <c r="AA47" s="334"/>
+      <c r="AB47" s="334"/>
+      <c r="AC47" s="334"/>
+      <c r="AD47" s="334"/>
+      <c r="AE47" s="344"/>
+      <c r="AF47" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="AG47" s="257"/>
-      <c r="AH47" s="257"/>
-      <c r="AI47" s="257"/>
-      <c r="AJ47" s="257"/>
-      <c r="AK47" s="258"/>
-      <c r="AL47" s="256" t="s">
+      <c r="AG47" s="334"/>
+      <c r="AH47" s="334"/>
+      <c r="AI47" s="334"/>
+      <c r="AJ47" s="334"/>
+      <c r="AK47" s="344"/>
+      <c r="AL47" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="AM47" s="257"/>
-      <c r="AN47" s="257"/>
-      <c r="AO47" s="257"/>
-      <c r="AP47" s="257"/>
-      <c r="AQ47" s="258"/>
-      <c r="AR47" s="256" t="s">
+      <c r="AM47" s="334"/>
+      <c r="AN47" s="334"/>
+      <c r="AO47" s="334"/>
+      <c r="AP47" s="334"/>
+      <c r="AQ47" s="344"/>
+      <c r="AR47" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="AS47" s="257"/>
-      <c r="AT47" s="257"/>
-      <c r="AU47" s="257"/>
-      <c r="AV47" s="257"/>
-      <c r="AW47" s="258"/>
+      <c r="AS47" s="334"/>
+      <c r="AT47" s="334"/>
+      <c r="AU47" s="334"/>
+      <c r="AV47" s="334"/>
+      <c r="AW47" s="344"/>
     </row>
     <row r="48" spans="7:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P48" s="245" t="s">
@@ -20763,7 +20766,7 @@
         <v>622</v>
       </c>
       <c r="U48" s="193"/>
-      <c r="X48" s="252" t="s">
+      <c r="X48" s="345" t="s">
         <v>1</v>
       </c>
       <c r="Y48" s="72" t="s">
@@ -20803,7 +20806,7 @@
       <c r="S49" s="224"/>
       <c r="T49" s="224"/>
       <c r="U49" s="193"/>
-      <c r="X49" s="252"/>
+      <c r="X49" s="345"/>
       <c r="Y49" s="72" t="s">
         <v>12</v>
       </c>
@@ -20841,7 +20844,7 @@
       <c r="S50" s="227"/>
       <c r="T50" s="227"/>
       <c r="U50" s="193"/>
-      <c r="X50" s="252" t="s">
+      <c r="X50" s="345" t="s">
         <v>32</v>
       </c>
       <c r="Y50" s="72" t="s">
@@ -20881,7 +20884,7 @@
       <c r="S51" s="219"/>
       <c r="T51" s="220"/>
       <c r="U51" s="193"/>
-      <c r="X51" s="252"/>
+      <c r="X51" s="345"/>
       <c r="Y51" s="72" t="s">
         <v>12</v>
       </c>
@@ -20919,7 +20922,7 @@
       <c r="S52" s="219"/>
       <c r="T52" s="220"/>
       <c r="U52" s="193"/>
-      <c r="X52" s="266" t="s">
+      <c r="X52" s="346" t="s">
         <v>33</v>
       </c>
       <c r="Y52" s="72" t="s">
@@ -20959,7 +20962,7 @@
       <c r="S53" s="219"/>
       <c r="T53" s="220"/>
       <c r="U53" s="193"/>
-      <c r="X53" s="267"/>
+      <c r="X53" s="347"/>
       <c r="Y53" s="72" t="s">
         <v>12</v>
       </c>
@@ -20997,10 +21000,10 @@
       <c r="S54" s="219"/>
       <c r="T54" s="220"/>
       <c r="U54" s="193"/>
-      <c r="X54" s="268" t="s">
+      <c r="X54" s="348" t="s">
         <v>34</v>
       </c>
-      <c r="Y54" s="269"/>
+      <c r="Y54" s="349"/>
       <c r="Z54" s="70"/>
       <c r="AA54" s="25"/>
       <c r="AB54" s="25"/>
@@ -21035,40 +21038,40 @@
       <c r="S55" s="219"/>
       <c r="T55" s="220"/>
       <c r="U55" s="193"/>
-      <c r="X55" s="259"/>
-      <c r="Y55" s="260"/>
-      <c r="Z55" s="259" t="s">
+      <c r="X55" s="353"/>
+      <c r="Y55" s="342"/>
+      <c r="Z55" s="353" t="s">
         <v>107</v>
       </c>
-      <c r="AA55" s="261"/>
-      <c r="AB55" s="261"/>
-      <c r="AC55" s="261"/>
-      <c r="AD55" s="261"/>
-      <c r="AE55" s="260"/>
-      <c r="AF55" s="259" t="s">
+      <c r="AA55" s="328"/>
+      <c r="AB55" s="328"/>
+      <c r="AC55" s="328"/>
+      <c r="AD55" s="328"/>
+      <c r="AE55" s="342"/>
+      <c r="AF55" s="353" t="s">
         <v>107</v>
       </c>
-      <c r="AG55" s="261"/>
-      <c r="AH55" s="261"/>
-      <c r="AI55" s="261"/>
-      <c r="AJ55" s="261"/>
-      <c r="AK55" s="260"/>
-      <c r="AL55" s="259" t="s">
+      <c r="AG55" s="328"/>
+      <c r="AH55" s="328"/>
+      <c r="AI55" s="328"/>
+      <c r="AJ55" s="328"/>
+      <c r="AK55" s="342"/>
+      <c r="AL55" s="353" t="s">
         <v>107</v>
       </c>
-      <c r="AM55" s="261"/>
-      <c r="AN55" s="261"/>
-      <c r="AO55" s="261"/>
-      <c r="AP55" s="261"/>
-      <c r="AQ55" s="260"/>
-      <c r="AR55" s="259" t="s">
+      <c r="AM55" s="328"/>
+      <c r="AN55" s="328"/>
+      <c r="AO55" s="328"/>
+      <c r="AP55" s="328"/>
+      <c r="AQ55" s="342"/>
+      <c r="AR55" s="353" t="s">
         <v>107</v>
       </c>
-      <c r="AS55" s="261"/>
-      <c r="AT55" s="261"/>
-      <c r="AU55" s="261"/>
-      <c r="AV55" s="261"/>
-      <c r="AW55" s="260"/>
+      <c r="AS55" s="328"/>
+      <c r="AT55" s="328"/>
+      <c r="AU55" s="328"/>
+      <c r="AV55" s="328"/>
+      <c r="AW55" s="342"/>
     </row>
     <row r="56" spans="16:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P56" s="227" t="s">
@@ -21079,10 +21082,10 @@
       <c r="S56" s="219"/>
       <c r="T56" s="220"/>
       <c r="U56" s="193"/>
-      <c r="X56" s="262" t="s">
+      <c r="X56" s="354" t="s">
         <v>37</v>
       </c>
-      <c r="Y56" s="263"/>
+      <c r="Y56" s="355"/>
       <c r="Z56" s="68"/>
       <c r="AA56" s="19"/>
       <c r="AB56" s="19"/>
@@ -21117,40 +21120,40 @@
       <c r="S57" s="219"/>
       <c r="T57" s="221"/>
       <c r="U57" s="210"/>
-      <c r="X57" s="264"/>
-      <c r="Y57" s="265"/>
-      <c r="Z57" s="256" t="s">
+      <c r="X57" s="356"/>
+      <c r="Y57" s="357"/>
+      <c r="Z57" s="343" t="s">
         <v>108</v>
       </c>
-      <c r="AA57" s="257"/>
-      <c r="AB57" s="257"/>
-      <c r="AC57" s="257"/>
-      <c r="AD57" s="257"/>
-      <c r="AE57" s="258"/>
-      <c r="AF57" s="256" t="s">
+      <c r="AA57" s="334"/>
+      <c r="AB57" s="334"/>
+      <c r="AC57" s="334"/>
+      <c r="AD57" s="334"/>
+      <c r="AE57" s="344"/>
+      <c r="AF57" s="343" t="s">
         <v>108</v>
       </c>
-      <c r="AG57" s="257"/>
-      <c r="AH57" s="257"/>
-      <c r="AI57" s="257"/>
-      <c r="AJ57" s="257"/>
-      <c r="AK57" s="258"/>
-      <c r="AL57" s="256" t="s">
+      <c r="AG57" s="334"/>
+      <c r="AH57" s="334"/>
+      <c r="AI57" s="334"/>
+      <c r="AJ57" s="334"/>
+      <c r="AK57" s="344"/>
+      <c r="AL57" s="343" t="s">
         <v>108</v>
       </c>
-      <c r="AM57" s="257"/>
-      <c r="AN57" s="257"/>
-      <c r="AO57" s="257"/>
-      <c r="AP57" s="257"/>
-      <c r="AQ57" s="258"/>
-      <c r="AR57" s="256" t="s">
+      <c r="AM57" s="334"/>
+      <c r="AN57" s="334"/>
+      <c r="AO57" s="334"/>
+      <c r="AP57" s="334"/>
+      <c r="AQ57" s="344"/>
+      <c r="AR57" s="343" t="s">
         <v>108</v>
       </c>
-      <c r="AS57" s="257"/>
-      <c r="AT57" s="257"/>
-      <c r="AU57" s="257"/>
-      <c r="AV57" s="257"/>
-      <c r="AW57" s="258"/>
+      <c r="AS57" s="334"/>
+      <c r="AT57" s="334"/>
+      <c r="AU57" s="334"/>
+      <c r="AV57" s="334"/>
+      <c r="AW57" s="344"/>
     </row>
     <row r="58" spans="16:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P58" s="230" t="s">
@@ -21161,10 +21164,10 @@
       <c r="S58" s="246"/>
       <c r="T58" s="247"/>
       <c r="U58" s="210"/>
-      <c r="X58" s="252" t="s">
+      <c r="X58" s="345" t="s">
         <v>38</v>
       </c>
-      <c r="Y58" s="253"/>
+      <c r="Y58" s="350"/>
       <c r="Z58" s="68"/>
       <c r="AA58" s="19"/>
       <c r="AB58" s="19"/>
@@ -21199,10 +21202,10 @@
       <c r="S59" s="219"/>
       <c r="T59" s="221"/>
       <c r="U59" s="210"/>
-      <c r="X59" s="252" t="s">
+      <c r="X59" s="345" t="s">
         <v>36</v>
       </c>
-      <c r="Y59" s="253"/>
+      <c r="Y59" s="350"/>
       <c r="Z59" s="68"/>
       <c r="AA59" s="19"/>
       <c r="AB59" s="19"/>
@@ -21237,10 +21240,10 @@
       <c r="S60" s="246"/>
       <c r="T60" s="247"/>
       <c r="U60" s="193"/>
-      <c r="X60" s="254" t="s">
+      <c r="X60" s="351" t="s">
         <v>39</v>
       </c>
-      <c r="Y60" s="255"/>
+      <c r="Y60" s="352"/>
       <c r="Z60" s="73"/>
       <c r="AA60" s="74"/>
       <c r="AB60" s="74"/>
@@ -21332,12 +21335,31 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="R4:R6"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="G5:M5"/>
+    <mergeCell ref="X58:Y58"/>
+    <mergeCell ref="X59:Y59"/>
+    <mergeCell ref="X60:Y60"/>
+    <mergeCell ref="AR57:AW57"/>
+    <mergeCell ref="X55:Y55"/>
+    <mergeCell ref="Z55:AE55"/>
+    <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="AL55:AQ55"/>
+    <mergeCell ref="AR55:AW55"/>
+    <mergeCell ref="X56:Y56"/>
+    <mergeCell ref="X57:Y57"/>
+    <mergeCell ref="Z57:AE57"/>
+    <mergeCell ref="AF57:AK57"/>
+    <mergeCell ref="AL57:AQ57"/>
+    <mergeCell ref="AR47:AW47"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="X50:X51"/>
+    <mergeCell ref="X52:X53"/>
+    <mergeCell ref="X54:Y54"/>
+    <mergeCell ref="AL47:AQ47"/>
+    <mergeCell ref="X45:Y45"/>
+    <mergeCell ref="X46:Y46"/>
+    <mergeCell ref="X47:Y47"/>
+    <mergeCell ref="Z47:AE47"/>
+    <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="AR44:AW44"/>
     <mergeCell ref="G8:M8"/>
     <mergeCell ref="G11:M11"/>
@@ -21354,31 +21376,12 @@
     <mergeCell ref="Z44:AE44"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="AL44:AQ44"/>
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="X46:Y46"/>
-    <mergeCell ref="X47:Y47"/>
-    <mergeCell ref="Z47:AE47"/>
-    <mergeCell ref="AF47:AK47"/>
-    <mergeCell ref="AR47:AW47"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="X50:X51"/>
-    <mergeCell ref="X52:X53"/>
-    <mergeCell ref="X54:Y54"/>
-    <mergeCell ref="AL47:AQ47"/>
-    <mergeCell ref="X58:Y58"/>
-    <mergeCell ref="X59:Y59"/>
-    <mergeCell ref="X60:Y60"/>
-    <mergeCell ref="AR57:AW57"/>
-    <mergeCell ref="X55:Y55"/>
-    <mergeCell ref="Z55:AE55"/>
-    <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="AL55:AQ55"/>
-    <mergeCell ref="AR55:AW55"/>
-    <mergeCell ref="X56:Y56"/>
-    <mergeCell ref="X57:Y57"/>
-    <mergeCell ref="Z57:AE57"/>
-    <mergeCell ref="AF57:AK57"/>
-    <mergeCell ref="AL57:AQ57"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="R4:R6"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="G5:M5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21420,15 +21423,15 @@
       <c r="V2" s="190"/>
     </row>
     <row r="3" spans="2:23" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G3" s="284" t="s">
+      <c r="G3" s="299" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="285"/>
-      <c r="I3" s="285"/>
-      <c r="J3" s="285"/>
-      <c r="K3" s="285"/>
-      <c r="L3" s="285"/>
-      <c r="M3" s="286"/>
+      <c r="H3" s="300"/>
+      <c r="I3" s="300"/>
+      <c r="J3" s="300"/>
+      <c r="K3" s="300"/>
+      <c r="L3" s="300"/>
+      <c r="M3" s="301"/>
       <c r="N3" s="213"/>
       <c r="O3" s="213"/>
       <c r="P3" s="213"/>
@@ -21468,39 +21471,39 @@
       <c r="O4" s="214"/>
       <c r="P4" s="214"/>
       <c r="Q4" s="194"/>
-      <c r="R4" s="287" t="s">
+      <c r="R4" s="322" t="s">
         <v>618</v>
       </c>
-      <c r="S4" s="290" t="s">
+      <c r="S4" s="325" t="s">
         <v>617</v>
       </c>
-      <c r="T4" s="291" t="s">
+      <c r="T4" s="326" t="s">
         <v>619</v>
       </c>
-      <c r="U4" s="291" t="s">
+      <c r="U4" s="326" t="s">
         <v>10</v>
       </c>
       <c r="V4" s="193"/>
       <c r="W4" s="39"/>
     </row>
     <row r="5" spans="2:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G5" s="292" t="s">
+      <c r="G5" s="327" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="261"/>
-      <c r="I5" s="261"/>
-      <c r="J5" s="261"/>
-      <c r="K5" s="261"/>
-      <c r="L5" s="261"/>
-      <c r="M5" s="293"/>
+      <c r="H5" s="328"/>
+      <c r="I5" s="328"/>
+      <c r="J5" s="328"/>
+      <c r="K5" s="328"/>
+      <c r="L5" s="328"/>
+      <c r="M5" s="329"/>
       <c r="N5" s="91"/>
       <c r="O5" s="91"/>
       <c r="P5" s="91"/>
       <c r="Q5" s="194"/>
-      <c r="R5" s="288"/>
-      <c r="S5" s="290"/>
-      <c r="T5" s="291"/>
-      <c r="U5" s="291"/>
+      <c r="R5" s="323"/>
+      <c r="S5" s="325"/>
+      <c r="T5" s="326"/>
+      <c r="U5" s="326"/>
       <c r="V5" s="193"/>
       <c r="W5" s="39"/>
     </row>
@@ -21526,7 +21529,7 @@
       <c r="O6" s="91"/>
       <c r="P6" s="91"/>
       <c r="Q6" s="194"/>
-      <c r="R6" s="289"/>
+      <c r="R6" s="324"/>
       <c r="S6" s="234" t="s">
         <v>620</v>
       </c>
@@ -21573,15 +21576,15 @@
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="193"/>
-      <c r="G8" s="278" t="s">
+      <c r="G8" s="333" t="s">
         <v>0</v>
       </c>
-      <c r="H8" s="257"/>
-      <c r="I8" s="257"/>
-      <c r="J8" s="257"/>
-      <c r="K8" s="257"/>
-      <c r="L8" s="257"/>
-      <c r="M8" s="279"/>
+      <c r="H8" s="334"/>
+      <c r="I8" s="334"/>
+      <c r="J8" s="334"/>
+      <c r="K8" s="334"/>
+      <c r="L8" s="334"/>
+      <c r="M8" s="335"/>
       <c r="N8" s="91"/>
       <c r="O8" s="91"/>
       <c r="P8" s="91"/>
@@ -21664,15 +21667,15 @@
       </c>
       <c r="D11" s="38"/>
       <c r="E11" s="193"/>
-      <c r="G11" s="278" t="s">
+      <c r="G11" s="333" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="257"/>
-      <c r="I11" s="257"/>
-      <c r="J11" s="257"/>
-      <c r="K11" s="257"/>
-      <c r="L11" s="257"/>
-      <c r="M11" s="279"/>
+      <c r="H11" s="334"/>
+      <c r="I11" s="334"/>
+      <c r="J11" s="334"/>
+      <c r="K11" s="334"/>
+      <c r="L11" s="334"/>
+      <c r="M11" s="335"/>
       <c r="N11" s="91"/>
       <c r="O11" s="91"/>
       <c r="P11" s="91"/>
@@ -21755,15 +21758,15 @@
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="193"/>
-      <c r="G14" s="278" t="s">
+      <c r="G14" s="333" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="257"/>
-      <c r="I14" s="257"/>
-      <c r="J14" s="257"/>
-      <c r="K14" s="257"/>
-      <c r="L14" s="257"/>
-      <c r="M14" s="279"/>
+      <c r="H14" s="334"/>
+      <c r="I14" s="334"/>
+      <c r="J14" s="334"/>
+      <c r="K14" s="334"/>
+      <c r="L14" s="334"/>
+      <c r="M14" s="335"/>
       <c r="N14" s="91"/>
       <c r="O14" s="91"/>
       <c r="P14" s="91"/>
@@ -21908,15 +21911,15 @@
       </c>
       <c r="D19" s="38"/>
       <c r="E19" s="193"/>
-      <c r="G19" s="278" t="s">
+      <c r="G19" s="333" t="s">
         <v>114</v>
       </c>
-      <c r="H19" s="257"/>
-      <c r="I19" s="257"/>
-      <c r="J19" s="257"/>
-      <c r="K19" s="257"/>
-      <c r="L19" s="257"/>
-      <c r="M19" s="279"/>
+      <c r="H19" s="334"/>
+      <c r="I19" s="334"/>
+      <c r="J19" s="334"/>
+      <c r="K19" s="334"/>
+      <c r="L19" s="334"/>
+      <c r="M19" s="335"/>
       <c r="N19" s="91"/>
       <c r="O19" s="91"/>
       <c r="P19" s="91"/>
@@ -22023,27 +22026,27 @@
       <c r="T23" s="192"/>
       <c r="U23" s="192"/>
       <c r="V23" s="193"/>
-      <c r="X23" s="280" t="s">
+      <c r="X23" s="336" t="s">
         <v>227</v>
       </c>
-      <c r="Y23" s="280"/>
-      <c r="Z23" s="280"/>
-      <c r="AA23" s="280"/>
-      <c r="AB23" s="280"/>
-      <c r="AC23" s="280"/>
-      <c r="AD23" s="280"/>
-      <c r="AE23" s="280"/>
-      <c r="AF23" s="280"/>
-      <c r="AG23" s="280"/>
-      <c r="AH23" s="280"/>
-      <c r="AI23" s="280"/>
-      <c r="AJ23" s="280"/>
-      <c r="AK23" s="280"/>
-      <c r="AL23" s="280"/>
-      <c r="AM23" s="280"/>
-      <c r="AN23" s="280"/>
-      <c r="AO23" s="280"/>
-      <c r="AP23" s="280"/>
+      <c r="Y23" s="336"/>
+      <c r="Z23" s="336"/>
+      <c r="AA23" s="336"/>
+      <c r="AB23" s="336"/>
+      <c r="AC23" s="336"/>
+      <c r="AD23" s="336"/>
+      <c r="AE23" s="336"/>
+      <c r="AF23" s="336"/>
+      <c r="AG23" s="336"/>
+      <c r="AH23" s="336"/>
+      <c r="AI23" s="336"/>
+      <c r="AJ23" s="336"/>
+      <c r="AK23" s="336"/>
+      <c r="AL23" s="336"/>
+      <c r="AM23" s="336"/>
+      <c r="AN23" s="336"/>
+      <c r="AO23" s="336"/>
+      <c r="AP23" s="336"/>
     </row>
     <row r="24" spans="2:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q24" s="196"/>
@@ -22055,36 +22058,36 @@
       <c r="X24" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Y24" s="281" t="s">
+      <c r="Y24" s="319" t="s">
         <v>18</v>
       </c>
-      <c r="Z24" s="282"/>
-      <c r="AA24" s="283"/>
-      <c r="AB24" s="281" t="s">
+      <c r="Z24" s="320"/>
+      <c r="AA24" s="321"/>
+      <c r="AB24" s="319" t="s">
         <v>17</v>
       </c>
-      <c r="AC24" s="282"/>
-      <c r="AD24" s="283"/>
-      <c r="AE24" s="281" t="s">
+      <c r="AC24" s="320"/>
+      <c r="AD24" s="321"/>
+      <c r="AE24" s="319" t="s">
         <v>16</v>
       </c>
-      <c r="AF24" s="282"/>
-      <c r="AG24" s="283"/>
-      <c r="AH24" s="281" t="s">
+      <c r="AF24" s="320"/>
+      <c r="AG24" s="321"/>
+      <c r="AH24" s="319" t="s">
         <v>13</v>
       </c>
-      <c r="AI24" s="282"/>
-      <c r="AJ24" s="283"/>
-      <c r="AK24" s="281" t="s">
+      <c r="AI24" s="320"/>
+      <c r="AJ24" s="321"/>
+      <c r="AK24" s="319" t="s">
         <v>20</v>
       </c>
-      <c r="AL24" s="282"/>
-      <c r="AM24" s="283"/>
-      <c r="AN24" s="281" t="s">
+      <c r="AL24" s="320"/>
+      <c r="AM24" s="321"/>
+      <c r="AN24" s="319" t="s">
         <v>553</v>
       </c>
-      <c r="AO24" s="282"/>
-      <c r="AP24" s="283"/>
+      <c r="AO24" s="320"/>
+      <c r="AP24" s="321"/>
     </row>
     <row r="25" spans="2:42" ht="81.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="X25" s="64" t="s">
@@ -22598,48 +22601,48 @@
       <c r="P43" s="39"/>
     </row>
     <row r="44" spans="7:49" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X44" s="275" t="s">
+      <c r="X44" s="330" t="s">
         <v>238</v>
       </c>
-      <c r="Y44" s="277"/>
-      <c r="Z44" s="275" t="s">
+      <c r="Y44" s="332"/>
+      <c r="Z44" s="330" t="s">
         <v>237</v>
       </c>
-      <c r="AA44" s="276"/>
-      <c r="AB44" s="276"/>
-      <c r="AC44" s="276"/>
-      <c r="AD44" s="276"/>
-      <c r="AE44" s="277"/>
-      <c r="AF44" s="275" t="s">
+      <c r="AA44" s="331"/>
+      <c r="AB44" s="331"/>
+      <c r="AC44" s="331"/>
+      <c r="AD44" s="331"/>
+      <c r="AE44" s="332"/>
+      <c r="AF44" s="330" t="s">
         <v>239</v>
       </c>
-      <c r="AG44" s="276"/>
-      <c r="AH44" s="276"/>
-      <c r="AI44" s="276"/>
-      <c r="AJ44" s="276"/>
-      <c r="AK44" s="277"/>
-      <c r="AL44" s="275" t="s">
+      <c r="AG44" s="331"/>
+      <c r="AH44" s="331"/>
+      <c r="AI44" s="331"/>
+      <c r="AJ44" s="331"/>
+      <c r="AK44" s="332"/>
+      <c r="AL44" s="330" t="s">
         <v>240</v>
       </c>
-      <c r="AM44" s="276"/>
-      <c r="AN44" s="276"/>
-      <c r="AO44" s="276"/>
-      <c r="AP44" s="276"/>
-      <c r="AQ44" s="277"/>
-      <c r="AR44" s="275" t="s">
+      <c r="AM44" s="331"/>
+      <c r="AN44" s="331"/>
+      <c r="AO44" s="331"/>
+      <c r="AP44" s="331"/>
+      <c r="AQ44" s="332"/>
+      <c r="AR44" s="330" t="s">
         <v>241</v>
       </c>
-      <c r="AS44" s="276"/>
-      <c r="AT44" s="276"/>
-      <c r="AU44" s="276"/>
-      <c r="AV44" s="276"/>
-      <c r="AW44" s="277"/>
+      <c r="AS44" s="331"/>
+      <c r="AT44" s="331"/>
+      <c r="AU44" s="331"/>
+      <c r="AV44" s="331"/>
+      <c r="AW44" s="332"/>
     </row>
     <row r="45" spans="7:49" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="X45" s="270" t="s">
+      <c r="X45" s="337" t="s">
         <v>40</v>
       </c>
-      <c r="Y45" s="271"/>
+      <c r="Y45" s="338"/>
       <c r="Z45" s="184" t="s">
         <v>117</v>
       </c>
@@ -22724,10 +22727,10 @@
       <c r="T46" s="215"/>
       <c r="U46" s="189"/>
       <c r="V46" s="190"/>
-      <c r="X46" s="272" t="s">
+      <c r="X46" s="339" t="s">
         <v>31</v>
       </c>
-      <c r="Y46" s="273"/>
+      <c r="Y46" s="340"/>
       <c r="Z46" s="66"/>
       <c r="AA46" s="22"/>
       <c r="AB46" s="22"/>
@@ -22764,47 +22767,47 @@
       <c r="T47" s="216"/>
       <c r="U47" s="211"/>
       <c r="V47" s="208"/>
-      <c r="X47" s="274"/>
-      <c r="Y47" s="260"/>
-      <c r="Z47" s="256" t="s">
+      <c r="X47" s="341"/>
+      <c r="Y47" s="342"/>
+      <c r="Z47" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="AA47" s="257"/>
-      <c r="AB47" s="257"/>
-      <c r="AC47" s="257"/>
-      <c r="AD47" s="257"/>
-      <c r="AE47" s="258"/>
-      <c r="AF47" s="256" t="s">
+      <c r="AA47" s="334"/>
+      <c r="AB47" s="334"/>
+      <c r="AC47" s="334"/>
+      <c r="AD47" s="334"/>
+      <c r="AE47" s="344"/>
+      <c r="AF47" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="AG47" s="257"/>
-      <c r="AH47" s="257"/>
-      <c r="AI47" s="257"/>
-      <c r="AJ47" s="257"/>
-      <c r="AK47" s="258"/>
-      <c r="AL47" s="256" t="s">
+      <c r="AG47" s="334"/>
+      <c r="AH47" s="334"/>
+      <c r="AI47" s="334"/>
+      <c r="AJ47" s="334"/>
+      <c r="AK47" s="344"/>
+      <c r="AL47" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="AM47" s="257"/>
-      <c r="AN47" s="257"/>
-      <c r="AO47" s="257"/>
-      <c r="AP47" s="257"/>
-      <c r="AQ47" s="258"/>
-      <c r="AR47" s="256" t="s">
+      <c r="AM47" s="334"/>
+      <c r="AN47" s="334"/>
+      <c r="AO47" s="334"/>
+      <c r="AP47" s="334"/>
+      <c r="AQ47" s="344"/>
+      <c r="AR47" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="AS47" s="257"/>
-      <c r="AT47" s="257"/>
-      <c r="AU47" s="257"/>
-      <c r="AV47" s="257"/>
-      <c r="AW47" s="258"/>
+      <c r="AS47" s="334"/>
+      <c r="AT47" s="334"/>
+      <c r="AU47" s="334"/>
+      <c r="AV47" s="334"/>
+      <c r="AW47" s="344"/>
     </row>
     <row r="48" spans="7:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O48" s="194"/>
-      <c r="P48" s="356" t="s">
+      <c r="P48" s="364" t="s">
         <v>621</v>
       </c>
-      <c r="Q48" s="357"/>
+      <c r="Q48" s="365"/>
       <c r="R48" s="151" t="s">
         <v>223</v>
       </c>
@@ -22818,7 +22821,7 @@
         <v>622</v>
       </c>
       <c r="V48" s="193"/>
-      <c r="X48" s="252" t="s">
+      <c r="X48" s="345" t="s">
         <v>1</v>
       </c>
       <c r="Y48" s="72" t="s">
@@ -22851,16 +22854,16 @@
     </row>
     <row r="49" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O49" s="194"/>
-      <c r="P49" s="356" t="s">
+      <c r="P49" s="364" t="s">
         <v>31</v>
       </c>
-      <c r="Q49" s="357"/>
+      <c r="Q49" s="365"/>
       <c r="R49" s="31"/>
       <c r="S49" s="89"/>
       <c r="T49" s="224"/>
       <c r="U49" s="224"/>
       <c r="V49" s="193"/>
-      <c r="X49" s="252"/>
+      <c r="X49" s="345"/>
       <c r="Y49" s="72" t="s">
         <v>12</v>
       </c>
@@ -22891,16 +22894,16 @@
     </row>
     <row r="50" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O50" s="194"/>
-      <c r="P50" s="290" t="s">
+      <c r="P50" s="325" t="s">
         <v>30</v>
       </c>
-      <c r="Q50" s="290"/>
-      <c r="R50" s="290"/>
-      <c r="S50" s="290"/>
-      <c r="T50" s="290"/>
-      <c r="U50" s="290"/>
+      <c r="Q50" s="325"/>
+      <c r="R50" s="325"/>
+      <c r="S50" s="325"/>
+      <c r="T50" s="325"/>
+      <c r="U50" s="325"/>
       <c r="V50" s="193"/>
-      <c r="X50" s="252" t="s">
+      <c r="X50" s="345" t="s">
         <v>32</v>
       </c>
       <c r="Y50" s="72" t="s">
@@ -22933,7 +22936,7 @@
     </row>
     <row r="51" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O51" s="194"/>
-      <c r="P51" s="361" t="s">
+      <c r="P51" s="363" t="s">
         <v>1</v>
       </c>
       <c r="Q51" s="151" t="s">
@@ -22944,7 +22947,7 @@
       <c r="T51" s="219"/>
       <c r="U51" s="220"/>
       <c r="V51" s="193"/>
-      <c r="X51" s="252"/>
+      <c r="X51" s="345"/>
       <c r="Y51" s="72" t="s">
         <v>12</v>
       </c>
@@ -22975,7 +22978,7 @@
     </row>
     <row r="52" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O52" s="194"/>
-      <c r="P52" s="361"/>
+      <c r="P52" s="363"/>
       <c r="Q52" s="151" t="s">
         <v>12</v>
       </c>
@@ -22984,7 +22987,7 @@
       <c r="T52" s="219"/>
       <c r="U52" s="220"/>
       <c r="V52" s="193"/>
-      <c r="X52" s="266" t="s">
+      <c r="X52" s="346" t="s">
         <v>33</v>
       </c>
       <c r="Y52" s="72" t="s">
@@ -23017,7 +23020,7 @@
     </row>
     <row r="53" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O53" s="194"/>
-      <c r="P53" s="361" t="s">
+      <c r="P53" s="363" t="s">
         <v>623</v>
       </c>
       <c r="Q53" s="151" t="s">
@@ -23028,7 +23031,7 @@
       <c r="T53" s="219"/>
       <c r="U53" s="220"/>
       <c r="V53" s="193"/>
-      <c r="X53" s="267"/>
+      <c r="X53" s="347"/>
       <c r="Y53" s="72" t="s">
         <v>12</v>
       </c>
@@ -23059,7 +23062,7 @@
     </row>
     <row r="54" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O54" s="194"/>
-      <c r="P54" s="361"/>
+      <c r="P54" s="363"/>
       <c r="Q54" s="151" t="s">
         <v>12</v>
       </c>
@@ -23068,10 +23071,10 @@
       <c r="T54" s="219"/>
       <c r="U54" s="220"/>
       <c r="V54" s="193"/>
-      <c r="X54" s="268" t="s">
+      <c r="X54" s="348" t="s">
         <v>34</v>
       </c>
-      <c r="Y54" s="269"/>
+      <c r="Y54" s="349"/>
       <c r="Z54" s="70"/>
       <c r="AA54" s="25"/>
       <c r="AB54" s="25"/>
@@ -23099,7 +23102,7 @@
     </row>
     <row r="55" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O55" s="194"/>
-      <c r="P55" s="361" t="s">
+      <c r="P55" s="363" t="s">
         <v>624</v>
       </c>
       <c r="Q55" s="151" t="s">
@@ -23110,44 +23113,44 @@
       <c r="T55" s="219"/>
       <c r="U55" s="220"/>
       <c r="V55" s="193"/>
-      <c r="X55" s="259"/>
-      <c r="Y55" s="260"/>
-      <c r="Z55" s="259" t="s">
+      <c r="X55" s="353"/>
+      <c r="Y55" s="342"/>
+      <c r="Z55" s="353" t="s">
         <v>107</v>
       </c>
-      <c r="AA55" s="261"/>
-      <c r="AB55" s="261"/>
-      <c r="AC55" s="261"/>
-      <c r="AD55" s="261"/>
-      <c r="AE55" s="260"/>
-      <c r="AF55" s="259" t="s">
+      <c r="AA55" s="328"/>
+      <c r="AB55" s="328"/>
+      <c r="AC55" s="328"/>
+      <c r="AD55" s="328"/>
+      <c r="AE55" s="342"/>
+      <c r="AF55" s="353" t="s">
         <v>107</v>
       </c>
-      <c r="AG55" s="261"/>
-      <c r="AH55" s="261"/>
-      <c r="AI55" s="261"/>
-      <c r="AJ55" s="261"/>
-      <c r="AK55" s="260"/>
-      <c r="AL55" s="259" t="s">
+      <c r="AG55" s="328"/>
+      <c r="AH55" s="328"/>
+      <c r="AI55" s="328"/>
+      <c r="AJ55" s="328"/>
+      <c r="AK55" s="342"/>
+      <c r="AL55" s="353" t="s">
         <v>107</v>
       </c>
-      <c r="AM55" s="261"/>
-      <c r="AN55" s="261"/>
-      <c r="AO55" s="261"/>
-      <c r="AP55" s="261"/>
-      <c r="AQ55" s="260"/>
-      <c r="AR55" s="259" t="s">
+      <c r="AM55" s="328"/>
+      <c r="AN55" s="328"/>
+      <c r="AO55" s="328"/>
+      <c r="AP55" s="328"/>
+      <c r="AQ55" s="342"/>
+      <c r="AR55" s="353" t="s">
         <v>107</v>
       </c>
-      <c r="AS55" s="261"/>
-      <c r="AT55" s="261"/>
-      <c r="AU55" s="261"/>
-      <c r="AV55" s="261"/>
-      <c r="AW55" s="260"/>
+      <c r="AS55" s="328"/>
+      <c r="AT55" s="328"/>
+      <c r="AU55" s="328"/>
+      <c r="AV55" s="328"/>
+      <c r="AW55" s="342"/>
     </row>
     <row r="56" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O56" s="194"/>
-      <c r="P56" s="361"/>
+      <c r="P56" s="363"/>
       <c r="Q56" s="151" t="s">
         <v>12</v>
       </c>
@@ -23156,10 +23159,10 @@
       <c r="T56" s="219"/>
       <c r="U56" s="220"/>
       <c r="V56" s="193"/>
-      <c r="X56" s="262" t="s">
+      <c r="X56" s="354" t="s">
         <v>37</v>
       </c>
-      <c r="Y56" s="263"/>
+      <c r="Y56" s="355"/>
       <c r="Z56" s="68"/>
       <c r="AA56" s="19"/>
       <c r="AB56" s="19"/>
@@ -23187,65 +23190,65 @@
     </row>
     <row r="57" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O57" s="194"/>
-      <c r="P57" s="363" t="s">
+      <c r="P57" s="359" t="s">
         <v>625</v>
       </c>
-      <c r="Q57" s="363"/>
+      <c r="Q57" s="359"/>
       <c r="R57" s="218"/>
       <c r="S57" s="218"/>
       <c r="T57" s="219"/>
       <c r="U57" s="221"/>
       <c r="V57" s="210"/>
-      <c r="X57" s="264"/>
-      <c r="Y57" s="265"/>
-      <c r="Z57" s="256" t="s">
+      <c r="X57" s="356"/>
+      <c r="Y57" s="357"/>
+      <c r="Z57" s="343" t="s">
         <v>108</v>
       </c>
-      <c r="AA57" s="257"/>
-      <c r="AB57" s="257"/>
-      <c r="AC57" s="257"/>
-      <c r="AD57" s="257"/>
-      <c r="AE57" s="258"/>
-      <c r="AF57" s="256" t="s">
+      <c r="AA57" s="334"/>
+      <c r="AB57" s="334"/>
+      <c r="AC57" s="334"/>
+      <c r="AD57" s="334"/>
+      <c r="AE57" s="344"/>
+      <c r="AF57" s="343" t="s">
         <v>108</v>
       </c>
-      <c r="AG57" s="257"/>
-      <c r="AH57" s="257"/>
-      <c r="AI57" s="257"/>
-      <c r="AJ57" s="257"/>
-      <c r="AK57" s="258"/>
-      <c r="AL57" s="256" t="s">
+      <c r="AG57" s="334"/>
+      <c r="AH57" s="334"/>
+      <c r="AI57" s="334"/>
+      <c r="AJ57" s="334"/>
+      <c r="AK57" s="344"/>
+      <c r="AL57" s="343" t="s">
         <v>108</v>
       </c>
-      <c r="AM57" s="257"/>
-      <c r="AN57" s="257"/>
-      <c r="AO57" s="257"/>
-      <c r="AP57" s="257"/>
-      <c r="AQ57" s="258"/>
-      <c r="AR57" s="256" t="s">
+      <c r="AM57" s="334"/>
+      <c r="AN57" s="334"/>
+      <c r="AO57" s="334"/>
+      <c r="AP57" s="334"/>
+      <c r="AQ57" s="344"/>
+      <c r="AR57" s="343" t="s">
         <v>108</v>
       </c>
-      <c r="AS57" s="257"/>
-      <c r="AT57" s="257"/>
-      <c r="AU57" s="257"/>
-      <c r="AV57" s="257"/>
-      <c r="AW57" s="258"/>
+      <c r="AS57" s="334"/>
+      <c r="AT57" s="334"/>
+      <c r="AU57" s="334"/>
+      <c r="AV57" s="334"/>
+      <c r="AW57" s="344"/>
     </row>
     <row r="58" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O58" s="194"/>
-      <c r="P58" s="358" t="s">
+      <c r="P58" s="360" t="s">
         <v>107</v>
       </c>
-      <c r="Q58" s="359"/>
-      <c r="R58" s="359"/>
-      <c r="S58" s="359"/>
-      <c r="T58" s="359"/>
-      <c r="U58" s="360"/>
+      <c r="Q58" s="361"/>
+      <c r="R58" s="361"/>
+      <c r="S58" s="361"/>
+      <c r="T58" s="361"/>
+      <c r="U58" s="362"/>
       <c r="V58" s="210"/>
-      <c r="X58" s="252" t="s">
+      <c r="X58" s="345" t="s">
         <v>38</v>
       </c>
-      <c r="Y58" s="253"/>
+      <c r="Y58" s="350"/>
       <c r="Z58" s="68"/>
       <c r="AA58" s="19"/>
       <c r="AB58" s="19"/>
@@ -23273,19 +23276,19 @@
     </row>
     <row r="59" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O59" s="194"/>
-      <c r="P59" s="363" t="s">
+      <c r="P59" s="359" t="s">
         <v>626</v>
       </c>
-      <c r="Q59" s="363"/>
+      <c r="Q59" s="359"/>
       <c r="R59" s="218"/>
       <c r="S59" s="218"/>
       <c r="T59" s="219"/>
       <c r="U59" s="221"/>
       <c r="V59" s="210"/>
-      <c r="X59" s="252" t="s">
+      <c r="X59" s="345" t="s">
         <v>36</v>
       </c>
-      <c r="Y59" s="253"/>
+      <c r="Y59" s="350"/>
       <c r="Z59" s="68"/>
       <c r="AA59" s="19"/>
       <c r="AB59" s="19"/>
@@ -23313,19 +23316,19 @@
     </row>
     <row r="60" spans="15:49" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O60" s="194"/>
-      <c r="P60" s="358" t="s">
+      <c r="P60" s="360" t="s">
         <v>627</v>
       </c>
-      <c r="Q60" s="359"/>
-      <c r="R60" s="359"/>
-      <c r="S60" s="359"/>
-      <c r="T60" s="359"/>
-      <c r="U60" s="360"/>
+      <c r="Q60" s="361"/>
+      <c r="R60" s="361"/>
+      <c r="S60" s="361"/>
+      <c r="T60" s="361"/>
+      <c r="U60" s="362"/>
       <c r="V60" s="193"/>
-      <c r="X60" s="254" t="s">
+      <c r="X60" s="351" t="s">
         <v>39</v>
       </c>
-      <c r="Y60" s="255"/>
+      <c r="Y60" s="352"/>
       <c r="Z60" s="73"/>
       <c r="AA60" s="74"/>
       <c r="AB60" s="74"/>
@@ -23353,10 +23356,10 @@
     </row>
     <row r="61" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O61" s="194"/>
-      <c r="P61" s="361" t="s">
+      <c r="P61" s="363" t="s">
         <v>628</v>
       </c>
-      <c r="Q61" s="361"/>
+      <c r="Q61" s="363"/>
       <c r="R61" s="218"/>
       <c r="S61" s="218"/>
       <c r="T61" s="219"/>
@@ -23365,10 +23368,10 @@
     </row>
     <row r="62" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O62" s="194"/>
-      <c r="P62" s="361" t="s">
+      <c r="P62" s="363" t="s">
         <v>629</v>
       </c>
-      <c r="Q62" s="361"/>
+      <c r="Q62" s="363"/>
       <c r="R62" s="218"/>
       <c r="S62" s="218"/>
       <c r="T62" s="219"/>
@@ -23377,10 +23380,10 @@
     </row>
     <row r="63" spans="15:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O63" s="194"/>
-      <c r="P63" s="362" t="s">
+      <c r="P63" s="358" t="s">
         <v>39</v>
       </c>
-      <c r="Q63" s="362"/>
+      <c r="Q63" s="358"/>
       <c r="R63" s="218"/>
       <c r="S63" s="218"/>
       <c r="T63" s="219"/>
@@ -23427,38 +23430,24 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="R4:R6"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="G19:M19"/>
-    <mergeCell ref="G14:M14"/>
-    <mergeCell ref="G11:M11"/>
-    <mergeCell ref="G8:M8"/>
-    <mergeCell ref="G5:M5"/>
-    <mergeCell ref="X23:AP23"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="AB24:AD24"/>
-    <mergeCell ref="AE24:AG24"/>
-    <mergeCell ref="AH24:AJ24"/>
-    <mergeCell ref="AK24:AM24"/>
-    <mergeCell ref="AN24:AP24"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="Z44:AE44"/>
-    <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="AL44:AQ44"/>
-    <mergeCell ref="AR44:AW44"/>
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="X46:Y46"/>
-    <mergeCell ref="X47:Y47"/>
-    <mergeCell ref="Z47:AE47"/>
-    <mergeCell ref="AF47:AK47"/>
-    <mergeCell ref="AL47:AQ47"/>
-    <mergeCell ref="AR47:AW47"/>
-    <mergeCell ref="X48:X49"/>
-    <mergeCell ref="X50:X51"/>
-    <mergeCell ref="X52:X53"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P60:U60"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P50:U50"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:U58"/>
+    <mergeCell ref="P51:P52"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="X58:Y58"/>
+    <mergeCell ref="X59:Y59"/>
+    <mergeCell ref="X60:Y60"/>
+    <mergeCell ref="X57:Y57"/>
+    <mergeCell ref="Z57:AE57"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="AL57:AQ57"/>
     <mergeCell ref="AR57:AW57"/>
@@ -23469,24 +23458,38 @@
     <mergeCell ref="X56:Y56"/>
     <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="AL55:AQ55"/>
-    <mergeCell ref="X58:Y58"/>
-    <mergeCell ref="X59:Y59"/>
-    <mergeCell ref="X60:Y60"/>
-    <mergeCell ref="X57:Y57"/>
-    <mergeCell ref="Z57:AE57"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P50:U50"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:U58"/>
-    <mergeCell ref="P51:P52"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="P55:P56"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P60:U60"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="AL47:AQ47"/>
+    <mergeCell ref="AR47:AW47"/>
+    <mergeCell ref="X48:X49"/>
+    <mergeCell ref="X50:X51"/>
+    <mergeCell ref="X52:X53"/>
+    <mergeCell ref="X45:Y45"/>
+    <mergeCell ref="X46:Y46"/>
+    <mergeCell ref="X47:Y47"/>
+    <mergeCell ref="Z47:AE47"/>
+    <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="Z44:AE44"/>
+    <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="AL44:AQ44"/>
+    <mergeCell ref="AR44:AW44"/>
+    <mergeCell ref="X23:AP23"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="AB24:AD24"/>
+    <mergeCell ref="AE24:AG24"/>
+    <mergeCell ref="AH24:AJ24"/>
+    <mergeCell ref="AK24:AM24"/>
+    <mergeCell ref="AN24:AP24"/>
+    <mergeCell ref="G19:M19"/>
+    <mergeCell ref="G14:M14"/>
+    <mergeCell ref="G11:M11"/>
+    <mergeCell ref="G8:M8"/>
+    <mergeCell ref="G5:M5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="R4:R6"/>
+    <mergeCell ref="G3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23514,48 +23517,48 @@
   <sheetData>
     <row r="1" spans="2:27" ht="11.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="275" t="s">
+      <c r="B2" s="330" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="277"/>
-      <c r="D2" s="275" t="s">
+      <c r="C2" s="332"/>
+      <c r="D2" s="330" t="s">
         <v>235</v>
       </c>
-      <c r="E2" s="276"/>
-      <c r="F2" s="276"/>
-      <c r="G2" s="276"/>
-      <c r="H2" s="276"/>
-      <c r="I2" s="277"/>
-      <c r="J2" s="275" t="s">
+      <c r="E2" s="331"/>
+      <c r="F2" s="331"/>
+      <c r="G2" s="331"/>
+      <c r="H2" s="331"/>
+      <c r="I2" s="332"/>
+      <c r="J2" s="330" t="s">
         <v>236</v>
       </c>
-      <c r="K2" s="276"/>
-      <c r="L2" s="276"/>
-      <c r="M2" s="276"/>
-      <c r="N2" s="276"/>
-      <c r="O2" s="277"/>
-      <c r="P2" s="275" t="s">
+      <c r="K2" s="331"/>
+      <c r="L2" s="331"/>
+      <c r="M2" s="331"/>
+      <c r="N2" s="331"/>
+      <c r="O2" s="332"/>
+      <c r="P2" s="330" t="s">
         <v>235</v>
       </c>
-      <c r="Q2" s="276"/>
-      <c r="R2" s="276"/>
-      <c r="S2" s="276"/>
-      <c r="T2" s="276"/>
-      <c r="U2" s="277"/>
-      <c r="V2" s="275" t="s">
+      <c r="Q2" s="331"/>
+      <c r="R2" s="331"/>
+      <c r="S2" s="331"/>
+      <c r="T2" s="331"/>
+      <c r="U2" s="332"/>
+      <c r="V2" s="330" t="s">
         <v>236</v>
       </c>
-      <c r="W2" s="276"/>
-      <c r="X2" s="276"/>
-      <c r="Y2" s="276"/>
-      <c r="Z2" s="276"/>
-      <c r="AA2" s="277"/>
+      <c r="W2" s="331"/>
+      <c r="X2" s="331"/>
+      <c r="Y2" s="331"/>
+      <c r="Z2" s="331"/>
+      <c r="AA2" s="332"/>
     </row>
     <row r="3" spans="2:27" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="373" t="s">
+      <c r="B3" s="375" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="374"/>
+      <c r="C3" s="376"/>
       <c r="D3" s="184" t="s">
         <v>117</v>
       </c>
@@ -23630,10 +23633,10 @@
       </c>
     </row>
     <row r="4" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="272" t="s">
+      <c r="B4" s="339" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="273"/>
+      <c r="C4" s="340"/>
       <c r="D4" s="141" t="s">
         <v>234</v>
       </c>
@@ -23662,43 +23665,43 @@
       <c r="AA4" s="158"/>
     </row>
     <row r="5" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="274"/>
-      <c r="C5" s="368"/>
-      <c r="D5" s="256" t="s">
+      <c r="B5" s="341"/>
+      <c r="C5" s="378"/>
+      <c r="D5" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="257"/>
-      <c r="F5" s="257"/>
-      <c r="G5" s="257"/>
-      <c r="H5" s="257"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="256" t="s">
+      <c r="E5" s="334"/>
+      <c r="F5" s="334"/>
+      <c r="G5" s="334"/>
+      <c r="H5" s="334"/>
+      <c r="I5" s="344"/>
+      <c r="J5" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="257"/>
-      <c r="L5" s="257"/>
-      <c r="M5" s="257"/>
-      <c r="N5" s="257"/>
-      <c r="O5" s="258"/>
-      <c r="P5" s="256" t="s">
+      <c r="K5" s="334"/>
+      <c r="L5" s="334"/>
+      <c r="M5" s="334"/>
+      <c r="N5" s="334"/>
+      <c r="O5" s="344"/>
+      <c r="P5" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="257"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="258"/>
-      <c r="V5" s="256" t="s">
+      <c r="Q5" s="334"/>
+      <c r="R5" s="334"/>
+      <c r="S5" s="334"/>
+      <c r="T5" s="334"/>
+      <c r="U5" s="344"/>
+      <c r="V5" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
-      <c r="AA5" s="258"/>
+      <c r="W5" s="334"/>
+      <c r="X5" s="334"/>
+      <c r="Y5" s="334"/>
+      <c r="Z5" s="334"/>
+      <c r="AA5" s="344"/>
     </row>
     <row r="6" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="367" t="s">
+      <c r="B6" s="377" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="72" t="s">
@@ -23732,7 +23735,7 @@
       <c r="AA6" s="161"/>
     </row>
     <row r="7" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="367"/>
+      <c r="B7" s="377"/>
       <c r="C7" s="72" t="s">
         <v>61</v>
       </c>
@@ -23764,7 +23767,7 @@
       <c r="AA7" s="161"/>
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="369" t="s">
+      <c r="B8" s="371" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="72" t="s">
@@ -23798,7 +23801,7 @@
       <c r="AA8" s="161"/>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="370"/>
+      <c r="B9" s="372"/>
       <c r="C9" s="72" t="s">
         <v>12</v>
       </c>
@@ -23830,7 +23833,7 @@
       <c r="AA9" s="161"/>
     </row>
     <row r="10" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="369" t="s">
+      <c r="B10" s="371" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="72" t="s">
@@ -23864,7 +23867,7 @@
       <c r="AA10" s="161"/>
     </row>
     <row r="11" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="370"/>
+      <c r="B11" s="372"/>
       <c r="C11" s="76" t="s">
         <v>12</v>
       </c>
@@ -23896,10 +23899,10 @@
       <c r="AA11" s="161"/>
     </row>
     <row r="12" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="268" t="s">
+      <c r="B12" s="348" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="269"/>
+      <c r="C12" s="349"/>
       <c r="D12" s="142" t="s">
         <v>122</v>
       </c>
@@ -23928,10 +23931,10 @@
       <c r="AA12" s="161"/>
     </row>
     <row r="13" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="371" t="s">
+      <c r="B13" s="373" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="372"/>
+      <c r="C13" s="374"/>
       <c r="D13" s="144" t="s">
         <v>122</v>
       </c>
@@ -23960,46 +23963,46 @@
       <c r="AA13" s="165"/>
     </row>
     <row r="14" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="262"/>
-      <c r="C14" s="263"/>
-      <c r="D14" s="259" t="s">
+      <c r="B14" s="354"/>
+      <c r="C14" s="355"/>
+      <c r="D14" s="353" t="s">
         <v>105</v>
       </c>
-      <c r="E14" s="261"/>
-      <c r="F14" s="261"/>
-      <c r="G14" s="261"/>
-      <c r="H14" s="261"/>
-      <c r="I14" s="260"/>
-      <c r="J14" s="259" t="s">
+      <c r="E14" s="328"/>
+      <c r="F14" s="328"/>
+      <c r="G14" s="328"/>
+      <c r="H14" s="328"/>
+      <c r="I14" s="342"/>
+      <c r="J14" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="K14" s="261"/>
-      <c r="L14" s="261"/>
-      <c r="M14" s="261"/>
-      <c r="N14" s="261"/>
-      <c r="O14" s="260"/>
-      <c r="P14" s="259" t="s">
+      <c r="K14" s="328"/>
+      <c r="L14" s="328"/>
+      <c r="M14" s="328"/>
+      <c r="N14" s="328"/>
+      <c r="O14" s="342"/>
+      <c r="P14" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="Q14" s="261"/>
-      <c r="R14" s="261"/>
-      <c r="S14" s="261"/>
-      <c r="T14" s="261"/>
-      <c r="U14" s="260"/>
-      <c r="V14" s="259" t="s">
+      <c r="Q14" s="328"/>
+      <c r="R14" s="328"/>
+      <c r="S14" s="328"/>
+      <c r="T14" s="328"/>
+      <c r="U14" s="342"/>
+      <c r="V14" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="W14" s="261"/>
-      <c r="X14" s="261"/>
-      <c r="Y14" s="261"/>
-      <c r="Z14" s="261"/>
-      <c r="AA14" s="260"/>
+      <c r="W14" s="328"/>
+      <c r="X14" s="328"/>
+      <c r="Y14" s="328"/>
+      <c r="Z14" s="328"/>
+      <c r="AA14" s="342"/>
     </row>
     <row r="15" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="262" t="s">
+      <c r="B15" s="354" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="263"/>
+      <c r="C15" s="355"/>
       <c r="D15" s="143" t="s">
         <v>135</v>
       </c>
@@ -24028,10 +24031,10 @@
       <c r="AA15" s="161"/>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="262" t="s">
+      <c r="B16" s="354" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="263"/>
+      <c r="C16" s="355"/>
       <c r="D16" s="142" t="s">
         <v>135</v>
       </c>
@@ -24060,10 +24063,10 @@
       <c r="AA16" s="161"/>
     </row>
     <row r="17" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="262" t="s">
+      <c r="B17" s="354" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="263"/>
+      <c r="C17" s="355"/>
       <c r="D17" s="142" t="s">
         <v>135</v>
       </c>
@@ -24092,10 +24095,10 @@
       <c r="AA17" s="161"/>
     </row>
     <row r="18" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="262" t="s">
+      <c r="B18" s="354" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="263"/>
+      <c r="C18" s="355"/>
       <c r="D18" s="142" t="s">
         <v>135</v>
       </c>
@@ -24124,46 +24127,46 @@
       <c r="AA18" s="161"/>
     </row>
     <row r="19" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="262"/>
-      <c r="C19" s="263"/>
-      <c r="D19" s="364" t="s">
+      <c r="B19" s="354"/>
+      <c r="C19" s="355"/>
+      <c r="D19" s="379" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="365"/>
-      <c r="F19" s="365"/>
-      <c r="G19" s="365"/>
-      <c r="H19" s="365"/>
-      <c r="I19" s="366"/>
-      <c r="J19" s="256" t="s">
+      <c r="E19" s="380"/>
+      <c r="F19" s="380"/>
+      <c r="G19" s="380"/>
+      <c r="H19" s="380"/>
+      <c r="I19" s="381"/>
+      <c r="J19" s="343" t="s">
         <v>65</v>
       </c>
-      <c r="K19" s="257"/>
-      <c r="L19" s="257"/>
-      <c r="M19" s="257"/>
-      <c r="N19" s="257"/>
-      <c r="O19" s="258"/>
-      <c r="P19" s="256" t="s">
+      <c r="K19" s="334"/>
+      <c r="L19" s="334"/>
+      <c r="M19" s="334"/>
+      <c r="N19" s="334"/>
+      <c r="O19" s="344"/>
+      <c r="P19" s="343" t="s">
         <v>65</v>
       </c>
-      <c r="Q19" s="257"/>
-      <c r="R19" s="257"/>
-      <c r="S19" s="257"/>
-      <c r="T19" s="257"/>
-      <c r="U19" s="258"/>
-      <c r="V19" s="256" t="s">
+      <c r="Q19" s="334"/>
+      <c r="R19" s="334"/>
+      <c r="S19" s="334"/>
+      <c r="T19" s="334"/>
+      <c r="U19" s="344"/>
+      <c r="V19" s="343" t="s">
         <v>65</v>
       </c>
-      <c r="W19" s="257"/>
-      <c r="X19" s="257"/>
-      <c r="Y19" s="257"/>
-      <c r="Z19" s="257"/>
-      <c r="AA19" s="258"/>
+      <c r="W19" s="334"/>
+      <c r="X19" s="334"/>
+      <c r="Y19" s="334"/>
+      <c r="Z19" s="334"/>
+      <c r="AA19" s="344"/>
     </row>
     <row r="20" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="252" t="s">
+      <c r="B20" s="345" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="253"/>
+      <c r="C20" s="350"/>
       <c r="D20" s="142" t="s">
         <v>233</v>
       </c>
@@ -24192,10 +24195,10 @@
       <c r="AA20" s="161"/>
     </row>
     <row r="21" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="252" t="s">
+      <c r="B21" s="345" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="253"/>
+      <c r="C21" s="350"/>
       <c r="D21" s="142" t="s">
         <v>233</v>
       </c>
@@ -24224,10 +24227,10 @@
       <c r="AA21" s="161"/>
     </row>
     <row r="22" spans="2:37" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="254" t="s">
+      <c r="B22" s="351" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="255"/>
+      <c r="C22" s="352"/>
       <c r="D22" s="145" t="s">
         <v>121</v>
       </c>
@@ -24290,52 +24293,52 @@
       <c r="AA29"/>
     </row>
     <row r="30" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="379" t="s">
+      <c r="B30" s="369" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="379"/>
-      <c r="D30" s="376" t="s">
+      <c r="C30" s="369"/>
+      <c r="D30" s="366" t="s">
         <v>644</v>
       </c>
-      <c r="E30" s="376"/>
-      <c r="F30" s="376"/>
-      <c r="G30" s="376"/>
-      <c r="H30" s="376" t="s">
+      <c r="E30" s="366"/>
+      <c r="F30" s="366"/>
+      <c r="G30" s="366"/>
+      <c r="H30" s="366" t="s">
         <v>17</v>
       </c>
-      <c r="I30" s="376"/>
-      <c r="J30" s="376"/>
-      <c r="K30" s="376"/>
-      <c r="L30" s="376" t="s">
+      <c r="I30" s="366"/>
+      <c r="J30" s="366"/>
+      <c r="K30" s="366"/>
+      <c r="L30" s="366" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="376"/>
-      <c r="N30" s="376"/>
-      <c r="O30" s="376"/>
-      <c r="P30" s="376" t="s">
+      <c r="M30" s="366"/>
+      <c r="N30" s="366"/>
+      <c r="O30" s="366"/>
+      <c r="P30" s="366" t="s">
         <v>13</v>
       </c>
-      <c r="Q30" s="376"/>
-      <c r="R30" s="376"/>
-      <c r="S30" s="376"/>
-      <c r="T30" s="376" t="s">
+      <c r="Q30" s="366"/>
+      <c r="R30" s="366"/>
+      <c r="S30" s="366"/>
+      <c r="T30" s="366" t="s">
         <v>20</v>
       </c>
-      <c r="U30" s="376"/>
-      <c r="V30" s="376"/>
-      <c r="W30" s="376"/>
-      <c r="X30" s="376" t="s">
+      <c r="U30" s="366"/>
+      <c r="V30" s="366"/>
+      <c r="W30" s="366"/>
+      <c r="X30" s="366" t="s">
         <v>553</v>
       </c>
-      <c r="Y30" s="376"/>
-      <c r="Z30" s="376"/>
-      <c r="AA30" s="376"/>
+      <c r="Y30" s="366"/>
+      <c r="Z30" s="366"/>
+      <c r="AA30" s="366"/>
     </row>
     <row r="31" spans="2:37" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="377" t="s">
+      <c r="B31" s="367" t="s">
         <v>632</v>
       </c>
-      <c r="C31" s="378"/>
+      <c r="C31" s="368"/>
       <c r="D31" s="232" t="s">
         <v>641</v>
       </c>
@@ -24410,10 +24413,10 @@
       </c>
     </row>
     <row r="32" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="312" t="s">
+      <c r="B32" s="277" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="312"/>
+      <c r="C32" s="277"/>
       <c r="D32" s="231" t="s">
         <v>234</v>
       </c>
@@ -24452,34 +24455,34 @@
       <c r="AK32" s="190"/>
     </row>
     <row r="33" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="320" t="s">
+      <c r="B33" s="269" t="s">
         <v>646</v>
       </c>
-      <c r="C33" s="321"/>
-      <c r="D33" s="321"/>
-      <c r="E33" s="321"/>
-      <c r="F33" s="321"/>
-      <c r="G33" s="321"/>
-      <c r="H33" s="321"/>
-      <c r="I33" s="321"/>
-      <c r="J33" s="321"/>
-      <c r="K33" s="321"/>
-      <c r="L33" s="321"/>
-      <c r="M33" s="321"/>
-      <c r="N33" s="321"/>
-      <c r="O33" s="321"/>
-      <c r="P33" s="321"/>
-      <c r="Q33" s="321"/>
-      <c r="R33" s="321"/>
-      <c r="S33" s="321"/>
-      <c r="T33" s="321"/>
-      <c r="U33" s="321"/>
-      <c r="V33" s="321"/>
-      <c r="W33" s="321"/>
-      <c r="X33" s="321"/>
-      <c r="Y33" s="321"/>
-      <c r="Z33" s="321"/>
-      <c r="AA33" s="322"/>
+      <c r="C33" s="270"/>
+      <c r="D33" s="270"/>
+      <c r="E33" s="270"/>
+      <c r="F33" s="270"/>
+      <c r="G33" s="270"/>
+      <c r="H33" s="270"/>
+      <c r="I33" s="270"/>
+      <c r="J33" s="270"/>
+      <c r="K33" s="270"/>
+      <c r="L33" s="270"/>
+      <c r="M33" s="270"/>
+      <c r="N33" s="270"/>
+      <c r="O33" s="270"/>
+      <c r="P33" s="270"/>
+      <c r="Q33" s="270"/>
+      <c r="R33" s="270"/>
+      <c r="S33" s="270"/>
+      <c r="T33" s="270"/>
+      <c r="U33" s="270"/>
+      <c r="V33" s="270"/>
+      <c r="W33" s="270"/>
+      <c r="X33" s="270"/>
+      <c r="Y33" s="270"/>
+      <c r="Z33" s="270"/>
+      <c r="AA33" s="271"/>
       <c r="AD33" s="194"/>
       <c r="AE33" s="216" t="s">
         <v>585</v>
@@ -24492,7 +24495,7 @@
       <c r="AK33" s="208"/>
     </row>
     <row r="34" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="306" t="s">
+      <c r="B34" s="279" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="111" t="s">
@@ -24525,10 +24528,10 @@
       <c r="Z34" s="62"/>
       <c r="AA34" s="148"/>
       <c r="AD34" s="194"/>
-      <c r="AE34" s="356" t="s">
+      <c r="AE34" s="364" t="s">
         <v>632</v>
       </c>
-      <c r="AF34" s="357"/>
+      <c r="AF34" s="365"/>
       <c r="AG34" s="151" t="s">
         <v>223</v>
       </c>
@@ -24544,7 +24547,7 @@
       <c r="AK34" s="193"/>
     </row>
     <row r="35" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="306"/>
+      <c r="B35" s="279"/>
       <c r="C35" s="111" t="s">
         <v>61</v>
       </c>
@@ -24575,10 +24578,10 @@
       <c r="Z35" s="62"/>
       <c r="AA35" s="148"/>
       <c r="AD35" s="194"/>
-      <c r="AE35" s="356" t="s">
+      <c r="AE35" s="364" t="s">
         <v>31</v>
       </c>
-      <c r="AF35" s="357"/>
+      <c r="AF35" s="365"/>
       <c r="AG35" s="31"/>
       <c r="AH35" s="89"/>
       <c r="AI35" s="89"/>
@@ -24586,7 +24589,7 @@
       <c r="AK35" s="193"/>
     </row>
     <row r="36" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="306" t="s">
+      <c r="B36" s="279" t="s">
         <v>33</v>
       </c>
       <c r="C36" s="111" t="s">
@@ -24619,18 +24622,18 @@
       <c r="Z36" s="62"/>
       <c r="AA36" s="148"/>
       <c r="AD36" s="194"/>
-      <c r="AE36" s="290" t="s">
+      <c r="AE36" s="325" t="s">
         <v>30</v>
       </c>
-      <c r="AF36" s="290"/>
-      <c r="AG36" s="290"/>
-      <c r="AH36" s="290"/>
-      <c r="AI36" s="290"/>
-      <c r="AJ36" s="290"/>
+      <c r="AF36" s="325"/>
+      <c r="AG36" s="325"/>
+      <c r="AH36" s="325"/>
+      <c r="AI36" s="325"/>
+      <c r="AJ36" s="325"/>
       <c r="AK36" s="193"/>
     </row>
     <row r="37" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="306"/>
+      <c r="B37" s="279"/>
       <c r="C37" s="111" t="s">
         <v>12</v>
       </c>
@@ -24661,7 +24664,7 @@
       <c r="Z37" s="62"/>
       <c r="AA37" s="148"/>
       <c r="AD37" s="194"/>
-      <c r="AE37" s="361" t="s">
+      <c r="AE37" s="363" t="s">
         <v>1</v>
       </c>
       <c r="AF37" s="151" t="s">
@@ -24674,7 +24677,7 @@
       <c r="AK37" s="193"/>
     </row>
     <row r="38" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="306" t="s">
+      <c r="B38" s="279" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="111" t="s">
@@ -24707,7 +24710,7 @@
       <c r="Z38" s="62"/>
       <c r="AA38" s="148"/>
       <c r="AD38" s="194"/>
-      <c r="AE38" s="361"/>
+      <c r="AE38" s="363"/>
       <c r="AF38" s="151" t="s">
         <v>61</v>
       </c>
@@ -24718,7 +24721,7 @@
       <c r="AK38" s="193"/>
     </row>
     <row r="39" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="306"/>
+      <c r="B39" s="279"/>
       <c r="C39" s="111" t="s">
         <v>12</v>
       </c>
@@ -24749,7 +24752,7 @@
       <c r="Z39" s="62"/>
       <c r="AA39" s="148"/>
       <c r="AD39" s="194"/>
-      <c r="AE39" s="361" t="s">
+      <c r="AE39" s="363" t="s">
         <v>624</v>
       </c>
       <c r="AF39" s="151" t="s">
@@ -24762,10 +24765,10 @@
       <c r="AK39" s="193"/>
     </row>
     <row r="40" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="306" t="s">
+      <c r="B40" s="279" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="306"/>
+      <c r="C40" s="279"/>
       <c r="D40" s="2" t="s">
         <v>122</v>
       </c>
@@ -24793,7 +24796,7 @@
       <c r="Z40" s="62"/>
       <c r="AA40" s="148"/>
       <c r="AD40" s="194"/>
-      <c r="AE40" s="361"/>
+      <c r="AE40" s="363"/>
       <c r="AF40" s="151" t="s">
         <v>12</v>
       </c>
@@ -24804,10 +24807,10 @@
       <c r="AK40" s="193"/>
     </row>
     <row r="41" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="306" t="s">
+      <c r="B41" s="279" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="306"/>
+      <c r="C41" s="279"/>
       <c r="D41" s="2" t="s">
         <v>122</v>
       </c>
@@ -24835,7 +24838,7 @@
       <c r="Z41" s="62"/>
       <c r="AA41" s="148"/>
       <c r="AD41" s="194"/>
-      <c r="AE41" s="361" t="s">
+      <c r="AE41" s="363" t="s">
         <v>634</v>
       </c>
       <c r="AF41" s="151" t="s">
@@ -24848,36 +24851,36 @@
       <c r="AK41" s="193"/>
     </row>
     <row r="42" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="320" t="s">
+      <c r="B42" s="269" t="s">
         <v>647</v>
       </c>
-      <c r="C42" s="321"/>
-      <c r="D42" s="321"/>
-      <c r="E42" s="321"/>
-      <c r="F42" s="321"/>
-      <c r="G42" s="321"/>
-      <c r="H42" s="321"/>
-      <c r="I42" s="321"/>
-      <c r="J42" s="321"/>
-      <c r="K42" s="321"/>
-      <c r="L42" s="321"/>
-      <c r="M42" s="321"/>
-      <c r="N42" s="321"/>
-      <c r="O42" s="321"/>
-      <c r="P42" s="321"/>
-      <c r="Q42" s="321"/>
-      <c r="R42" s="321"/>
-      <c r="S42" s="321"/>
-      <c r="T42" s="321"/>
-      <c r="U42" s="321"/>
-      <c r="V42" s="321"/>
-      <c r="W42" s="321"/>
-      <c r="X42" s="321"/>
-      <c r="Y42" s="321"/>
-      <c r="Z42" s="321"/>
-      <c r="AA42" s="322"/>
+      <c r="C42" s="270"/>
+      <c r="D42" s="270"/>
+      <c r="E42" s="270"/>
+      <c r="F42" s="270"/>
+      <c r="G42" s="270"/>
+      <c r="H42" s="270"/>
+      <c r="I42" s="270"/>
+      <c r="J42" s="270"/>
+      <c r="K42" s="270"/>
+      <c r="L42" s="270"/>
+      <c r="M42" s="270"/>
+      <c r="N42" s="270"/>
+      <c r="O42" s="270"/>
+      <c r="P42" s="270"/>
+      <c r="Q42" s="270"/>
+      <c r="R42" s="270"/>
+      <c r="S42" s="270"/>
+      <c r="T42" s="270"/>
+      <c r="U42" s="270"/>
+      <c r="V42" s="270"/>
+      <c r="W42" s="270"/>
+      <c r="X42" s="270"/>
+      <c r="Y42" s="270"/>
+      <c r="Z42" s="270"/>
+      <c r="AA42" s="271"/>
       <c r="AD42" s="194"/>
-      <c r="AE42" s="361"/>
+      <c r="AE42" s="363"/>
       <c r="AF42" s="151" t="s">
         <v>12</v>
       </c>
@@ -24888,10 +24891,10 @@
       <c r="AK42" s="193"/>
     </row>
     <row r="43" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="375" t="s">
+      <c r="B43" s="370" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="375"/>
+      <c r="C43" s="370"/>
       <c r="D43" s="2" t="s">
         <v>135</v>
       </c>
@@ -24919,10 +24922,10 @@
       <c r="Z43" s="62"/>
       <c r="AA43" s="148"/>
       <c r="AD43" s="194"/>
-      <c r="AE43" s="363" t="s">
+      <c r="AE43" s="359" t="s">
         <v>635</v>
       </c>
-      <c r="AF43" s="363"/>
+      <c r="AF43" s="359"/>
       <c r="AG43" s="218"/>
       <c r="AH43" s="218"/>
       <c r="AI43" s="218"/>
@@ -24930,10 +24933,10 @@
       <c r="AK43" s="210"/>
     </row>
     <row r="44" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="375" t="s">
+      <c r="B44" s="370" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="375"/>
+      <c r="C44" s="370"/>
       <c r="D44" s="2" t="s">
         <v>135</v>
       </c>
@@ -24961,10 +24964,10 @@
       <c r="Z44" s="62"/>
       <c r="AA44" s="148"/>
       <c r="AD44" s="194"/>
-      <c r="AE44" s="363" t="s">
+      <c r="AE44" s="359" t="s">
         <v>636</v>
       </c>
-      <c r="AF44" s="363"/>
+      <c r="AF44" s="359"/>
       <c r="AG44" s="218"/>
       <c r="AH44" s="218"/>
       <c r="AI44" s="218"/>
@@ -24972,10 +24975,10 @@
       <c r="AK44" s="210"/>
     </row>
     <row r="45" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="375" t="s">
+      <c r="B45" s="370" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="375"/>
+      <c r="C45" s="370"/>
       <c r="D45" s="2" t="s">
         <v>135</v>
       </c>
@@ -25003,21 +25006,21 @@
       <c r="Z45" s="62"/>
       <c r="AA45" s="148"/>
       <c r="AD45" s="194"/>
-      <c r="AE45" s="358" t="s">
+      <c r="AE45" s="360" t="s">
         <v>107</v>
       </c>
-      <c r="AF45" s="359"/>
-      <c r="AG45" s="359"/>
-      <c r="AH45" s="359"/>
-      <c r="AI45" s="359"/>
-      <c r="AJ45" s="360"/>
+      <c r="AF45" s="361"/>
+      <c r="AG45" s="361"/>
+      <c r="AH45" s="361"/>
+      <c r="AI45" s="361"/>
+      <c r="AJ45" s="362"/>
       <c r="AK45" s="210"/>
     </row>
     <row r="46" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="375" t="s">
+      <c r="B46" s="370" t="s">
         <v>64</v>
       </c>
-      <c r="C46" s="375"/>
+      <c r="C46" s="370"/>
       <c r="D46" s="2" t="s">
         <v>135</v>
       </c>
@@ -25045,10 +25048,10 @@
       <c r="Z46" s="62"/>
       <c r="AA46" s="148"/>
       <c r="AD46" s="194"/>
-      <c r="AE46" s="358" t="s">
+      <c r="AE46" s="360" t="s">
         <v>634</v>
       </c>
-      <c r="AF46" s="360"/>
+      <c r="AF46" s="362"/>
       <c r="AG46" s="218"/>
       <c r="AH46" s="218"/>
       <c r="AI46" s="218"/>
@@ -25056,39 +25059,39 @@
       <c r="AK46" s="210"/>
     </row>
     <row r="47" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="320" t="s">
+      <c r="B47" s="269" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="321"/>
-      <c r="D47" s="321"/>
-      <c r="E47" s="321"/>
-      <c r="F47" s="321"/>
-      <c r="G47" s="321"/>
-      <c r="H47" s="321"/>
-      <c r="I47" s="321"/>
-      <c r="J47" s="321"/>
-      <c r="K47" s="321"/>
-      <c r="L47" s="321"/>
-      <c r="M47" s="321"/>
-      <c r="N47" s="321"/>
-      <c r="O47" s="321"/>
-      <c r="P47" s="321"/>
-      <c r="Q47" s="321"/>
-      <c r="R47" s="321"/>
-      <c r="S47" s="321"/>
-      <c r="T47" s="321"/>
-      <c r="U47" s="321"/>
-      <c r="V47" s="321"/>
-      <c r="W47" s="321"/>
-      <c r="X47" s="321"/>
-      <c r="Y47" s="321"/>
-      <c r="Z47" s="321"/>
-      <c r="AA47" s="322"/>
+      <c r="C47" s="270"/>
+      <c r="D47" s="270"/>
+      <c r="E47" s="270"/>
+      <c r="F47" s="270"/>
+      <c r="G47" s="270"/>
+      <c r="H47" s="270"/>
+      <c r="I47" s="270"/>
+      <c r="J47" s="270"/>
+      <c r="K47" s="270"/>
+      <c r="L47" s="270"/>
+      <c r="M47" s="270"/>
+      <c r="N47" s="270"/>
+      <c r="O47" s="270"/>
+      <c r="P47" s="270"/>
+      <c r="Q47" s="270"/>
+      <c r="R47" s="270"/>
+      <c r="S47" s="270"/>
+      <c r="T47" s="270"/>
+      <c r="U47" s="270"/>
+      <c r="V47" s="270"/>
+      <c r="W47" s="270"/>
+      <c r="X47" s="270"/>
+      <c r="Y47" s="270"/>
+      <c r="Z47" s="270"/>
+      <c r="AA47" s="271"/>
       <c r="AD47" s="194"/>
-      <c r="AE47" s="358" t="s">
+      <c r="AE47" s="360" t="s">
         <v>624</v>
       </c>
-      <c r="AF47" s="360"/>
+      <c r="AF47" s="362"/>
       <c r="AG47" s="218"/>
       <c r="AH47" s="218"/>
       <c r="AI47" s="218"/>
@@ -25096,10 +25099,10 @@
       <c r="AK47" s="193"/>
     </row>
     <row r="48" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="375" t="s">
+      <c r="B48" s="370" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="375"/>
+      <c r="C48" s="370"/>
       <c r="D48" s="2" t="s">
         <v>233</v>
       </c>
@@ -25127,10 +25130,10 @@
       <c r="Z48" s="62"/>
       <c r="AA48" s="148"/>
       <c r="AD48" s="194"/>
-      <c r="AE48" s="358" t="s">
+      <c r="AE48" s="360" t="s">
         <v>635</v>
       </c>
-      <c r="AF48" s="360"/>
+      <c r="AF48" s="362"/>
       <c r="AG48" s="218"/>
       <c r="AH48" s="218"/>
       <c r="AI48" s="218"/>
@@ -25138,10 +25141,10 @@
       <c r="AK48" s="193"/>
     </row>
     <row r="49" spans="2:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="375" t="s">
+      <c r="B49" s="370" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="375"/>
+      <c r="C49" s="370"/>
       <c r="D49" s="2" t="s">
         <v>233</v>
       </c>
@@ -25169,10 +25172,10 @@
       <c r="Z49" s="62"/>
       <c r="AA49" s="148"/>
       <c r="AD49" s="194"/>
-      <c r="AE49" s="358" t="s">
+      <c r="AE49" s="360" t="s">
         <v>637</v>
       </c>
-      <c r="AF49" s="360"/>
+      <c r="AF49" s="362"/>
       <c r="AG49" s="218"/>
       <c r="AH49" s="218"/>
       <c r="AI49" s="218"/>
@@ -25180,10 +25183,10 @@
       <c r="AK49" s="193"/>
     </row>
     <row r="50" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="375" t="s">
+      <c r="B50" s="370" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="375"/>
+      <c r="C50" s="370"/>
       <c r="D50" s="2" t="s">
         <v>121</v>
       </c>
@@ -25211,22 +25214,22 @@
       <c r="Z50" s="62"/>
       <c r="AA50" s="148"/>
       <c r="AD50" s="194"/>
-      <c r="AE50" s="358" t="s">
+      <c r="AE50" s="360" t="s">
         <v>65</v>
       </c>
-      <c r="AF50" s="359"/>
-      <c r="AG50" s="359"/>
-      <c r="AH50" s="359"/>
-      <c r="AI50" s="359"/>
-      <c r="AJ50" s="360"/>
+      <c r="AF50" s="361"/>
+      <c r="AG50" s="361"/>
+      <c r="AH50" s="361"/>
+      <c r="AI50" s="361"/>
+      <c r="AJ50" s="362"/>
       <c r="AK50" s="193"/>
     </row>
     <row r="51" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AD51" s="194"/>
-      <c r="AE51" s="358" t="s">
+      <c r="AE51" s="360" t="s">
         <v>639</v>
       </c>
-      <c r="AF51" s="360"/>
+      <c r="AF51" s="362"/>
       <c r="AG51" s="218"/>
       <c r="AH51" s="218"/>
       <c r="AI51" s="218"/>
@@ -25235,10 +25238,10 @@
     </row>
     <row r="52" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AD52" s="194"/>
-      <c r="AE52" s="358" t="s">
+      <c r="AE52" s="360" t="s">
         <v>638</v>
       </c>
-      <c r="AF52" s="360"/>
+      <c r="AF52" s="362"/>
       <c r="AG52" s="218"/>
       <c r="AH52" s="218"/>
       <c r="AI52" s="218"/>
@@ -25247,10 +25250,10 @@
     </row>
     <row r="53" spans="2:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AD53" s="194"/>
-      <c r="AE53" s="358" t="s">
+      <c r="AE53" s="360" t="s">
         <v>640</v>
       </c>
-      <c r="AF53" s="360"/>
+      <c r="AF53" s="362"/>
       <c r="AG53" s="218"/>
       <c r="AH53" s="218"/>
       <c r="AI53" s="218"/>
@@ -25279,55 +25282,16 @@
     </row>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="P30:S30"/>
-    <mergeCell ref="T30:W30"/>
-    <mergeCell ref="X30:AA30"/>
-    <mergeCell ref="B42:AA42"/>
-    <mergeCell ref="B33:AA33"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B47:AA47"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="AE50:AJ50"/>
-    <mergeCell ref="AE46:AF46"/>
-    <mergeCell ref="AE51:AF51"/>
-    <mergeCell ref="AE52:AF52"/>
-    <mergeCell ref="AE53:AF53"/>
-    <mergeCell ref="AE47:AF47"/>
-    <mergeCell ref="AE48:AF48"/>
-    <mergeCell ref="AE49:AF49"/>
-    <mergeCell ref="AE44:AF44"/>
-    <mergeCell ref="AE45:AJ45"/>
-    <mergeCell ref="AE41:AE42"/>
-    <mergeCell ref="AE43:AF43"/>
-    <mergeCell ref="AE34:AF34"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AE36:AJ36"/>
-    <mergeCell ref="AE37:AE38"/>
-    <mergeCell ref="AE39:AE40"/>
-    <mergeCell ref="V2:AA2"/>
-    <mergeCell ref="V5:AA5"/>
-    <mergeCell ref="V14:AA14"/>
-    <mergeCell ref="V19:AA19"/>
-    <mergeCell ref="P2:U2"/>
-    <mergeCell ref="P5:U5"/>
-    <mergeCell ref="P14:U14"/>
-    <mergeCell ref="P19:U19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="J2:O2"/>
     <mergeCell ref="J5:O5"/>
     <mergeCell ref="J19:O19"/>
@@ -25344,16 +25308,55 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="V2:AA2"/>
+    <mergeCell ref="V5:AA5"/>
+    <mergeCell ref="V14:AA14"/>
+    <mergeCell ref="V19:AA19"/>
+    <mergeCell ref="P2:U2"/>
+    <mergeCell ref="P5:U5"/>
+    <mergeCell ref="P14:U14"/>
+    <mergeCell ref="P19:U19"/>
+    <mergeCell ref="AE44:AF44"/>
+    <mergeCell ref="AE45:AJ45"/>
+    <mergeCell ref="AE41:AE42"/>
+    <mergeCell ref="AE43:AF43"/>
+    <mergeCell ref="AE34:AF34"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AE36:AJ36"/>
+    <mergeCell ref="AE37:AE38"/>
+    <mergeCell ref="AE39:AE40"/>
+    <mergeCell ref="AE50:AJ50"/>
+    <mergeCell ref="AE46:AF46"/>
+    <mergeCell ref="AE51:AF51"/>
+    <mergeCell ref="AE52:AF52"/>
+    <mergeCell ref="AE53:AF53"/>
+    <mergeCell ref="AE47:AF47"/>
+    <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AE49:AF49"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B47:AA47"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="P30:S30"/>
+    <mergeCell ref="T30:W30"/>
+    <mergeCell ref="X30:AA30"/>
+    <mergeCell ref="B42:AA42"/>
+    <mergeCell ref="B33:AA33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:O30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25385,15 +25388,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="384" t="s">
+      <c r="B2" s="387" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="384"/>
-      <c r="D2" s="384"/>
-      <c r="E2" s="384"/>
-      <c r="F2" s="384"/>
-      <c r="G2" s="384"/>
-      <c r="H2" s="384"/>
+      <c r="C2" s="387"/>
+      <c r="D2" s="387"/>
+      <c r="E2" s="387"/>
+      <c r="F2" s="387"/>
+      <c r="G2" s="387"/>
+      <c r="H2" s="387"/>
     </row>
     <row r="3" spans="2:28" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
@@ -25419,15 +25422,15 @@
       </c>
     </row>
     <row r="4" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="292" t="s">
+      <c r="B4" s="327" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="261"/>
-      <c r="D4" s="261"/>
-      <c r="E4" s="261"/>
-      <c r="F4" s="261"/>
-      <c r="G4" s="261"/>
-      <c r="H4" s="293"/>
+      <c r="C4" s="328"/>
+      <c r="D4" s="328"/>
+      <c r="E4" s="328"/>
+      <c r="F4" s="328"/>
+      <c r="G4" s="328"/>
+      <c r="H4" s="329"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
@@ -25479,10 +25482,10 @@
       <c r="L6"/>
       <c r="M6"/>
       <c r="Y6" s="194"/>
-      <c r="Z6" s="358" t="s">
+      <c r="Z6" s="360" t="s">
         <v>663</v>
       </c>
-      <c r="AA6" s="360"/>
+      <c r="AA6" s="362"/>
       <c r="AB6" s="193"/>
     </row>
     <row r="7" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -25578,15 +25581,15 @@
       <c r="AB10" s="193"/>
     </row>
     <row r="11" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="292" t="s">
+      <c r="B11" s="327" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="389"/>
-      <c r="D11" s="389"/>
-      <c r="E11" s="389"/>
-      <c r="F11" s="389"/>
-      <c r="G11" s="389"/>
-      <c r="H11" s="347"/>
+      <c r="C11" s="386"/>
+      <c r="D11" s="386"/>
+      <c r="E11" s="386"/>
+      <c r="F11" s="386"/>
+      <c r="G11" s="386"/>
+      <c r="H11" s="296"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11"/>
@@ -25638,22 +25641,22 @@
       <c r="L13"/>
       <c r="M13"/>
       <c r="Y13" s="194"/>
-      <c r="Z13" s="358" t="s">
+      <c r="Z13" s="360" t="s">
         <v>107</v>
       </c>
-      <c r="AA13" s="360"/>
+      <c r="AA13" s="362"/>
       <c r="AB13" s="193"/>
     </row>
     <row r="14" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="292" t="s">
+      <c r="B14" s="327" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="389"/>
-      <c r="D14" s="389"/>
-      <c r="E14" s="389"/>
-      <c r="F14" s="389"/>
-      <c r="G14" s="389"/>
-      <c r="H14" s="347"/>
+      <c r="C14" s="386"/>
+      <c r="D14" s="386"/>
+      <c r="E14" s="386"/>
+      <c r="F14" s="386"/>
+      <c r="G14" s="386"/>
+      <c r="H14" s="296"/>
       <c r="J14"/>
       <c r="K14"/>
       <c r="L14"/>
@@ -25712,15 +25715,15 @@
       <c r="AB16" s="210"/>
     </row>
     <row r="17" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="292" t="s">
+      <c r="B17" s="327" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="389"/>
-      <c r="D17" s="389"/>
-      <c r="E17" s="389"/>
-      <c r="F17" s="389"/>
-      <c r="G17" s="389"/>
-      <c r="H17" s="347"/>
+      <c r="C17" s="386"/>
+      <c r="D17" s="386"/>
+      <c r="E17" s="386"/>
+      <c r="F17" s="386"/>
+      <c r="G17" s="386"/>
+      <c r="H17" s="296"/>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17"/>
@@ -25772,10 +25775,10 @@
       <c r="L19"/>
       <c r="M19"/>
       <c r="Y19" s="194"/>
-      <c r="Z19" s="358" t="s">
+      <c r="Z19" s="360" t="s">
         <v>50</v>
       </c>
-      <c r="AA19" s="360"/>
+      <c r="AA19" s="362"/>
       <c r="AB19" s="193"/>
     </row>
     <row r="20" spans="2:28" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -25867,16 +25870,16 @@
       <c r="AB24" s="193"/>
     </row>
     <row r="25" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J25" s="384" t="s">
+      <c r="J25" s="387" t="s">
         <v>90</v>
       </c>
-      <c r="K25" s="384"/>
-      <c r="L25" s="384"/>
-      <c r="M25" s="384"/>
-      <c r="N25" s="384"/>
-      <c r="O25" s="384"/>
-      <c r="P25" s="384"/>
-      <c r="Q25" s="384"/>
+      <c r="K25" s="387"/>
+      <c r="L25" s="387"/>
+      <c r="M25" s="387"/>
+      <c r="N25" s="387"/>
+      <c r="O25" s="387"/>
+      <c r="P25" s="387"/>
+      <c r="Q25" s="387"/>
       <c r="Y25" s="194"/>
       <c r="Z25" s="230" t="s">
         <v>662</v>
@@ -25885,10 +25888,10 @@
       <c r="AB25" s="193"/>
     </row>
     <row r="26" spans="2:28" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J26" s="385" t="s">
+      <c r="J26" s="390" t="s">
         <v>40</v>
       </c>
-      <c r="K26" s="386"/>
+      <c r="K26" s="391"/>
       <c r="L26" s="184" t="s">
         <v>117</v>
       </c>
@@ -25913,26 +25916,26 @@
       <c r="AB26" s="193"/>
     </row>
     <row r="27" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J27" s="292" t="s">
+      <c r="J27" s="327" t="s">
         <v>30</v>
       </c>
-      <c r="K27" s="261"/>
-      <c r="L27" s="261"/>
-      <c r="M27" s="261"/>
-      <c r="N27" s="261"/>
-      <c r="O27" s="261"/>
-      <c r="P27" s="261"/>
-      <c r="Q27" s="293"/>
+      <c r="K27" s="328"/>
+      <c r="L27" s="328"/>
+      <c r="M27" s="328"/>
+      <c r="N27" s="328"/>
+      <c r="O27" s="328"/>
+      <c r="P27" s="328"/>
+      <c r="Q27" s="329"/>
       <c r="Y27" s="196"/>
       <c r="Z27" s="197"/>
       <c r="AA27" s="223"/>
       <c r="AB27" s="198"/>
     </row>
     <row r="28" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J28" s="387" t="s">
+      <c r="J28" s="392" t="s">
         <v>91</v>
       </c>
-      <c r="K28" s="388"/>
+      <c r="K28" s="393"/>
       <c r="L28" s="36"/>
       <c r="M28" s="36"/>
       <c r="N28" s="36"/>
@@ -25941,7 +25944,7 @@
       <c r="Q28" s="37"/>
     </row>
     <row r="29" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J29" s="381" t="s">
+      <c r="J29" s="384" t="s">
         <v>92</v>
       </c>
       <c r="K29" s="34" t="s">
@@ -25955,7 +25958,7 @@
       <c r="Q29" s="45"/>
     </row>
     <row r="30" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J30" s="382"/>
+      <c r="J30" s="389"/>
       <c r="K30" s="34" t="s">
         <v>94</v>
       </c>
@@ -25974,7 +25977,7 @@
       <c r="W30" s="190"/>
     </row>
     <row r="31" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J31" s="383"/>
+      <c r="J31" s="385"/>
       <c r="K31" s="34" t="s">
         <v>95</v>
       </c>
@@ -25993,7 +25996,7 @@
       <c r="W31" s="208"/>
     </row>
     <row r="32" spans="2:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J32" s="381" t="s">
+      <c r="J32" s="384" t="s">
         <v>100</v>
       </c>
       <c r="K32" s="34" t="s">
@@ -26006,15 +26009,15 @@
       <c r="P32" s="40"/>
       <c r="Q32" s="45"/>
       <c r="S32" s="194"/>
-      <c r="T32" s="290" t="s">
+      <c r="T32" s="325" t="s">
         <v>663</v>
       </c>
-      <c r="U32" s="290"/>
-      <c r="V32" s="290"/>
+      <c r="U32" s="325"/>
+      <c r="V32" s="325"/>
       <c r="W32" s="193"/>
     </row>
     <row r="33" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J33" s="382"/>
+      <c r="J33" s="389"/>
       <c r="K33" s="34" t="s">
         <v>93</v>
       </c>
@@ -26033,7 +26036,7 @@
       <c r="W33" s="193"/>
     </row>
     <row r="34" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J34" s="382"/>
+      <c r="J34" s="389"/>
       <c r="K34" s="34" t="s">
         <v>97</v>
       </c>
@@ -26056,7 +26059,7 @@
       <c r="W34" s="193"/>
     </row>
     <row r="35" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J35" s="383"/>
+      <c r="J35" s="385"/>
       <c r="K35" s="34" t="s">
         <v>98</v>
       </c>
@@ -26075,7 +26078,7 @@
       <c r="W35" s="193"/>
     </row>
     <row r="36" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J36" s="381" t="s">
+      <c r="J36" s="384" t="s">
         <v>319</v>
       </c>
       <c r="K36" s="34" t="s">
@@ -26096,7 +26099,7 @@
       <c r="W36" s="193"/>
     </row>
     <row r="37" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J37" s="382"/>
+      <c r="J37" s="389"/>
       <c r="K37" s="34" t="s">
         <v>93</v>
       </c>
@@ -26115,7 +26118,7 @@
       <c r="W37" s="193"/>
     </row>
     <row r="38" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J38" s="382"/>
+      <c r="J38" s="389"/>
       <c r="K38" s="34" t="s">
         <v>94</v>
       </c>
@@ -26134,7 +26137,7 @@
       <c r="W38" s="193"/>
     </row>
     <row r="39" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J39" s="383"/>
+      <c r="J39" s="385"/>
       <c r="K39" s="34" t="s">
         <v>95</v>
       </c>
@@ -26153,7 +26156,7 @@
       <c r="W39" s="193"/>
     </row>
     <row r="40" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J40" s="381" t="s">
+      <c r="J40" s="384" t="s">
         <v>99</v>
       </c>
       <c r="K40" s="34" t="s">
@@ -26176,7 +26179,7 @@
       <c r="X40"/>
     </row>
     <row r="41" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J41" s="382"/>
+      <c r="J41" s="389"/>
       <c r="K41" s="34" t="s">
         <v>93</v>
       </c>
@@ -26197,7 +26200,7 @@
       <c r="X41"/>
     </row>
     <row r="42" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J42" s="382"/>
+      <c r="J42" s="389"/>
       <c r="K42" s="34" t="s">
         <v>97</v>
       </c>
@@ -26218,7 +26221,7 @@
       <c r="X42"/>
     </row>
     <row r="43" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J43" s="382"/>
+      <c r="J43" s="389"/>
       <c r="K43" s="102" t="s">
         <v>98</v>
       </c>
@@ -26230,25 +26233,25 @@
       <c r="Q43" s="37"/>
       <c r="R43"/>
       <c r="S43" s="194"/>
-      <c r="T43" s="290" t="s">
+      <c r="T43" s="325" t="s">
         <v>107</v>
       </c>
-      <c r="U43" s="290"/>
+      <c r="U43" s="325"/>
       <c r="V43" s="235"/>
       <c r="W43" s="193"/>
       <c r="X43"/>
     </row>
     <row r="44" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J44" s="380" t="s">
+      <c r="J44" s="388" t="s">
         <v>107</v>
       </c>
-      <c r="K44" s="380"/>
-      <c r="L44" s="380"/>
-      <c r="M44" s="380"/>
-      <c r="N44" s="380"/>
-      <c r="O44" s="380"/>
-      <c r="P44" s="380"/>
-      <c r="Q44" s="380"/>
+      <c r="K44" s="388"/>
+      <c r="L44" s="388"/>
+      <c r="M44" s="388"/>
+      <c r="N44" s="388"/>
+      <c r="O44" s="388"/>
+      <c r="P44" s="388"/>
+      <c r="Q44" s="388"/>
       <c r="S44" s="194"/>
       <c r="T44" s="227" t="s">
         <v>649</v>
@@ -26258,10 +26261,10 @@
       <c r="W44" s="193"/>
     </row>
     <row r="45" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J45" s="306" t="s">
+      <c r="J45" s="279" t="s">
         <v>42</v>
       </c>
-      <c r="K45" s="306"/>
+      <c r="K45" s="279"/>
       <c r="L45" s="62"/>
       <c r="M45" s="62"/>
       <c r="N45" s="62"/>
@@ -26277,10 +26280,10 @@
       <c r="W45" s="193"/>
     </row>
     <row r="46" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J46" s="390" t="s">
+      <c r="J46" s="382" t="s">
         <v>314</v>
       </c>
-      <c r="K46" s="391"/>
+      <c r="K46" s="383"/>
       <c r="L46" s="62"/>
       <c r="M46" s="62"/>
       <c r="N46" s="62"/>
@@ -26296,10 +26299,10 @@
       <c r="W46" s="193"/>
     </row>
     <row r="47" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J47" s="390" t="s">
+      <c r="J47" s="382" t="s">
         <v>322</v>
       </c>
-      <c r="K47" s="391"/>
+      <c r="K47" s="383"/>
       <c r="L47" s="62"/>
       <c r="M47" s="62"/>
       <c r="N47" s="62"/>
@@ -26315,10 +26318,10 @@
       <c r="W47" s="193"/>
     </row>
     <row r="48" spans="10:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J48" s="390" t="s">
+      <c r="J48" s="382" t="s">
         <v>321</v>
       </c>
-      <c r="K48" s="391"/>
+      <c r="K48" s="383"/>
       <c r="L48" s="62"/>
       <c r="M48" s="62"/>
       <c r="N48" s="62"/>
@@ -26334,10 +26337,10 @@
       <c r="W48" s="193"/>
     </row>
     <row r="49" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J49" s="390" t="s">
+      <c r="J49" s="382" t="s">
         <v>320</v>
       </c>
-      <c r="K49" s="391"/>
+      <c r="K49" s="383"/>
       <c r="L49" s="62"/>
       <c r="M49" s="62"/>
       <c r="N49" s="62"/>
@@ -26353,7 +26356,7 @@
       <c r="W49" s="193"/>
     </row>
     <row r="50" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J50" s="381" t="s">
+      <c r="J50" s="384" t="s">
         <v>37</v>
       </c>
       <c r="K50" s="111" t="s">
@@ -26374,7 +26377,7 @@
       <c r="W50" s="193"/>
     </row>
     <row r="51" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J51" s="383"/>
+      <c r="J51" s="385"/>
       <c r="K51" s="111" t="s">
         <v>318</v>
       </c>
@@ -26393,10 +26396,10 @@
       <c r="W51" s="193"/>
     </row>
     <row r="52" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J52" s="390" t="s">
+      <c r="J52" s="382" t="s">
         <v>64</v>
       </c>
-      <c r="K52" s="391"/>
+      <c r="K52" s="383"/>
       <c r="L52" s="62"/>
       <c r="M52" s="62"/>
       <c r="N52" s="62"/>
@@ -26412,10 +26415,10 @@
       <c r="W52" s="193"/>
     </row>
     <row r="53" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J53" s="390" t="s">
+      <c r="J53" s="382" t="s">
         <v>10</v>
       </c>
-      <c r="K53" s="391"/>
+      <c r="K53" s="383"/>
       <c r="L53" s="62"/>
       <c r="M53" s="62"/>
       <c r="N53" s="62"/>
@@ -26431,10 +26434,10 @@
       <c r="W53" s="193"/>
     </row>
     <row r="54" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J54" s="390" t="s">
+      <c r="J54" s="382" t="s">
         <v>315</v>
       </c>
-      <c r="K54" s="391"/>
+      <c r="K54" s="383"/>
       <c r="L54" s="62"/>
       <c r="M54" s="62"/>
       <c r="N54" s="62"/>
@@ -26450,10 +26453,10 @@
       <c r="W54" s="193"/>
     </row>
     <row r="55" spans="10:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J55" s="390" t="s">
+      <c r="J55" s="382" t="s">
         <v>316</v>
       </c>
-      <c r="K55" s="391"/>
+      <c r="K55" s="383"/>
       <c r="L55" s="62"/>
       <c r="M55" s="62"/>
       <c r="N55" s="62"/>
@@ -26475,11 +26478,20 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="T32:V32"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="J44:Q44"/>
+    <mergeCell ref="J32:J35"/>
+    <mergeCell ref="J36:J39"/>
+    <mergeCell ref="J40:J43"/>
+    <mergeCell ref="J25:Q25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:Q27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:J31"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B2:H2"/>
     <mergeCell ref="J55:K55"/>
     <mergeCell ref="J49:K49"/>
     <mergeCell ref="J48:K48"/>
@@ -26490,20 +26502,11 @@
     <mergeCell ref="J53:K53"/>
     <mergeCell ref="J52:K52"/>
     <mergeCell ref="J54:K54"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="J44:Q44"/>
-    <mergeCell ref="J32:J35"/>
-    <mergeCell ref="J36:J39"/>
-    <mergeCell ref="J40:J43"/>
-    <mergeCell ref="J25:Q25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:Q27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:J31"/>
+    <mergeCell ref="T32:V32"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="Z19:AA19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -26536,22 +26539,22 @@
   <sheetData>
     <row r="1" spans="2:20" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="280" t="s">
+      <c r="B2" s="336" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="280"/>
-      <c r="D2" s="280"/>
-      <c r="E2" s="280"/>
-      <c r="F2" s="280"/>
-      <c r="G2" s="280"/>
-      <c r="H2" s="280"/>
-      <c r="I2" s="280"/>
+      <c r="C2" s="336"/>
+      <c r="D2" s="336"/>
+      <c r="E2" s="336"/>
+      <c r="F2" s="336"/>
+      <c r="G2" s="336"/>
+      <c r="H2" s="336"/>
+      <c r="I2" s="336"/>
     </row>
     <row r="3" spans="2:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="385" t="s">
+      <c r="B3" s="390" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="386"/>
+      <c r="C3" s="391"/>
       <c r="D3" s="183" t="s">
         <v>117</v>
       </c>
@@ -26572,16 +26575,16 @@
       </c>
     </row>
     <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="292" t="s">
+      <c r="B4" s="327" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="261"/>
-      <c r="D4" s="261"/>
-      <c r="E4" s="261"/>
-      <c r="F4" s="261"/>
-      <c r="G4" s="261"/>
-      <c r="H4" s="261"/>
-      <c r="I4" s="293"/>
+      <c r="C4" s="328"/>
+      <c r="D4" s="328"/>
+      <c r="E4" s="328"/>
+      <c r="F4" s="328"/>
+      <c r="G4" s="328"/>
+      <c r="H4" s="328"/>
+      <c r="I4" s="329"/>
       <c r="L4" s="225"/>
       <c r="M4" s="215" t="s">
         <v>686</v>
@@ -26596,10 +26599,10 @@
       <c r="T4" s="190"/>
     </row>
     <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="387" t="s">
+      <c r="B5" s="392" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="388"/>
+      <c r="C5" s="393"/>
       <c r="D5" s="21"/>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
@@ -26620,10 +26623,10 @@
       <c r="T5" s="208"/>
     </row>
     <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="387" t="s">
+      <c r="B6" s="392" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="388"/>
+      <c r="C6" s="393"/>
       <c r="D6" s="21"/>
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
@@ -26631,16 +26634,16 @@
       <c r="H6" s="21"/>
       <c r="I6" s="32"/>
       <c r="L6" s="194"/>
-      <c r="M6" s="290" t="s">
+      <c r="M6" s="325" t="s">
         <v>107</v>
       </c>
-      <c r="N6" s="290"/>
+      <c r="N6" s="325"/>
       <c r="O6" s="193"/>
       <c r="Q6" s="194"/>
-      <c r="R6" s="290" t="s">
+      <c r="R6" s="325" t="s">
         <v>107</v>
       </c>
-      <c r="S6" s="290"/>
+      <c r="S6" s="325"/>
       <c r="T6" s="193"/>
     </row>
     <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26668,10 +26671,10 @@
       <c r="T7" s="193"/>
     </row>
     <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="387" t="s">
+      <c r="B8" s="392" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="388"/>
+      <c r="C8" s="393"/>
       <c r="D8" s="21"/>
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
@@ -26692,16 +26695,16 @@
       <c r="T8" s="193"/>
     </row>
     <row r="9" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="292" t="s">
+      <c r="B9" s="327" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="261"/>
-      <c r="D9" s="261"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="261"/>
-      <c r="G9" s="261"/>
-      <c r="H9" s="261"/>
-      <c r="I9" s="293"/>
+      <c r="C9" s="328"/>
+      <c r="D9" s="328"/>
+      <c r="E9" s="328"/>
+      <c r="F9" s="328"/>
+      <c r="G9" s="328"/>
+      <c r="H9" s="328"/>
+      <c r="I9" s="329"/>
       <c r="L9" s="194"/>
       <c r="M9" s="227" t="s">
         <v>634</v>
@@ -26716,7 +26719,7 @@
       <c r="T9" s="193"/>
     </row>
     <row r="10" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="394" t="s">
+      <c r="B10" s="402" t="s">
         <v>73</v>
       </c>
       <c r="C10" s="35" t="s">
@@ -26742,7 +26745,7 @@
       <c r="T10" s="193"/>
     </row>
     <row r="11" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="395"/>
+      <c r="B11" s="403"/>
       <c r="C11" s="35" t="s">
         <v>12</v>
       </c>
@@ -26753,20 +26756,20 @@
       <c r="H11" s="19"/>
       <c r="I11" s="24"/>
       <c r="L11" s="194"/>
-      <c r="M11" s="290" t="s">
+      <c r="M11" s="325" t="s">
         <v>663</v>
       </c>
-      <c r="N11" s="290"/>
+      <c r="N11" s="325"/>
       <c r="O11" s="193"/>
       <c r="Q11" s="194"/>
-      <c r="R11" s="290" t="s">
+      <c r="R11" s="325" t="s">
         <v>663</v>
       </c>
-      <c r="S11" s="290"/>
+      <c r="S11" s="325"/>
       <c r="T11" s="193"/>
     </row>
     <row r="12" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="394" t="s">
+      <c r="B12" s="402" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="35" t="s">
@@ -26792,7 +26795,7 @@
       <c r="T12" s="193"/>
     </row>
     <row r="13" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="395"/>
+      <c r="B13" s="403"/>
       <c r="C13" s="35" t="s">
         <v>12</v>
       </c>
@@ -26865,16 +26868,16 @@
     </row>
     <row r="17" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
-      <c r="B17" s="280" t="s">
+      <c r="B17" s="336" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="280"/>
-      <c r="D17" s="280"/>
-      <c r="E17" s="280"/>
-      <c r="F17" s="280"/>
-      <c r="G17" s="280"/>
-      <c r="H17" s="280"/>
-      <c r="I17" s="280"/>
+      <c r="C17" s="336"/>
+      <c r="D17" s="336"/>
+      <c r="E17" s="336"/>
+      <c r="F17" s="336"/>
+      <c r="G17" s="336"/>
+      <c r="H17" s="336"/>
+      <c r="I17" s="336"/>
       <c r="K17"/>
       <c r="L17" s="238"/>
       <c r="M17" s="239"/>
@@ -26888,10 +26891,10 @@
     </row>
     <row r="18" spans="1:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
-      <c r="B18" s="385" t="s">
+      <c r="B18" s="390" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="386"/>
+      <c r="C18" s="391"/>
       <c r="D18" s="183" t="s">
         <v>117</v>
       </c>
@@ -26922,16 +26925,16 @@
     </row>
     <row r="19" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
-      <c r="B19" s="292" t="s">
+      <c r="B19" s="327" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="261"/>
-      <c r="D19" s="261"/>
-      <c r="E19" s="261"/>
-      <c r="F19" s="261"/>
-      <c r="G19" s="261"/>
-      <c r="H19" s="261"/>
-      <c r="I19" s="293"/>
+      <c r="C19" s="328"/>
+      <c r="D19" s="328"/>
+      <c r="E19" s="328"/>
+      <c r="F19" s="328"/>
+      <c r="G19" s="328"/>
+      <c r="H19" s="328"/>
+      <c r="I19" s="329"/>
       <c r="K19"/>
       <c r="L19"/>
       <c r="M19"/>
@@ -26944,10 +26947,10 @@
     </row>
     <row r="20" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
-      <c r="B20" s="387" t="s">
+      <c r="B20" s="392" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="388"/>
+      <c r="C20" s="393"/>
       <c r="D20" s="21"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
@@ -26966,10 +26969,10 @@
     </row>
     <row r="21" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
-      <c r="B21" s="387" t="s">
+      <c r="B21" s="392" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="388"/>
+      <c r="C21" s="393"/>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
@@ -27010,10 +27013,10 @@
     </row>
     <row r="23" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
-      <c r="B23" s="398" t="s">
+      <c r="B23" s="397" t="s">
         <v>244</v>
       </c>
-      <c r="C23" s="399"/>
+      <c r="C23" s="406"/>
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
@@ -27032,16 +27035,16 @@
     </row>
     <row r="24" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
-      <c r="B24" s="292" t="s">
+      <c r="B24" s="327" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="261"/>
-      <c r="D24" s="261"/>
-      <c r="E24" s="261"/>
-      <c r="F24" s="261"/>
-      <c r="G24" s="261"/>
-      <c r="H24" s="261"/>
-      <c r="I24" s="293"/>
+      <c r="C24" s="328"/>
+      <c r="D24" s="328"/>
+      <c r="E24" s="328"/>
+      <c r="F24" s="328"/>
+      <c r="G24" s="328"/>
+      <c r="H24" s="328"/>
+      <c r="I24" s="329"/>
       <c r="K24"/>
       <c r="L24"/>
       <c r="M24"/>
@@ -27054,10 +27057,10 @@
     </row>
     <row r="25" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
-      <c r="B25" s="396" t="s">
+      <c r="B25" s="404" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="397"/>
+      <c r="C25" s="405"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
@@ -27076,10 +27079,10 @@
     </row>
     <row r="26" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
-      <c r="B26" s="396" t="s">
+      <c r="B26" s="404" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="397"/>
+      <c r="C26" s="405"/>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
@@ -27098,10 +27101,10 @@
     </row>
     <row r="27" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
-      <c r="B27" s="396" t="s">
+      <c r="B27" s="404" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="397"/>
+      <c r="C27" s="405"/>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
@@ -27120,8 +27123,8 @@
     </row>
     <row r="28" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
-      <c r="B28" s="392"/>
-      <c r="C28" s="393"/>
+      <c r="B28" s="400"/>
+      <c r="C28" s="401"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="19"/>
@@ -27151,23 +27154,23 @@
       <c r="S29"/>
     </row>
     <row r="30" spans="1:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="280" t="s">
+      <c r="B30" s="336" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="280"/>
-      <c r="D30" s="280"/>
-      <c r="E30" s="280"/>
-      <c r="F30" s="280"/>
-      <c r="G30" s="280"/>
-      <c r="H30" s="280"/>
-      <c r="I30" s="280"/>
+      <c r="C30" s="336"/>
+      <c r="D30" s="336"/>
+      <c r="E30" s="336"/>
+      <c r="F30" s="336"/>
+      <c r="G30" s="336"/>
+      <c r="H30" s="336"/>
+      <c r="I30" s="336"/>
       <c r="J30"/>
     </row>
     <row r="31" spans="1:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="385" t="s">
+      <c r="B31" s="390" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="386"/>
+      <c r="C31" s="391"/>
       <c r="D31" s="183" t="s">
         <v>117</v>
       </c>
@@ -27189,10 +27192,10 @@
       <c r="J31"/>
     </row>
     <row r="32" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="400" t="s">
+      <c r="B32" s="394" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="401"/>
+      <c r="C32" s="395"/>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -27208,16 +27211,16 @@
       <c r="O32" s="190"/>
     </row>
     <row r="33" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="292" t="s">
+      <c r="B33" s="327" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="261"/>
-      <c r="D33" s="261"/>
-      <c r="E33" s="261"/>
-      <c r="F33" s="261"/>
-      <c r="G33" s="261"/>
-      <c r="H33" s="261"/>
-      <c r="I33" s="293"/>
+      <c r="C33" s="328"/>
+      <c r="D33" s="328"/>
+      <c r="E33" s="328"/>
+      <c r="F33" s="328"/>
+      <c r="G33" s="328"/>
+      <c r="H33" s="328"/>
+      <c r="I33" s="329"/>
       <c r="J33"/>
       <c r="L33" s="194"/>
       <c r="M33" s="216" t="s">
@@ -27227,7 +27230,7 @@
       <c r="O33" s="208"/>
     </row>
     <row r="34" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="375" t="s">
+      <c r="B34" s="370" t="s">
         <v>83</v>
       </c>
       <c r="C34" s="35" t="s">
@@ -27248,7 +27251,7 @@
       <c r="O34" s="193"/>
     </row>
     <row r="35" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="375"/>
+      <c r="B35" s="370"/>
       <c r="C35" s="35" t="s">
         <v>12</v>
       </c>
@@ -27260,14 +27263,14 @@
       <c r="I35" s="24"/>
       <c r="J35"/>
       <c r="L35" s="194"/>
-      <c r="M35" s="358" t="s">
+      <c r="M35" s="360" t="s">
         <v>663</v>
       </c>
-      <c r="N35" s="360"/>
+      <c r="N35" s="362"/>
       <c r="O35" s="193"/>
     </row>
     <row r="36" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="375" t="s">
+      <c r="B36" s="370" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="35" t="s">
@@ -27288,7 +27291,7 @@
       <c r="O36" s="193"/>
     </row>
     <row r="37" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="375"/>
+      <c r="B37" s="370"/>
       <c r="C37" s="35" t="s">
         <v>12</v>
       </c>
@@ -27307,10 +27310,10 @@
       <c r="O37" s="193"/>
     </row>
     <row r="38" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="387" t="s">
+      <c r="B38" s="392" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="388"/>
+      <c r="C38" s="393"/>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
@@ -27326,16 +27329,16 @@
       <c r="O38" s="193"/>
     </row>
     <row r="39" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="402" t="s">
+      <c r="B39" s="399" t="s">
         <v>65</v>
       </c>
-      <c r="C39" s="389"/>
-      <c r="D39" s="261"/>
-      <c r="E39" s="261"/>
-      <c r="F39" s="261"/>
-      <c r="G39" s="261"/>
-      <c r="H39" s="261"/>
-      <c r="I39" s="293"/>
+      <c r="C39" s="386"/>
+      <c r="D39" s="328"/>
+      <c r="E39" s="328"/>
+      <c r="F39" s="328"/>
+      <c r="G39" s="328"/>
+      <c r="H39" s="328"/>
+      <c r="I39" s="329"/>
       <c r="J39"/>
       <c r="L39" s="194"/>
       <c r="M39" s="227" t="s">
@@ -27345,10 +27348,10 @@
       <c r="O39" s="193"/>
     </row>
     <row r="40" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="375" t="s">
+      <c r="B40" s="370" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="375"/>
+      <c r="C40" s="370"/>
       <c r="D40" s="33"/>
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
@@ -27364,10 +27367,10 @@
       <c r="O40" s="193"/>
     </row>
     <row r="41" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="375" t="s">
+      <c r="B41" s="370" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="375"/>
+      <c r="C41" s="370"/>
       <c r="D41" s="33"/>
       <c r="E41" s="19"/>
       <c r="F41" s="19"/>
@@ -27376,17 +27379,17 @@
       <c r="I41" s="24"/>
       <c r="J41"/>
       <c r="L41" s="194"/>
-      <c r="M41" s="358" t="s">
+      <c r="M41" s="360" t="s">
         <v>65</v>
       </c>
-      <c r="N41" s="360"/>
+      <c r="N41" s="362"/>
       <c r="O41" s="193"/>
     </row>
     <row r="42" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="304" t="s">
+      <c r="B42" s="274" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="305"/>
+      <c r="C42" s="275"/>
       <c r="D42" s="33"/>
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
@@ -27402,10 +27405,10 @@
       <c r="O42" s="193"/>
     </row>
     <row r="43" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="375" t="s">
+      <c r="B43" s="370" t="s">
         <v>85</v>
       </c>
-      <c r="C43" s="375"/>
+      <c r="C43" s="370"/>
       <c r="D43" s="33"/>
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
@@ -27464,22 +27467,22 @@
       <c r="J48"/>
     </row>
     <row r="49" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="280" t="s">
+      <c r="B49" s="336" t="s">
         <v>89</v>
       </c>
-      <c r="C49" s="280"/>
-      <c r="D49" s="280"/>
-      <c r="E49" s="280"/>
-      <c r="F49" s="280"/>
-      <c r="G49" s="280"/>
-      <c r="H49" s="280"/>
-      <c r="I49" s="280"/>
+      <c r="C49" s="336"/>
+      <c r="D49" s="336"/>
+      <c r="E49" s="336"/>
+      <c r="F49" s="336"/>
+      <c r="G49" s="336"/>
+      <c r="H49" s="336"/>
+      <c r="I49" s="336"/>
     </row>
     <row r="50" spans="2:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="385" t="s">
+      <c r="B50" s="390" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="386"/>
+      <c r="C50" s="391"/>
       <c r="D50" s="183" t="s">
         <v>117</v>
       </c>
@@ -27500,10 +27503,10 @@
       </c>
     </row>
     <row r="51" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="400" t="s">
+      <c r="B51" s="394" t="s">
         <v>86</v>
       </c>
-      <c r="C51" s="401"/>
+      <c r="C51" s="395"/>
       <c r="D51" s="22"/>
       <c r="E51" s="22"/>
       <c r="F51" s="22"/>
@@ -27512,10 +27515,10 @@
       <c r="I51" s="27"/>
     </row>
     <row r="52" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="387" t="s">
+      <c r="B52" s="392" t="s">
         <v>87</v>
       </c>
-      <c r="C52" s="388"/>
+      <c r="C52" s="393"/>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
       <c r="F52" s="21"/>
@@ -27524,10 +27527,10 @@
       <c r="I52" s="32"/>
     </row>
     <row r="53" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="387" t="s">
+      <c r="B53" s="392" t="s">
         <v>88</v>
       </c>
-      <c r="C53" s="388"/>
+      <c r="C53" s="393"/>
       <c r="D53" s="25"/>
       <c r="E53" s="25"/>
       <c r="F53" s="25"/>
@@ -27536,22 +27539,22 @@
       <c r="I53" s="26"/>
     </row>
     <row r="55" spans="2:20" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="280" t="s">
+      <c r="B55" s="336" t="s">
         <v>308</v>
       </c>
-      <c r="C55" s="280"/>
-      <c r="D55" s="280"/>
-      <c r="E55" s="280"/>
-      <c r="F55" s="280"/>
-      <c r="G55" s="280"/>
-      <c r="H55" s="280"/>
-      <c r="I55" s="280"/>
+      <c r="C55" s="336"/>
+      <c r="D55" s="336"/>
+      <c r="E55" s="336"/>
+      <c r="F55" s="336"/>
+      <c r="G55" s="336"/>
+      <c r="H55" s="336"/>
+      <c r="I55" s="336"/>
     </row>
     <row r="56" spans="2:20" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="385" t="s">
+      <c r="B56" s="390" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="386"/>
+      <c r="C56" s="391"/>
       <c r="D56" s="183" t="s">
         <v>117</v>
       </c>
@@ -27572,10 +27575,10 @@
       </c>
     </row>
     <row r="57" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="400" t="s">
+      <c r="B57" s="394" t="s">
         <v>309</v>
       </c>
-      <c r="C57" s="401"/>
+      <c r="C57" s="395"/>
       <c r="D57" s="109"/>
       <c r="E57" s="109"/>
       <c r="F57" s="109"/>
@@ -27596,10 +27599,10 @@
       <c r="T57" s="190"/>
     </row>
     <row r="58" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="304" t="s">
+      <c r="B58" s="274" t="s">
         <v>310</v>
       </c>
-      <c r="C58" s="403"/>
+      <c r="C58" s="396"/>
       <c r="D58" s="23"/>
       <c r="E58" s="23"/>
       <c r="F58" s="23"/>
@@ -27620,10 +27623,10 @@
       <c r="T58" s="208"/>
     </row>
     <row r="59" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="398" t="s">
+      <c r="B59" s="397" t="s">
         <v>311</v>
       </c>
-      <c r="C59" s="404"/>
+      <c r="C59" s="398"/>
       <c r="D59" s="23"/>
       <c r="E59" s="23"/>
       <c r="F59" s="23"/>
@@ -27644,10 +27647,10 @@
       <c r="T59" s="193"/>
     </row>
     <row r="60" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="387" t="s">
+      <c r="B60" s="392" t="s">
         <v>312</v>
       </c>
-      <c r="C60" s="388"/>
+      <c r="C60" s="393"/>
       <c r="D60" s="109"/>
       <c r="E60" s="109"/>
       <c r="F60" s="109"/>
@@ -27668,10 +27671,10 @@
       <c r="T60" s="193"/>
     </row>
     <row r="61" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="387" t="s">
+      <c r="B61" s="392" t="s">
         <v>313</v>
       </c>
-      <c r="C61" s="388"/>
+      <c r="C61" s="393"/>
       <c r="D61" s="25"/>
       <c r="E61" s="25"/>
       <c r="F61" s="25"/>
@@ -27729,36 +27732,12 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="B55:I55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B39:I39"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B4:I4"/>
@@ -27773,12 +27752,36 @@
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R11:S11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -27799,12 +27802,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="280" t="s">
+      <c r="A1" s="336" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="280"/>
-      <c r="C1" s="280"/>
-      <c r="D1" s="280"/>
+      <c r="B1" s="336"/>
+      <c r="C1" s="336"/>
+      <c r="D1" s="336"/>
     </row>
     <row r="2" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -27907,13 +27910,13 @@
       <c r="D15" s="43"/>
     </row>
     <row r="16" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F16" s="280" t="s">
+      <c r="F16" s="336" t="s">
         <v>142</v>
       </c>
-      <c r="G16" s="280"/>
-      <c r="H16" s="280"/>
-      <c r="I16" s="280"/>
-      <c r="J16" s="280"/>
+      <c r="G16" s="336"/>
+      <c r="H16" s="336"/>
+      <c r="I16" s="336"/>
+      <c r="J16" s="336"/>
     </row>
     <row r="17" spans="6:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F17" s="3"/>
@@ -27976,23 +27979,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="280" t="s">
+      <c r="A1" s="336" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="280"/>
-      <c r="C1" s="280"/>
-      <c r="D1" s="280"/>
-      <c r="E1" s="280"/>
-      <c r="F1" s="280"/>
-      <c r="G1" s="280"/>
-      <c r="H1" s="280"/>
-      <c r="I1" s="280"/>
-      <c r="J1" s="280"/>
-      <c r="K1" s="280"/>
-      <c r="L1" s="280"/>
-      <c r="M1" s="280"/>
-      <c r="N1" s="280"/>
-      <c r="O1" s="280"/>
+      <c r="B1" s="336"/>
+      <c r="C1" s="336"/>
+      <c r="D1" s="336"/>
+      <c r="E1" s="336"/>
+      <c r="F1" s="336"/>
+      <c r="G1" s="336"/>
+      <c r="H1" s="336"/>
+      <c r="I1" s="336"/>
+      <c r="J1" s="336"/>
+      <c r="K1" s="336"/>
+      <c r="L1" s="336"/>
+      <c r="M1" s="336"/>
+      <c r="N1" s="336"/>
+      <c r="O1" s="336"/>
     </row>
     <row r="2" spans="1:15" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="s">
@@ -28042,7 +28045,7 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="380" t="s">
+      <c r="A3" s="388" t="s">
         <v>150</v>
       </c>
       <c r="B3" s="44" t="s">
@@ -28089,7 +28092,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="380"/>
+      <c r="A4" s="388"/>
       <c r="B4" s="57" t="s">
         <v>22</v>
       </c>
@@ -28134,7 +28137,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="380" t="s">
+      <c r="A5" s="388" t="s">
         <v>151</v>
       </c>
       <c r="B5" s="44" t="s">
@@ -28155,7 +28158,7 @@
       <c r="O5" s="43"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="380"/>
+      <c r="A6" s="388"/>
       <c r="B6" s="57" t="s">
         <v>22</v>
       </c>
@@ -28174,7 +28177,7 @@
       <c r="O6" s="43"/>
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="380" t="s">
+      <c r="A7" s="388" t="s">
         <v>152</v>
       </c>
       <c r="B7" s="44" t="s">
@@ -28195,7 +28198,7 @@
       <c r="O7" s="43"/>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="380"/>
+      <c r="A8" s="388"/>
       <c r="B8" s="57" t="s">
         <v>22</v>
       </c>
@@ -28214,7 +28217,7 @@
       <c r="O8" s="43"/>
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="380" t="s">
+      <c r="A9" s="388" t="s">
         <v>153</v>
       </c>
       <c r="B9" s="44" t="s">
@@ -28235,7 +28238,7 @@
       <c r="O9" s="43"/>
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="380"/>
+      <c r="A10" s="388"/>
       <c r="B10" s="57" t="s">
         <v>22</v>
       </c>
@@ -28254,7 +28257,7 @@
       <c r="O10" s="43"/>
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="380" t="s">
+      <c r="A11" s="388" t="s">
         <v>154</v>
       </c>
       <c r="B11" s="44" t="s">
@@ -28275,7 +28278,7 @@
       <c r="O11" s="43"/>
     </row>
     <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="380"/>
+      <c r="A12" s="388"/>
       <c r="B12" s="57" t="s">
         <v>22</v>
       </c>
@@ -28294,7 +28297,7 @@
       <c r="O12" s="43"/>
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="380" t="s">
+      <c r="A13" s="388" t="s">
         <v>155</v>
       </c>
       <c r="B13" s="44" t="s">
@@ -28315,7 +28318,7 @@
       <c r="O13" s="43"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="380"/>
+      <c r="A14" s="388"/>
       <c r="B14" s="57" t="s">
         <v>22</v>
       </c>
@@ -28334,7 +28337,7 @@
       <c r="O14" s="43"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="380" t="s">
+      <c r="A15" s="388" t="s">
         <v>156</v>
       </c>
       <c r="B15" s="44" t="s">
@@ -28355,7 +28358,7 @@
       <c r="O15" s="43"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="380"/>
+      <c r="A16" s="388"/>
       <c r="B16" s="57" t="s">
         <v>22</v>
       </c>
@@ -28394,7 +28397,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="380" t="s">
+      <c r="A19" s="388" t="s">
         <v>174</v>
       </c>
       <c r="B19" s="44" t="s">
@@ -28414,7 +28417,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="380"/>
+      <c r="A20" s="388"/>
       <c r="B20" s="57" t="s">
         <v>22</v>
       </c>
@@ -28432,7 +28435,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="380" t="s">
+      <c r="A21" s="388" t="s">
         <v>175</v>
       </c>
       <c r="B21" s="44" t="s">
@@ -28444,7 +28447,7 @@
       <c r="F21" s="43"/>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="380"/>
+      <c r="A22" s="388"/>
       <c r="B22" s="57" t="s">
         <v>22</v>
       </c>
@@ -28454,7 +28457,7 @@
       <c r="F22" s="58"/>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="380" t="s">
+      <c r="A23" s="388" t="s">
         <v>173</v>
       </c>
       <c r="B23" s="44" t="s">
@@ -28466,7 +28469,7 @@
       <c r="F23" s="43"/>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="380"/>
+      <c r="A24" s="388"/>
       <c r="B24" s="57" t="s">
         <v>22</v>
       </c>
@@ -28502,7 +28505,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="380" t="s">
+      <c r="A27" s="388" t="s">
         <v>182</v>
       </c>
       <c r="B27" s="44" t="s">
@@ -28528,7 +28531,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="380"/>
+      <c r="A28" s="388"/>
       <c r="B28" s="57" t="s">
         <v>22</v>
       </c>
@@ -28552,7 +28555,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="380" t="s">
+      <c r="A29" s="388" t="s">
         <v>183</v>
       </c>
       <c r="B29" s="44" t="s">
@@ -28566,7 +28569,7 @@
       <c r="H29" s="43"/>
     </row>
     <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="380"/>
+      <c r="A30" s="388"/>
       <c r="B30" s="57" t="s">
         <v>22</v>
       </c>
@@ -28578,7 +28581,7 @@
       <c r="H30" s="58"/>
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="380" t="s">
+      <c r="A31" s="388" t="s">
         <v>184</v>
       </c>
       <c r="B31" s="44" t="s">
@@ -28592,7 +28595,7 @@
       <c r="H31" s="43"/>
     </row>
     <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="380"/>
+      <c r="A32" s="388"/>
       <c r="B32" s="57" t="s">
         <v>22</v>
       </c>
@@ -28604,7 +28607,7 @@
       <c r="H32" s="43"/>
     </row>
     <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="380" t="s">
+      <c r="A33" s="388" t="s">
         <v>185</v>
       </c>
       <c r="B33" s="44" t="s">
@@ -28618,7 +28621,7 @@
       <c r="H33" s="43"/>
     </row>
     <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="380"/>
+      <c r="A34" s="388"/>
       <c r="B34" s="57" t="s">
         <v>22</v>
       </c>
@@ -28650,7 +28653,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="380" t="s">
+      <c r="A37" s="388" t="s">
         <v>192</v>
       </c>
       <c r="B37" s="44" t="s">
@@ -28670,7 +28673,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="380"/>
+      <c r="A38" s="388"/>
       <c r="B38" s="57" t="s">
         <v>22</v>
       </c>
@@ -28688,7 +28691,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="380" t="s">
+      <c r="A39" s="388" t="s">
         <v>193</v>
       </c>
       <c r="B39" s="44" t="s">
@@ -28700,7 +28703,7 @@
       <c r="F39" s="43"/>
     </row>
     <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="380"/>
+      <c r="A40" s="388"/>
       <c r="B40" s="57" t="s">
         <v>22</v>
       </c>
@@ -28710,7 +28713,7 @@
       <c r="F40" s="58"/>
     </row>
     <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="380" t="s">
+      <c r="A41" s="388" t="s">
         <v>194</v>
       </c>
       <c r="B41" s="44" t="s">
@@ -28722,7 +28725,7 @@
       <c r="F41" s="43"/>
     </row>
     <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="380"/>
+      <c r="A42" s="388"/>
       <c r="B42" s="57" t="s">
         <v>22</v>
       </c>
@@ -28733,6 +28736,14 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="A37:A38"/>
     <mergeCell ref="A39:A40"/>
@@ -28743,14 +28754,6 @@
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -28769,13 +28772,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="280" t="s">
+      <c r="A1" s="336" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="280"/>
-      <c r="C1" s="280"/>
-      <c r="D1" s="280"/>
-      <c r="E1" s="280"/>
+      <c r="B1" s="336"/>
+      <c r="C1" s="336"/>
+      <c r="D1" s="336"/>
+      <c r="E1" s="336"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="59" t="s">
@@ -28784,10 +28787,10 @@
       <c r="B2" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="407" t="s">
+      <c r="C2" s="409" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="408"/>
+      <c r="D2" s="410"/>
       <c r="E2" s="60" t="s">
         <v>22</v>
       </c>
@@ -28797,10 +28800,10 @@
         <v>201</v>
       </c>
       <c r="B3" s="43"/>
-      <c r="C3" s="405" t="s">
+      <c r="C3" s="407" t="s">
         <v>213</v>
       </c>
-      <c r="D3" s="406"/>
+      <c r="D3" s="408"/>
       <c r="E3" s="43"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28808,10 +28811,10 @@
         <v>202</v>
       </c>
       <c r="B4" s="43"/>
-      <c r="C4" s="405" t="s">
+      <c r="C4" s="407" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="406"/>
+      <c r="D4" s="408"/>
       <c r="E4" s="43"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28819,10 +28822,10 @@
         <v>203</v>
       </c>
       <c r="B5" s="43"/>
-      <c r="C5" s="405" t="s">
+      <c r="C5" s="407" t="s">
         <v>215</v>
       </c>
-      <c r="D5" s="406"/>
+      <c r="D5" s="408"/>
       <c r="E5" s="43"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28830,10 +28833,10 @@
         <v>209</v>
       </c>
       <c r="B6" s="43"/>
-      <c r="C6" s="405" t="s">
+      <c r="C6" s="407" t="s">
         <v>216</v>
       </c>
-      <c r="D6" s="406"/>
+      <c r="D6" s="408"/>
       <c r="E6" s="43"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28841,10 +28844,10 @@
         <v>204</v>
       </c>
       <c r="B7" s="43"/>
-      <c r="C7" s="405" t="s">
+      <c r="C7" s="407" t="s">
         <v>218</v>
       </c>
-      <c r="D7" s="406"/>
+      <c r="D7" s="408"/>
       <c r="E7" s="43"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28852,10 +28855,10 @@
         <v>205</v>
       </c>
       <c r="B8" s="43"/>
-      <c r="C8" s="405" t="s">
+      <c r="C8" s="407" t="s">
         <v>217</v>
       </c>
-      <c r="D8" s="406"/>
+      <c r="D8" s="408"/>
       <c r="E8" s="43"/>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28863,10 +28866,10 @@
         <v>206</v>
       </c>
       <c r="B9" s="43"/>
-      <c r="C9" s="405" t="s">
+      <c r="C9" s="407" t="s">
         <v>219</v>
       </c>
-      <c r="D9" s="406"/>
+      <c r="D9" s="408"/>
       <c r="E9" s="43"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28874,10 +28877,10 @@
         <v>207</v>
       </c>
       <c r="B10" s="43"/>
-      <c r="C10" s="304" t="s">
+      <c r="C10" s="274" t="s">
         <v>222</v>
       </c>
-      <c r="D10" s="305"/>
+      <c r="D10" s="275"/>
       <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28885,10 +28888,10 @@
         <v>208</v>
       </c>
       <c r="B11" s="43"/>
-      <c r="C11" s="304" t="s">
+      <c r="C11" s="274" t="s">
         <v>226</v>
       </c>
-      <c r="D11" s="305"/>
+      <c r="D11" s="275"/>
       <c r="E11" s="43"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -28980,25 +28983,25 @@
   <sheetData>
     <row r="1" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="296" t="s">
+      <c r="A2" s="256" t="s">
         <v>540</v>
       </c>
-      <c r="B2" s="296"/>
-      <c r="C2" s="298" t="s">
+      <c r="B2" s="256"/>
+      <c r="C2" s="258" t="s">
         <v>250</v>
       </c>
-      <c r="D2" s="298"/>
-      <c r="E2" s="298"/>
-      <c r="F2" s="298"/>
-      <c r="G2" s="298"/>
-      <c r="H2" s="298"/>
-      <c r="I2" s="295" t="s">
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="255" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="296"/>
-      <c r="B3" s="296"/>
+      <c r="A3" s="256"/>
+      <c r="B3" s="256"/>
       <c r="C3" s="138" t="s">
         <v>527</v>
       </c>
@@ -29017,13 +29020,13 @@
       <c r="H3" s="138" t="s">
         <v>248</v>
       </c>
-      <c r="I3" s="295"/>
+      <c r="I3" s="255"/>
     </row>
     <row r="4" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="294" t="s">
+      <c r="A4" s="254" t="s">
         <v>541</v>
       </c>
-      <c r="B4" s="294"/>
+      <c r="B4" s="254"/>
       <c r="C4" s="62" t="s">
         <v>247</v>
       </c>
@@ -29047,10 +29050,10 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="297" t="s">
+      <c r="A5" s="257" t="s">
         <v>543</v>
       </c>
-      <c r="B5" s="297"/>
+      <c r="B5" s="257"/>
       <c r="C5" s="62" t="s">
         <v>247</v>
       </c>
@@ -29074,10 +29077,10 @@
       </c>
     </row>
     <row r="6" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="294" t="s">
+      <c r="A6" s="254" t="s">
         <v>542</v>
       </c>
-      <c r="B6" s="294"/>
+      <c r="B6" s="254"/>
       <c r="C6" s="62" t="s">
         <v>247</v>
       </c>
@@ -29101,10 +29104,10 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="294" t="s">
+      <c r="A7" s="254" t="s">
         <v>533</v>
       </c>
-      <c r="B7" s="294"/>
+      <c r="B7" s="254"/>
       <c r="C7" s="62" t="s">
         <v>246</v>
       </c>
@@ -29687,228 +29690,228 @@
   <sheetData>
     <row r="1" spans="2:16" ht="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="301" t="s">
+      <c r="B2" s="261" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="301"/>
-      <c r="D2" s="301"/>
-      <c r="E2" s="301"/>
-      <c r="F2" s="301"/>
-      <c r="G2" s="301"/>
-      <c r="H2" s="301"/>
-      <c r="J2" s="320" t="s">
+      <c r="C2" s="261"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="261"/>
+      <c r="J2" s="269" t="s">
         <v>425</v>
       </c>
-      <c r="K2" s="321"/>
-      <c r="L2" s="321"/>
-      <c r="M2" s="321"/>
-      <c r="N2" s="321"/>
-      <c r="O2" s="321"/>
-      <c r="P2" s="322"/>
+      <c r="K2" s="270"/>
+      <c r="L2" s="270"/>
+      <c r="M2" s="270"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="270"/>
+      <c r="P2" s="271"/>
     </row>
     <row r="3" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="303" t="s">
+      <c r="B3" s="265" t="s">
         <v>419</v>
       </c>
       <c r="C3" s="117" t="s">
         <v>415</v>
       </c>
       <c r="D3" s="118"/>
-      <c r="E3" s="303" t="s">
+      <c r="E3" s="265" t="s">
         <v>420</v>
       </c>
-      <c r="F3" s="299" t="s">
+      <c r="F3" s="259" t="s">
         <v>342</v>
       </c>
-      <c r="G3" s="300"/>
+      <c r="G3" s="260"/>
       <c r="H3" s="123"/>
-      <c r="J3" s="313" t="s">
+      <c r="J3" s="262" t="s">
         <v>424</v>
       </c>
       <c r="K3" s="41" t="s">
         <v>421</v>
       </c>
       <c r="L3" s="118"/>
-      <c r="M3" s="303" t="s">
+      <c r="M3" s="265" t="s">
         <v>427</v>
       </c>
-      <c r="N3" s="299" t="s">
+      <c r="N3" s="259" t="s">
         <v>416</v>
       </c>
-      <c r="O3" s="300"/>
+      <c r="O3" s="260"/>
       <c r="P3" s="118"/>
     </row>
     <row r="4" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="303"/>
+      <c r="B4" s="265"/>
       <c r="C4" s="117" t="s">
         <v>414</v>
       </c>
       <c r="D4" s="123"/>
-      <c r="E4" s="303"/>
-      <c r="F4" s="299" t="s">
+      <c r="E4" s="265"/>
+      <c r="F4" s="259" t="s">
         <v>413</v>
       </c>
-      <c r="G4" s="300"/>
+      <c r="G4" s="260"/>
       <c r="H4" s="123"/>
-      <c r="J4" s="314"/>
+      <c r="J4" s="263"/>
       <c r="K4" s="41" t="s">
         <v>422</v>
       </c>
       <c r="L4" s="118"/>
-      <c r="M4" s="303"/>
-      <c r="N4" s="299" t="s">
+      <c r="M4" s="265"/>
+      <c r="N4" s="259" t="s">
         <v>417</v>
       </c>
-      <c r="O4" s="300"/>
+      <c r="O4" s="260"/>
       <c r="P4" s="118"/>
     </row>
     <row r="5" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="303"/>
+      <c r="B5" s="265"/>
       <c r="C5" s="117" t="s">
         <v>340</v>
       </c>
       <c r="D5" s="123"/>
-      <c r="E5" s="303"/>
-      <c r="F5" s="299" t="s">
+      <c r="E5" s="265"/>
+      <c r="F5" s="259" t="s">
         <v>343</v>
       </c>
-      <c r="G5" s="300"/>
+      <c r="G5" s="260"/>
       <c r="H5" s="123"/>
-      <c r="J5" s="302"/>
+      <c r="J5" s="264"/>
       <c r="K5" s="41" t="s">
         <v>423</v>
       </c>
       <c r="L5" s="118"/>
-      <c r="M5" s="303"/>
-      <c r="N5" s="299" t="s">
+      <c r="M5" s="265"/>
+      <c r="N5" s="259" t="s">
         <v>418</v>
       </c>
-      <c r="O5" s="300"/>
+      <c r="O5" s="260"/>
       <c r="P5" s="118"/>
     </row>
     <row r="6" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="303"/>
+      <c r="B6" s="265"/>
       <c r="C6" s="117" t="s">
         <v>341</v>
       </c>
       <c r="D6" s="118"/>
-      <c r="E6" s="303"/>
-      <c r="F6" s="299" t="s">
+      <c r="E6" s="265"/>
+      <c r="F6" s="259" t="s">
         <v>113</v>
       </c>
-      <c r="G6" s="300"/>
+      <c r="G6" s="260"/>
       <c r="H6" s="123"/>
-      <c r="J6" s="303" t="s">
+      <c r="J6" s="265" t="s">
         <v>366</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>385</v>
       </c>
       <c r="L6" s="23"/>
-      <c r="M6" s="303" t="s">
+      <c r="M6" s="265" t="s">
         <v>366</v>
       </c>
-      <c r="N6" s="304" t="s">
+      <c r="N6" s="274" t="s">
         <v>410</v>
       </c>
-      <c r="O6" s="305"/>
+      <c r="O6" s="275"/>
       <c r="P6" s="23"/>
     </row>
     <row r="7" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="301" t="s">
+      <c r="B7" s="261" t="s">
         <v>238</v>
       </c>
-      <c r="C7" s="301"/>
-      <c r="D7" s="301"/>
-      <c r="E7" s="301"/>
-      <c r="F7" s="301"/>
-      <c r="G7" s="301"/>
-      <c r="H7" s="301"/>
-      <c r="J7" s="303"/>
+      <c r="C7" s="261"/>
+      <c r="D7" s="261"/>
+      <c r="E7" s="261"/>
+      <c r="F7" s="261"/>
+      <c r="G7" s="261"/>
+      <c r="H7" s="261"/>
+      <c r="J7" s="265"/>
       <c r="K7" s="3" t="s">
         <v>386</v>
       </c>
       <c r="L7" s="23"/>
-      <c r="M7" s="303"/>
-      <c r="N7" s="304" t="s">
+      <c r="M7" s="265"/>
+      <c r="N7" s="274" t="s">
         <v>411</v>
       </c>
-      <c r="O7" s="305"/>
+      <c r="O7" s="275"/>
       <c r="P7" s="23"/>
     </row>
     <row r="8" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="313" t="s">
+      <c r="B8" s="262" t="s">
         <v>389</v>
       </c>
       <c r="C8" s="117" t="s">
         <v>57</v>
       </c>
       <c r="D8" s="118"/>
-      <c r="E8" s="303" t="s">
+      <c r="E8" s="265" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="299" t="s">
+      <c r="F8" s="259" t="s">
         <v>388</v>
       </c>
-      <c r="G8" s="300"/>
+      <c r="G8" s="260"/>
       <c r="H8" s="118"/>
-      <c r="J8" s="303"/>
+      <c r="J8" s="265"/>
       <c r="K8" s="3" t="s">
         <v>409</v>
       </c>
       <c r="L8" s="23"/>
-      <c r="M8" s="303"/>
-      <c r="N8" s="315"/>
-      <c r="O8" s="316"/>
+      <c r="M8" s="265"/>
+      <c r="N8" s="272"/>
+      <c r="O8" s="273"/>
       <c r="P8" s="118"/>
     </row>
     <row r="9" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="314"/>
+      <c r="B9" s="263"/>
       <c r="C9" s="117" t="s">
         <v>356</v>
       </c>
       <c r="D9" s="118"/>
-      <c r="E9" s="303"/>
-      <c r="F9" s="299" t="s">
+      <c r="E9" s="265"/>
+      <c r="F9" s="259" t="s">
         <v>364</v>
       </c>
-      <c r="G9" s="300"/>
+      <c r="G9" s="260"/>
       <c r="H9" s="118"/>
-      <c r="J9" s="301" t="s">
+      <c r="J9" s="261" t="s">
         <v>431</v>
       </c>
-      <c r="K9" s="301"/>
-      <c r="L9" s="301"/>
-      <c r="M9" s="301"/>
-      <c r="N9" s="301"/>
-      <c r="O9" s="301"/>
-      <c r="P9" s="301"/>
+      <c r="K9" s="261"/>
+      <c r="L9" s="261"/>
+      <c r="M9" s="261"/>
+      <c r="N9" s="261"/>
+      <c r="O9" s="261"/>
+      <c r="P9" s="261"/>
     </row>
     <row r="10" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="314"/>
+      <c r="B10" s="263"/>
       <c r="C10" s="117" t="s">
         <v>357</v>
       </c>
       <c r="D10" s="118" t="s">
         <v>358</v>
       </c>
-      <c r="E10" s="303"/>
-      <c r="F10" s="299" t="s">
+      <c r="E10" s="265"/>
+      <c r="F10" s="259" t="s">
         <v>365</v>
       </c>
-      <c r="G10" s="300"/>
+      <c r="G10" s="260"/>
       <c r="H10" s="118"/>
-      <c r="J10" s="312" t="s">
+      <c r="J10" s="277" t="s">
         <v>323</v>
       </c>
-      <c r="K10" s="312"/>
+      <c r="K10" s="277"/>
       <c r="L10" s="99" t="s">
         <v>344</v>
       </c>
-      <c r="M10" s="311" t="s">
+      <c r="M10" s="278" t="s">
         <v>345</v>
       </c>
-      <c r="N10" s="311"/>
+      <c r="N10" s="278"/>
       <c r="O10" s="99" t="s">
         <v>346</v>
       </c>
@@ -29917,186 +29920,186 @@
       </c>
     </row>
     <row r="11" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="314"/>
+      <c r="B11" s="263"/>
       <c r="C11" s="117" t="s">
         <v>112</v>
       </c>
       <c r="D11" s="118"/>
-      <c r="E11" s="303"/>
-      <c r="F11" s="299" t="s">
+      <c r="E11" s="265"/>
+      <c r="F11" s="259" t="s">
         <v>396</v>
       </c>
-      <c r="G11" s="300"/>
+      <c r="G11" s="260"/>
       <c r="H11" s="118"/>
-      <c r="J11" s="306" t="s">
+      <c r="J11" s="279" t="s">
         <v>348</v>
       </c>
-      <c r="K11" s="306"/>
+      <c r="K11" s="279"/>
       <c r="L11" s="62"/>
-      <c r="M11" s="308"/>
-      <c r="N11" s="308"/>
+      <c r="M11" s="276"/>
+      <c r="N11" s="276"/>
       <c r="O11" s="62"/>
       <c r="P11" s="127"/>
     </row>
     <row r="12" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="314"/>
+      <c r="B12" s="263"/>
       <c r="C12" s="117" t="s">
         <v>360</v>
       </c>
       <c r="D12" s="118"/>
-      <c r="E12" s="303"/>
-      <c r="F12" s="299" t="s">
+      <c r="E12" s="265"/>
+      <c r="F12" s="259" t="s">
         <v>392</v>
       </c>
-      <c r="G12" s="300"/>
+      <c r="G12" s="260"/>
       <c r="H12" s="118"/>
-      <c r="J12" s="306" t="s">
+      <c r="J12" s="279" t="s">
         <v>350</v>
       </c>
-      <c r="K12" s="306"/>
+      <c r="K12" s="279"/>
       <c r="L12" s="62"/>
-      <c r="M12" s="308"/>
-      <c r="N12" s="308"/>
+      <c r="M12" s="276"/>
+      <c r="N12" s="276"/>
       <c r="O12" s="62"/>
       <c r="P12" s="127"/>
     </row>
     <row r="13" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="314"/>
+      <c r="B13" s="263"/>
       <c r="C13" s="117" t="s">
         <v>391</v>
       </c>
       <c r="D13" s="118"/>
-      <c r="E13" s="303"/>
-      <c r="F13" s="299" t="s">
+      <c r="E13" s="265"/>
+      <c r="F13" s="259" t="s">
         <v>367</v>
       </c>
-      <c r="G13" s="300"/>
+      <c r="G13" s="260"/>
       <c r="H13" s="118"/>
-      <c r="J13" s="306" t="s">
+      <c r="J13" s="279" t="s">
         <v>352</v>
       </c>
-      <c r="K13" s="306"/>
+      <c r="K13" s="279"/>
       <c r="L13" s="127"/>
-      <c r="M13" s="308"/>
-      <c r="N13" s="308"/>
+      <c r="M13" s="276"/>
+      <c r="N13" s="276"/>
       <c r="O13" s="127"/>
       <c r="P13" s="127"/>
     </row>
     <row r="14" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="314"/>
+      <c r="B14" s="263"/>
       <c r="C14" s="117" t="s">
         <v>361</v>
       </c>
       <c r="D14" s="118"/>
-      <c r="E14" s="313" t="s">
+      <c r="E14" s="262" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="299" t="s">
+      <c r="F14" s="259" t="s">
         <v>368</v>
       </c>
-      <c r="G14" s="300"/>
+      <c r="G14" s="260"/>
       <c r="H14" s="118"/>
-      <c r="J14" s="306" t="s">
+      <c r="J14" s="279" t="s">
         <v>353</v>
       </c>
-      <c r="K14" s="306"/>
+      <c r="K14" s="279"/>
       <c r="L14" s="127"/>
-      <c r="M14" s="308"/>
-      <c r="N14" s="308"/>
+      <c r="M14" s="276"/>
+      <c r="N14" s="276"/>
       <c r="O14" s="127"/>
       <c r="P14" s="127"/>
     </row>
     <row r="15" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="314"/>
+      <c r="B15" s="263"/>
       <c r="C15" s="117" t="s">
         <v>362</v>
       </c>
       <c r="D15" s="118"/>
-      <c r="E15" s="314"/>
-      <c r="F15" s="299" t="s">
+      <c r="E15" s="263"/>
+      <c r="F15" s="259" t="s">
         <v>369</v>
       </c>
-      <c r="G15" s="300"/>
+      <c r="G15" s="260"/>
       <c r="H15" s="118"/>
-      <c r="J15" s="306" t="s">
+      <c r="J15" s="279" t="s">
         <v>354</v>
       </c>
-      <c r="K15" s="306"/>
+      <c r="K15" s="279"/>
       <c r="L15" s="127"/>
-      <c r="M15" s="308"/>
-      <c r="N15" s="308"/>
+      <c r="M15" s="276"/>
+      <c r="N15" s="276"/>
       <c r="O15" s="127"/>
       <c r="P15" s="127"/>
     </row>
     <row r="16" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="302"/>
+      <c r="B16" s="264"/>
       <c r="C16" s="147"/>
       <c r="D16" s="118"/>
-      <c r="E16" s="302"/>
-      <c r="F16" s="299" t="s">
+      <c r="E16" s="264"/>
+      <c r="F16" s="259" t="s">
         <v>370</v>
       </c>
-      <c r="G16" s="300"/>
+      <c r="G16" s="260"/>
       <c r="H16" s="118"/>
-      <c r="J16" s="306" t="s">
+      <c r="J16" s="279" t="s">
         <v>355</v>
       </c>
-      <c r="K16" s="306"/>
+      <c r="K16" s="279"/>
       <c r="L16" s="127"/>
-      <c r="M16" s="308"/>
-      <c r="N16" s="308"/>
+      <c r="M16" s="276"/>
+      <c r="N16" s="276"/>
       <c r="O16" s="127"/>
       <c r="P16" s="127"/>
     </row>
     <row r="17" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="313" t="s">
+      <c r="B17" s="262" t="s">
         <v>412</v>
       </c>
       <c r="C17" s="146" t="s">
         <v>347</v>
       </c>
       <c r="D17" s="118"/>
-      <c r="E17" s="313" t="s">
+      <c r="E17" s="262" t="s">
         <v>390</v>
       </c>
-      <c r="F17" s="299" t="s">
+      <c r="F17" s="259" t="s">
         <v>393</v>
       </c>
-      <c r="G17" s="300"/>
+      <c r="G17" s="260"/>
       <c r="H17" s="118"/>
-      <c r="J17" s="301" t="s">
+      <c r="J17" s="261" t="s">
         <v>432</v>
       </c>
-      <c r="K17" s="301"/>
-      <c r="L17" s="301"/>
-      <c r="M17" s="301"/>
-      <c r="N17" s="301"/>
-      <c r="O17" s="301"/>
-      <c r="P17" s="301"/>
+      <c r="K17" s="261"/>
+      <c r="L17" s="261"/>
+      <c r="M17" s="261"/>
+      <c r="N17" s="261"/>
+      <c r="O17" s="261"/>
+      <c r="P17" s="261"/>
     </row>
     <row r="18" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="314"/>
+      <c r="B18" s="263"/>
       <c r="C18" s="146" t="s">
         <v>349</v>
       </c>
       <c r="D18" s="118"/>
-      <c r="E18" s="314"/>
-      <c r="F18" s="299" t="s">
+      <c r="E18" s="263"/>
+      <c r="F18" s="259" t="s">
         <v>395</v>
       </c>
-      <c r="G18" s="300"/>
+      <c r="G18" s="260"/>
       <c r="H18" s="118"/>
-      <c r="J18" s="312" t="s">
+      <c r="J18" s="277" t="s">
         <v>323</v>
       </c>
-      <c r="K18" s="312"/>
+      <c r="K18" s="277"/>
       <c r="L18" s="99" t="s">
         <v>344</v>
       </c>
-      <c r="M18" s="311" t="s">
+      <c r="M18" s="278" t="s">
         <v>110</v>
       </c>
-      <c r="N18" s="311"/>
+      <c r="N18" s="278"/>
       <c r="O18" s="99" t="s">
         <v>359</v>
       </c>
@@ -30105,44 +30108,44 @@
       </c>
     </row>
     <row r="19" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="314"/>
+      <c r="B19" s="263"/>
       <c r="C19" s="146" t="s">
         <v>351</v>
       </c>
       <c r="D19" s="118"/>
-      <c r="E19" s="302"/>
-      <c r="F19" s="299" t="s">
+      <c r="E19" s="264"/>
+      <c r="F19" s="259" t="s">
         <v>394</v>
       </c>
-      <c r="G19" s="300"/>
+      <c r="G19" s="260"/>
       <c r="H19" s="118"/>
-      <c r="J19" s="306" t="s">
+      <c r="J19" s="279" t="s">
         <v>405</v>
       </c>
-      <c r="K19" s="306"/>
+      <c r="K19" s="279"/>
       <c r="L19" s="62"/>
-      <c r="M19" s="308"/>
-      <c r="N19" s="308"/>
+      <c r="M19" s="276"/>
+      <c r="N19" s="276"/>
       <c r="O19" s="62"/>
       <c r="P19" s="62"/>
     </row>
     <row r="20" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="301" t="s">
+      <c r="B20" s="261" t="s">
         <v>428</v>
       </c>
-      <c r="C20" s="301"/>
-      <c r="D20" s="301"/>
-      <c r="E20" s="301"/>
-      <c r="F20" s="301"/>
-      <c r="G20" s="301"/>
-      <c r="H20" s="301"/>
-      <c r="J20" s="306" t="s">
+      <c r="C20" s="261"/>
+      <c r="D20" s="261"/>
+      <c r="E20" s="261"/>
+      <c r="F20" s="261"/>
+      <c r="G20" s="261"/>
+      <c r="H20" s="261"/>
+      <c r="J20" s="279" t="s">
         <v>406</v>
       </c>
-      <c r="K20" s="306"/>
+      <c r="K20" s="279"/>
       <c r="L20" s="62"/>
-      <c r="M20" s="308"/>
-      <c r="N20" s="308"/>
+      <c r="M20" s="276"/>
+      <c r="N20" s="276"/>
       <c r="O20" s="62"/>
       <c r="P20" s="62"/>
       <c r="Q20" s="119"/>
@@ -30151,28 +30154,28 @@
       <c r="T20" s="119"/>
     </row>
     <row r="21" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="302" t="s">
+      <c r="B21" s="264" t="s">
         <v>429</v>
       </c>
       <c r="C21" s="41" t="s">
         <v>371</v>
       </c>
       <c r="D21" s="128"/>
-      <c r="E21" s="303" t="s">
+      <c r="E21" s="265" t="s">
         <v>426</v>
       </c>
-      <c r="F21" s="304" t="s">
+      <c r="F21" s="274" t="s">
         <v>371</v>
       </c>
-      <c r="G21" s="305"/>
+      <c r="G21" s="275"/>
       <c r="H21" s="118"/>
-      <c r="J21" s="306" t="s">
+      <c r="J21" s="279" t="s">
         <v>407</v>
       </c>
-      <c r="K21" s="306"/>
+      <c r="K21" s="279"/>
       <c r="L21" s="62"/>
-      <c r="M21" s="308"/>
-      <c r="N21" s="308"/>
+      <c r="M21" s="276"/>
+      <c r="N21" s="276"/>
       <c r="O21" s="62"/>
       <c r="P21" s="62"/>
       <c r="Q21" s="119"/>
@@ -30181,24 +30184,24 @@
       <c r="T21" s="119"/>
     </row>
     <row r="22" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="303"/>
+      <c r="B22" s="265"/>
       <c r="C22" s="41" t="s">
         <v>384</v>
       </c>
       <c r="D22" s="128"/>
-      <c r="E22" s="303"/>
-      <c r="F22" s="304" t="s">
+      <c r="E22" s="265"/>
+      <c r="F22" s="274" t="s">
         <v>384</v>
       </c>
-      <c r="G22" s="305"/>
+      <c r="G22" s="275"/>
       <c r="H22" s="118"/>
-      <c r="J22" s="306" t="s">
+      <c r="J22" s="279" t="s">
         <v>408</v>
       </c>
-      <c r="K22" s="306"/>
+      <c r="K22" s="279"/>
       <c r="L22" s="62"/>
-      <c r="M22" s="308"/>
-      <c r="N22" s="308"/>
+      <c r="M22" s="276"/>
+      <c r="N22" s="276"/>
       <c r="O22" s="62"/>
       <c r="P22" s="62"/>
       <c r="Q22" s="119"/>
@@ -30207,13 +30210,13 @@
       <c r="T22" s="119"/>
     </row>
     <row r="23" spans="2:42" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J23" s="307" t="s">
+      <c r="J23" s="280" t="s">
         <v>363</v>
       </c>
-      <c r="K23" s="307"/>
+      <c r="K23" s="280"/>
       <c r="L23" s="62"/>
-      <c r="M23" s="309"/>
-      <c r="N23" s="310"/>
+      <c r="M23" s="281"/>
+      <c r="N23" s="282"/>
       <c r="O23" s="124"/>
       <c r="P23" s="124"/>
       <c r="Q23" s="119"/>
@@ -30280,42 +30283,42 @@
       <c r="M27"/>
       <c r="N27"/>
       <c r="O27"/>
-      <c r="U27" s="319" t="s">
+      <c r="U27" s="268" t="s">
         <v>64</v>
       </c>
-      <c r="V27" s="317" t="s">
+      <c r="V27" s="266" t="s">
         <v>344</v>
       </c>
-      <c r="W27" s="318" t="s">
+      <c r="W27" s="267" t="s">
         <v>372</v>
       </c>
-      <c r="X27" s="318"/>
-      <c r="Y27" s="318"/>
-      <c r="Z27" s="318"/>
-      <c r="AA27" s="318"/>
-      <c r="AB27" s="318"/>
-      <c r="AC27" s="318"/>
-      <c r="AD27" s="318"/>
-      <c r="AE27" s="318" t="s">
+      <c r="X27" s="267"/>
+      <c r="Y27" s="267"/>
+      <c r="Z27" s="267"/>
+      <c r="AA27" s="267"/>
+      <c r="AB27" s="267"/>
+      <c r="AC27" s="267"/>
+      <c r="AD27" s="267"/>
+      <c r="AE27" s="267" t="s">
         <v>373</v>
       </c>
-      <c r="AF27" s="318"/>
-      <c r="AG27" s="318"/>
-      <c r="AH27" s="318"/>
-      <c r="AI27" s="318"/>
-      <c r="AJ27" s="318"/>
-      <c r="AK27" s="318"/>
-      <c r="AL27" s="318"/>
-      <c r="AM27" s="317" t="s">
+      <c r="AF27" s="267"/>
+      <c r="AG27" s="267"/>
+      <c r="AH27" s="267"/>
+      <c r="AI27" s="267"/>
+      <c r="AJ27" s="267"/>
+      <c r="AK27" s="267"/>
+      <c r="AL27" s="267"/>
+      <c r="AM27" s="266" t="s">
         <v>345</v>
       </c>
-      <c r="AN27" s="317" t="s">
+      <c r="AN27" s="266" t="s">
         <v>374</v>
       </c>
-      <c r="AO27" s="317" t="s">
+      <c r="AO27" s="266" t="s">
         <v>346</v>
       </c>
-      <c r="AP27" s="317" t="s">
+      <c r="AP27" s="266" t="s">
         <v>375</v>
       </c>
     </row>
@@ -30326,8 +30329,8 @@
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28"/>
-      <c r="U28" s="319"/>
-      <c r="V28" s="317"/>
+      <c r="U28" s="268"/>
+      <c r="V28" s="266"/>
       <c r="W28" s="125" t="s">
         <v>143</v>
       </c>
@@ -30376,10 +30379,10 @@
       <c r="AL28" s="125" t="s">
         <v>382</v>
       </c>
-      <c r="AM28" s="317"/>
-      <c r="AN28" s="317"/>
-      <c r="AO28" s="317"/>
-      <c r="AP28" s="317"/>
+      <c r="AM28" s="266"/>
+      <c r="AN28" s="266"/>
+      <c r="AO28" s="266"/>
+      <c r="AP28" s="266"/>
     </row>
     <row r="29" spans="2:42" x14ac:dyDescent="0.25">
       <c r="J29"/>
@@ -30621,6 +30624,67 @@
     </row>
   </sheetData>
   <mergeCells count="77">
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="AP27:AP28"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="W27:AD27"/>
+    <mergeCell ref="AE27:AL27"/>
+    <mergeCell ref="AM27:AM28"/>
+    <mergeCell ref="AN27:AN28"/>
+    <mergeCell ref="AO27:AO28"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="J2:P2"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F3:G3"/>
@@ -30637,67 +30701,6 @@
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B8:B16"/>
     <mergeCell ref="E8:E13"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="AP27:AP28"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="W27:AD27"/>
-    <mergeCell ref="AE27:AL27"/>
-    <mergeCell ref="AM27:AM28"/>
-    <mergeCell ref="AN27:AN28"/>
-    <mergeCell ref="AO27:AO28"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="J2:P2"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -30726,16 +30729,16 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="323" t="s">
+      <c r="F1" s="283" t="s">
         <v>329</v>
       </c>
-      <c r="G1" s="323"/>
-      <c r="H1" s="323"/>
+      <c r="G1" s="283"/>
+      <c r="H1" s="283"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="325" t="s">
+      <c r="J1" s="285" t="s">
         <v>339</v>
       </c>
-      <c r="K1" s="325"/>
+      <c r="K1" s="285"/>
     </row>
     <row r="2" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="114" t="s">
@@ -30744,12 +30747,12 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="323"/>
-      <c r="G2" s="323"/>
-      <c r="H2" s="323"/>
+      <c r="F2" s="283"/>
+      <c r="G2" s="283"/>
+      <c r="H2" s="283"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="325"/>
-      <c r="K2" s="325"/>
+      <c r="J2" s="285"/>
+      <c r="K2" s="285"/>
     </row>
     <row r="3" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="104"/>
@@ -30759,9 +30762,9 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="324"/>
-      <c r="G3" s="324"/>
-      <c r="H3" s="324"/>
+      <c r="F3" s="284"/>
+      <c r="G3" s="284"/>
+      <c r="H3" s="284"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="116" t="s">
@@ -30845,16 +30848,16 @@
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="323" t="s">
+      <c r="F56" s="283" t="s">
         <v>329</v>
       </c>
-      <c r="G56" s="323"/>
-      <c r="H56" s="323"/>
+      <c r="G56" s="283"/>
+      <c r="H56" s="283"/>
       <c r="I56" s="1"/>
-      <c r="J56" s="325" t="s">
+      <c r="J56" s="285" t="s">
         <v>339</v>
       </c>
-      <c r="K56" s="325"/>
+      <c r="K56" s="285"/>
     </row>
     <row r="57" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="114" t="s">
@@ -30863,12 +30866,12 @@
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="323"/>
-      <c r="G57" s="323"/>
-      <c r="H57" s="323"/>
+      <c r="F57" s="283"/>
+      <c r="G57" s="283"/>
+      <c r="H57" s="283"/>
       <c r="I57" s="1"/>
-      <c r="J57" s="325"/>
-      <c r="K57" s="325"/>
+      <c r="J57" s="285"/>
+      <c r="K57" s="285"/>
     </row>
     <row r="58" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="104"/>
@@ -30878,9 +30881,9 @@
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
-      <c r="F58" s="324"/>
-      <c r="G58" s="324"/>
-      <c r="H58" s="324"/>
+      <c r="F58" s="284"/>
+      <c r="G58" s="284"/>
+      <c r="H58" s="284"/>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
       <c r="K58" s="116" t="s">
@@ -30964,16 +30967,16 @@
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="323" t="s">
+      <c r="F111" s="283" t="s">
         <v>329</v>
       </c>
-      <c r="G111" s="323"/>
-      <c r="H111" s="323"/>
+      <c r="G111" s="283"/>
+      <c r="H111" s="283"/>
       <c r="I111" s="1"/>
-      <c r="J111" s="325" t="s">
+      <c r="J111" s="285" t="s">
         <v>339</v>
       </c>
-      <c r="K111" s="325"/>
+      <c r="K111" s="285"/>
     </row>
     <row r="112" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="114" t="s">
@@ -30982,12 +30985,12 @@
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
-      <c r="F112" s="323"/>
-      <c r="G112" s="323"/>
-      <c r="H112" s="323"/>
+      <c r="F112" s="283"/>
+      <c r="G112" s="283"/>
+      <c r="H112" s="283"/>
       <c r="I112" s="1"/>
-      <c r="J112" s="325"/>
-      <c r="K112" s="325"/>
+      <c r="J112" s="285"/>
+      <c r="K112" s="285"/>
     </row>
     <row r="113" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="104"/>
@@ -30997,9 +31000,9 @@
       <c r="C113" s="8"/>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
-      <c r="F113" s="324"/>
-      <c r="G113" s="324"/>
-      <c r="H113" s="324"/>
+      <c r="F113" s="284"/>
+      <c r="G113" s="284"/>
+      <c r="H113" s="284"/>
       <c r="I113" s="8"/>
       <c r="J113" s="8"/>
       <c r="K113" s="116" t="s">
@@ -31083,16 +31086,16 @@
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
-      <c r="F166" s="323" t="s">
+      <c r="F166" s="283" t="s">
         <v>329</v>
       </c>
-      <c r="G166" s="323"/>
-      <c r="H166" s="323"/>
+      <c r="G166" s="283"/>
+      <c r="H166" s="283"/>
       <c r="I166" s="1"/>
-      <c r="J166" s="325" t="s">
+      <c r="J166" s="285" t="s">
         <v>339</v>
       </c>
-      <c r="K166" s="325"/>
+      <c r="K166" s="285"/>
     </row>
     <row r="167" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B167" s="114" t="s">
@@ -31101,12 +31104,12 @@
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
-      <c r="F167" s="323"/>
-      <c r="G167" s="323"/>
-      <c r="H167" s="323"/>
+      <c r="F167" s="283"/>
+      <c r="G167" s="283"/>
+      <c r="H167" s="283"/>
       <c r="I167" s="1"/>
-      <c r="J167" s="325"/>
-      <c r="K167" s="325"/>
+      <c r="J167" s="285"/>
+      <c r="K167" s="285"/>
     </row>
     <row r="168" spans="1:12" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="104"/>
@@ -31116,9 +31119,9 @@
       <c r="C168" s="8"/>
       <c r="D168" s="8"/>
       <c r="E168" s="8"/>
-      <c r="F168" s="324"/>
-      <c r="G168" s="324"/>
-      <c r="H168" s="324"/>
+      <c r="F168" s="284"/>
+      <c r="G168" s="284"/>
+      <c r="H168" s="284"/>
       <c r="I168" s="8"/>
       <c r="J168" s="8"/>
       <c r="K168" s="116" t="s">
@@ -31272,32 +31275,32 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="328" t="s">
+      <c r="A3" s="291" t="s">
         <v>544</v>
       </c>
-      <c r="B3" s="329"/>
-      <c r="C3" s="330"/>
-      <c r="H3" s="319" t="s">
+      <c r="B3" s="292"/>
+      <c r="C3" s="293"/>
+      <c r="H3" s="268" t="s">
         <v>256</v>
       </c>
-      <c r="I3" s="319" t="s">
+      <c r="I3" s="268" t="s">
         <v>323</v>
       </c>
-      <c r="J3" s="319" t="s">
+      <c r="J3" s="268" t="s">
         <v>459</v>
       </c>
-      <c r="K3" s="319" t="s">
+      <c r="K3" s="268" t="s">
         <v>471</v>
       </c>
-      <c r="L3" s="319" t="s">
+      <c r="L3" s="268" t="s">
         <v>478</v>
       </c>
-      <c r="M3" s="319"/>
-      <c r="N3" s="332" t="s">
+      <c r="M3" s="268"/>
+      <c r="N3" s="289" t="s">
         <v>477</v>
       </c>
-      <c r="O3" s="333"/>
-      <c r="P3" s="318" t="s">
+      <c r="O3" s="290"/>
+      <c r="P3" s="267" t="s">
         <v>498</v>
       </c>
     </row>
@@ -31305,12 +31308,12 @@
       <c r="A4" s="132" t="s">
         <v>545</v>
       </c>
-      <c r="B4" s="297"/>
-      <c r="C4" s="297"/>
-      <c r="H4" s="319"/>
-      <c r="I4" s="319"/>
-      <c r="J4" s="319"/>
-      <c r="K4" s="319"/>
+      <c r="B4" s="257"/>
+      <c r="C4" s="257"/>
+      <c r="H4" s="268"/>
+      <c r="I4" s="268"/>
+      <c r="J4" s="268"/>
+      <c r="K4" s="268"/>
       <c r="L4" s="100" t="s">
         <v>61</v>
       </c>
@@ -31323,14 +31326,14 @@
       <c r="O4" s="100" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="331"/>
+      <c r="P4" s="286"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="132" t="s">
         <v>548</v>
       </c>
-      <c r="B5" s="326"/>
-      <c r="C5" s="327"/>
+      <c r="B5" s="287"/>
+      <c r="C5" s="288"/>
       <c r="H5" s="132" t="s">
         <v>465</v>
       </c>
@@ -31359,8 +31362,8 @@
       <c r="A6" s="132" t="s">
         <v>546</v>
       </c>
-      <c r="B6" s="326"/>
-      <c r="C6" s="327"/>
+      <c r="B6" s="287"/>
+      <c r="C6" s="288"/>
       <c r="H6" s="132" t="s">
         <v>464</v>
       </c>
@@ -31389,8 +31392,8 @@
       <c r="A7" s="132" t="s">
         <v>549</v>
       </c>
-      <c r="B7" s="326"/>
-      <c r="C7" s="327"/>
+      <c r="B7" s="287"/>
+      <c r="C7" s="288"/>
       <c r="H7" s="132" t="s">
         <v>463</v>
       </c>
@@ -31419,8 +31422,8 @@
       <c r="A8" s="132" t="s">
         <v>550</v>
       </c>
-      <c r="B8" s="326"/>
-      <c r="C8" s="327"/>
+      <c r="B8" s="287"/>
+      <c r="C8" s="288"/>
       <c r="H8" s="132" t="s">
         <v>494</v>
       </c>
@@ -31449,8 +31452,8 @@
       <c r="A9" s="132" t="s">
         <v>551</v>
       </c>
-      <c r="B9" s="326"/>
-      <c r="C9" s="327"/>
+      <c r="B9" s="287"/>
+      <c r="C9" s="288"/>
       <c r="H9" s="132" t="s">
         <v>495</v>
       </c>
@@ -31463,10 +31466,10 @@
       <c r="K9" s="133" t="s">
         <v>251</v>
       </c>
-      <c r="L9" s="326" t="s">
+      <c r="L9" s="287" t="s">
         <v>469</v>
       </c>
-      <c r="M9" s="327"/>
+      <c r="M9" s="288"/>
       <c r="N9" s="95"/>
       <c r="O9" s="95"/>
       <c r="P9" s="99" t="s">
@@ -31560,10 +31563,10 @@
       <c r="K12" s="134" t="s">
         <v>251</v>
       </c>
-      <c r="L12" s="326" t="s">
+      <c r="L12" s="287" t="s">
         <v>470</v>
       </c>
-      <c r="M12" s="327"/>
+      <c r="M12" s="288"/>
       <c r="N12" s="95"/>
       <c r="O12" s="95"/>
       <c r="P12" s="99" t="s">
@@ -32563,6 +32566,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="L12:M12"/>
@@ -32572,13 +32582,6 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -32603,39 +32606,39 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="284" t="s">
+      <c r="B2" s="299" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="285"/>
-      <c r="D2" s="285"/>
-      <c r="E2" s="285"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="285"/>
-      <c r="H2" s="285"/>
-      <c r="I2" s="285"/>
-      <c r="J2" s="285"/>
-      <c r="K2" s="285"/>
-      <c r="L2" s="285"/>
-      <c r="M2" s="286"/>
-      <c r="N2" s="350" t="s">
+      <c r="C2" s="300"/>
+      <c r="D2" s="300"/>
+      <c r="E2" s="300"/>
+      <c r="F2" s="300"/>
+      <c r="G2" s="300"/>
+      <c r="H2" s="300"/>
+      <c r="I2" s="300"/>
+      <c r="J2" s="300"/>
+      <c r="K2" s="300"/>
+      <c r="L2" s="300"/>
+      <c r="M2" s="301"/>
+      <c r="N2" s="302" t="s">
         <v>552</v>
       </c>
-      <c r="O2" s="351"/>
-      <c r="Q2" s="334" t="s">
+      <c r="O2" s="303"/>
+      <c r="Q2" s="308" t="s">
         <v>583</v>
       </c>
-      <c r="R2" s="335"/>
-      <c r="S2" s="335"/>
-      <c r="T2" s="335"/>
-      <c r="U2" s="335"/>
-      <c r="V2" s="335"/>
-      <c r="W2" s="335"/>
-      <c r="X2" s="335"/>
-      <c r="Y2" s="335"/>
-      <c r="Z2" s="335"/>
-      <c r="AA2" s="335"/>
-      <c r="AB2" s="335"/>
-      <c r="AC2" s="336"/>
+      <c r="R2" s="309"/>
+      <c r="S2" s="309"/>
+      <c r="T2" s="309"/>
+      <c r="U2" s="309"/>
+      <c r="V2" s="309"/>
+      <c r="W2" s="309"/>
+      <c r="X2" s="309"/>
+      <c r="Y2" s="309"/>
+      <c r="Z2" s="309"/>
+      <c r="AA2" s="309"/>
+      <c r="AB2" s="309"/>
+      <c r="AC2" s="310"/>
     </row>
     <row r="3" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5"/>
@@ -32650,10 +32653,10 @@
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="7"/>
-      <c r="N3" s="345" t="s">
+      <c r="N3" s="294" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="347"/>
+      <c r="O3" s="296"/>
       <c r="Q3" s="200" t="s">
         <v>569</v>
       </c>
@@ -32685,8 +32688,8 @@
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="7"/>
-      <c r="N4" s="348"/>
-      <c r="O4" s="349"/>
+      <c r="N4" s="297"/>
+      <c r="O4" s="298"/>
       <c r="Q4" s="194"/>
       <c r="R4" s="195"/>
       <c r="S4" s="192"/>
@@ -32721,19 +32724,19 @@
       <c r="Q5" s="191" t="s">
         <v>579</v>
       </c>
-      <c r="R5" s="339" t="s">
+      <c r="R5" s="313" t="s">
         <v>584</v>
       </c>
-      <c r="S5" s="340"/>
-      <c r="T5" s="340"/>
-      <c r="U5" s="340"/>
-      <c r="V5" s="340"/>
-      <c r="W5" s="340"/>
-      <c r="X5" s="340"/>
-      <c r="Y5" s="340"/>
-      <c r="Z5" s="340"/>
-      <c r="AA5" s="340"/>
-      <c r="AB5" s="341"/>
+      <c r="S5" s="314"/>
+      <c r="T5" s="314"/>
+      <c r="U5" s="314"/>
+      <c r="V5" s="314"/>
+      <c r="W5" s="314"/>
+      <c r="X5" s="314"/>
+      <c r="Y5" s="314"/>
+      <c r="Z5" s="314"/>
+      <c r="AA5" s="314"/>
+      <c r="AB5" s="315"/>
       <c r="AC5" s="193"/>
     </row>
     <row r="6" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -32756,17 +32759,17 @@
       <c r="Q6" s="191" t="s">
         <v>580</v>
       </c>
-      <c r="R6" s="342"/>
-      <c r="S6" s="343"/>
-      <c r="T6" s="343"/>
-      <c r="U6" s="343"/>
-      <c r="V6" s="343"/>
-      <c r="W6" s="343"/>
-      <c r="X6" s="343"/>
-      <c r="Y6" s="343"/>
-      <c r="Z6" s="343"/>
-      <c r="AA6" s="343"/>
-      <c r="AB6" s="344"/>
+      <c r="R6" s="316"/>
+      <c r="S6" s="317"/>
+      <c r="T6" s="317"/>
+      <c r="U6" s="317"/>
+      <c r="V6" s="317"/>
+      <c r="W6" s="317"/>
+      <c r="X6" s="317"/>
+      <c r="Y6" s="317"/>
+      <c r="Z6" s="317"/>
+      <c r="AA6" s="317"/>
+      <c r="AB6" s="318"/>
       <c r="AC6" s="193"/>
     </row>
     <row r="7" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -32787,17 +32790,17 @@
       <c r="Q7" s="191" t="s">
         <v>581</v>
       </c>
-      <c r="R7" s="342"/>
-      <c r="S7" s="343"/>
-      <c r="T7" s="343"/>
-      <c r="U7" s="343"/>
-      <c r="V7" s="343"/>
-      <c r="W7" s="343"/>
-      <c r="X7" s="343"/>
-      <c r="Y7" s="343"/>
-      <c r="Z7" s="343"/>
-      <c r="AA7" s="343"/>
-      <c r="AB7" s="344"/>
+      <c r="R7" s="316"/>
+      <c r="S7" s="317"/>
+      <c r="T7" s="317"/>
+      <c r="U7" s="317"/>
+      <c r="V7" s="317"/>
+      <c r="W7" s="317"/>
+      <c r="X7" s="317"/>
+      <c r="Y7" s="317"/>
+      <c r="Z7" s="317"/>
+      <c r="AA7" s="317"/>
+      <c r="AB7" s="318"/>
       <c r="AC7" s="193"/>
     </row>
     <row r="8" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -32818,17 +32821,17 @@
       <c r="Q8" s="191" t="s">
         <v>582</v>
       </c>
-      <c r="R8" s="342"/>
-      <c r="S8" s="343"/>
-      <c r="T8" s="343"/>
-      <c r="U8" s="343"/>
-      <c r="V8" s="343"/>
-      <c r="W8" s="343"/>
-      <c r="X8" s="343"/>
-      <c r="Y8" s="343"/>
-      <c r="Z8" s="343"/>
-      <c r="AA8" s="343"/>
-      <c r="AB8" s="344"/>
+      <c r="R8" s="316"/>
+      <c r="S8" s="317"/>
+      <c r="T8" s="317"/>
+      <c r="U8" s="317"/>
+      <c r="V8" s="317"/>
+      <c r="W8" s="317"/>
+      <c r="X8" s="317"/>
+      <c r="Y8" s="317"/>
+      <c r="Z8" s="317"/>
+      <c r="AA8" s="317"/>
+      <c r="AB8" s="318"/>
       <c r="AC8" s="193"/>
     </row>
     <row r="9" spans="2:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -32864,23 +32867,23 @@
       <c r="B12" s="182" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="284" t="s">
+      <c r="C12" s="299" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="285"/>
-      <c r="E12" s="285"/>
-      <c r="F12" s="285"/>
-      <c r="G12" s="285"/>
-      <c r="H12" s="285"/>
-      <c r="I12" s="285"/>
-      <c r="J12" s="285"/>
-      <c r="K12" s="285"/>
-      <c r="L12" s="285"/>
-      <c r="M12" s="286"/>
-      <c r="N12" s="352" t="s">
+      <c r="D12" s="300"/>
+      <c r="E12" s="300"/>
+      <c r="F12" s="300"/>
+      <c r="G12" s="300"/>
+      <c r="H12" s="300"/>
+      <c r="I12" s="300"/>
+      <c r="J12" s="300"/>
+      <c r="K12" s="300"/>
+      <c r="L12" s="300"/>
+      <c r="M12" s="301"/>
+      <c r="N12" s="304" t="s">
         <v>103</v>
       </c>
-      <c r="O12" s="353"/>
+      <c r="O12" s="305"/>
       <c r="Q12" s="204" t="s">
         <v>631</v>
       </c>
@@ -32910,10 +32913,10 @@
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
-      <c r="N13" s="354" t="s">
+      <c r="N13" s="306" t="s">
         <v>21</v>
       </c>
-      <c r="O13" s="355"/>
+      <c r="O13" s="307"/>
       <c r="Q13" s="200" t="s">
         <v>568</v>
       </c>
@@ -33028,19 +33031,19 @@
       <c r="Q16" s="191" t="s">
         <v>579</v>
       </c>
-      <c r="R16" s="338" t="s">
+      <c r="R16" s="312" t="s">
         <v>578</v>
       </c>
-      <c r="S16" s="338"/>
-      <c r="T16" s="338"/>
-      <c r="U16" s="338"/>
-      <c r="V16" s="338"/>
-      <c r="W16" s="338"/>
-      <c r="X16" s="338"/>
-      <c r="Y16" s="338"/>
-      <c r="Z16" s="338"/>
-      <c r="AA16" s="338"/>
-      <c r="AB16" s="338"/>
+      <c r="S16" s="312"/>
+      <c r="T16" s="312"/>
+      <c r="U16" s="312"/>
+      <c r="V16" s="312"/>
+      <c r="W16" s="312"/>
+      <c r="X16" s="312"/>
+      <c r="Y16" s="312"/>
+      <c r="Z16" s="312"/>
+      <c r="AA16" s="312"/>
+      <c r="AB16" s="312"/>
       <c r="AC16" s="193"/>
     </row>
     <row r="17" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33056,24 +33059,24 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
-      <c r="N17" s="345" t="s">
+      <c r="N17" s="294" t="s">
         <v>21</v>
       </c>
-      <c r="O17" s="346"/>
+      <c r="O17" s="295"/>
       <c r="Q17" s="191" t="s">
         <v>580</v>
       </c>
-      <c r="R17" s="337"/>
-      <c r="S17" s="337"/>
-      <c r="T17" s="337"/>
-      <c r="U17" s="337"/>
-      <c r="V17" s="337"/>
-      <c r="W17" s="337"/>
-      <c r="X17" s="337"/>
-      <c r="Y17" s="337"/>
-      <c r="Z17" s="337"/>
-      <c r="AA17" s="337"/>
-      <c r="AB17" s="337"/>
+      <c r="R17" s="311"/>
+      <c r="S17" s="311"/>
+      <c r="T17" s="311"/>
+      <c r="U17" s="311"/>
+      <c r="V17" s="311"/>
+      <c r="W17" s="311"/>
+      <c r="X17" s="311"/>
+      <c r="Y17" s="311"/>
+      <c r="Z17" s="311"/>
+      <c r="AA17" s="311"/>
+      <c r="AB17" s="311"/>
       <c r="AC17" s="193"/>
     </row>
     <row r="18" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33098,17 +33101,17 @@
       <c r="Q18" s="191" t="s">
         <v>581</v>
       </c>
-      <c r="R18" s="337"/>
-      <c r="S18" s="337"/>
-      <c r="T18" s="337"/>
-      <c r="U18" s="337"/>
-      <c r="V18" s="337"/>
-      <c r="W18" s="337"/>
-      <c r="X18" s="337"/>
-      <c r="Y18" s="337"/>
-      <c r="Z18" s="337"/>
-      <c r="AA18" s="337"/>
-      <c r="AB18" s="337"/>
+      <c r="R18" s="311"/>
+      <c r="S18" s="311"/>
+      <c r="T18" s="311"/>
+      <c r="U18" s="311"/>
+      <c r="V18" s="311"/>
+      <c r="W18" s="311"/>
+      <c r="X18" s="311"/>
+      <c r="Y18" s="311"/>
+      <c r="Z18" s="311"/>
+      <c r="AA18" s="311"/>
+      <c r="AB18" s="311"/>
       <c r="AC18" s="193"/>
     </row>
     <row r="19" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33133,17 +33136,17 @@
       <c r="Q19" s="191" t="s">
         <v>582</v>
       </c>
-      <c r="R19" s="337"/>
-      <c r="S19" s="337"/>
-      <c r="T19" s="337"/>
-      <c r="U19" s="337"/>
-      <c r="V19" s="337"/>
-      <c r="W19" s="337"/>
-      <c r="X19" s="337"/>
-      <c r="Y19" s="337"/>
-      <c r="Z19" s="337"/>
-      <c r="AA19" s="337"/>
-      <c r="AB19" s="337"/>
+      <c r="R19" s="311"/>
+      <c r="S19" s="311"/>
+      <c r="T19" s="311"/>
+      <c r="U19" s="311"/>
+      <c r="V19" s="311"/>
+      <c r="W19" s="311"/>
+      <c r="X19" s="311"/>
+      <c r="Y19" s="311"/>
+      <c r="Z19" s="311"/>
+      <c r="AA19" s="311"/>
+      <c r="AB19" s="311"/>
       <c r="AC19" s="193"/>
     </row>
     <row r="20" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33190,10 +33193,10 @@
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
-      <c r="N21" s="345" t="s">
+      <c r="N21" s="294" t="s">
         <v>21</v>
       </c>
-      <c r="O21" s="346"/>
+      <c r="O21" s="295"/>
     </row>
     <row r="22" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="188" t="s">
@@ -33266,10 +33269,10 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
-      <c r="N25" s="345" t="s">
+      <c r="N25" s="294" t="s">
         <v>21</v>
       </c>
-      <c r="O25" s="346"/>
+      <c r="O25" s="295"/>
     </row>
     <row r="26" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="188" t="s">
@@ -33342,10 +33345,10 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
-      <c r="N29" s="345" t="s">
+      <c r="N29" s="294" t="s">
         <v>21</v>
       </c>
-      <c r="O29" s="346"/>
+      <c r="O29" s="295"/>
     </row>
     <row r="30" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="188" t="s">
@@ -33418,10 +33421,10 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
-      <c r="N33" s="345" t="s">
+      <c r="N33" s="294" t="s">
         <v>21</v>
       </c>
-      <c r="O33" s="346"/>
+      <c r="O33" s="295"/>
     </row>
     <row r="34" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="188" t="s">
@@ -33483,6 +33486,15 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="Q2:AC2"/>
+    <mergeCell ref="R19:AB19"/>
+    <mergeCell ref="R16:AB16"/>
+    <mergeCell ref="R17:AB17"/>
+    <mergeCell ref="R18:AB18"/>
+    <mergeCell ref="R5:AB5"/>
+    <mergeCell ref="R6:AB6"/>
+    <mergeCell ref="R7:AB7"/>
+    <mergeCell ref="R8:AB8"/>
     <mergeCell ref="N33:O33"/>
     <mergeCell ref="N3:O4"/>
     <mergeCell ref="B2:M2"/>
@@ -33494,15 +33506,6 @@
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="N12:O12"/>
     <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q2:AC2"/>
-    <mergeCell ref="R19:AB19"/>
-    <mergeCell ref="R16:AB16"/>
-    <mergeCell ref="R17:AB17"/>
-    <mergeCell ref="R18:AB18"/>
-    <mergeCell ref="R5:AB5"/>
-    <mergeCell ref="R6:AB6"/>
-    <mergeCell ref="R7:AB7"/>
-    <mergeCell ref="R8:AB8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -34070,36 +34073,36 @@
       <c r="B3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="281" t="s">
+      <c r="C3" s="319" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="282"/>
-      <c r="E3" s="283"/>
-      <c r="F3" s="281" t="s">
+      <c r="D3" s="320"/>
+      <c r="E3" s="321"/>
+      <c r="F3" s="319" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="282"/>
-      <c r="H3" s="283"/>
-      <c r="I3" s="281" t="s">
+      <c r="G3" s="320"/>
+      <c r="H3" s="321"/>
+      <c r="I3" s="319" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="282"/>
-      <c r="K3" s="283"/>
-      <c r="L3" s="281" t="s">
+      <c r="J3" s="320"/>
+      <c r="K3" s="321"/>
+      <c r="L3" s="319" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="282"/>
-      <c r="N3" s="283"/>
-      <c r="O3" s="281" t="s">
+      <c r="M3" s="320"/>
+      <c r="N3" s="321"/>
+      <c r="O3" s="319" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="282"/>
-      <c r="Q3" s="283"/>
-      <c r="R3" s="281" t="s">
+      <c r="P3" s="320"/>
+      <c r="Q3" s="321"/>
+      <c r="R3" s="319" t="s">
         <v>553</v>
       </c>
-      <c r="S3" s="282"/>
-      <c r="T3" s="283"/>
+      <c r="S3" s="320"/>
+      <c r="T3" s="321"/>
     </row>
     <row r="4" spans="2:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="241" t="s">
@@ -34164,11 +34167,15 @@
       <c r="B5" s="43" t="s">
         <v>712</v>
       </c>
-      <c r="C5" s="62" t="s">
-        <v>713</v>
-      </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
+      <c r="C5" s="43" t="s">
+        <v>763</v>
+      </c>
+      <c r="D5" s="62">
+        <v>72</v>
+      </c>
+      <c r="E5" s="62">
+        <v>48</v>
+      </c>
       <c r="F5" s="62" t="s">
         <v>713</v>
       </c>
@@ -34199,9 +34206,15 @@
       <c r="B6" s="43" t="s">
         <v>715</v>
       </c>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
+      <c r="C6" s="62">
+        <v>390</v>
+      </c>
+      <c r="D6" s="62">
+        <v>83</v>
+      </c>
+      <c r="E6" s="62">
+        <v>62</v>
+      </c>
       <c r="F6" s="62"/>
       <c r="G6" s="62"/>
       <c r="H6" s="62"/>
@@ -34222,9 +34235,15 @@
       <c r="B7" s="43" t="s">
         <v>716</v>
       </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
+      <c r="C7" s="62">
+        <v>385</v>
+      </c>
+      <c r="D7" s="62">
+        <v>82</v>
+      </c>
+      <c r="E7" s="62">
+        <v>61</v>
+      </c>
       <c r="F7" s="62"/>
       <c r="G7" s="62"/>
       <c r="H7" s="62"/>
@@ -34245,9 +34264,15 @@
       <c r="B8" s="43" t="s">
         <v>717</v>
       </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
+      <c r="C8" s="62">
+        <v>395</v>
+      </c>
+      <c r="D8" s="62">
+        <v>83</v>
+      </c>
+      <c r="E8" s="62">
+        <v>61</v>
+      </c>
       <c r="F8" s="62"/>
       <c r="G8" s="62"/>
       <c r="H8" s="62"/>
@@ -34268,9 +34293,15 @@
       <c r="B9" s="43" t="s">
         <v>718</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="62"/>
+      <c r="C9" s="62">
+        <v>400</v>
+      </c>
+      <c r="D9" s="62">
+        <v>85</v>
+      </c>
+      <c r="E9" s="62">
+        <v>63</v>
+      </c>
       <c r="F9" s="62"/>
       <c r="G9" s="62"/>
       <c r="H9" s="62"/>
@@ -34291,9 +34322,15 @@
       <c r="B10" s="43" t="s">
         <v>719</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
+      <c r="C10" s="62">
+        <v>395</v>
+      </c>
+      <c r="D10" s="62">
+        <v>84</v>
+      </c>
+      <c r="E10" s="62">
+        <v>62</v>
+      </c>
       <c r="F10" s="62"/>
       <c r="G10" s="62"/>
       <c r="H10" s="62"/>
@@ -34314,9 +34351,15 @@
       <c r="B11" s="43" t="s">
         <v>720</v>
       </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
+      <c r="C11" s="62">
+        <v>396</v>
+      </c>
+      <c r="D11" s="62">
+        <v>82</v>
+      </c>
+      <c r="E11" s="62">
+        <v>62</v>
+      </c>
       <c r="F11" s="62"/>
       <c r="G11" s="62"/>
       <c r="H11" s="62"/>
